--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,129 +364,129 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
+    <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Croatia Druga HNL</t>
-  </si>
-  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
+    <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
+    <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
@@ -523,27 +523,27 @@
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>France Ligue 2</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>France Ligue 2</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -556,12 +556,12 @@
     <t>Portugal LigaPro</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Portugal Liga NOS</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -571,33 +571,33 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -610,876 +610,876 @@
     <t>Espanyol W</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
     <t>Bochum</t>
   </si>
   <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Phu Dong</t>
   </si>
   <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
+    <t>Cibalia</t>
+  </si>
+  <si>
+    <t>Hegelmann Litauen</t>
+  </si>
+  <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
+    <t>Young Lions</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>DPMM FC</t>
+  </si>
+  <si>
+    <t>Melaka</t>
+  </si>
+  <si>
+    <t>Widzew Łódź</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Cherno More</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Burgos CF</t>
+  </si>
+  <si>
+    <t>Albacete Balompié</t>
+  </si>
+  <si>
+    <t>Sevilla FC</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Sumqayıt</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Levski Sofia</t>
+  </si>
+  <si>
+    <t>Al Khaleej</t>
+  </si>
+  <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Beerschot-Wilrijk</t>
+  </si>
+  <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Varaždin</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Maribor</t>
+  </si>
+  <si>
+    <t>Górnik Zabrze</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Lecce</t>
+  </si>
+  <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes II</t>
+  </si>
+  <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
+    <t>Guabirá</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Gotham FC</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>Angel City</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
+    <t>Colorado Rapids</t>
+  </si>
+  <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
+    <t>Phoenix Rising</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>NWS Spirit</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>PSM</t>
+  </si>
+  <si>
+    <t>Sydney Olympic</t>
+  </si>
+  <si>
+    <t>Sutherland Sharks</t>
+  </si>
+  <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Granada W</t>
+  </si>
+  <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Lokomotiv Sofia 1929</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Cibalia</t>
-  </si>
-  <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>DPMM FC</t>
-  </si>
-  <si>
-    <t>Melaka</t>
-  </si>
-  <si>
-    <t>Widzew Łódź</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Cherno More</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
-    <t>Hoffenheim</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
-    <t>Albacete Balompié</t>
-  </si>
-  <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
-    <t>Waldhof Mannheim</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
-  </si>
-  <si>
-    <t>Al Khaleej</t>
-  </si>
-  <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Lazio</t>
-  </si>
-  <si>
-    <t>Al Najma</t>
-  </si>
-  <si>
-    <t>Beerschot-Wilrijk</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Varaždin</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Górnik Zabrze</t>
-  </si>
-  <si>
-    <t>Maribor</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Club Brugge</t>
-  </si>
-  <si>
-    <t>Lecce</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
-    <t>Montreal Impact</t>
-  </si>
-  <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>Guabirá</t>
-  </si>
-  <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Gotham FC</t>
-  </si>
-  <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Brooklyn FC</t>
-  </si>
-  <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Angel City</t>
-  </si>
-  <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>Colorado Rapids</t>
-  </si>
-  <si>
-    <t>Phoenix Rising</t>
-  </si>
-  <si>
-    <t>Oakland Roots</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>NWS Spirit</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>PSM</t>
-  </si>
-  <si>
-    <t>Sydney Olympic</t>
-  </si>
-  <si>
-    <t>Sutherland Sharks</t>
-  </si>
-  <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
-    <t>Granada W</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
-    <t>Lokomotiv Sofia 1929</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Hegelmann Litauen</t>
-  </si>
-  <si>
-    <t>Sesvete</t>
+    <t>Tanjong Pagar</t>
   </si>
   <si>
     <t>Geylang International</t>
   </si>
   <si>
-    <t>Tanjong Pagar</t>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>Slovácko</t>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
   </si>
   <si>
     <t>Zlín</t>
   </si>
   <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
     <t>Baník Ostrava</t>
   </si>
   <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,114 +1489,114 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>AmaZulu</t>
   </si>
   <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>FC Caspiy</t>
   </si>
   <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
     <t>Qarabağ</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
     <t>St. Pauli</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
-    <t>Werder Bremen</t>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
   </si>
   <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
     <t>Almería</t>
   </si>
   <si>
@@ -1609,57 +1609,57 @@
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
     <t>Orijent 1919</t>
   </si>
   <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
     <t>SSC Farul</t>
   </si>
   <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Araz</t>
+  </si>
+  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Araz</t>
-  </si>
-  <si>
     <t>Aluminij</t>
   </si>
   <si>
@@ -1675,118 +1675,124 @@
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Inter Milan</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Inter Milan</t>
+    <t>Lommel United</t>
   </si>
   <si>
     <t>Al Hazm</t>
   </si>
   <si>
-    <t>Lommel United</t>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
   </si>
   <si>
     <t>Bayern München</t>
   </si>
   <si>
-    <t>Celta de Vigo</t>
+    <t>Panaitolikos</t>
   </si>
   <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
     <t>Fleury 91</t>
   </si>
   <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
+    <t>OFK Beograd</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
@@ -1795,135 +1801,129 @@
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
   </si>
   <si>
     <t>Los Andes</t>
   </si>
   <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
+    <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Olimpija</t>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
   </si>
   <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
-    <t>Schalke 04</t>
+    <t>New York RB</t>
   </si>
   <si>
     <t>Servette</t>
   </si>
   <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
+    <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
-    <t>Juventus</t>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
+    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1939,105 +1939,105 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
     <t>Sporting JAX</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
-    <t>Operário PR</t>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
   </si>
   <si>
     <t>Leixões</t>
   </si>
   <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>North Texas</t>
   </si>
   <si>
     <t>Cruzeiro</t>
   </si>
   <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
     <t>Sporting Braga</t>
   </si>
   <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2047,28 +2047,28 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
-  </si>
-  <si>
     <t>Sporting KC</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>San Diego</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2816,7 +2816,7 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
         <v>182</v>
@@ -3001,7 +3001,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -3371,7 +3371,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -3741,7 +3741,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>182</v>
@@ -4111,7 +4111,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
@@ -4666,7 +4666,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5036,10 +5036,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
         <v>198</v>
@@ -5221,10 +5221,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
         <v>199</v>
@@ -5406,10 +5406,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
         <v>200</v>
@@ -5594,7 +5594,7 @@
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
         <v>201</v>
@@ -6331,7 +6331,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>183</v>
@@ -6516,7 +6516,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
         <v>183</v>
@@ -6701,10 +6701,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
         <v>207</v>
@@ -6886,7 +6886,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>182</v>
@@ -7071,10 +7071,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E26" t="s">
         <v>209</v>
@@ -7256,7 +7256,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
         <v>182</v>
@@ -7441,7 +7441,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>182</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7814,7 +7814,7 @@
         <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
         <v>213</v>
@@ -7999,7 +7999,7 @@
         <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
         <v>214</v>
@@ -8554,7 +8554,7 @@
         <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -9294,7 +9294,7 @@
         <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -9849,7 +9849,7 @@
         <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10401,7 +10401,7 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -10586,10 +10586,10 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
         <v>228</v>
@@ -10771,7 +10771,7 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -11326,10 +11326,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
         <v>232</v>
@@ -11696,7 +11696,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -11881,10 +11881,10 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s">
         <v>235</v>
@@ -12066,7 +12066,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
         <v>183</v>
@@ -12251,7 +12251,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
         <v>183</v>
@@ -13030,13 +13030,13 @@
         <v>685</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13176,7 +13176,7 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
         <v>182</v>
@@ -13361,10 +13361,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E60" t="s">
         <v>243</v>
@@ -13546,7 +13546,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
         <v>183</v>
@@ -13731,10 +13731,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E62" t="s">
         <v>245</v>
@@ -13916,7 +13916,7 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
         <v>182</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14286,7 +14286,7 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
         <v>182</v>
@@ -14471,7 +14471,7 @@
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
         <v>183</v>
@@ -14659,7 +14659,7 @@
         <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
         <v>250</v>
@@ -14841,7 +14841,7 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
         <v>183</v>
@@ -14880,13 +14880,13 @@
         <v>685</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15065,13 +15065,13 @@
         <v>685</v>
       </c>
       <c r="P69">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15211,7 +15211,7 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
         <v>182</v>
@@ -15396,10 +15396,10 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="D71" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E71" t="s">
         <v>254</v>
@@ -15435,13 +15435,13 @@
         <v>685</v>
       </c>
       <c r="P71">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15581,10 +15581,10 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
         <v>255</v>
@@ -15990,13 +15990,13 @@
         <v>685</v>
       </c>
       <c r="P74">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Q74">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="R74">
-        <v>7.21</v>
+        <v>5.33</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16041,10 +16041,10 @@
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AH74">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="Q76">
-        <v>3.71</v>
+        <v>5.18</v>
       </c>
       <c r="R76">
-        <v>3.07</v>
+        <v>7.21</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16405,16 +16405,16 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,61 +16545,61 @@
         <v>685</v>
       </c>
       <c r="P77">
+        <v>2.38</v>
+      </c>
+      <c r="Q77">
+        <v>3.71</v>
+      </c>
+      <c r="R77">
+        <v>3.07</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+      <c r="AE77">
         <v>1.61</v>
       </c>
-      <c r="Q77">
-        <v>4.88</v>
-      </c>
-      <c r="R77">
-        <v>5.33</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>0</v>
-      </c>
-      <c r="AB77">
-        <v>0</v>
-      </c>
-      <c r="AC77">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>0</v>
-      </c>
-      <c r="AE77">
-        <v>0</v>
-      </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH77">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16691,10 +16691,10 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
         <v>261</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17655,13 +17655,13 @@
         <v>685</v>
       </c>
       <c r="P83">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D85" t="s">
         <v>183</v>
@@ -18171,10 +18171,10 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D86" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E86" t="s">
         <v>269</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18395,13 +18395,13 @@
         <v>685</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18765,13 +18765,13 @@
         <v>685</v>
       </c>
       <c r="P89">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -19096,7 +19096,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D91" t="s">
         <v>183</v>
@@ -19135,13 +19135,13 @@
         <v>685</v>
       </c>
       <c r="P91">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19281,7 +19281,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D92" t="s">
         <v>183</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -20021,7 +20021,7 @@
         <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D96" t="s">
         <v>183</v>
@@ -20391,7 +20391,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
         <v>183</v>
@@ -20761,10 +20761,10 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="D100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
         <v>283</v>
@@ -20946,7 +20946,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="D101" t="s">
         <v>183</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D102" t="s">
         <v>182</v>
@@ -21316,7 +21316,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D103" t="s">
         <v>183</v>
@@ -21501,10 +21501,10 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="D104" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E104" t="s">
         <v>287</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -22056,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
         <v>183</v>
@@ -22241,7 +22241,7 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
         <v>182</v>
@@ -22426,7 +22426,7 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D109" t="s">
         <v>183</v>
@@ -22611,7 +22611,7 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D110" t="s">
         <v>183</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -25201,7 +25201,7 @@
         <v>87</v>
       </c>
       <c r="C124" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D124" t="s">
         <v>183</v>
@@ -25240,13 +25240,13 @@
         <v>685</v>
       </c>
       <c r="P124">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q124">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25386,7 +25386,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D125" t="s">
         <v>183</v>
@@ -25571,7 +25571,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D126" t="s">
         <v>183</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25795,13 +25795,13 @@
         <v>685</v>
       </c>
       <c r="P127">
-        <v>5.74</v>
+        <v>1.36</v>
       </c>
       <c r="Q127">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="R127">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25941,7 +25941,7 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D128" t="s">
         <v>183</v>
@@ -26126,10 +26126,10 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129" t="s">
         <v>312</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26350,13 +26350,13 @@
         <v>685</v>
       </c>
       <c r="P130">
-        <v>1.36</v>
+        <v>5.74</v>
       </c>
       <c r="Q130">
-        <v>6.19</v>
+        <v>5.53</v>
       </c>
       <c r="R130">
-        <v>8.6</v>
+        <v>1.51</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26496,7 +26496,7 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
         <v>183</v>
@@ -26681,10 +26681,10 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="D132" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E132" t="s">
         <v>315</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27051,10 +27051,10 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D134" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E134" t="s">
         <v>317</v>
@@ -27421,10 +27421,10 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E136" t="s">
         <v>319</v>
@@ -27791,10 +27791,10 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E138" t="s">
         <v>321</v>
@@ -27976,10 +27976,10 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E139" t="s">
         <v>322</v>
@@ -28716,7 +28716,7 @@
         <v>91</v>
       </c>
       <c r="C143" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="D143" t="s">
         <v>183</v>
@@ -29086,7 +29086,7 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D145" t="s">
         <v>183</v>
@@ -29456,7 +29456,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D147" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -31861,7 +31861,7 @@
         <v>93</v>
       </c>
       <c r="C160" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D160" t="s">
         <v>183</v>
@@ -32046,7 +32046,7 @@
         <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -32234,7 +32234,7 @@
         <v>169</v>
       </c>
       <c r="D162" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E162" t="s">
         <v>345</v>
@@ -32416,7 +32416,7 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D163" t="s">
         <v>183</v>
@@ -32601,7 +32601,7 @@
         <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D164" t="s">
         <v>183</v>
@@ -32786,7 +32786,7 @@
         <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D165" t="s">
         <v>183</v>
@@ -32971,7 +32971,7 @@
         <v>94</v>
       </c>
       <c r="C166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>183</v>
@@ -33156,7 +33156,7 @@
         <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
         <v>183</v>
@@ -33341,7 +33341,7 @@
         <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D168" t="s">
         <v>183</v>
@@ -33380,13 +33380,13 @@
         <v>685</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33526,7 +33526,7 @@
         <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
         <v>183</v>
@@ -33565,13 +33565,13 @@
         <v>685</v>
       </c>
       <c r="P169">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q169">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R169">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33711,7 +33711,7 @@
         <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D170" t="s">
         <v>182</v>
@@ -33896,7 +33896,7 @@
         <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D171" t="s">
         <v>183</v>
@@ -34081,7 +34081,7 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D172" t="s">
         <v>183</v>
@@ -34266,7 +34266,7 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D173" t="s">
         <v>183</v>
@@ -34451,7 +34451,7 @@
         <v>94</v>
       </c>
       <c r="C174" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D174" t="s">
         <v>183</v>
@@ -34639,7 +34639,7 @@
         <v>170</v>
       </c>
       <c r="D175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E175" t="s">
         <v>358</v>
@@ -34821,7 +34821,7 @@
         <v>95</v>
       </c>
       <c r="C176" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D176" t="s">
         <v>183</v>
@@ -35006,7 +35006,7 @@
         <v>95</v>
       </c>
       <c r="C177" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D177" t="s">
         <v>183</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35561,10 +35561,10 @@
         <v>96</v>
       </c>
       <c r="C180" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D180" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E180" t="s">
         <v>363</v>
@@ -35746,7 +35746,7 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D181" t="s">
         <v>182</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q181">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R181">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,10 +35830,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF181">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D182" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E182" t="s">
         <v>365</v>
@@ -36116,7 +36116,7 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D183" t="s">
         <v>182</v>
@@ -36301,7 +36301,7 @@
         <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D184" t="s">
         <v>182</v>
@@ -36340,13 +36340,13 @@
         <v>685</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36385,10 +36385,10 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q186">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R186">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36895,13 +36895,13 @@
         <v>685</v>
       </c>
       <c r="P187">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q187">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R187">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37041,10 +37041,10 @@
         <v>98</v>
       </c>
       <c r="C188" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="D188" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E188" t="s">
         <v>371</v>
@@ -37226,10 +37226,10 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D189" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E189" t="s">
         <v>372</v>
@@ -37411,10 +37411,10 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D190" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E190" t="s">
         <v>373</v>
@@ -37450,13 +37450,13 @@
         <v>685</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37596,7 +37596,7 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D191" t="s">
         <v>183</v>
@@ -37781,10 +37781,10 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D192" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -37966,10 +37966,10 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="D193" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38151,7 +38151,7 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D194" t="s">
         <v>183</v>
@@ -38336,10 +38336,10 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="D195" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E195" t="s">
         <v>378</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q200">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39485,13 +39485,13 @@
         <v>685</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39530,10 +39530,10 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39816,7 +39816,7 @@
         <v>102</v>
       </c>
       <c r="C203" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D203" t="s">
         <v>182</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,10 +42406,10 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D217" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E217" t="s">
         <v>400</v>
@@ -42591,7 +42591,7 @@
         <v>108</v>
       </c>
       <c r="C218" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D218" t="s">
         <v>183</v>
@@ -42776,7 +42776,7 @@
         <v>108</v>
       </c>
       <c r="C219" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D219" t="s">
         <v>183</v>
@@ -42961,7 +42961,7 @@
         <v>108</v>
       </c>
       <c r="C220" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D220" t="s">
         <v>182</v>
@@ -43146,7 +43146,7 @@
         <v>108</v>
       </c>
       <c r="C221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D221" t="s">
         <v>182</v>
@@ -43185,13 +43185,13 @@
         <v>685</v>
       </c>
       <c r="P221">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q221">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R221">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -43331,10 +43331,10 @@
         <v>108</v>
       </c>
       <c r="C222" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D222" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E222" t="s">
         <v>405</v>
@@ -43886,7 +43886,7 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D225" t="s">
         <v>183</v>
@@ -44071,10 +44071,10 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D226" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E226" t="s">
         <v>409</v>
@@ -44256,7 +44256,7 @@
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D227" t="s">
         <v>183</v>
@@ -44441,7 +44441,7 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D228" t="s">
         <v>183</v>
@@ -44626,7 +44626,7 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
         <v>183</v>
@@ -44811,7 +44811,7 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D230" t="s">
         <v>183</v>
@@ -44996,7 +44996,7 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D231" t="s">
         <v>183</v>
@@ -45181,7 +45181,7 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D232" t="s">
         <v>183</v>
@@ -45366,7 +45366,7 @@
         <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D233" t="s">
         <v>183</v>
@@ -45736,7 +45736,7 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D235" t="s">
         <v>183</v>
@@ -46106,7 +46106,7 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D237" t="s">
         <v>183</v>
@@ -46291,10 +46291,10 @@
         <v>108</v>
       </c>
       <c r="C238" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D238" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E238" t="s">
         <v>421</v>
@@ -46476,7 +46476,7 @@
         <v>108</v>
       </c>
       <c r="C239" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D239" t="s">
         <v>182</v>
@@ -46515,13 +46515,13 @@
         <v>685</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46661,7 +46661,7 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D240" t="s">
         <v>183</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47401,7 +47401,7 @@
         <v>112</v>
       </c>
       <c r="C244" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,36 +364,36 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -406,27 +406,30 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -439,57 +442,54 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -508,21 +508,21 @@
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
     <t>Turkey Süper Lig</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -532,15 +532,15 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
@@ -553,15 +553,15 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -571,12 +571,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
@@ -589,15 +589,15 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -607,129 +607,129 @@
     <t>St George City FA</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
     <t>Espanyol W</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
+    <t>Oddevold</t>
   </si>
   <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
     <t>Young Lions</t>
   </si>
   <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
     <t>1860 München</t>
   </si>
   <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
     <t>Elche CF</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
   </si>
   <si>
     <t>Dukla Praha</t>
   </si>
   <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
-    <t>Teplice</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,114 +739,114 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
     <t>Panserraikos</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
     <t>Kristianstad</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
     <t>Växjö</t>
   </si>
   <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
     <t>Hoffenheim</t>
   </si>
   <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Augsburg</t>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Larissa</t>
   </si>
   <si>
     <t>St. Mirren</t>
   </si>
   <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
     <t>Dundee</t>
   </si>
   <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
     <t>Falkirk</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
     <t>Burgos CF</t>
   </si>
   <si>
@@ -859,51 +859,54 @@
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>AEL</t>
-  </si>
-  <si>
     <t>Ried</t>
   </si>
   <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
     <t>Omonia Aradippou</t>
   </si>
   <si>
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Sumqayıt</t>
   </si>
   <si>
@@ -913,9 +916,6 @@
     <t>Koper</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
@@ -925,255 +925,255 @@
     <t>Athletic Club W</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Prostějov</t>
+    <t>Zürich</t>
   </si>
   <si>
     <t>Winterthur</t>
   </si>
   <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
     <t>Al Najma</t>
   </si>
   <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
     <t>Manchester City</t>
   </si>
   <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
     <t>İstanbul Başakşehir</t>
   </si>
   <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Eyüpspor</t>
   </si>
   <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
     <t>Konyaspor</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
+    <t>Gençlerbirliği</t>
   </si>
   <si>
     <t>Beşiktaş</t>
   </si>
   <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
-    <t>Bourg-en-Bresse</t>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Rouen</t>
   </si>
   <si>
     <t>Stade Briochin</t>
   </si>
   <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
   </si>
   <si>
     <t>Clermont</t>
   </si>
   <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
     <t>Laval</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
     <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
     <t>Técnico Universitario</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
+    <t>Club Brugge</t>
   </si>
   <si>
     <t>Lecce</t>
   </si>
   <si>
-    <t>Club Brugge</t>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
   </si>
   <si>
     <t>Goiás</t>
   </si>
   <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1186,108 +1186,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
     <t>Louisville City</t>
   </si>
   <si>
-    <t>Brooklyn FC</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Indy Eleven</t>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
   </si>
   <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>Real Tomayapo</t>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
   </si>
   <si>
     <t>Houston Dash</t>
   </si>
   <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Alverca</t>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
   </si>
   <si>
     <t>Farense</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1297,36 +1297,36 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Phoenix Rising</t>
+  </si>
+  <si>
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>Phoenix Rising</t>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
   </si>
   <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
+    <t>FC Seoul</t>
   </si>
   <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
@@ -1339,15 +1339,15 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1357,129 +1357,129 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Granada W</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
     <t>Badalona W</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Granada W</t>
-  </si>
-  <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
     <t>Magdeburg</t>
   </si>
   <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Ha Noi</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
+    <t>Landskrona</t>
   </si>
   <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
     <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
     <t>Geylang International</t>
   </si>
   <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
     <t>Deportivo Alavés</t>
   </si>
   <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
   </si>
   <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Zlín</t>
   </si>
   <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,114 +1489,114 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
     <t>Kifisia</t>
   </si>
   <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>Norrköping W</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>AIK Women</t>
   </si>
   <si>
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
     <t>Werder Bremen</t>
   </si>
   <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Bayer Leverkusen</t>
   </si>
   <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t>Borussia M'gladbach</t>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
   </si>
   <si>
     <t>Kilmarnock</t>
   </si>
   <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
     <t>Livingston</t>
   </si>
   <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
     <t>Hibernian</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
     <t>Almería</t>
   </si>
   <si>
@@ -1609,51 +1609,54 @@
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Akritas</t>
   </si>
   <si>
     <t>Ljungskile</t>
   </si>
   <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Araz</t>
   </si>
   <si>
@@ -1663,9 +1666,6 @@
     <t>Aluminij</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
@@ -1675,255 +1675,255 @@
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>České Budějovice</t>
+    <t>Grasshopper</t>
   </si>
   <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
     <t>Lommel United</t>
   </si>
   <si>
     <t>Al Hazm</t>
   </si>
   <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
     <t>Brentford</t>
   </si>
   <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
     <t>Trakai</t>
   </si>
   <si>
     <t>Samsunspor</t>
   </si>
   <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Rizespor</t>
   </si>
   <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
     <t>Fenerbahçe</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
+    <t>Kasımpaşa</t>
   </si>
   <si>
     <t>Trabzonspor</t>
   </si>
   <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>Valenciennes</t>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Versailles</t>
   </si>
   <si>
     <t>Quevilly Rouen</t>
   </si>
   <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
   </si>
   <si>
     <t>Guingamp</t>
   </si>
   <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
     <t>Boulogne</t>
   </si>
   <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Delfin SC</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
+    <t>Sint-Truiden</t>
   </si>
   <si>
     <t>Juventus</t>
   </si>
   <si>
-    <t>Sint-Truiden</t>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Internacional</t>
   </si>
   <si>
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
     <t>Hearts</t>
   </si>
   <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
     <t>Unión Española</t>
   </si>
   <si>
     <t>Real Betis</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1936,108 +1936,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
-    <t>Sporting JAX</t>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
   </si>
   <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
   </si>
   <si>
     <t>Denver Summit W</t>
   </si>
   <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
   </si>
   <si>
     <t>Paços de Ferreira</t>
   </si>
   <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2047,28 +2047,28 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>Las Vegas Lights</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>El Paso Locomotive</t>
   </si>
   <si>
-    <t>San Antonio</t>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>San Diego</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -3371,7 +3371,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -3741,7 +3741,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>182</v>
@@ -3926,7 +3926,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
@@ -4666,7 +4666,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5036,7 +5036,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
         <v>182</v>
@@ -5221,7 +5221,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
         <v>183</v>
@@ -5406,10 +5406,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
         <v>200</v>
@@ -5591,10 +5591,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
         <v>201</v>
@@ -6331,10 +6331,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
         <v>205</v>
@@ -6516,10 +6516,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E23" t="s">
         <v>206</v>
@@ -6701,10 +6701,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
         <v>207</v>
@@ -6886,10 +6886,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
         <v>208</v>
@@ -7071,7 +7071,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
         <v>183</v>
@@ -7441,7 +7441,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
         <v>182</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8220,13 +8220,13 @@
         <v>685</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8366,10 +8366,10 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8551,10 +8551,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -8736,10 +8736,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E35" t="s">
         <v>218</v>
@@ -8921,10 +8921,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
         <v>219</v>
@@ -8960,13 +8960,13 @@
         <v>685</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9106,10 +9106,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E37" t="s">
         <v>220</v>
@@ -9291,10 +9291,10 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -9661,7 +9661,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
         <v>183</v>
@@ -9846,10 +9846,10 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10401,10 +10401,10 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
         <v>227</v>
@@ -10586,10 +10586,10 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E45" t="s">
         <v>228</v>
@@ -10771,7 +10771,7 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -10956,7 +10956,7 @@
         <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D47" t="s">
         <v>183</v>
@@ -11141,10 +11141,10 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
         <v>231</v>
@@ -11511,7 +11511,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
         <v>183</v>
@@ -11696,7 +11696,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -11881,7 +11881,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D52" t="s">
         <v>182</v>
@@ -12066,7 +12066,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
         <v>183</v>
@@ -12251,7 +12251,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>183</v>
@@ -13030,13 +13030,13 @@
         <v>685</v>
       </c>
       <c r="P58">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S58">
         <v>0</v>
@@ -13176,7 +13176,7 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D59" t="s">
         <v>182</v>
@@ -13361,10 +13361,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E60" t="s">
         <v>243</v>
@@ -13546,7 +13546,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D61" t="s">
         <v>183</v>
@@ -13585,13 +13585,13 @@
         <v>685</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13731,7 +13731,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>182</v>
@@ -13916,10 +13916,10 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E63" t="s">
         <v>246</v>
@@ -14101,7 +14101,7 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
         <v>183</v>
@@ -14140,13 +14140,13 @@
         <v>685</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14286,7 +14286,7 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D65" t="s">
         <v>182</v>
@@ -14471,10 +14471,10 @@
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
@@ -14656,10 +14656,10 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E67" t="s">
         <v>250</v>
@@ -14841,10 +14841,10 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E68" t="s">
         <v>251</v>
@@ -14880,13 +14880,13 @@
         <v>685</v>
       </c>
       <c r="P68">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15026,7 +15026,7 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D69" t="s">
         <v>183</v>
@@ -15211,10 +15211,10 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D70" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E70" t="s">
         <v>253</v>
@@ -15396,7 +15396,7 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D71" t="s">
         <v>182</v>
@@ -15581,7 +15581,7 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="D72" t="s">
         <v>183</v>
@@ -16175,13 +16175,13 @@
         <v>685</v>
       </c>
       <c r="P75">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q75">
-        <v>4.16</v>
+        <v>3.71</v>
       </c>
       <c r="R75">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -16220,16 +16220,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG75">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>685</v>
       </c>
       <c r="P77">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q77">
-        <v>3.71</v>
+        <v>4.16</v>
       </c>
       <c r="R77">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16590,16 +16590,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>1.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q82">
-        <v>5.48</v>
+        <v>3.86</v>
       </c>
       <c r="R82">
-        <v>8.300000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17655,13 +17655,13 @@
         <v>685</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17986,10 +17986,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D85" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E85" t="s">
         <v>268</v>
@@ -18171,10 +18171,10 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D86" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E86" t="s">
         <v>269</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18395,13 +18395,13 @@
         <v>685</v>
       </c>
       <c r="P87">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -19096,7 +19096,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D91" t="s">
         <v>183</v>
@@ -19281,7 +19281,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D92" t="s">
         <v>183</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -20021,7 +20021,7 @@
         <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D96" t="s">
         <v>183</v>
@@ -20391,10 +20391,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E98" t="s">
         <v>281</v>
@@ -20761,7 +20761,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D100" t="s">
         <v>183</v>
@@ -20946,7 +20946,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D101" t="s">
         <v>183</v>
@@ -21131,10 +21131,10 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E102" t="s">
         <v>285</v>
@@ -21316,7 +21316,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="D103" t="s">
         <v>183</v>
@@ -21501,10 +21501,10 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E104" t="s">
         <v>287</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -22056,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D107" t="s">
         <v>183</v>
@@ -22241,7 +22241,7 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D108" t="s">
         <v>182</v>
@@ -22426,7 +22426,7 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D109" t="s">
         <v>183</v>
@@ -22611,10 +22611,10 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E110" t="s">
         <v>293</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -24870,13 +24870,13 @@
         <v>685</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25795,13 +25795,13 @@
         <v>685</v>
       </c>
       <c r="P127">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25941,10 +25941,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E128" t="s">
         <v>311</v>
@@ -26126,10 +26126,10 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129" t="s">
         <v>312</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26350,13 +26350,13 @@
         <v>685</v>
       </c>
       <c r="P130">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26496,7 +26496,7 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D131" t="s">
         <v>183</v>
@@ -26535,13 +26535,13 @@
         <v>685</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26720,13 +26720,13 @@
         <v>685</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -27051,10 +27051,10 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E134" t="s">
         <v>317</v>
@@ -27239,7 +27239,7 @@
         <v>164</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27421,7 +27421,7 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D136" t="s">
         <v>183</v>
@@ -27606,7 +27606,7 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
         <v>183</v>
@@ -27791,7 +27791,7 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D138" t="s">
         <v>182</v>
@@ -27976,7 +27976,7 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
         <v>183</v>
@@ -28161,7 +28161,7 @@
         <v>91</v>
       </c>
       <c r="C140" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D140" t="s">
         <v>183</v>
@@ -28346,7 +28346,7 @@
         <v>91</v>
       </c>
       <c r="C141" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D141" t="s">
         <v>183</v>
@@ -28531,7 +28531,7 @@
         <v>91</v>
       </c>
       <c r="C142" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D142" t="s">
         <v>183</v>
@@ -28716,7 +28716,7 @@
         <v>91</v>
       </c>
       <c r="C143" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D143" t="s">
         <v>183</v>
@@ -28901,7 +28901,7 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D144" t="s">
         <v>183</v>
@@ -29086,7 +29086,7 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D145" t="s">
         <v>183</v>
@@ -29456,7 +29456,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D147" t="s">
         <v>183</v>
@@ -30011,7 +30011,7 @@
         <v>93</v>
       </c>
       <c r="C150" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D150" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30566,7 +30566,7 @@
         <v>93</v>
       </c>
       <c r="C153" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D153" t="s">
         <v>183</v>
@@ -30751,7 +30751,7 @@
         <v>93</v>
       </c>
       <c r="C154" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D154" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -32601,7 +32601,7 @@
         <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D164" t="s">
         <v>183</v>
@@ -32786,7 +32786,7 @@
         <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D165" t="s">
         <v>183</v>
@@ -32971,7 +32971,7 @@
         <v>94</v>
       </c>
       <c r="C166" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="D166" t="s">
         <v>183</v>
@@ -33156,7 +33156,7 @@
         <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D167" t="s">
         <v>183</v>
@@ -33195,13 +33195,13 @@
         <v>685</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33341,7 +33341,7 @@
         <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D168" t="s">
         <v>183</v>
@@ -33380,13 +33380,13 @@
         <v>685</v>
       </c>
       <c r="P168">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q168">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33896,7 +33896,7 @@
         <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D171" t="s">
         <v>183</v>
@@ -34266,10 +34266,10 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E173" t="s">
         <v>356</v>
@@ -34636,10 +34636,10 @@
         <v>94</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D175" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E175" t="s">
         <v>358</v>
@@ -34821,7 +34821,7 @@
         <v>95</v>
       </c>
       <c r="C176" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D176" t="s">
         <v>183</v>
@@ -35191,10 +35191,10 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D178" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E178" t="s">
         <v>361</v>
@@ -35376,10 +35376,10 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="D179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E179" t="s">
         <v>362</v>
@@ -35415,13 +35415,13 @@
         <v>685</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35460,10 +35460,10 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -35746,10 +35746,10 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="D181" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E181" t="s">
         <v>364</v>
@@ -35931,10 +35931,10 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D182" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E182" t="s">
         <v>365</v>
@@ -36301,7 +36301,7 @@
         <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D184" t="s">
         <v>182</v>
@@ -36340,13 +36340,13 @@
         <v>685</v>
       </c>
       <c r="P184">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q184">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36385,10 +36385,10 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF184">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36859,7 +36859,7 @@
         <v>172</v>
       </c>
       <c r="D187" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E187" t="s">
         <v>370</v>
@@ -37041,7 +37041,7 @@
         <v>98</v>
       </c>
       <c r="C188" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D188" t="s">
         <v>183</v>
@@ -37226,7 +37226,7 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D189" t="s">
         <v>183</v>
@@ -37596,10 +37596,10 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D191" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E191" t="s">
         <v>374</v>
@@ -37781,7 +37781,7 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D192" t="s">
         <v>182</v>
@@ -37966,7 +37966,7 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D193" t="s">
         <v>183</v>
@@ -38151,10 +38151,10 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D194" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E194" t="s">
         <v>377</v>
@@ -38336,10 +38336,10 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="D195" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E195" t="s">
         <v>378</v>
@@ -38891,7 +38891,7 @@
         <v>100</v>
       </c>
       <c r="C198" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D198" t="s">
         <v>182</v>
@@ -39076,7 +39076,7 @@
         <v>101</v>
       </c>
       <c r="C199" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D199" t="s">
         <v>182</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39485,13 +39485,13 @@
         <v>685</v>
       </c>
       <c r="P201">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q201">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39530,10 +39530,10 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF201">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41296,7 +41296,7 @@
         <v>107</v>
       </c>
       <c r="C211" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D211" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,7 +42406,7 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D217" t="s">
         <v>182</v>
@@ -42445,13 +42445,13 @@
         <v>685</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42961,10 +42961,10 @@
         <v>108</v>
       </c>
       <c r="C220" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D220" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E220" t="s">
         <v>403</v>
@@ -43146,10 +43146,10 @@
         <v>108</v>
       </c>
       <c r="C221" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E221" t="s">
         <v>404</v>
@@ -43331,7 +43331,7 @@
         <v>108</v>
       </c>
       <c r="C222" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D222" t="s">
         <v>183</v>
@@ -43886,7 +43886,7 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D225" t="s">
         <v>183</v>
@@ -44071,7 +44071,7 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
         <v>183</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44626,10 +44626,10 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D229" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E229" t="s">
         <v>412</v>
@@ -44811,7 +44811,7 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D230" t="s">
         <v>183</v>
@@ -44996,7 +44996,7 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D231" t="s">
         <v>183</v>
@@ -45181,7 +45181,7 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D232" t="s">
         <v>183</v>
@@ -45366,7 +45366,7 @@
         <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D233" t="s">
         <v>183</v>
@@ -45551,7 +45551,7 @@
         <v>108</v>
       </c>
       <c r="C234" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D234" t="s">
         <v>183</v>
@@ -45736,10 +45736,10 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D235" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E235" t="s">
         <v>418</v>
@@ -45921,7 +45921,7 @@
         <v>108</v>
       </c>
       <c r="C236" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D236" t="s">
         <v>183</v>
@@ -46106,7 +46106,7 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D237" t="s">
         <v>183</v>
@@ -46476,10 +46476,10 @@
         <v>108</v>
       </c>
       <c r="C239" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D239" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E239" t="s">
         <v>422</v>
@@ -46515,13 +46515,13 @@
         <v>685</v>
       </c>
       <c r="P239">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q239">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R239">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S239">
         <v>0</v>
@@ -46661,7 +46661,7 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D240" t="s">
         <v>183</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47031,7 +47031,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D242" t="s">
         <v>182</v>
@@ -47401,7 +47401,7 @@
         <v>112</v>
       </c>
       <c r="C244" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>
@@ -47771,7 +47771,7 @@
         <v>113</v>
       </c>
       <c r="C246" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D246" t="s">
         <v>182</v>
@@ -48326,7 +48326,7 @@
         <v>115</v>
       </c>
       <c r="C249" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D249" t="s">
         <v>182</v>
@@ -48511,7 +48511,7 @@
         <v>115</v>
       </c>
       <c r="C250" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D250" t="s">
         <v>182</v>
@@ -48696,7 +48696,7 @@
         <v>115</v>
       </c>
       <c r="C251" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D251" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -376,72 +376,72 @@
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
+    <t>Lithuania A Lyga</t>
+  </si>
+  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
-    <t>Lithuania A Lyga</t>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
@@ -451,45 +451,45 @@
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -508,21 +508,21 @@
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>Turkey Süper Lig</t>
+  </si>
+  <si>
     <t>USA MLS</t>
   </si>
   <si>
-    <t>Turkey Süper Lig</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>France National</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -532,15 +532,15 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
@@ -589,15 +589,15 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -607,129 +607,129 @@
     <t>St George City FA</t>
   </si>
   <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Phu Dong</t>
   </si>
   <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
+    <t>Aston Villa Ladies</t>
   </si>
   <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
+    <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Cibalia</t>
   </si>
   <si>
-    <t>Hegelmann Litauen</t>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
+    <t>Young Lions</t>
   </si>
   <si>
     <t>Goa</t>
   </si>
   <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
     <t>Adama Kenema</t>
   </si>
   <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
     <t>Osnabrück</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Ceuta</t>
   </si>
   <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
     <t>Rot-Weiss Essen</t>
   </si>
   <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
     <t>Persis Solo</t>
   </si>
   <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
     <t>Teplice</t>
   </si>
   <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,114 +739,114 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
     <t>Norrby</t>
   </si>
   <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
     <t>Bravo</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
     <t>Panserraikos</t>
   </si>
   <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>Kristianstad</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
+    <t>Dinamo Zagreb</t>
   </si>
   <si>
     <t>Zulte-Waregem</t>
   </si>
   <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
     <t>Jamshedpur</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
   </si>
   <si>
     <t>Fulham</t>
   </si>
   <si>
-    <t>Brighton &amp; Hove Albion</t>
+    <t>CD Trofense</t>
   </si>
   <si>
     <t>Viktoria Plzeň</t>
   </si>
   <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Dundee</t>
   </si>
   <si>
     <t>Aberdeen</t>
   </si>
   <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
     <t>Burgos CF</t>
   </si>
   <si>
@@ -859,57 +859,57 @@
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
+    <t>Sumqayıt</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
@@ -922,24 +922,24 @@
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Lazio</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
@@ -949,63 +949,78 @@
     <t>Atlético Madrid</t>
   </si>
   <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
     <t>Recoleta</t>
   </si>
   <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
     <t>Real Valladolid</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
-    <t>İstanbul Başakşehir</t>
+    <t>Konyaspor</t>
   </si>
   <si>
     <t>Göztepe</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
@@ -1015,144 +1030,129 @@
     <t>Znicz Pruszków</t>
   </si>
   <si>
-    <t>Hapoel Petah Tikva</t>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
   </si>
   <si>
     <t>Partizan</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
     <t>Le Puy F.43 Auvergne</t>
   </si>
   <si>
-    <t>Châteauroux</t>
+    <t>Paris 13 Atletico</t>
   </si>
   <si>
     <t>Bourg-en-Bresse</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
     <t>Bastia</t>
   </si>
   <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
     <t>Saint-Étienne</t>
   </si>
   <si>
-    <t>Al Feiha</t>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Clermont</t>
   </si>
   <si>
     <t>Grenoble Foot 38</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
     <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
     <t>Luzern</t>
   </si>
   <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
+    <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>Lecce</t>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
   </si>
   <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
     <t>CD Mafra</t>
   </si>
   <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Real Oruro</t>
   </si>
   <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>Guayaquil City FC</t>
   </si>
   <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1186,108 +1186,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
-    <t>Brooklyn FC</t>
-  </si>
-  <si>
     <t>Louisville City</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
     <t>Bahia</t>
   </si>
   <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
     <t>Benfica II</t>
   </si>
   <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
   </si>
   <si>
     <t>GD Chaves</t>
   </si>
   <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Farense</t>
   </si>
   <si>
     <t>FC Penafiel</t>
   </si>
   <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
     <t>Lusitania Lourosa</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1306,12 +1306,12 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
     <t>Phoenix Rising</t>
   </si>
   <si>
-    <t>Oakland Roots</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
@@ -1339,15 +1339,15 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1357,129 +1357,129 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Granada W</t>
+  </si>
+  <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Granada W</t>
-  </si>
-  <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>Hai Phong</t>
   </si>
   <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
+    <t>Arsenal Women</t>
   </si>
   <si>
     <t>Ha Noi</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Sesvete</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
+    <t>Geylang International</t>
   </si>
   <si>
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>Shire Endaselassie</t>
   </si>
   <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
     <t>Ulm</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>CD Castellón</t>
   </si>
   <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
     <t>Verl</t>
   </si>
   <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
     <t>Baník Ostrava</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,114 +1489,114 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
     <t>Helsingborg</t>
   </si>
   <si>
+    <t>Udinese</t>
+  </si>
+  <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
     <t>Kifisia</t>
   </si>
   <si>
     <t>FC Caspiy</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
     <t>Mjällby</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
     <t>Norrköping W</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
-    <t>Borussia M'gladbach</t>
-  </si>
-  <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t>Bayer Leverkusen</t>
+    <t>Hajduk Split</t>
   </si>
   <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
     <t>Bengaluru</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
   </si>
   <si>
     <t>AFC Bournemouth</t>
   </si>
   <si>
-    <t>Wolverhampton Wanderers</t>
+    <t>Vitória Guimarães II</t>
   </si>
   <si>
     <t>Slovan Liberec</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Livingston</t>
   </si>
   <si>
     <t>Dundee United</t>
   </si>
   <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
     <t>Almería</t>
   </si>
   <si>
@@ -1609,57 +1609,57 @@
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
     <t>Irtysh</t>
   </si>
   <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Siwelele</t>
+    <t>Araz</t>
   </si>
   <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Araz</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
@@ -1672,24 +1672,24 @@
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
     <t>Inter Milan</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
     <t>Lommel United</t>
   </si>
   <si>
@@ -1699,63 +1699,78 @@
     <t>Celta de Vigo</t>
   </si>
   <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
     <t>Brentford</t>
   </si>
   <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
     <t>Trakai</t>
   </si>
   <si>
-    <t>Samsunspor</t>
+    <t>Fenerbahçe</t>
   </si>
   <si>
     <t>Gaziantep FK</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
@@ -1765,144 +1780,129 @@
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>Hapoel Be'er Sheva</t>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
   </si>
   <si>
     <t>OFK Beograd</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
     <t>Dijon</t>
   </si>
   <si>
-    <t>Sochaux</t>
+    <t>Aubagne</t>
   </si>
   <si>
     <t>Valenciennes</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
     <t>Le Mans</t>
   </si>
   <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
     <t>Amiens SC</t>
   </si>
   <si>
-    <t>Al Quadisiya</t>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
   </si>
   <si>
     <t>Troyes</t>
   </si>
   <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Servette</t>
   </si>
   <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Delfin SC</t>
+    <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
-    <t>Juventus</t>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Hearts</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
@@ -1915,15 +1915,15 @@
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1936,108 +1936,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>Operário PR</t>
   </si>
   <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
     <t>Casa Pia</t>
   </si>
   <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
     <t>Academico Viseu</t>
   </si>
   <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Porto II</t>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
   </si>
   <si>
     <t>Leixões</t>
   </si>
   <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
   </si>
   <si>
     <t>CS Marítimo</t>
   </si>
   <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
     <t>Torreense</t>
   </si>
   <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2056,10 +2056,10 @@
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
-  </si>
-  <si>
-    <t>El Paso Locomotive</t>
   </si>
   <si>
     <t>San Diego</t>
@@ -3741,7 +3741,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>182</v>
@@ -3926,7 +3926,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
@@ -5036,10 +5036,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
         <v>198</v>
@@ -5221,10 +5221,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E16" t="s">
         <v>199</v>
@@ -5406,10 +5406,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
         <v>200</v>
@@ -5591,10 +5591,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
         <v>201</v>
@@ -5964,7 +5964,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
         <v>203</v>
@@ -6331,10 +6331,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
         <v>205</v>
@@ -6516,7 +6516,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
         <v>182</v>
@@ -6886,10 +6886,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E25" t="s">
         <v>208</v>
@@ -7071,10 +7071,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E26" t="s">
         <v>209</v>
@@ -7259,7 +7259,7 @@
         <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
         <v>210</v>
@@ -7441,10 +7441,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
         <v>211</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7814,7 +7814,7 @@
         <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E30" t="s">
         <v>213</v>
@@ -7999,7 +7999,7 @@
         <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E31" t="s">
         <v>214</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8220,13 +8220,13 @@
         <v>685</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
         <v>182</v>
@@ -8736,10 +8736,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E35" t="s">
         <v>218</v>
@@ -8921,10 +8921,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E36" t="s">
         <v>219</v>
@@ -8960,13 +8960,13 @@
         <v>685</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9106,10 +9106,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
         <v>220</v>
@@ -9291,10 +9291,10 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -9661,10 +9661,10 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E40" t="s">
         <v>223</v>
@@ -9846,7 +9846,7 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
         <v>183</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10404,7 +10404,7 @@
         <v>138</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E44" t="s">
         <v>227</v>
@@ -10586,10 +10586,10 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
         <v>228</v>
@@ -10771,10 +10771,10 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E46" t="s">
         <v>229</v>
@@ -10956,7 +10956,7 @@
         <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D47" t="s">
         <v>183</v>
@@ -11141,10 +11141,10 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
         <v>231</v>
@@ -11326,7 +11326,7 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D49" t="s">
         <v>183</v>
@@ -11511,7 +11511,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
         <v>183</v>
@@ -11696,7 +11696,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -11884,7 +11884,7 @@
         <v>141</v>
       </c>
       <c r="D52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E52" t="s">
         <v>235</v>
@@ -12066,7 +12066,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
         <v>183</v>
@@ -12251,7 +12251,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D54" t="s">
         <v>183</v>
@@ -13176,10 +13176,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E59" t="s">
         <v>242</v>
@@ -13361,10 +13361,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E60" t="s">
         <v>243</v>
@@ -13546,7 +13546,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D61" t="s">
         <v>183</v>
@@ -13585,13 +13585,13 @@
         <v>685</v>
       </c>
       <c r="P61">
-        <v>3.13</v>
+        <v>2.54</v>
       </c>
       <c r="Q61">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="R61">
-        <v>2.42</v>
+        <v>3.21</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13731,10 +13731,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E62" t="s">
         <v>245</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14140,13 +14140,13 @@
         <v>685</v>
       </c>
       <c r="P64">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14286,7 +14286,7 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
         <v>182</v>
@@ -14471,10 +14471,10 @@
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D66" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
@@ -14659,7 +14659,7 @@
         <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
         <v>250</v>
@@ -14695,13 +14695,13 @@
         <v>685</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14841,7 +14841,7 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="D68" t="s">
         <v>182</v>
@@ -15026,10 +15026,10 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E69" t="s">
         <v>252</v>
@@ -15211,7 +15211,7 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
         <v>183</v>
@@ -15396,7 +15396,7 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
         <v>182</v>
@@ -15581,10 +15581,10 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E72" t="s">
         <v>255</v>
@@ -15990,61 +15990,61 @@
         <v>685</v>
       </c>
       <c r="P74">
+        <v>2.38</v>
+      </c>
+      <c r="Q74">
+        <v>3.71</v>
+      </c>
+      <c r="R74">
+        <v>3.07</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
         <v>1.61</v>
       </c>
-      <c r="Q74">
-        <v>4.88</v>
-      </c>
-      <c r="R74">
-        <v>5.33</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>0</v>
-      </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
-      <c r="W74">
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <v>0</v>
-      </c>
-      <c r="Y74">
-        <v>0</v>
-      </c>
-      <c r="Z74">
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <v>0</v>
-      </c>
-      <c r="AB74">
-        <v>0</v>
-      </c>
-      <c r="AC74">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>0</v>
-      </c>
-      <c r="AE74">
-        <v>0</v>
-      </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG74">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH74">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16175,13 +16175,13 @@
         <v>685</v>
       </c>
       <c r="P75">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="Q75">
-        <v>3.71</v>
+        <v>5.18</v>
       </c>
       <c r="R75">
-        <v>3.07</v>
+        <v>7.21</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -16220,16 +16220,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q76">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R76">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16411,10 +16411,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH76">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>685</v>
       </c>
       <c r="P77">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q77">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R77">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16596,10 +16596,10 @@
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH77">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17655,13 +17655,13 @@
         <v>685</v>
       </c>
       <c r="P83">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D85" t="s">
         <v>182</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>4.06</v>
+        <v>1.4</v>
       </c>
       <c r="Q86">
-        <v>3.98</v>
+        <v>5.48</v>
       </c>
       <c r="R86">
-        <v>1.93</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18395,13 +18395,13 @@
         <v>685</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -19096,7 +19096,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D91" t="s">
         <v>183</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -20021,7 +20021,7 @@
         <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D96" t="s">
         <v>183</v>
@@ -20206,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D97" t="s">
         <v>183</v>
@@ -20391,10 +20391,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D98" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
         <v>281</v>
@@ -20576,7 +20576,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D99" t="s">
         <v>183</v>
@@ -20946,10 +20946,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E101" t="s">
         <v>284</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D102" t="s">
         <v>183</v>
@@ -21316,7 +21316,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D103" t="s">
         <v>183</v>
@@ -21501,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
         <v>183</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -22056,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
         <v>183</v>
@@ -22241,7 +22241,7 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D108" t="s">
         <v>182</v>
@@ -22426,7 +22426,7 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D109" t="s">
         <v>183</v>
@@ -22611,7 +22611,7 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D110" t="s">
         <v>182</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25941,10 +25941,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E128" t="s">
         <v>311</v>
@@ -25980,13 +25980,13 @@
         <v>685</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26126,10 +26126,10 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129" t="s">
         <v>312</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26496,7 +26496,7 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D131" t="s">
         <v>183</v>
@@ -26535,13 +26535,13 @@
         <v>685</v>
       </c>
       <c r="P131">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27051,7 +27051,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D134" t="s">
         <v>183</v>
@@ -27239,7 +27239,7 @@
         <v>164</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27421,7 +27421,7 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
         <v>183</v>
@@ -27606,7 +27606,7 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="D137" t="s">
         <v>183</v>
@@ -27791,10 +27791,10 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E138" t="s">
         <v>321</v>
@@ -27976,7 +27976,7 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
         <v>183</v>
@@ -28161,7 +28161,7 @@
         <v>91</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D140" t="s">
         <v>183</v>
@@ -28346,7 +28346,7 @@
         <v>91</v>
       </c>
       <c r="C141" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D141" t="s">
         <v>183</v>
@@ -28534,7 +28534,7 @@
         <v>165</v>
       </c>
       <c r="D142" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E142" t="s">
         <v>325</v>
@@ -28716,10 +28716,10 @@
         <v>91</v>
       </c>
       <c r="C143" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="D143" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E143" t="s">
         <v>326</v>
@@ -28901,7 +28901,7 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D144" t="s">
         <v>183</v>
@@ -29086,7 +29086,7 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D145" t="s">
         <v>183</v>
@@ -29641,7 +29641,7 @@
         <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D148" t="s">
         <v>183</v>
@@ -29826,7 +29826,7 @@
         <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D149" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -31861,7 +31861,7 @@
         <v>93</v>
       </c>
       <c r="C160" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D160" t="s">
         <v>183</v>
@@ -32046,7 +32046,7 @@
         <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -32416,7 +32416,7 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="D163" t="s">
         <v>183</v>
@@ -32601,7 +32601,7 @@
         <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D164" t="s">
         <v>183</v>
@@ -32786,7 +32786,7 @@
         <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D165" t="s">
         <v>183</v>
@@ -32971,7 +32971,7 @@
         <v>94</v>
       </c>
       <c r="C166" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>183</v>
@@ -33156,7 +33156,7 @@
         <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
         <v>183</v>
@@ -33195,13 +33195,13 @@
         <v>685</v>
       </c>
       <c r="P167">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q167">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R167">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33526,10 +33526,10 @@
         <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D169" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E169" t="s">
         <v>352</v>
@@ -33711,10 +33711,10 @@
         <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E170" t="s">
         <v>353</v>
@@ -34081,10 +34081,10 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D172" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E172" t="s">
         <v>355</v>
@@ -34266,10 +34266,10 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D173" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E173" t="s">
         <v>356</v>
@@ -34305,13 +34305,13 @@
         <v>685</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34821,7 +34821,7 @@
         <v>95</v>
       </c>
       <c r="C176" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D176" t="s">
         <v>183</v>
@@ -35191,10 +35191,10 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D178" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E178" t="s">
         <v>361</v>
@@ -35415,13 +35415,13 @@
         <v>685</v>
       </c>
       <c r="P179">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q179">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R179">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35460,10 +35460,10 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF179">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -35561,10 +35561,10 @@
         <v>96</v>
       </c>
       <c r="C180" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="D180" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E180" t="s">
         <v>363</v>
@@ -35746,10 +35746,10 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E181" t="s">
         <v>364</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,10 +35830,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D182" t="s">
         <v>182</v>
@@ -36301,10 +36301,10 @@
         <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D184" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E184" t="s">
         <v>367</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q186">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R186">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36859,7 +36859,7 @@
         <v>172</v>
       </c>
       <c r="D187" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E187" t="s">
         <v>370</v>
@@ -37041,7 +37041,7 @@
         <v>98</v>
       </c>
       <c r="C188" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D188" t="s">
         <v>183</v>
@@ -37226,10 +37226,10 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D189" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E189" t="s">
         <v>372</v>
@@ -37411,10 +37411,10 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="D190" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E190" t="s">
         <v>373</v>
@@ -37450,13 +37450,13 @@
         <v>685</v>
       </c>
       <c r="P190">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37596,10 +37596,10 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D191" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E191" t="s">
         <v>374</v>
@@ -37781,10 +37781,10 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D192" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -37966,10 +37966,10 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D193" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38005,13 +38005,13 @@
         <v>685</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38151,10 +38151,10 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D194" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E194" t="s">
         <v>377</v>
@@ -38336,10 +38336,10 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="D195" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E195" t="s">
         <v>378</v>
@@ -38891,7 +38891,7 @@
         <v>100</v>
       </c>
       <c r="C198" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D198" t="s">
         <v>182</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q200">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39670,13 +39670,13 @@
         <v>685</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39715,10 +39715,10 @@
         <v>0</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG202">
         <v>0</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41296,7 +41296,7 @@
         <v>107</v>
       </c>
       <c r="C211" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D211" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,7 +42406,7 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D217" t="s">
         <v>182</v>
@@ -42961,7 +42961,7 @@
         <v>108</v>
       </c>
       <c r="C220" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D220" t="s">
         <v>183</v>
@@ -44256,7 +44256,7 @@
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D227" t="s">
         <v>183</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D228" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44626,7 +44626,7 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D229" t="s">
         <v>182</v>
@@ -44811,10 +44811,10 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D230" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E230" t="s">
         <v>413</v>
@@ -44996,10 +44996,10 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D231" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E231" t="s">
         <v>414</v>
@@ -46291,10 +46291,10 @@
         <v>108</v>
       </c>
       <c r="C238" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D238" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E238" t="s">
         <v>421</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47031,7 +47031,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D242" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>
@@ -47771,7 +47771,7 @@
         <v>113</v>
       </c>
       <c r="C246" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D246" t="s">
         <v>182</v>
@@ -48326,7 +48326,7 @@
         <v>115</v>
       </c>
       <c r="C249" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D249" t="s">
         <v>182</v>
@@ -48511,7 +48511,7 @@
         <v>115</v>
       </c>
       <c r="C250" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D250" t="s">
         <v>182</v>
@@ -48696,7 +48696,7 @@
         <v>115</v>
       </c>
       <c r="C251" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D251" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,46 +364,49 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
+    <t>Croatia Druga HNL</t>
+  </si>
+  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Croatia Druga HNL</t>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Singapore S.League</t>
@@ -412,9 +415,6 @@
     <t>China China League One</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>England Premier League</t>
   </si>
   <si>
@@ -424,72 +424,72 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -508,21 +508,21 @@
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
     <t>Turkey Süper Lig</t>
   </si>
   <si>
-    <t>USA MLS</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -532,18 +532,18 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Portugal Liga NOS</t>
   </si>
   <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -571,18 +571,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>SD Raiders</t>
   </si>
   <si>
@@ -592,12 +592,12 @@
     <t>Suwon Bluewings</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -607,129 +607,129 @@
     <t>St George City FA</t>
   </si>
   <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>Holstein Kiel</t>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
   </si>
   <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
     <t>Zhetysu</t>
   </si>
   <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
+    <t>Cibalia</t>
+  </si>
+  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
-    <t>Cibalia</t>
+    <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
+    <t>Young Lions</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
     <t>Goa</t>
   </si>
   <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
-    <t>Adama Kenema</t>
+    <t>1860 München</t>
   </si>
   <si>
     <t>Elche CF</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
     <t>Brommapojkarna W</t>
   </si>
   <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,25 +739,43 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
     <t>Orbit College</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Växjö</t>
+    <t>Västerås SK</t>
   </si>
   <si>
     <t>IFK Göteborg</t>
@@ -766,177 +784,159 @@
     <t>Hadiya Hosaena</t>
   </si>
   <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
     <t>Augsburg</t>
   </si>
   <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Hoffenheim</t>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
   </si>
   <si>
     <t>Dinamo Zagreb</t>
   </si>
   <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
     <t>Zulte-Waregem</t>
   </si>
   <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
     <t>Burgos CF</t>
   </si>
   <si>
+    <t>Sevilla FC</t>
+  </si>
+  <si>
     <t>Albacete Balompié</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
     <t>Wattens</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
   </si>
   <si>
     <t>AEL</t>
   </si>
   <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Tobol</t>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Koper</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Sumqayıt</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
-    <t>Koper</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Athletic Club W</t>
+    <t>Winterthur</t>
   </si>
   <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
@@ -946,234 +946,234 @@
     <t>Al Najma</t>
   </si>
   <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
     <t>Atlético Madrid</t>
   </si>
   <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
     <t>Kocaelispor</t>
   </si>
   <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
     <t>Châteauroux</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
   </si>
   <si>
     <t>Bastia</t>
   </si>
   <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
     <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
+    <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
     <t>Guayaquil City FC</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1186,108 +1186,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
     <t>Louisville City</t>
   </si>
   <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
     <t>New England Revolution</t>
   </si>
   <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Alverca</t>
   </si>
   <si>
     <t>Bahia</t>
   </si>
   <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
   </si>
   <si>
     <t>Sporting CP II</t>
   </si>
   <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1297,12 +1297,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>New Mexico United</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1315,10 +1315,16 @@
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
   </si>
   <si>
     <t>FC Seoul</t>
@@ -1327,12 +1333,6 @@
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>NWS Spirit</t>
   </si>
   <si>
@@ -1342,12 +1342,12 @@
     <t>Daegu</t>
   </si>
   <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1357,129 +1357,129 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
     <t>Granada W</t>
   </si>
   <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Magdeburg</t>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
   </si>
   <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
     <t>Ha Noi</t>
   </si>
   <si>
+    <t>Sesvete</t>
+  </si>
+  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Sesvete</t>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
+    <t>Geylang International</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
-    <t>Shire Endaselassie</t>
+    <t>Ingolstadt</t>
   </si>
   <si>
     <t>Deportivo Alavés</t>
   </si>
   <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
     <t>Eskilstuna United</t>
   </si>
   <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,25 +1489,43 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>AIK Women</t>
+    <t>GAIS</t>
   </si>
   <si>
     <t>Hammarby</t>
@@ -1516,177 +1534,159 @@
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
     <t>St. Pauli</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
-    <t>Werder Bremen</t>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
   </si>
   <si>
     <t>Hajduk Split</t>
   </si>
   <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
     <t>Almería</t>
   </si>
   <si>
+    <t>RCD Espanyol</t>
+  </si>
+  <si>
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Orijent 1919</t>
   </si>
   <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
     <t>Blau-Weiß Linz</t>
   </si>
   <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Akritas</t>
   </si>
   <si>
     <t>Olympiakos</t>
   </si>
   <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Aluminij</t>
   </si>
   <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Araz</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>Deportivo de La Coruña W</t>
+    <t>Lausanne Sport</t>
   </si>
   <si>
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
     <t>Grasshopper</t>
   </si>
   <si>
@@ -1696,234 +1696,234 @@
     <t>Al Hazm</t>
   </si>
   <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
     <t>Celta de Vigo</t>
   </si>
   <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Brentford</t>
   </si>
   <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
     <t>Sochaux</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Midland</t>
   </si>
   <si>
     <t>Le Mans</t>
   </si>
   <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
     <t>Al Quadisiya</t>
   </si>
   <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
     <t>Los Andes</t>
   </si>
   <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Real Betis</t>
   </si>
   <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
+    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1936,108 +1936,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
     <t>Operário PR</t>
   </si>
   <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
   </si>
   <si>
     <t>Cruzeiro</t>
   </si>
   <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
   </si>
   <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2047,12 +2047,12 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
@@ -2065,10 +2065,10 @@
     <t>San Diego</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2816,7 +2816,7 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>182</v>
@@ -3001,7 +3001,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -3371,7 +3371,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -3741,7 +3741,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>182</v>
@@ -4111,7 +4111,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
@@ -4666,7 +4666,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5221,7 +5221,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
         <v>182</v>
@@ -5409,7 +5409,7 @@
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
         <v>200</v>
@@ -5594,7 +5594,7 @@
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
         <v>201</v>
@@ -5964,7 +5964,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E20" t="s">
         <v>203</v>
@@ -6331,10 +6331,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
         <v>205</v>
@@ -6516,7 +6516,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>182</v>
@@ -6701,10 +6701,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
         <v>207</v>
@@ -6886,10 +6886,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
         <v>208</v>
@@ -7071,10 +7071,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E26" t="s">
         <v>209</v>
@@ -7256,10 +7256,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
         <v>210</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7814,7 +7814,7 @@
         <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
         <v>213</v>
@@ -7999,7 +7999,7 @@
         <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
         <v>214</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8369,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8554,7 +8554,7 @@
         <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -8921,10 +8921,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
         <v>219</v>
@@ -8960,13 +8960,13 @@
         <v>685</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9106,10 +9106,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E37" t="s">
         <v>220</v>
@@ -9145,13 +9145,13 @@
         <v>685</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9664,7 +9664,7 @@
         <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E40" t="s">
         <v>223</v>
@@ -9846,10 +9846,10 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10586,7 +10586,7 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
         <v>183</v>
@@ -10771,10 +10771,10 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
         <v>229</v>
@@ -11141,10 +11141,10 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
         <v>231</v>
@@ -11326,7 +11326,7 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
         <v>183</v>
@@ -11511,7 +11511,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
         <v>183</v>
@@ -11696,10 +11696,10 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E51" t="s">
         <v>234</v>
@@ -11881,7 +11881,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
         <v>183</v>
@@ -12066,7 +12066,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
         <v>183</v>
@@ -12254,7 +12254,7 @@
         <v>141</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E54" t="s">
         <v>237</v>
@@ -12991,10 +12991,10 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
         <v>241</v>
@@ -13215,13 +13215,13 @@
         <v>685</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -13361,10 +13361,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E60" t="s">
         <v>243</v>
@@ -13400,13 +13400,13 @@
         <v>685</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13546,7 +13546,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D61" t="s">
         <v>183</v>
@@ -13585,13 +13585,13 @@
         <v>685</v>
       </c>
       <c r="P61">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13731,10 +13731,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E62" t="s">
         <v>245</v>
@@ -13916,10 +13916,10 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E63" t="s">
         <v>246</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14286,7 +14286,7 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D65" t="s">
         <v>182</v>
@@ -14471,10 +14471,10 @@
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
@@ -14656,7 +14656,7 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
         <v>183</v>
@@ -14695,13 +14695,13 @@
         <v>685</v>
       </c>
       <c r="P67">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14841,10 +14841,10 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
         <v>251</v>
@@ -15029,7 +15029,7 @@
         <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E69" t="s">
         <v>252</v>
@@ -15211,10 +15211,10 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
         <v>253</v>
@@ -15396,7 +15396,7 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
         <v>182</v>
@@ -15581,10 +15581,10 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D72" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
         <v>255</v>
@@ -16175,13 +16175,13 @@
         <v>685</v>
       </c>
       <c r="P75">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q75">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R75">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -16226,10 +16226,10 @@
         <v>0</v>
       </c>
       <c r="AG75">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH75">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q76">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R76">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16411,10 +16411,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH76">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>685</v>
       </c>
       <c r="P77">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="Q77">
-        <v>4.88</v>
+        <v>5.18</v>
       </c>
       <c r="R77">
-        <v>5.33</v>
+        <v>7.21</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16596,10 +16596,10 @@
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH77">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16691,10 +16691,10 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D78" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E78" t="s">
         <v>261</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -16915,13 +16915,13 @@
         <v>685</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17986,10 +17986,10 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D85" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E85" t="s">
         <v>268</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18395,13 +18395,13 @@
         <v>685</v>
       </c>
       <c r="P87">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -20206,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D97" t="s">
         <v>183</v>
@@ -20394,7 +20394,7 @@
         <v>121</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E98" t="s">
         <v>281</v>
@@ -20576,10 +20576,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D99" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E99" t="s">
         <v>282</v>
@@ -20761,7 +20761,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D100" t="s">
         <v>183</v>
@@ -20946,7 +20946,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D101" t="s">
         <v>182</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D102" t="s">
         <v>183</v>
@@ -21316,7 +21316,7 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D103" t="s">
         <v>183</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -22056,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D107" t="s">
         <v>183</v>
@@ -22241,10 +22241,10 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="D108" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
         <v>291</v>
@@ -22611,10 +22611,10 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D110" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
         <v>293</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -24870,13 +24870,13 @@
         <v>685</v>
       </c>
       <c r="P122">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25016,7 +25016,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D123" t="s">
         <v>183</v>
@@ -25055,13 +25055,13 @@
         <v>685</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25795,13 +25795,13 @@
         <v>685</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25941,7 +25941,7 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D128" t="s">
         <v>183</v>
@@ -25980,13 +25980,13 @@
         <v>685</v>
       </c>
       <c r="P128">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q128">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R128">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26126,10 +26126,10 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129" t="s">
         <v>312</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26496,10 +26496,10 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
         <v>314</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27051,10 +27051,10 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D134" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E134" t="s">
         <v>317</v>
@@ -27239,7 +27239,7 @@
         <v>164</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27421,7 +27421,7 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D136" t="s">
         <v>183</v>
@@ -27606,7 +27606,7 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
         <v>183</v>
@@ -27791,7 +27791,7 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D138" t="s">
         <v>183</v>
@@ -27976,7 +27976,7 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
         <v>183</v>
@@ -28161,7 +28161,7 @@
         <v>91</v>
       </c>
       <c r="C140" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D140" t="s">
         <v>183</v>
@@ -28346,7 +28346,7 @@
         <v>91</v>
       </c>
       <c r="C141" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D141" t="s">
         <v>183</v>
@@ -28531,10 +28531,10 @@
         <v>91</v>
       </c>
       <c r="C142" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="D142" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E142" t="s">
         <v>325</v>
@@ -28716,10 +28716,10 @@
         <v>91</v>
       </c>
       <c r="C143" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="D143" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E143" t="s">
         <v>326</v>
@@ -28901,7 +28901,7 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D144" t="s">
         <v>183</v>
@@ -29086,7 +29086,7 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D145" t="s">
         <v>183</v>
@@ -29826,7 +29826,7 @@
         <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D149" t="s">
         <v>183</v>
@@ -30011,7 +30011,7 @@
         <v>93</v>
       </c>
       <c r="C150" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D150" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30566,7 +30566,7 @@
         <v>93</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D153" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -31861,7 +31861,7 @@
         <v>93</v>
       </c>
       <c r="C160" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D160" t="s">
         <v>183</v>
@@ -32046,7 +32046,7 @@
         <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -32416,7 +32416,7 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D163" t="s">
         <v>183</v>
@@ -32455,13 +32455,13 @@
         <v>685</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32786,7 +32786,7 @@
         <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D165" t="s">
         <v>183</v>
@@ -33526,10 +33526,10 @@
         <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E169" t="s">
         <v>352</v>
@@ -33896,7 +33896,7 @@
         <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="D171" t="s">
         <v>183</v>
@@ -34266,7 +34266,7 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D173" t="s">
         <v>183</v>
@@ -34305,13 +34305,13 @@
         <v>685</v>
       </c>
       <c r="P173">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34451,7 +34451,7 @@
         <v>94</v>
       </c>
       <c r="C174" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D174" t="s">
         <v>183</v>
@@ -34636,10 +34636,10 @@
         <v>94</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E175" t="s">
         <v>358</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35376,10 +35376,10 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E179" t="s">
         <v>362</v>
@@ -35561,10 +35561,10 @@
         <v>96</v>
       </c>
       <c r="C180" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="D180" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E180" t="s">
         <v>363</v>
@@ -35600,13 +35600,13 @@
         <v>685</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35645,10 +35645,10 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -35746,10 +35746,10 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="D181" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E181" t="s">
         <v>364</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q181">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R181">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,10 +35830,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF181">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D183" t="s">
         <v>182</v>
@@ -36301,10 +36301,10 @@
         <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D184" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E184" t="s">
         <v>367</v>
@@ -36856,7 +36856,7 @@
         <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D187" t="s">
         <v>182</v>
@@ -37041,10 +37041,10 @@
         <v>98</v>
       </c>
       <c r="C188" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D188" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E188" t="s">
         <v>371</v>
@@ -37080,13 +37080,13 @@
         <v>685</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37226,7 +37226,7 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D189" t="s">
         <v>182</v>
@@ -37411,7 +37411,7 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D190" t="s">
         <v>183</v>
@@ -37596,10 +37596,10 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D191" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E191" t="s">
         <v>374</v>
@@ -37781,7 +37781,7 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="D192" t="s">
         <v>183</v>
@@ -37966,10 +37966,10 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D193" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38005,13 +38005,13 @@
         <v>685</v>
       </c>
       <c r="P193">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q193">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38151,7 +38151,7 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D194" t="s">
         <v>183</v>
@@ -38336,10 +38336,10 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="D195" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E195" t="s">
         <v>378</v>
@@ -38891,7 +38891,7 @@
         <v>100</v>
       </c>
       <c r="C198" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D198" t="s">
         <v>182</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39670,13 +39670,13 @@
         <v>685</v>
       </c>
       <c r="P202">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q202">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39715,10 +39715,10 @@
         <v>0</v>
       </c>
       <c r="AE202">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF202">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG202">
         <v>0</v>
@@ -39816,7 +39816,7 @@
         <v>102</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D203" t="s">
         <v>182</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41296,7 +41296,7 @@
         <v>107</v>
       </c>
       <c r="C211" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D211" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,10 +42406,10 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D217" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E217" t="s">
         <v>400</v>
@@ -42445,13 +42445,13 @@
         <v>685</v>
       </c>
       <c r="P217">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q217">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R217">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -43886,7 +43886,7 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D225" t="s">
         <v>183</v>
@@ -44071,7 +44071,7 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D226" t="s">
         <v>183</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D228" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44626,10 +44626,10 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D229" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E229" t="s">
         <v>412</v>
@@ -44811,10 +44811,10 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D230" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E230" t="s">
         <v>413</v>
@@ -45181,10 +45181,10 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D232" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E232" t="s">
         <v>415</v>
@@ -45366,7 +45366,7 @@
         <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D233" t="s">
         <v>183</v>
@@ -45736,7 +45736,7 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D235" t="s">
         <v>182</v>
@@ -46106,10 +46106,10 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D237" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E237" t="s">
         <v>420</v>
@@ -46145,13 +46145,13 @@
         <v>685</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S237">
         <v>0</v>
@@ -46476,7 +46476,7 @@
         <v>108</v>
       </c>
       <c r="C239" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D239" t="s">
         <v>183</v>
@@ -46661,7 +46661,7 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D240" t="s">
         <v>183</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47031,7 +47031,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D242" t="s">
         <v>182</v>
@@ -47401,7 +47401,7 @@
         <v>112</v>
       </c>
       <c r="C244" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>
@@ -47771,7 +47771,7 @@
         <v>113</v>
       </c>
       <c r="C246" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D246" t="s">
         <v>182</v>
@@ -48326,7 +48326,7 @@
         <v>115</v>
       </c>
       <c r="C249" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D249" t="s">
         <v>182</v>
@@ -48511,7 +48511,7 @@
         <v>115</v>
       </c>
       <c r="C250" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D250" t="s">
         <v>182</v>
@@ -48696,7 +48696,7 @@
         <v>115</v>
       </c>
       <c r="C251" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D251" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -391,54 +391,54 @@
     <t>Vietnam V.League 1</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>England FA Women's Super League</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>England FA Women's Super League</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>China China League One</t>
+    <t>India Indian Super League</t>
   </si>
   <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
+    <t>Spain La Liga</t>
   </si>
   <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -448,6 +448,12 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
@@ -457,28 +463,25 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
+    <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
@@ -487,9 +490,6 @@
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -508,21 +508,21 @@
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>Turkey Süper Lig</t>
+  </si>
+  <si>
     <t>USA MLS</t>
   </si>
   <si>
-    <t>Turkey Süper Lig</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>France National</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -532,18 +532,18 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -574,27 +574,27 @@
     <t>Hwaseong</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Gwangju</t>
   </si>
   <si>
@@ -607,12 +607,12 @@
     <t>St George City FA</t>
   </si>
   <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
     <t>Espanyol W</t>
   </si>
   <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
@@ -628,73 +628,94 @@
     <t>Phu Dong</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Young Lions</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
+    <t>Goa</t>
+  </si>
+  <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Goa</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
-    <t>Ceuta</t>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
   </si>
   <si>
     <t>Dukla Praha</t>
@@ -703,33 +724,12 @@
     <t>Osnabrück</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
+    <t>Brommapojkarna W</t>
   </si>
   <si>
     <t>Teplice</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,163 +739,169 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
     <t>Cagliari</t>
   </si>
   <si>
     <t>Bravo</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
     <t>Växjö</t>
   </si>
   <si>
-    <t>Norrby</t>
-  </si>
-  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
+    <t>Hadiya Hosaena</t>
   </si>
   <si>
     <t>Västerås SK</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
     <t>Augsburg</t>
   </si>
   <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Hoffenheim</t>
-  </si>
-  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
     <t>Vaprus</t>
   </si>
   <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
     <t>Fulham</t>
   </si>
   <si>
-    <t>Eibar W</t>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
   </si>
   <si>
     <t>CD Trofense</t>
   </si>
   <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Larissa</t>
+    <t>RAAL La Louvière</t>
   </si>
   <si>
     <t>Brighton &amp; Hove Albion</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
+    <t>Albacete Balompié</t>
+  </si>
+  <si>
+    <t>Sevilla FC</t>
   </si>
   <si>
     <t>Burgos CF</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
-    <t>Albacete Balompié</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Wattens</t>
   </si>
   <si>
     <t>Grazer AK</t>
   </si>
   <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
+    <t>AEL</t>
   </si>
   <si>
     <t>Enosis</t>
   </si>
   <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>AEL</t>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Sumqayıt</t>
   </si>
   <si>
     <t>Železničar Pančevo</t>
@@ -907,12 +913,6 @@
     <t>Koper</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
@@ -922,258 +922,258 @@
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
-    <t>Prostějov</t>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Lazio</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
-    <t>Al Najma</t>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
   </si>
   <si>
     <t>Wolfsburg</t>
   </si>
   <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
     <t>Real Valladolid</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
     <t>Znicz Pruszków</t>
   </si>
   <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
     <t>Stade Briochin</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Clermont</t>
   </si>
   <si>
     <t>Annecy</t>
   </si>
   <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
+    <t>Górnik Zabrze</t>
+  </si>
+  <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Górnik Zabrze</t>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
   </si>
   <si>
     <t>San Miguel</t>
   </si>
   <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
     <t>Luzern</t>
   </si>
   <si>
     <t>Acassuso</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>Coritiba</t>
+    <t>CD Mafra</t>
   </si>
   <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Guayaquil City FC</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1189,105 +1189,105 @@
     <t>Indy Eleven</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
     <t>Louisville City</t>
   </si>
   <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
     <t>Charlotte</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>CRB</t>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
   </si>
   <si>
     <t>FC Penafiel</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
     <t>GD Chaves</t>
   </si>
   <si>
-    <t>CD Feirense</t>
+    <t>Alverca</t>
   </si>
   <si>
     <t>FC Vizela</t>
   </si>
   <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1297,54 +1297,54 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Phoenix Rising</t>
+  </si>
+  <si>
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>Phoenix Rising</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
     <t>Suwon</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Gangwon</t>
   </si>
   <si>
@@ -1357,12 +1357,12 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Granada W</t>
+  </si>
+  <si>
     <t>Badalona W</t>
   </si>
   <si>
-    <t>Granada W</t>
-  </si>
-  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
@@ -1378,73 +1378,94 @@
     <t>Hai Phong</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>Magdeburg</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
     <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Geylang International</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
     <t>Henan Jianye</t>
   </si>
   <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>CD Castellón</t>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Zlín</t>
   </si>
   <si>
     <t>Slovácko</t>
@@ -1453,33 +1474,12 @@
     <t>Ulm</t>
   </si>
   <si>
-    <t>Verl</t>
+    <t>Eskilstuna United</t>
   </si>
   <si>
     <t>Baník Ostrava</t>
   </si>
   <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,163 +1489,169 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
     <t>FC Caspiy</t>
   </si>
   <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
     <t>Udinese</t>
   </si>
   <si>
     <t>Radomlje</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>AIK Women</t>
   </si>
   <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
+    <t>Awassa Kenema</t>
   </si>
   <si>
     <t>GAIS</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
-    <t>Werder Bremen</t>
-  </si>
-  <si>
     <t>St. Pauli</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
     <t>AFC Bournemouth</t>
   </si>
   <si>
-    <t>Alhama</t>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
   </si>
   <si>
     <t>Vitória Guimarães II</t>
   </si>
   <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
+    <t>Cercle Brugge</t>
   </si>
   <si>
     <t>Wolverhampton Wanderers</t>
   </si>
   <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
+    <t>Cultural y Deportiva Leonesa</t>
+  </si>
+  <si>
+    <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Almería</t>
   </si>
   <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
-    <t>Cultural y Deportiva Leonesa</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
     <t>Irtysh</t>
   </si>
   <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
   </si>
   <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
+    <t>Olympiakos</t>
   </si>
   <si>
     <t>Ethnikos Achna</t>
   </si>
   <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
+    <t>Siwelele</t>
+  </si>
+  <si>
+    <t>Araz</t>
   </si>
   <si>
     <t>Radnik Surdulica</t>
@@ -1657,12 +1663,6 @@
     <t>Aluminij</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
-    <t>Araz</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
@@ -1672,258 +1672,258 @@
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
-    <t>České Budějovice</t>
+    <t>Inter Milan</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
   </si>
   <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Inter Milan</t>
-  </si>
-  <si>
     <t>Grasshopper</t>
   </si>
   <si>
+    <t>Al Hazm</t>
+  </si>
+  <si>
     <t>Lommel United</t>
   </si>
   <si>
-    <t>Al Hazm</t>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
   </si>
   <si>
     <t>Bayern München</t>
   </si>
   <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Brentford</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
     <t>Trakai</t>
   </si>
   <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
     <t>Quevilly Rouen</t>
   </si>
   <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
   </si>
   <si>
     <t>Rodez</t>
   </si>
   <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
     <t>Los Andes</t>
   </si>
   <si>
+    <t>Zagłębie Lubin</t>
+  </si>
+  <si>
     <t>Olimpija</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>New York RB</t>
   </si>
   <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Servette</t>
   </si>
   <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Internacional</t>
+    <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
     <t>Hearts</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1939,105 +1939,105 @@
     <t>Sporting JAX</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Operário PR</t>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
   </si>
   <si>
     <t>CS Marítimo</t>
   </si>
   <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
     <t>Leixões</t>
   </si>
   <si>
-    <t>UD Oliveirense</t>
+    <t>GD Estoril Praia</t>
   </si>
   <si>
     <t>União de Leiria</t>
   </si>
   <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2047,28 +2047,28 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>Las Vegas Lights</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>El Paso Locomotive</t>
   </si>
   <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
     <t>San Diego</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2816,7 +2816,7 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
         <v>182</v>
@@ -3001,7 +3001,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -3186,7 +3186,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -3926,7 +3926,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
@@ -5815,13 +5815,13 @@
         <v>685</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -6149,7 +6149,7 @@
         <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
         <v>204</v>
@@ -6331,7 +6331,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
         <v>182</v>
@@ -6519,7 +6519,7 @@
         <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E23" t="s">
         <v>206</v>
@@ -6701,10 +6701,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
         <v>207</v>
@@ -6740,13 +6740,13 @@
         <v>685</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -6785,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6889,7 +6889,7 @@
         <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E25" t="s">
         <v>208</v>
@@ -7071,7 +7071,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>183</v>
@@ -7110,13 +7110,13 @@
         <v>685</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
         <v>210</v>
@@ -7441,10 +7441,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
         <v>211</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7665,13 +7665,13 @@
         <v>685</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8369,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8551,10 +8551,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -8736,10 +8736,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E35" t="s">
         <v>218</v>
@@ -8921,7 +8921,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
         <v>182</v>
@@ -9145,13 +9145,13 @@
         <v>685</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9330,13 +9330,13 @@
         <v>685</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9664,7 +9664,7 @@
         <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E40" t="s">
         <v>223</v>
@@ -9846,10 +9846,10 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10401,7 +10401,7 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -10586,10 +10586,10 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E45" t="s">
         <v>228</v>
@@ -10771,7 +10771,7 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -11141,7 +11141,7 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
         <v>183</v>
@@ -11326,7 +11326,7 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
         <v>183</v>
@@ -11511,7 +11511,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D50" t="s">
         <v>183</v>
@@ -11696,10 +11696,10 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E51" t="s">
         <v>234</v>
@@ -11881,7 +11881,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
         <v>183</v>
@@ -12066,10 +12066,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E53" t="s">
         <v>236</v>
@@ -12251,10 +12251,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s">
         <v>237</v>
@@ -12845,13 +12845,13 @@
         <v>685</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12991,10 +12991,10 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="D58" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
         <v>241</v>
@@ -13176,10 +13176,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E59" t="s">
         <v>242</v>
@@ -13215,13 +13215,13 @@
         <v>685</v>
       </c>
       <c r="P59">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q59">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -13400,13 +13400,13 @@
         <v>685</v>
       </c>
       <c r="P60">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13585,13 +13585,13 @@
         <v>685</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13731,10 +13731,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E62" t="s">
         <v>245</v>
@@ -13916,7 +13916,7 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D63" t="s">
         <v>182</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14286,10 +14286,10 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
         <v>248</v>
@@ -14325,13 +14325,13 @@
         <v>685</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14474,7 +14474,7 @@
         <v>148</v>
       </c>
       <c r="D66" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
@@ -14659,7 +14659,7 @@
         <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E67" t="s">
         <v>250</v>
@@ -14841,10 +14841,10 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E68" t="s">
         <v>251</v>
@@ -15026,10 +15026,10 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E69" t="s">
         <v>252</v>
@@ -15211,10 +15211,10 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E70" t="s">
         <v>253</v>
@@ -15396,10 +15396,10 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="D71" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E71" t="s">
         <v>254</v>
@@ -15581,10 +15581,10 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E72" t="s">
         <v>255</v>
@@ -15805,13 +15805,13 @@
         <v>685</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15990,13 +15990,13 @@
         <v>685</v>
       </c>
       <c r="P74">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q74">
-        <v>3.71</v>
+        <v>4.16</v>
       </c>
       <c r="R74">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16035,16 +16035,16 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF74">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16175,13 +16175,13 @@
         <v>685</v>
       </c>
       <c r="P75">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q75">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R75">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -16226,10 +16226,10 @@
         <v>0</v>
       </c>
       <c r="AG75">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH75">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,61 +16360,61 @@
         <v>685</v>
       </c>
       <c r="P76">
+        <v>2.38</v>
+      </c>
+      <c r="Q76">
+        <v>3.71</v>
+      </c>
+      <c r="R76">
+        <v>3.07</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
+      <c r="AE76">
         <v>1.61</v>
       </c>
-      <c r="Q76">
-        <v>4.88</v>
-      </c>
-      <c r="R76">
-        <v>5.33</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>0</v>
-      </c>
-      <c r="Z76">
-        <v>0</v>
-      </c>
-      <c r="AA76">
-        <v>0</v>
-      </c>
-      <c r="AB76">
-        <v>0</v>
-      </c>
-      <c r="AC76">
-        <v>0</v>
-      </c>
-      <c r="AD76">
-        <v>0</v>
-      </c>
-      <c r="AE76">
-        <v>0</v>
-      </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG76">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH76">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16691,7 +16691,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s">
         <v>182</v>
@@ -16915,13 +16915,13 @@
         <v>685</v>
       </c>
       <c r="P79">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17285,13 +17285,13 @@
         <v>685</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>4.06</v>
+        <v>2.41</v>
       </c>
       <c r="Q82">
-        <v>3.98</v>
+        <v>3.86</v>
       </c>
       <c r="R82">
-        <v>1.93</v>
+        <v>2.92</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17655,13 +17655,13 @@
         <v>685</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D85" t="s">
         <v>183</v>
@@ -18025,13 +18025,13 @@
         <v>685</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18255,10 +18255,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18625,10 +18625,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18765,13 +18765,13 @@
         <v>685</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -18950,13 +18950,13 @@
         <v>685</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18995,10 +18995,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19096,7 +19096,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D91" t="s">
         <v>183</v>
@@ -19281,7 +19281,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D92" t="s">
         <v>183</v>
@@ -19320,13 +19320,13 @@
         <v>685</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19505,13 +19505,13 @@
         <v>685</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19690,13 +19690,13 @@
         <v>685</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19735,10 +19735,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -20060,13 +20060,13 @@
         <v>685</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D97" t="s">
         <v>183</v>
@@ -20391,10 +20391,10 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
         <v>281</v>
@@ -20576,7 +20576,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D99" t="s">
         <v>182</v>
@@ -20946,7 +20946,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D101" t="s">
         <v>182</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D102" t="s">
         <v>183</v>
@@ -21501,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D104" t="s">
         <v>183</v>
@@ -21540,13 +21540,13 @@
         <v>685</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21686,10 +21686,10 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="D105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E105" t="s">
         <v>288</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -21910,13 +21910,13 @@
         <v>685</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22095,13 +22095,13 @@
         <v>685</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22140,10 +22140,10 @@
         <v>0</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG107">
         <v>0</v>
@@ -22241,7 +22241,7 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D108" t="s">
         <v>183</v>
@@ -22280,13 +22280,13 @@
         <v>685</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22426,7 +22426,7 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D109" t="s">
         <v>183</v>
@@ -22611,7 +22611,7 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D110" t="s">
         <v>183</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23760,13 +23760,13 @@
         <v>685</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23945,13 +23945,13 @@
         <v>685</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24870,13 +24870,13 @@
         <v>685</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25016,7 +25016,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
         <v>183</v>
@@ -25055,13 +25055,13 @@
         <v>685</v>
       </c>
       <c r="P123">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25240,13 +25240,13 @@
         <v>685</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25386,7 +25386,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D125" t="s">
         <v>183</v>
@@ -25571,7 +25571,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D126" t="s">
         <v>183</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25795,13 +25795,13 @@
         <v>685</v>
       </c>
       <c r="P127">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S127">
         <v>0</v>
@@ -25941,10 +25941,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E128" t="s">
         <v>311</v>
@@ -26126,7 +26126,7 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D129" t="s">
         <v>183</v>
@@ -26165,13 +26165,13 @@
         <v>685</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26350,13 +26350,13 @@
         <v>685</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26496,10 +26496,10 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D131" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E131" t="s">
         <v>314</v>
@@ -26535,13 +26535,13 @@
         <v>685</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26720,13 +26720,13 @@
         <v>685</v>
       </c>
       <c r="P132">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27051,10 +27051,10 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D134" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E134" t="s">
         <v>317</v>
@@ -27239,7 +27239,7 @@
         <v>164</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27421,7 +27421,7 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
         <v>183</v>
@@ -27606,10 +27606,10 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D137" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E137" t="s">
         <v>320</v>
@@ -27791,7 +27791,7 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
         <v>183</v>
@@ -27976,7 +27976,7 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
         <v>183</v>
@@ -28161,7 +28161,7 @@
         <v>91</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D140" t="s">
         <v>183</v>
@@ -28346,7 +28346,7 @@
         <v>91</v>
       </c>
       <c r="C141" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="D141" t="s">
         <v>183</v>
@@ -28531,7 +28531,7 @@
         <v>91</v>
       </c>
       <c r="C142" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="D142" t="s">
         <v>183</v>
@@ -28716,7 +28716,7 @@
         <v>91</v>
       </c>
       <c r="C143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D143" t="s">
         <v>183</v>
@@ -28901,7 +28901,7 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D144" t="s">
         <v>183</v>
@@ -29089,7 +29089,7 @@
         <v>165</v>
       </c>
       <c r="D145" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E145" t="s">
         <v>328</v>
@@ -29641,7 +29641,7 @@
         <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D148" t="s">
         <v>183</v>
@@ -29826,7 +29826,7 @@
         <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D149" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30566,7 +30566,7 @@
         <v>93</v>
       </c>
       <c r="C153" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D153" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -31861,7 +31861,7 @@
         <v>93</v>
       </c>
       <c r="C160" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D160" t="s">
         <v>183</v>
@@ -32046,7 +32046,7 @@
         <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -32416,10 +32416,10 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D163" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E163" t="s">
         <v>346</v>
@@ -32455,13 +32455,13 @@
         <v>685</v>
       </c>
       <c r="P163">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q163">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R163">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -33896,7 +33896,7 @@
         <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D171" t="s">
         <v>183</v>
@@ -34081,10 +34081,10 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D172" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E172" t="s">
         <v>355</v>
@@ -34451,7 +34451,7 @@
         <v>94</v>
       </c>
       <c r="C174" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D174" t="s">
         <v>183</v>
@@ -34490,13 +34490,13 @@
         <v>685</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34821,7 +34821,7 @@
         <v>95</v>
       </c>
       <c r="C176" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D176" t="s">
         <v>183</v>
@@ -35006,7 +35006,7 @@
         <v>95</v>
       </c>
       <c r="C177" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D177" t="s">
         <v>183</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35376,10 +35376,10 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E179" t="s">
         <v>362</v>
@@ -35600,13 +35600,13 @@
         <v>685</v>
       </c>
       <c r="P180">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q180">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R180">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35645,10 +35645,10 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF180">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -35746,7 +35746,7 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D181" t="s">
         <v>183</v>
@@ -35931,7 +35931,7 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D182" t="s">
         <v>182</v>
@@ -36116,10 +36116,10 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D183" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E183" t="s">
         <v>366</v>
@@ -36340,13 +36340,13 @@
         <v>685</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36385,10 +36385,10 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36856,10 +36856,10 @@
         <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="D187" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E187" t="s">
         <v>370</v>
@@ -37080,13 +37080,13 @@
         <v>685</v>
       </c>
       <c r="P188">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q188">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R188">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37226,10 +37226,10 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="D189" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E189" t="s">
         <v>372</v>
@@ -37411,10 +37411,10 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="D190" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E190" t="s">
         <v>373</v>
@@ -37450,13 +37450,13 @@
         <v>685</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37599,7 +37599,7 @@
         <v>174</v>
       </c>
       <c r="D191" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E191" t="s">
         <v>374</v>
@@ -37781,10 +37781,10 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D192" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -37966,7 +37966,7 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D193" t="s">
         <v>183</v>
@@ -38154,7 +38154,7 @@
         <v>175</v>
       </c>
       <c r="D194" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E194" t="s">
         <v>377</v>
@@ -38336,7 +38336,7 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D195" t="s">
         <v>183</v>
@@ -38375,13 +38375,13 @@
         <v>685</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38420,10 +38420,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -38891,7 +38891,7 @@
         <v>100</v>
       </c>
       <c r="C198" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D198" t="s">
         <v>182</v>
@@ -39076,7 +39076,7 @@
         <v>101</v>
       </c>
       <c r="C199" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D199" t="s">
         <v>182</v>
@@ -39115,13 +39115,13 @@
         <v>685</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S199">
         <v>0</v>
@@ -39160,10 +39160,10 @@
         <v>0</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG199">
         <v>0</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q200">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39816,7 +39816,7 @@
         <v>102</v>
       </c>
       <c r="C203" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D203" t="s">
         <v>182</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41296,7 +41296,7 @@
         <v>107</v>
       </c>
       <c r="C211" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D211" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,10 +42406,10 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D217" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E217" t="s">
         <v>400</v>
@@ -42776,7 +42776,7 @@
         <v>108</v>
       </c>
       <c r="C219" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D219" t="s">
         <v>183</v>
@@ -42961,7 +42961,7 @@
         <v>108</v>
       </c>
       <c r="C220" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D220" t="s">
         <v>183</v>
@@ -43146,7 +43146,7 @@
         <v>108</v>
       </c>
       <c r="C221" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D221" t="s">
         <v>183</v>
@@ -43516,7 +43516,7 @@
         <v>108</v>
       </c>
       <c r="C223" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
         <v>183</v>
@@ -43701,10 +43701,10 @@
         <v>108</v>
       </c>
       <c r="C224" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D224" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E224" t="s">
         <v>407</v>
@@ -43740,13 +43740,13 @@
         <v>685</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43886,10 +43886,10 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D225" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E225" t="s">
         <v>408</v>
@@ -44071,10 +44071,10 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D226" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E226" t="s">
         <v>409</v>
@@ -44256,7 +44256,7 @@
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D227" t="s">
         <v>183</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D228" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44811,7 +44811,7 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D230" t="s">
         <v>183</v>
@@ -44996,10 +44996,10 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D231" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E231" t="s">
         <v>414</v>
@@ -45181,10 +45181,10 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D232" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E232" t="s">
         <v>415</v>
@@ -45366,7 +45366,7 @@
         <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D233" t="s">
         <v>183</v>
@@ -45736,7 +45736,7 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D235" t="s">
         <v>182</v>
@@ -46106,10 +46106,10 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D237" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E237" t="s">
         <v>420</v>
@@ -46145,13 +46145,13 @@
         <v>685</v>
       </c>
       <c r="P237">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q237">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R237">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S237">
         <v>0</v>
@@ -46291,7 +46291,7 @@
         <v>108</v>
       </c>
       <c r="C238" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D238" t="s">
         <v>183</v>
@@ -46476,7 +46476,7 @@
         <v>108</v>
       </c>
       <c r="C239" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D239" t="s">
         <v>183</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47031,7 +47031,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D242" t="s">
         <v>182</v>
@@ -47401,7 +47401,7 @@
         <v>112</v>
       </c>
       <c r="C244" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>
@@ -47771,7 +47771,7 @@
         <v>113</v>
       </c>
       <c r="C246" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D246" t="s">
         <v>182</v>
@@ -48326,7 +48326,7 @@
         <v>115</v>
       </c>
       <c r="C249" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D249" t="s">
         <v>182</v>
@@ -48511,7 +48511,7 @@
         <v>115</v>
       </c>
       <c r="C250" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D250" t="s">
         <v>182</v>
@@ -48696,7 +48696,7 @@
         <v>115</v>
       </c>
       <c r="C251" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D251" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,12 +364,12 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
@@ -388,108 +388,108 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
+    <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
-    <t>China China League One</t>
+    <t>England Premier League</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -535,12 +535,12 @@
     <t>Bolivia LFPB</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -571,33 +571,33 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Jeju United</t>
+    <t>Asan Mugunghwa</t>
   </si>
   <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
     <t>SD Raiders</t>
   </si>
   <si>
     <t>Cheongju</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -625,111 +625,111 @@
     <t>Montana</t>
   </si>
   <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
     <t>Phu Dong</t>
   </si>
   <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Oddevold</t>
   </si>
   <si>
-    <t>United Nordic</t>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
   </si>
   <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
     <t>Young Lions</t>
   </si>
   <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
     <t>Nanjing City</t>
   </si>
   <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
     <t>Ceuta</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Teplice</t>
   </si>
   <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,130 +739,157 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>Qabala</t>
   </si>
   <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
     <t>Degerfors</t>
   </si>
   <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>Hoffenheim</t>
-  </si>
-  <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
   </si>
   <si>
     <t>Vaprus</t>
   </si>
   <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
     <t>Jamshedpur</t>
   </si>
   <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
+    <t>Dundee</t>
   </si>
   <si>
     <t>Fulham</t>
   </si>
   <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
     <t>Albacete Balompié</t>
   </si>
   <si>
+    <t>Burgos CF</t>
+  </si>
+  <si>
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
-    <t>GIF Sundsvall</t>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Wattens</t>
   </si>
   <si>
     <t>Ethiopia Bunna</t>
@@ -871,309 +898,282 @@
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Enosis</t>
+    <t>Sumqayıt</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Sumqayıt</t>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
   </si>
   <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
     <t>Lazio</t>
   </si>
   <si>
     <t>Winterthur</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
+    <t>Beerschot-Wilrijk</t>
+  </si>
+  <si>
     <t>Al Najma</t>
   </si>
   <si>
-    <t>Beerschot-Wilrijk</t>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Atromitos</t>
   </si>
   <si>
     <t>Atlético Madrid</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
     <t>Wolfsburg</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
+    <t>Slavia Praha</t>
   </si>
   <si>
     <t>Beşiktaş</t>
   </si>
   <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
     <t>Rouen</t>
   </si>
   <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
     <t>Orléans</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
   </si>
   <si>
     <t>Bastia</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Nancy</t>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Annecy</t>
   </si>
   <si>
     <t>Grenoble Foot 38</t>
   </si>
   <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Magesi</t>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
   </si>
   <si>
     <t>Al Feiha</t>
   </si>
   <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
+    <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
-    <t>Maribor</t>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Temperley</t>
   </si>
   <si>
     <t>Técnico Universitario</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
+    <t>Club Brugge</t>
   </si>
   <si>
     <t>Lecce</t>
   </si>
   <si>
-    <t>Club Brugge</t>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
+    <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1189,105 +1189,105 @@
     <t>Indy Eleven</t>
   </si>
   <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
-    <t>Brooklyn FC</t>
-  </si>
-  <si>
-    <t>Louisville City</t>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
   </si>
   <si>
     <t>Real Tomayapo</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
   </si>
   <si>
     <t>Houston Dash</t>
   </si>
   <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
     <t>Sporting CP II</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
+    <t>FC Penafiel</t>
   </si>
   <si>
     <t>CD Feirense</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
   </si>
   <si>
     <t>Farense</t>
   </si>
   <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1312,42 +1312,42 @@
     <t>Oakland Roots</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
+    <t>FC Seoul</t>
   </si>
   <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>FC Seoul</t>
+    <t>Seoul E-Land</t>
   </si>
   <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>NWS Spirit</t>
   </si>
   <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1375,111 +1375,111 @@
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
     <t>Hai Phong</t>
   </si>
   <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
-    <t>Öster</t>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
   </si>
   <si>
     <t>Arsenal Women</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
     <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
     <t>Geylang International</t>
   </si>
   <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
     <t>CD Castellón</t>
   </si>
   <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,130 +1489,157 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
     <t>Qarabağ</t>
   </si>
   <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
     <t>Mjällby</t>
   </si>
   <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Bayer Leverkusen</t>
   </si>
   <si>
-    <t>Werder Bremen</t>
-  </si>
-  <si>
-    <t>Borussia M'gladbach</t>
-  </si>
-  <si>
-    <t>St. Pauli</t>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
     <t>Bengaluru</t>
   </si>
   <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
+    <t>Livingston</t>
   </si>
   <si>
     <t>AFC Bournemouth</t>
   </si>
   <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
+    <t>Almería</t>
+  </si>
+  <si>
     <t>RCD Espanyol</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
     <t>Orijent 1919</t>
   </si>
   <si>
-    <t>Norrköping</t>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
   </si>
   <si>
     <t>Mekelakeya</t>
@@ -1621,309 +1648,282 @@
     <t>Ljungskile</t>
   </si>
   <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
+    <t>Araz</t>
   </si>
   <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Araz</t>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Aluminij</t>
+  </si>
+  <si>
+    <t>Pogoń Szczecin</t>
   </si>
   <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Deportivo de La Coruña W</t>
-  </si>
-  <si>
     <t>Inter Milan</t>
   </si>
   <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
     <t>Grasshopper</t>
   </si>
   <si>
+    <t>Lommel United</t>
+  </si>
+  <si>
     <t>Al Hazm</t>
   </si>
   <si>
-    <t>Lommel United</t>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Panaitolikos</t>
   </si>
   <si>
     <t>Celta de Vigo</t>
   </si>
   <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
     <t>Bayern München</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
+    <t>Sparta Praha</t>
   </si>
   <si>
     <t>Trabzonspor</t>
   </si>
   <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
     <t>Versailles</t>
   </si>
   <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
     <t>Fleury 91</t>
   </si>
   <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Midland</t>
   </si>
   <si>
     <t>Le Mans</t>
   </si>
   <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Rodez</t>
   </si>
   <si>
     <t>Troyes</t>
   </si>
   <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
   </si>
   <si>
     <t>Al Quadisiya</t>
   </si>
   <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
+    <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Olimpija</t>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
   </si>
   <si>
     <t>Delfin SC</t>
   </si>
   <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
+    <t>Sint-Truiden</t>
   </si>
   <si>
     <t>Juventus</t>
   </si>
   <si>
-    <t>Sint-Truiden</t>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
   </si>
   <si>
     <t>Real Betis</t>
   </si>
   <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Hearts</t>
+    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1939,105 +1939,105 @@
     <t>Sporting JAX</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
-    <t>Pittsburgh Riverhounds</t>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
   </si>
   <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
   </si>
   <si>
     <t>Denver Summit W</t>
   </si>
   <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
+    <t>CS Marítimo</t>
   </si>
   <si>
     <t>UD Oliveirense</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Torreense</t>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
   </si>
   <si>
     <t>Paços de Ferreira</t>
   </si>
   <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2062,13 +2062,13 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>San Diego</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -3001,7 +3001,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -3186,7 +3186,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -4111,7 +4111,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
@@ -5221,7 +5221,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
         <v>182</v>
@@ -5964,7 +5964,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
         <v>203</v>
@@ -6149,7 +6149,7 @@
         <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E21" t="s">
         <v>204</v>
@@ -6331,7 +6331,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>182</v>
@@ -6516,7 +6516,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>183</v>
@@ -6701,10 +6701,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
         <v>207</v>
@@ -6740,13 +6740,13 @@
         <v>685</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -6785,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24">
         <v>0</v>
@@ -6886,7 +6886,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
         <v>182</v>
@@ -7071,7 +7071,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
         <v>183</v>
@@ -7110,13 +7110,13 @@
         <v>685</v>
       </c>
       <c r="P26">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
         <v>183</v>
@@ -7295,13 +7295,13 @@
         <v>685</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7441,10 +7441,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
         <v>211</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7665,13 +7665,13 @@
         <v>685</v>
       </c>
       <c r="P29">
-        <v>2.55</v>
+        <v>2.86</v>
       </c>
       <c r="Q29">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R29">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8369,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8554,7 +8554,7 @@
         <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -8736,7 +8736,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
@@ -8921,7 +8921,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
         <v>182</v>
@@ -9145,13 +9145,13 @@
         <v>685</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9294,7 +9294,7 @@
         <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -9330,13 +9330,13 @@
         <v>685</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9664,7 +9664,7 @@
         <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E40" t="s">
         <v>223</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10401,7 +10401,7 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -10586,7 +10586,7 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D45" t="s">
         <v>182</v>
@@ -10771,7 +10771,7 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -10956,7 +10956,7 @@
         <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
         <v>183</v>
@@ -11141,7 +11141,7 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
         <v>183</v>
@@ -11326,10 +11326,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
         <v>232</v>
@@ -11511,7 +11511,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
         <v>183</v>
@@ -11550,13 +11550,13 @@
         <v>685</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11696,7 +11696,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -11881,7 +11881,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>183</v>
@@ -12066,10 +12066,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
         <v>236</v>
@@ -12251,10 +12251,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E54" t="s">
         <v>237</v>
@@ -12991,10 +12991,10 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
         <v>241</v>
@@ -13176,10 +13176,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E59" t="s">
         <v>242</v>
@@ -13215,13 +13215,13 @@
         <v>685</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -13400,13 +13400,13 @@
         <v>685</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13546,10 +13546,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E61" t="s">
         <v>244</v>
@@ -13585,13 +13585,13 @@
         <v>685</v>
       </c>
       <c r="P61">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13731,7 +13731,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D62" t="s">
         <v>183</v>
@@ -13916,7 +13916,7 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="D63" t="s">
         <v>182</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14325,13 +14325,13 @@
         <v>685</v>
       </c>
       <c r="P65">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14471,10 +14471,10 @@
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
@@ -14656,7 +14656,7 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
         <v>182</v>
@@ -14844,7 +14844,7 @@
         <v>149</v>
       </c>
       <c r="D68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
         <v>251</v>
@@ -15026,10 +15026,10 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E69" t="s">
         <v>252</v>
@@ -15211,10 +15211,10 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
         <v>253</v>
@@ -15581,7 +15581,7 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D72" t="s">
         <v>182</v>
@@ -15990,13 +15990,13 @@
         <v>685</v>
       </c>
       <c r="P74">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q74">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R74">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16041,10 +16041,10 @@
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH74">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16175,61 +16175,61 @@
         <v>685</v>
       </c>
       <c r="P75">
+        <v>2.38</v>
+      </c>
+      <c r="Q75">
+        <v>3.71</v>
+      </c>
+      <c r="R75">
+        <v>3.07</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
         <v>1.61</v>
       </c>
-      <c r="Q75">
-        <v>4.88</v>
-      </c>
-      <c r="R75">
-        <v>5.33</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>0</v>
-      </c>
-      <c r="AB75">
-        <v>0</v>
-      </c>
-      <c r="AC75">
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <v>0</v>
-      </c>
-      <c r="AE75">
-        <v>0</v>
-      </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG75">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="Q76">
-        <v>3.71</v>
+        <v>5.18</v>
       </c>
       <c r="R76">
-        <v>3.07</v>
+        <v>7.21</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16405,16 +16405,16 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>685</v>
       </c>
       <c r="P77">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q77">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R77">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16596,10 +16596,10 @@
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH77">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16691,10 +16691,10 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
         <v>261</v>
@@ -16730,13 +16730,13 @@
         <v>685</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -16915,13 +16915,13 @@
         <v>685</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17285,13 +17285,13 @@
         <v>685</v>
       </c>
       <c r="P81">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17434,7 +17434,7 @@
         <v>134</v>
       </c>
       <c r="D82" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E82" t="s">
         <v>265</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17655,13 +17655,13 @@
         <v>685</v>
       </c>
       <c r="P83">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q83">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="R83">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17700,10 +17700,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
         <v>183</v>
@@ -18025,13 +18025,13 @@
         <v>685</v>
       </c>
       <c r="P85">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="Q85">
-        <v>4.13</v>
+        <v>3.62</v>
       </c>
       <c r="R85">
-        <v>4.85</v>
+        <v>3.11</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18070,10 +18070,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q86">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="R86">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18255,10 +18255,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18625,10 +18625,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -18950,13 +18950,13 @@
         <v>685</v>
       </c>
       <c r="P90">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q90">
-        <v>3.62</v>
+        <v>4.13</v>
       </c>
       <c r="R90">
-        <v>3.11</v>
+        <v>4.85</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18995,10 +18995,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19096,7 +19096,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D91" t="s">
         <v>183</v>
@@ -19281,7 +19281,7 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D92" t="s">
         <v>183</v>
@@ -19320,13 +19320,13 @@
         <v>685</v>
       </c>
       <c r="P92">
-        <v>2.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q92">
-        <v>3.61</v>
+        <v>4.15</v>
       </c>
       <c r="R92">
-        <v>2.43</v>
+        <v>5.06</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19365,10 +19365,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19505,13 +19505,13 @@
         <v>685</v>
       </c>
       <c r="P93">
-        <v>1.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q93">
-        <v>5.48</v>
+        <v>3.86</v>
       </c>
       <c r="R93">
-        <v>8.300000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -19875,13 +19875,13 @@
         <v>685</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20021,7 +20021,7 @@
         <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D96" t="s">
         <v>183</v>
@@ -20060,13 +20060,13 @@
         <v>685</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R96">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D97" t="s">
         <v>183</v>
@@ -20391,7 +20391,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
         <v>183</v>
@@ -20430,13 +20430,13 @@
         <v>685</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20576,10 +20576,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E99" t="s">
         <v>282</v>
@@ -20615,13 +20615,13 @@
         <v>685</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20761,7 +20761,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D100" t="s">
         <v>183</v>
@@ -20946,7 +20946,7 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
         <v>182</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D102" t="s">
         <v>183</v>
@@ -21316,10 +21316,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D103" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E103" t="s">
         <v>286</v>
@@ -21501,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D104" t="s">
         <v>183</v>
@@ -21540,13 +21540,13 @@
         <v>685</v>
       </c>
       <c r="P104">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21686,10 +21686,10 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D105" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E105" t="s">
         <v>288</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -21910,13 +21910,13 @@
         <v>685</v>
       </c>
       <c r="P106">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q106">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22056,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D107" t="s">
         <v>183</v>
@@ -22095,13 +22095,13 @@
         <v>685</v>
       </c>
       <c r="P107">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22140,10 +22140,10 @@
         <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG107">
         <v>0</v>
@@ -22241,7 +22241,7 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D108" t="s">
         <v>183</v>
@@ -22280,13 +22280,13 @@
         <v>685</v>
       </c>
       <c r="P108">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q108">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R108">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22426,7 +22426,7 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D109" t="s">
         <v>183</v>
@@ -22611,10 +22611,10 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="D110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E110" t="s">
         <v>293</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23575,13 +23575,13 @@
         <v>685</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -23760,13 +23760,13 @@
         <v>685</v>
       </c>
       <c r="P116">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -24870,13 +24870,13 @@
         <v>685</v>
       </c>
       <c r="P122">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="Q122">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="R122">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25016,7 +25016,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>183</v>
@@ -25055,13 +25055,13 @@
         <v>685</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25386,7 +25386,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D125" t="s">
         <v>183</v>
@@ -25571,7 +25571,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D126" t="s">
         <v>183</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25941,10 +25941,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="D128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E128" t="s">
         <v>311</v>
@@ -25980,13 +25980,13 @@
         <v>685</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26126,10 +26126,10 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E129" t="s">
         <v>312</v>
@@ -26165,13 +26165,13 @@
         <v>685</v>
       </c>
       <c r="P129">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26496,7 +26496,7 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D131" t="s">
         <v>183</v>
@@ -26535,13 +26535,13 @@
         <v>685</v>
       </c>
       <c r="P131">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26720,13 +26720,13 @@
         <v>685</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27236,10 +27236,10 @@
         <v>91</v>
       </c>
       <c r="C135" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27606,10 +27606,10 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E137" t="s">
         <v>320</v>
@@ -27791,10 +27791,10 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E138" t="s">
         <v>321</v>
@@ -28346,7 +28346,7 @@
         <v>91</v>
       </c>
       <c r="C141" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D141" t="s">
         <v>183</v>
@@ -28901,7 +28901,7 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="D144" t="s">
         <v>183</v>
@@ -29086,10 +29086,10 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D145" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E145" t="s">
         <v>328</v>
@@ -29641,7 +29641,7 @@
         <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D148" t="s">
         <v>183</v>
@@ -29826,7 +29826,7 @@
         <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D149" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30751,7 +30751,7 @@
         <v>93</v>
       </c>
       <c r="C154" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D154" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31861,7 +31861,7 @@
         <v>93</v>
       </c>
       <c r="C160" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D160" t="s">
         <v>183</v>
@@ -32231,7 +32231,7 @@
         <v>94</v>
       </c>
       <c r="C162" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="D162" t="s">
         <v>183</v>
@@ -32416,10 +32416,10 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D163" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E163" t="s">
         <v>346</v>
@@ -33156,10 +33156,10 @@
         <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D167" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E167" t="s">
         <v>350</v>
@@ -33896,7 +33896,7 @@
         <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="D171" t="s">
         <v>183</v>
@@ -34081,7 +34081,7 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D172" t="s">
         <v>183</v>
@@ -34120,13 +34120,13 @@
         <v>685</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34266,10 +34266,10 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E173" t="s">
         <v>356</v>
@@ -34451,7 +34451,7 @@
         <v>94</v>
       </c>
       <c r="C174" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D174" t="s">
         <v>183</v>
@@ -34490,13 +34490,13 @@
         <v>685</v>
       </c>
       <c r="P174">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34636,10 +34636,10 @@
         <v>94</v>
       </c>
       <c r="C175" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D175" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E175" t="s">
         <v>358</v>
@@ -34821,7 +34821,7 @@
         <v>95</v>
       </c>
       <c r="C176" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D176" t="s">
         <v>183</v>
@@ -35006,7 +35006,7 @@
         <v>95</v>
       </c>
       <c r="C177" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D177" t="s">
         <v>183</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35376,10 +35376,10 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="D179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E179" t="s">
         <v>362</v>
@@ -35746,10 +35746,10 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="D181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E181" t="s">
         <v>364</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,10 +35830,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D182" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E182" t="s">
         <v>365</v>
@@ -36116,10 +36116,10 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D183" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E183" t="s">
         <v>366</v>
@@ -36301,7 +36301,7 @@
         <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D184" t="s">
         <v>182</v>
@@ -36340,13 +36340,13 @@
         <v>685</v>
       </c>
       <c r="P184">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q184">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36385,10 +36385,10 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF184">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36856,7 +36856,7 @@
         <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D187" t="s">
         <v>183</v>
@@ -36895,13 +36895,13 @@
         <v>685</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -36940,10 +36940,10 @@
         <v>0</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG187">
         <v>0</v>
@@ -37226,7 +37226,7 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="D189" t="s">
         <v>183</v>
@@ -37411,7 +37411,7 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D190" t="s">
         <v>182</v>
@@ -37596,7 +37596,7 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D191" t="s">
         <v>183</v>
@@ -37781,10 +37781,10 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D192" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -37966,10 +37966,10 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D193" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38151,7 +38151,7 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D194" t="s">
         <v>182</v>
@@ -38336,7 +38336,7 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D195" t="s">
         <v>183</v>
@@ -38375,13 +38375,13 @@
         <v>685</v>
       </c>
       <c r="P195">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q195">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38420,10 +38420,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF195">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -39076,7 +39076,7 @@
         <v>101</v>
       </c>
       <c r="C199" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D199" t="s">
         <v>182</v>
@@ -39115,13 +39115,13 @@
         <v>685</v>
       </c>
       <c r="P199">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q199">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R199">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S199">
         <v>0</v>
@@ -39160,10 +39160,10 @@
         <v>0</v>
       </c>
       <c r="AE199">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF199">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG199">
         <v>0</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -41296,7 +41296,7 @@
         <v>107</v>
       </c>
       <c r="C211" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D211" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,10 +42406,10 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D217" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E217" t="s">
         <v>400</v>
@@ -43516,10 +43516,10 @@
         <v>108</v>
       </c>
       <c r="C223" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D223" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E223" t="s">
         <v>406</v>
@@ -43555,13 +43555,13 @@
         <v>685</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43701,7 +43701,7 @@
         <v>108</v>
       </c>
       <c r="C224" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D224" t="s">
         <v>182</v>
@@ -43740,13 +43740,13 @@
         <v>685</v>
       </c>
       <c r="P224">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q224">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R224">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43886,10 +43886,10 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D225" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E225" t="s">
         <v>408</v>
@@ -44071,10 +44071,10 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E226" t="s">
         <v>409</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D228" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44811,7 +44811,7 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D230" t="s">
         <v>183</v>
@@ -45181,10 +45181,10 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D232" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E232" t="s">
         <v>415</v>
@@ -45736,10 +45736,10 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D235" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E235" t="s">
         <v>418</v>
@@ -46106,7 +46106,7 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D237" t="s">
         <v>183</v>
@@ -46476,10 +46476,10 @@
         <v>108</v>
       </c>
       <c r="C239" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D239" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E239" t="s">
         <v>422</v>
@@ -46661,7 +46661,7 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D240" t="s">
         <v>183</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,75 +364,75 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>England FA Women's Super League</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>England FA Women's Super League</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -448,60 +448,60 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -517,12 +517,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -535,15 +535,15 @@
     <t>Bolivia LFPB</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Portugal Liga NOS</t>
   </si>
   <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -571,33 +571,33 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -610,25 +610,43 @@
     <t>Real Sociedad W</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Espanyol W</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
+    <t>Kedus Giorgis</t>
   </si>
   <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>FLC Thanh Hoa</t>
+    <t>Holstein Kiel</t>
   </si>
   <si>
     <t>United Nordic</t>
@@ -637,99 +655,81 @@
     <t>Phu Dong</t>
   </si>
   <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
+    <t>Young Lions</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
     <t>Dukla Praha</t>
   </si>
   <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
     <t>Rot-Weiss Essen</t>
   </si>
   <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
     <t>Adama Kenema</t>
   </si>
   <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
     <t>Ceuta</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
     <t>1860 München</t>
   </si>
   <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,73 +739,103 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
     <t>Kristianstad</t>
   </si>
   <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
     <t>Augsburg</t>
   </si>
   <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
   </si>
   <si>
     <t>Sunderland</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
   </si>
   <si>
     <t>CD Trofense</t>
@@ -814,37 +844,10 @@
     <t>Vaprus</t>
   </si>
   <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
     <t>Larissa</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Fulham</t>
+    <t>Sevilla FC</t>
   </si>
   <si>
     <t>Albacete Balompié</t>
@@ -853,93 +856,90 @@
     <t>Burgos CF</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
     <t>Grazer AK</t>
   </si>
   <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
     <t>Oţelul Galaţi</t>
   </si>
   <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
   </si>
   <si>
     <t>Sumqayıt</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Koper</t>
-  </si>
-  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Zürich</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
@@ -949,207 +949,207 @@
     <t>Real Valladolid</t>
   </si>
   <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
     <t>Manchester City</t>
   </si>
   <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
     <t>Atlético Madrid</t>
   </si>
   <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
     <t>Galatasaray</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
   </si>
   <si>
     <t>Alanyaspor</t>
   </si>
   <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
     <t>Bourg-en-Bresse</t>
   </si>
   <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
     <t>Châteauroux</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Orléans</t>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
   </si>
   <si>
     <t>Magesi</t>
   </si>
   <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
     <t>Nancy</t>
   </si>
   <si>
-    <t>Reims</t>
-  </si>
-  <si>
     <t>Red Star</t>
   </si>
   <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
     <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Técnico Universitario</t>
+    <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>Lecce</t>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
   </si>
   <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Real Oruro</t>
+    <t>Goiás</t>
   </si>
   <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
     <t>Málaga CF</t>
   </si>
   <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
@@ -1162,18 +1162,18 @@
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1186,108 +1186,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Brooklyn FC</t>
+    <t>Hartford Athletic</t>
   </si>
   <si>
     <t>Louisville City</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
   </si>
   <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
     <t>Real Tomayapo</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Benfica</t>
   </si>
   <si>
     <t>AVS</t>
   </si>
   <si>
-    <t>Alverca</t>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
   </si>
   <si>
     <t>Santa Clara</t>
   </si>
   <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
     <t>CD Feirense</t>
   </si>
   <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1297,12 +1297,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>New Mexico United</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1312,42 +1312,42 @@
     <t>Oakland Roots</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1360,25 +1360,43 @@
     <t>Granada W</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Badalona W</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
+    <t>Mekelle Kenema</t>
   </si>
   <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Ha Noi</t>
+    <t>Magdeburg</t>
   </si>
   <si>
     <t>Öster</t>
@@ -1387,99 +1405,81 @@
     <t>Hai Phong</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
     <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
+    <t>Geylang International</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
     <t>Slovácko</t>
   </si>
   <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
     <t>Verl</t>
   </si>
   <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
     <t>Shire Endaselassie</t>
   </si>
   <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
     <t>CD Castellón</t>
   </si>
   <si>
-    <t>Zlín</t>
-  </si>
-  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,73 +1489,103 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
     <t>Norrköping W</t>
   </si>
   <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t>Bayer Leverkusen</t>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
   </si>
   <si>
     <t>Manchester United</t>
   </si>
   <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Alhama</t>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
   </si>
   <si>
     <t>Vitória Guimarães II</t>
@@ -1564,37 +1594,10 @@
     <t>Trans</t>
   </si>
   <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
     <t>Asteras Tripolis</t>
   </si>
   <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
+    <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Cultural y Deportiva Leonesa</t>
@@ -1603,93 +1606,90 @@
     <t>Almería</t>
   </si>
   <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
     <t>SSC Farul</t>
   </si>
   <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
+    <t>Aluminij</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
   </si>
   <si>
     <t>Araz</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
     <t>Lommel United</t>
   </si>
   <si>
@@ -1699,207 +1699,207 @@
     <t>Real Zaragoza</t>
   </si>
   <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
     <t>Brentford</t>
   </si>
   <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
     <t>Celta de Vigo</t>
   </si>
   <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
     <t>Antalyaspor</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
   </si>
   <si>
     <t>Kayserispor</t>
   </si>
   <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
     <t>Valenciennes</t>
   </si>
   <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
     <t>Sochaux</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Midland</t>
   </si>
   <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
     <t>Dunkerque</t>
   </si>
   <si>
-    <t>Pau</t>
-  </si>
-  <si>
     <t>Montpellier</t>
   </si>
   <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
-    <t>Delfin SC</t>
+    <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
-    <t>Juventus</t>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Internacional</t>
   </si>
   <si>
     <t>Hearts</t>
   </si>
   <si>
-    <t>Universitario de Vinto</t>
+    <t>Vila Nova</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Sporting Gijón</t>
   </si>
   <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
     <t>Real Betis</t>
   </si>
   <si>
@@ -1912,18 +1912,18 @@
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1936,108 +1936,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Sporting JAX</t>
   </si>
   <si>
-    <t>Loudoun United</t>
+    <t>Detroit City FC</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
   </si>
   <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
   </si>
   <si>
     <t>Porto</t>
   </si>
   <si>
-    <t>GD Estoril Praia</t>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
   </si>
   <si>
     <t>CD Nacional</t>
   </si>
   <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
     <t>UD Oliveirense</t>
   </si>
   <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2047,12 +2047,12 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
@@ -2062,10 +2062,10 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>San Diego</t>
@@ -3001,7 +3001,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>182</v>
@@ -3371,7 +3371,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
@@ -3741,7 +3741,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>182</v>
@@ -4111,7 +4111,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
@@ -4666,7 +4666,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5036,10 +5036,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
         <v>198</v>
@@ -5221,10 +5221,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
         <v>199</v>
@@ -5409,7 +5409,7 @@
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
         <v>200</v>
@@ -5594,7 +5594,7 @@
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
         <v>201</v>
@@ -5964,7 +5964,7 @@
         <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E20" t="s">
         <v>203</v>
@@ -6000,13 +6000,13 @@
         <v>685</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -6149,7 +6149,7 @@
         <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
         <v>204</v>
@@ -6334,7 +6334,7 @@
         <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E22" t="s">
         <v>205</v>
@@ -6370,13 +6370,13 @@
         <v>685</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6415,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>183</v>
@@ -6701,7 +6701,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
         <v>182</v>
@@ -6886,10 +6886,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
         <v>208</v>
@@ -7071,10 +7071,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E26" t="s">
         <v>209</v>
@@ -7110,13 +7110,13 @@
         <v>685</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -7256,7 +7256,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
         <v>183</v>
@@ -7441,10 +7441,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
         <v>211</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7665,13 +7665,13 @@
         <v>685</v>
       </c>
       <c r="P29">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8220,13 +8220,13 @@
         <v>685</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8551,7 +8551,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
@@ -8739,7 +8739,7 @@
         <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
         <v>218</v>
@@ -8921,7 +8921,7 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
         <v>182</v>
@@ -9106,10 +9106,10 @@
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E37" t="s">
         <v>220</v>
@@ -9145,13 +9145,13 @@
         <v>685</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9291,7 +9291,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
         <v>182</v>
@@ -9849,7 +9849,7 @@
         <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,7 +10216,7 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -10401,7 +10401,7 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -10586,10 +10586,10 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
         <v>228</v>
@@ -10771,7 +10771,7 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -10956,7 +10956,7 @@
         <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D47" t="s">
         <v>183</v>
@@ -11141,7 +11141,7 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
         <v>183</v>
@@ -11326,10 +11326,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
         <v>232</v>
@@ -11511,10 +11511,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E50" t="s">
         <v>233</v>
@@ -11550,13 +11550,13 @@
         <v>685</v>
       </c>
       <c r="P50">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -11696,7 +11696,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -11881,10 +11881,10 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s">
         <v>235</v>
@@ -12066,7 +12066,7 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
         <v>183</v>
@@ -12105,13 +12105,13 @@
         <v>685</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12251,10 +12251,10 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s">
         <v>237</v>
@@ -12991,7 +12991,7 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D58" t="s">
         <v>182</v>
@@ -13176,10 +13176,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E59" t="s">
         <v>242</v>
@@ -13215,13 +13215,13 @@
         <v>685</v>
       </c>
       <c r="P59">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q59">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -13400,13 +13400,13 @@
         <v>685</v>
       </c>
       <c r="P60">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13546,10 +13546,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E61" t="s">
         <v>244</v>
@@ -13731,10 +13731,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E62" t="s">
         <v>245</v>
@@ -13916,7 +13916,7 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
         <v>182</v>
@@ -14101,7 +14101,7 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D64" t="s">
         <v>183</v>
@@ -14286,10 +14286,10 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E65" t="s">
         <v>248</v>
@@ -14471,10 +14471,10 @@
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
@@ -14656,10 +14656,10 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
         <v>250</v>
@@ -14841,7 +14841,7 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
         <v>183</v>
@@ -14880,13 +14880,13 @@
         <v>685</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15211,10 +15211,10 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E70" t="s">
         <v>253</v>
@@ -15250,13 +15250,13 @@
         <v>685</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15399,7 +15399,7 @@
         <v>122</v>
       </c>
       <c r="D71" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E71" t="s">
         <v>254</v>
@@ -15581,7 +15581,7 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D72" t="s">
         <v>182</v>
@@ -15990,13 +15990,13 @@
         <v>685</v>
       </c>
       <c r="P74">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="Q74">
-        <v>4.88</v>
+        <v>5.18</v>
       </c>
       <c r="R74">
-        <v>5.33</v>
+        <v>7.21</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16041,10 +16041,10 @@
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH74">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16175,13 +16175,13 @@
         <v>685</v>
       </c>
       <c r="P75">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="Q75">
-        <v>3.71</v>
+        <v>4.88</v>
       </c>
       <c r="R75">
-        <v>3.07</v>
+        <v>5.33</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -16220,16 +16220,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q76">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R76">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16411,10 +16411,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH76">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>685</v>
       </c>
       <c r="P77">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q77">
-        <v>4.16</v>
+        <v>3.71</v>
       </c>
       <c r="R77">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16590,16 +16590,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH77">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16691,7 +16691,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D78" t="s">
         <v>183</v>
@@ -16730,13 +16730,13 @@
         <v>685</v>
       </c>
       <c r="P78">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17285,13 +17285,13 @@
         <v>685</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17431,10 +17431,10 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E82" t="s">
         <v>265</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q84">
-        <v>5.48</v>
+        <v>4.15</v>
       </c>
       <c r="R84">
-        <v>8.300000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17885,10 +17885,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D85" t="s">
         <v>183</v>
@@ -18025,13 +18025,13 @@
         <v>685</v>
       </c>
       <c r="P85">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18070,10 +18070,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,10 +18210,10 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="Q86">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="R86">
         <v>3.11</v>
@@ -18255,10 +18255,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18541,7 +18541,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="D88" t="s">
         <v>183</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18765,13 +18765,13 @@
         <v>685</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q89">
-        <v>3.46</v>
+        <v>5.48</v>
       </c>
       <c r="R89">
-        <v>2.42</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -18950,13 +18950,13 @@
         <v>685</v>
       </c>
       <c r="P90">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>4.13</v>
+        <v>3.46</v>
       </c>
       <c r="R90">
-        <v>4.85</v>
+        <v>2.42</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18995,10 +18995,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19096,7 +19096,7 @@
         <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D91" t="s">
         <v>183</v>
@@ -19281,10 +19281,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="D92" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E92" t="s">
         <v>275</v>
@@ -19320,13 +19320,13 @@
         <v>685</v>
       </c>
       <c r="P92">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19365,10 +19365,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19505,13 +19505,13 @@
         <v>685</v>
       </c>
       <c r="P93">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="Q93">
-        <v>3.86</v>
+        <v>3.01</v>
       </c>
       <c r="R93">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19690,13 +19690,13 @@
         <v>685</v>
       </c>
       <c r="P94">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19735,10 +19735,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19875,13 +19875,13 @@
         <v>685</v>
       </c>
       <c r="P95">
-        <v>2.47</v>
+        <v>2.04</v>
       </c>
       <c r="Q95">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R95">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19920,10 +19920,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -20021,7 +20021,7 @@
         <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D96" t="s">
         <v>183</v>
@@ -20060,13 +20060,13 @@
         <v>685</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D97" t="s">
         <v>183</v>
@@ -20391,7 +20391,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
         <v>183</v>
@@ -20430,13 +20430,13 @@
         <v>685</v>
       </c>
       <c r="P98">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20576,7 +20576,7 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
         <v>183</v>
@@ -20615,13 +20615,13 @@
         <v>685</v>
       </c>
       <c r="P99">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20761,10 +20761,10 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E100" t="s">
         <v>283</v>
@@ -20946,10 +20946,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D101" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E101" t="s">
         <v>284</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D102" t="s">
         <v>183</v>
@@ -21170,13 +21170,13 @@
         <v>685</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21215,10 +21215,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21316,10 +21316,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E103" t="s">
         <v>286</v>
@@ -21355,13 +21355,13 @@
         <v>685</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21501,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
         <v>183</v>
@@ -21540,13 +21540,13 @@
         <v>685</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -21910,13 +21910,13 @@
         <v>685</v>
       </c>
       <c r="P106">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22056,10 +22056,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D107" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E107" t="s">
         <v>290</v>
@@ -22241,7 +22241,7 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D108" t="s">
         <v>183</v>
@@ -22280,13 +22280,13 @@
         <v>685</v>
       </c>
       <c r="P108">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22429,7 +22429,7 @@
         <v>122</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E109" t="s">
         <v>292</v>
@@ -22611,10 +22611,10 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="D110" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
         <v>293</v>
@@ -22650,13 +22650,13 @@
         <v>685</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23575,13 +23575,13 @@
         <v>685</v>
       </c>
       <c r="P115">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q115">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R115">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -23760,13 +23760,13 @@
         <v>685</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24315,13 +24315,13 @@
         <v>685</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -24870,13 +24870,13 @@
         <v>685</v>
       </c>
       <c r="P122">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25016,7 +25016,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
         <v>183</v>
@@ -25055,13 +25055,13 @@
         <v>685</v>
       </c>
       <c r="P123">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25201,7 +25201,7 @@
         <v>87</v>
       </c>
       <c r="C124" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D124" t="s">
         <v>183</v>
@@ -25240,13 +25240,13 @@
         <v>685</v>
       </c>
       <c r="P124">
-        <v>2.24</v>
+        <v>4.55</v>
       </c>
       <c r="Q124">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="R124">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25941,7 +25941,7 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D128" t="s">
         <v>183</v>
@@ -25980,13 +25980,13 @@
         <v>685</v>
       </c>
       <c r="P128">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="Q128">
-        <v>6.19</v>
+        <v>3.33</v>
       </c>
       <c r="R128">
-        <v>8.6</v>
+        <v>3.96</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26126,10 +26126,10 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129" t="s">
         <v>312</v>
@@ -26165,13 +26165,13 @@
         <v>685</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26350,13 +26350,13 @@
         <v>685</v>
       </c>
       <c r="P130">
-        <v>1.93</v>
+        <v>5.74</v>
       </c>
       <c r="Q130">
-        <v>3.33</v>
+        <v>5.53</v>
       </c>
       <c r="R130">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26496,10 +26496,10 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
         <v>314</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26720,13 +26720,13 @@
         <v>685</v>
       </c>
       <c r="P132">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27051,7 +27051,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="D134" t="s">
         <v>183</v>
@@ -27236,10 +27236,10 @@
         <v>91</v>
       </c>
       <c r="C135" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27421,10 +27421,10 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D136" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E136" t="s">
         <v>319</v>
@@ -27606,10 +27606,10 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E137" t="s">
         <v>320</v>
@@ -27791,10 +27791,10 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E138" t="s">
         <v>321</v>
@@ -28901,7 +28901,7 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="D144" t="s">
         <v>183</v>
@@ -29456,7 +29456,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D147" t="s">
         <v>183</v>
@@ -30011,7 +30011,7 @@
         <v>93</v>
       </c>
       <c r="C150" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D150" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30566,7 +30566,7 @@
         <v>93</v>
       </c>
       <c r="C153" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D153" t="s">
         <v>183</v>
@@ -30751,7 +30751,7 @@
         <v>93</v>
       </c>
       <c r="C154" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D154" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -31861,7 +31861,7 @@
         <v>93</v>
       </c>
       <c r="C160" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D160" t="s">
         <v>183</v>
@@ -32046,7 +32046,7 @@
         <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -32231,7 +32231,7 @@
         <v>94</v>
       </c>
       <c r="C162" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D162" t="s">
         <v>183</v>
@@ -33156,10 +33156,10 @@
         <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D167" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E167" t="s">
         <v>350</v>
@@ -33341,10 +33341,10 @@
         <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D168" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E168" t="s">
         <v>351</v>
@@ -33526,10 +33526,10 @@
         <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D169" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E169" t="s">
         <v>352</v>
@@ -33711,7 +33711,7 @@
         <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="D170" t="s">
         <v>183</v>
@@ -34081,7 +34081,7 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D172" t="s">
         <v>183</v>
@@ -34120,13 +34120,13 @@
         <v>685</v>
       </c>
       <c r="P172">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q172">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R172">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34266,10 +34266,10 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D173" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E173" t="s">
         <v>356</v>
@@ -34305,13 +34305,13 @@
         <v>685</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34636,7 +34636,7 @@
         <v>94</v>
       </c>
       <c r="C175" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D175" t="s">
         <v>183</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35376,7 +35376,7 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D179" t="s">
         <v>183</v>
@@ -35561,7 +35561,7 @@
         <v>96</v>
       </c>
       <c r="C180" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D180" t="s">
         <v>182</v>
@@ -35746,10 +35746,10 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D181" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E181" t="s">
         <v>364</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q181">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R181">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,10 +35830,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF181">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D182" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E182" t="s">
         <v>365</v>
@@ -35970,13 +35970,13 @@
         <v>685</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36015,10 +36015,10 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG182">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D183" t="s">
         <v>182</v>
@@ -36301,7 +36301,7 @@
         <v>96</v>
       </c>
       <c r="C184" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D184" t="s">
         <v>182</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q186">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R186">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36856,7 +36856,7 @@
         <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D187" t="s">
         <v>183</v>
@@ -36895,13 +36895,13 @@
         <v>685</v>
       </c>
       <c r="P187">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q187">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R187">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -36940,10 +36940,10 @@
         <v>0</v>
       </c>
       <c r="AE187">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF187">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG187">
         <v>0</v>
@@ -37226,10 +37226,10 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D189" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E189" t="s">
         <v>372</v>
@@ -37411,7 +37411,7 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D190" t="s">
         <v>182</v>
@@ -37596,7 +37596,7 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D191" t="s">
         <v>183</v>
@@ -37635,13 +37635,13 @@
         <v>685</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37680,10 +37680,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37781,10 +37781,10 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D192" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -37969,7 +37969,7 @@
         <v>175</v>
       </c>
       <c r="D193" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38151,10 +38151,10 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="D194" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E194" t="s">
         <v>377</v>
@@ -39076,7 +39076,7 @@
         <v>101</v>
       </c>
       <c r="C199" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D199" t="s">
         <v>182</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q200">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39345,10 +39345,10 @@
         <v>0</v>
       </c>
       <c r="AE200">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG200">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39670,13 +39670,13 @@
         <v>685</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39715,10 +39715,10 @@
         <v>0</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG202">
         <v>0</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41296,7 +41296,7 @@
         <v>107</v>
       </c>
       <c r="C211" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D211" t="s">
         <v>182</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42591,7 +42591,7 @@
         <v>108</v>
       </c>
       <c r="C218" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D218" t="s">
         <v>183</v>
@@ -43146,7 +43146,7 @@
         <v>108</v>
       </c>
       <c r="C221" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D221" t="s">
         <v>183</v>
@@ -43331,10 +43331,10 @@
         <v>108</v>
       </c>
       <c r="C222" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D222" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E222" t="s">
         <v>405</v>
@@ -43516,10 +43516,10 @@
         <v>108</v>
       </c>
       <c r="C223" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D223" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E223" t="s">
         <v>406</v>
@@ -43555,13 +43555,13 @@
         <v>685</v>
       </c>
       <c r="P223">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q223">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R223">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43701,7 +43701,7 @@
         <v>108</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D224" t="s">
         <v>182</v>
@@ -43886,10 +43886,10 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D225" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E225" t="s">
         <v>408</v>
@@ -44071,10 +44071,10 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D226" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E226" t="s">
         <v>409</v>
@@ -44110,13 +44110,13 @@
         <v>685</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44256,7 +44256,7 @@
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D227" t="s">
         <v>183</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D228" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44626,7 +44626,7 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D229" t="s">
         <v>183</v>
@@ -44811,10 +44811,10 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D230" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E230" t="s">
         <v>413</v>
@@ -45181,10 +45181,10 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D232" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E232" t="s">
         <v>415</v>
@@ -45366,7 +45366,7 @@
         <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D233" t="s">
         <v>183</v>
@@ -45551,7 +45551,7 @@
         <v>108</v>
       </c>
       <c r="C234" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D234" t="s">
         <v>183</v>
@@ -46291,7 +46291,7 @@
         <v>108</v>
       </c>
       <c r="C238" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D238" t="s">
         <v>183</v>
@@ -46476,10 +46476,10 @@
         <v>108</v>
       </c>
       <c r="C239" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D239" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E239" t="s">
         <v>422</v>
@@ -46661,7 +46661,7 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D240" t="s">
         <v>183</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47401,7 +47401,7 @@
         <v>112</v>
       </c>
       <c r="C244" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,12 +364,12 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
@@ -388,6 +388,9 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
@@ -397,9 +400,6 @@
     <t>England FA Women's Super League</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
@@ -409,75 +409,75 @@
     <t>England Premier League</t>
   </si>
   <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
@@ -496,12 +496,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -517,12 +517,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>France National</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -532,6 +532,9 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
@@ -541,9 +544,6 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -571,12 +571,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
@@ -589,15 +589,15 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -625,36 +625,36 @@
     <t>Montana</t>
   </si>
   <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
   </si>
   <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
@@ -664,72 +664,72 @@
     <t>Liverpool</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
     <t>Young Lions</t>
   </si>
   <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
     <t>Brommapojkarna W</t>
   </si>
   <si>
-    <t>Persis Solo</t>
+    <t>Sarpsborg 08</t>
   </si>
   <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
+    <t>Teplice</t>
+  </si>
+  <si>
     <t>Dukla Praha</t>
   </si>
   <si>
     <t>Elche CF</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,82 +739,97 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
     <t>Västerås SK</t>
   </si>
   <si>
+    <t>Qabala</t>
+  </si>
+  <si>
     <t>Norrby</t>
   </si>
   <si>
-    <t>Qabala</t>
-  </si>
-  <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
     <t>Hoffenheim</t>
   </si>
   <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Augsburg</t>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
   </si>
   <si>
     <t>Eibar W</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
   </si>
   <si>
     <t>Dinamo Zagreb</t>
   </si>
   <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
+    <t>Vaprus</t>
   </si>
   <si>
     <t>Dundee</t>
@@ -823,357 +838,342 @@
     <t>Jamshedpur</t>
   </si>
   <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
     <t>Aberdeen</t>
   </si>
   <si>
     <t>Viktoria Plzeň</t>
   </si>
   <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Larissa</t>
+    <t>Albacete Balompié</t>
+  </si>
+  <si>
+    <t>Burgos CF</t>
   </si>
   <si>
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Albacete Balompié</t>
-  </si>
-  <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
     <t>Dugopolje</t>
   </si>
   <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
     <t>AEL</t>
   </si>
   <si>
-    <t>Omonia Aradippou</t>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
   </si>
   <si>
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Sumqayıt</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Lazio</t>
-  </si>
-  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
     <t>Al Najma</t>
   </si>
   <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
     <t>Real Valladolid</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Rouen</t>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
   </si>
   <si>
     <t>Caen</t>
   </si>
   <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
+    <t>Le Puy F.43 Auvergne</t>
   </si>
   <si>
     <t>Paris 13 Atletico</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
-    <t>Châteauroux</t>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Al Feiha</t>
   </si>
   <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
     <t>Annecy</t>
   </si>
   <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
     <t>Saint-Étienne</t>
   </si>
   <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Red Star</t>
+    <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Górnik Zabrze</t>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
   </si>
   <si>
     <t>San Miguel</t>
   </si>
   <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
     <t>Nürnberg</t>
   </si>
   <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
     <t>Luzern</t>
   </si>
   <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
     <t>Temperley</t>
   </si>
   <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
     <t>Lecce</t>
   </si>
   <si>
-    <t>Club Brugge</t>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Goiás</t>
   </si>
   <si>
     <t>CD Mafra</t>
   </si>
   <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>St. Louis City II</t>
+    <t>Fluminense</t>
   </si>
   <si>
     <t>Guayaquil City FC</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1186,108 +1186,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
     <t>Louisville City</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Real Tomayapo</t>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
   </si>
   <si>
     <t>FC Vizela</t>
   </si>
   <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
-    <t>FC Penafiel</t>
+    <t>Estrela Amadora</t>
   </si>
   <si>
     <t>GD Chaves</t>
   </si>
   <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
   </si>
   <si>
     <t>Grafičar</t>
   </si>
   <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
     <t>CSD Independiente del Valle</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
     <t>Benfica II</t>
   </si>
   <si>
-    <t>Farense</t>
-  </si>
-  <si>
     <t>Houston Dash</t>
   </si>
   <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1306,27 +1306,27 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
     <t>Phoenix Rising</t>
   </si>
   <si>
-    <t>Oakland Roots</t>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
   </si>
   <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
-    <t>Seattle Sounders</t>
+    <t>FC Seoul</t>
   </si>
   <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
@@ -1339,15 +1339,15 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1375,36 +1375,36 @@
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
   </si>
   <si>
     <t>Arsenal Women</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
     <t>Sesvete</t>
   </si>
   <si>
@@ -1414,72 +1414,72 @@
     <t>Chelsea</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
     <t>Geylang International</t>
   </si>
   <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
     <t>Eskilstuna United</t>
   </si>
   <si>
-    <t>Persebaya Surabaya</t>
+    <t>Fredrikstad</t>
   </si>
   <si>
     <t>Stuttgart II</t>
   </si>
   <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
     <t>Slovácko</t>
   </si>
   <si>
     <t>Deportivo Alavés</t>
   </si>
   <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
     <t>Zlín</t>
   </si>
   <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,82 +1489,97 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>GAIS</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
     <t>St. Pauli</t>
   </si>
   <si>
     <t>Werder Bremen</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
-    <t>Borussia M'gladbach</t>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
   </si>
   <si>
     <t>Alhama</t>
   </si>
   <si>
-    <t>Cercle Brugge</t>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
   </si>
   <si>
     <t>Hajduk Split</t>
   </si>
   <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
+    <t>Trans</t>
   </si>
   <si>
     <t>Livingston</t>
@@ -1573,357 +1588,342 @@
     <t>Bengaluru</t>
   </si>
   <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
     <t>Dundee United</t>
   </si>
   <si>
     <t>Slovan Liberec</t>
   </si>
   <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
+    <t>Cultural y Deportiva Leonesa</t>
+  </si>
+  <si>
+    <t>Almería</t>
   </si>
   <si>
     <t>RCD Espanyol</t>
   </si>
   <si>
-    <t>Cultural y Deportiva Leonesa</t>
-  </si>
-  <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
     <t>Bijelo Brdo</t>
   </si>
   <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
     <t>Olympiakos</t>
   </si>
   <si>
-    <t>Akritas</t>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
   </si>
   <si>
     <t>Ljungskile</t>
   </si>
   <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
+    <t>Pogoń Szczecin</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
   </si>
   <si>
     <t>Aluminij</t>
   </si>
   <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Araz</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Inter Milan</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Deportivo de La Coruña W</t>
-  </si>
-  <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Inter Milan</t>
-  </si>
-  <si>
     <t>Lommel United</t>
   </si>
   <si>
     <t>Al Hazm</t>
   </si>
   <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Versailles</t>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
   </si>
   <si>
     <t>Concarneau</t>
   </si>
   <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
+    <t>Dijon</t>
   </si>
   <si>
     <t>Aubagne</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>Sochaux</t>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
   </si>
   <si>
     <t>Al Quadisiya</t>
   </si>
   <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
     <t>Rodez</t>
   </si>
   <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
     <t>Amiens SC</t>
   </si>
   <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
+    <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
   </si>
   <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
     <t>Schalke 04</t>
   </si>
   <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
     <t>Servette</t>
   </si>
   <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
+    <t>Sint-Truiden</t>
+  </si>
+  <si>
     <t>Juventus</t>
   </si>
   <si>
-    <t>Sint-Truiden</t>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
   </si>
   <si>
     <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
+    <t>Vitória</t>
   </si>
   <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1936,108 +1936,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
   </si>
   <si>
     <t>Sporting JAX</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
     <t>Operário PR</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>San Antonio Bulo Bulo</t>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
   </si>
   <si>
     <t>União de Leiria</t>
   </si>
   <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
     <t>Casa Pia</t>
   </si>
   <si>
-    <t>CS Marítimo</t>
+    <t>Famalicão</t>
   </si>
   <si>
     <t>Leixões</t>
   </si>
   <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>North Texas</t>
   </si>
   <si>
     <t>Dubočica</t>
   </si>
   <si>
-    <t>North Texas</t>
-  </si>
-  <si>
     <t>Barcelona</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
     <t>Academico Viseu</t>
   </si>
   <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
     <t>Denver Summit W</t>
   </si>
   <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2056,19 +2056,19 @@
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Sporting KC</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>San Diego</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -3371,7 +3371,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -3926,7 +3926,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
@@ -4666,7 +4666,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5036,7 +5036,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
         <v>182</v>
@@ -6000,13 +6000,13 @@
         <v>685</v>
       </c>
       <c r="P20">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -6146,10 +6146,10 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E21" t="s">
         <v>204</v>
@@ -6331,7 +6331,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
         <v>183</v>
@@ -6370,13 +6370,13 @@
         <v>685</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R22">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6415,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E23" t="s">
         <v>206</v>
@@ -6701,7 +6701,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
         <v>182</v>
@@ -6886,7 +6886,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
         <v>183</v>
@@ -6925,13 +6925,13 @@
         <v>685</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6970,10 +6970,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -7074,7 +7074,7 @@
         <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E26" t="s">
         <v>209</v>
@@ -7110,13 +7110,13 @@
         <v>685</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
         <v>210</v>
@@ -7295,13 +7295,13 @@
         <v>685</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>182</v>
@@ -8369,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8551,10 +8551,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -8590,13 +8590,13 @@
         <v>685</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8635,10 +8635,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -8736,10 +8736,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E35" t="s">
         <v>218</v>
@@ -8921,10 +8921,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E36" t="s">
         <v>219</v>
@@ -9109,7 +9109,7 @@
         <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
         <v>220</v>
@@ -9291,7 +9291,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
         <v>182</v>
@@ -9661,7 +9661,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
         <v>183</v>
@@ -9846,10 +9846,10 @@
         <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10401,7 +10401,7 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -10586,7 +10586,7 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
         <v>183</v>
@@ -10625,13 +10625,13 @@
         <v>685</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -10771,10 +10771,10 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E46" t="s">
         <v>229</v>
@@ -11144,7 +11144,7 @@
         <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E48" t="s">
         <v>231</v>
@@ -11326,10 +11326,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
         <v>232</v>
@@ -11511,10 +11511,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E50" t="s">
         <v>233</v>
@@ -11696,7 +11696,7 @@
         <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
         <v>183</v>
@@ -11884,7 +11884,7 @@
         <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E52" t="s">
         <v>235</v>
@@ -12105,13 +12105,13 @@
         <v>685</v>
       </c>
       <c r="P53">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12251,7 +12251,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>183</v>
@@ -12994,7 +12994,7 @@
         <v>144</v>
       </c>
       <c r="D58" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
         <v>241</v>
@@ -13176,10 +13176,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E59" t="s">
         <v>242</v>
@@ -13361,10 +13361,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E60" t="s">
         <v>243</v>
@@ -13546,10 +13546,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E61" t="s">
         <v>244</v>
@@ -13731,7 +13731,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>182</v>
@@ -13916,10 +13916,10 @@
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E63" t="s">
         <v>246</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14286,10 +14286,10 @@
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
         <v>248</v>
@@ -14510,13 +14510,13 @@
         <v>685</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
         <v>183</v>
@@ -14695,13 +14695,13 @@
         <v>685</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14841,10 +14841,10 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E68" t="s">
         <v>251</v>
@@ -14880,13 +14880,13 @@
         <v>685</v>
       </c>
       <c r="P68">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15026,10 +15026,10 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E69" t="s">
         <v>252</v>
@@ -15250,13 +15250,13 @@
         <v>685</v>
       </c>
       <c r="P70">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15396,7 +15396,7 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>182</v>
@@ -15581,10 +15581,10 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
         <v>255</v>
@@ -15990,13 +15990,13 @@
         <v>685</v>
       </c>
       <c r="P74">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q74">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R74">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16041,10 +16041,10 @@
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH74">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16175,61 +16175,61 @@
         <v>685</v>
       </c>
       <c r="P75">
+        <v>2.38</v>
+      </c>
+      <c r="Q75">
+        <v>3.71</v>
+      </c>
+      <c r="R75">
+        <v>3.07</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
         <v>1.61</v>
       </c>
-      <c r="Q75">
-        <v>4.88</v>
-      </c>
-      <c r="R75">
-        <v>5.33</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>0</v>
-      </c>
-      <c r="AB75">
-        <v>0</v>
-      </c>
-      <c r="AC75">
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <v>0</v>
-      </c>
-      <c r="AE75">
-        <v>0</v>
-      </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG75">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="Q76">
-        <v>4.16</v>
+        <v>5.18</v>
       </c>
       <c r="R76">
-        <v>3.23</v>
+        <v>7.21</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16411,10 +16411,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH76">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,13 +16545,13 @@
         <v>685</v>
       </c>
       <c r="P77">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="Q77">
-        <v>3.71</v>
+        <v>4.88</v>
       </c>
       <c r="R77">
-        <v>3.07</v>
+        <v>5.33</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16590,16 +16590,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16691,7 +16691,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
         <v>183</v>
@@ -16730,13 +16730,13 @@
         <v>685</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -16915,13 +16915,13 @@
         <v>685</v>
       </c>
       <c r="P79">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="Q79">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="R79">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17100,13 +17100,13 @@
         <v>685</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17246,7 +17246,7 @@
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D81" t="s">
         <v>183</v>
@@ -17285,13 +17285,13 @@
         <v>685</v>
       </c>
       <c r="P81">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="Q81">
-        <v>4.13</v>
+        <v>3.46</v>
       </c>
       <c r="R81">
-        <v>4.85</v>
+        <v>2.42</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17330,10 +17330,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="Q84">
-        <v>4.15</v>
+        <v>3.01</v>
       </c>
       <c r="R84">
-        <v>5.06</v>
+        <v>3.11</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17885,10 +17885,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D85" t="s">
         <v>183</v>
@@ -18025,13 +18025,13 @@
         <v>685</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q86">
-        <v>3.62</v>
+        <v>4.13</v>
       </c>
       <c r="R86">
-        <v>3.11</v>
+        <v>4.85</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18255,10 +18255,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18541,10 +18541,10 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E88" t="s">
         <v>271</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18765,13 +18765,13 @@
         <v>685</v>
       </c>
       <c r="P89">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q89">
-        <v>5.48</v>
+        <v>4.15</v>
       </c>
       <c r="R89">
-        <v>8.300000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -18950,13 +18950,13 @@
         <v>685</v>
       </c>
       <c r="P90">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -18995,10 +18995,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19281,10 +19281,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E92" t="s">
         <v>275</v>
@@ -19320,13 +19320,13 @@
         <v>685</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19365,10 +19365,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19505,13 +19505,13 @@
         <v>685</v>
       </c>
       <c r="P93">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19690,13 +19690,13 @@
         <v>685</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19735,10 +19735,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -19875,13 +19875,13 @@
         <v>685</v>
       </c>
       <c r="P95">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q95">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R95">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19920,10 +19920,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -20060,13 +20060,13 @@
         <v>685</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R96">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20391,7 +20391,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
         <v>183</v>
@@ -20430,13 +20430,13 @@
         <v>685</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20475,10 +20475,10 @@
         <v>0</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -20761,10 +20761,10 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="D100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
         <v>283</v>
@@ -20800,13 +20800,13 @@
         <v>685</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -21131,7 +21131,7 @@
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D102" t="s">
         <v>183</v>
@@ -21170,13 +21170,13 @@
         <v>685</v>
       </c>
       <c r="P102">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21215,10 +21215,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21316,10 +21316,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D103" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E103" t="s">
         <v>286</v>
@@ -21355,13 +21355,13 @@
         <v>685</v>
       </c>
       <c r="P103">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21501,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D104" t="s">
         <v>183</v>
@@ -21540,13 +21540,13 @@
         <v>685</v>
       </c>
       <c r="P104">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21725,13 +21725,13 @@
         <v>685</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -22056,10 +22056,10 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
         <v>290</v>
@@ -22241,10 +22241,10 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="D108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E108" t="s">
         <v>291</v>
@@ -22426,10 +22426,10 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D109" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
         <v>292</v>
@@ -22465,13 +22465,13 @@
         <v>685</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22611,10 +22611,10 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E110" t="s">
         <v>293</v>
@@ -22650,13 +22650,13 @@
         <v>685</v>
       </c>
       <c r="P110">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22835,13 +22835,13 @@
         <v>685</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -23760,13 +23760,13 @@
         <v>685</v>
       </c>
       <c r="P116">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24315,13 +24315,13 @@
         <v>685</v>
       </c>
       <c r="P119">
-        <v>2.24</v>
+        <v>4.55</v>
       </c>
       <c r="Q119">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="R119">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -25016,7 +25016,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>183</v>
@@ -25055,13 +25055,13 @@
         <v>685</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25201,7 +25201,7 @@
         <v>87</v>
       </c>
       <c r="C124" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D124" t="s">
         <v>183</v>
@@ -25240,13 +25240,13 @@
         <v>685</v>
       </c>
       <c r="P124">
-        <v>4.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q124">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R124">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25941,10 +25941,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E128" t="s">
         <v>311</v>
@@ -25980,13 +25980,13 @@
         <v>685</v>
       </c>
       <c r="P128">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q128">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R128">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26126,7 +26126,7 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D129" t="s">
         <v>183</v>
@@ -26165,13 +26165,13 @@
         <v>685</v>
       </c>
       <c r="P129">
-        <v>1.36</v>
+        <v>5.74</v>
       </c>
       <c r="Q129">
-        <v>6.19</v>
+        <v>5.53</v>
       </c>
       <c r="R129">
-        <v>8.6</v>
+        <v>1.51</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26311,7 +26311,7 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D130" t="s">
         <v>183</v>
@@ -26350,13 +26350,13 @@
         <v>685</v>
       </c>
       <c r="P130">
-        <v>5.74</v>
+        <v>1.36</v>
       </c>
       <c r="Q130">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="R130">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26496,10 +26496,10 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D131" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E131" t="s">
         <v>314</v>
@@ -26535,13 +26535,13 @@
         <v>685</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27051,7 +27051,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="D134" t="s">
         <v>183</v>
@@ -27421,10 +27421,10 @@
         <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D136" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E136" t="s">
         <v>319</v>
@@ -27606,10 +27606,10 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E137" t="s">
         <v>320</v>
@@ -27791,10 +27791,10 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E138" t="s">
         <v>321</v>
@@ -27976,10 +27976,10 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D139" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E139" t="s">
         <v>322</v>
@@ -28015,13 +28015,13 @@
         <v>685</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28066,10 +28066,10 @@
         <v>0</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH139">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI139">
         <v>0</v>
@@ -29086,7 +29086,7 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D145" t="s">
         <v>183</v>
@@ -29456,7 +29456,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D147" t="s">
         <v>183</v>
@@ -29641,7 +29641,7 @@
         <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D148" t="s">
         <v>183</v>
@@ -29826,7 +29826,7 @@
         <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D149" t="s">
         <v>183</v>
@@ -30011,7 +30011,7 @@
         <v>93</v>
       </c>
       <c r="C150" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D150" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30566,7 +30566,7 @@
         <v>93</v>
       </c>
       <c r="C153" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D153" t="s">
         <v>183</v>
@@ -30751,7 +30751,7 @@
         <v>93</v>
       </c>
       <c r="C154" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D154" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31121,7 +31121,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D156" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31491,7 +31491,7 @@
         <v>93</v>
       </c>
       <c r="C158" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D158" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -32231,7 +32231,7 @@
         <v>94</v>
       </c>
       <c r="C162" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D162" t="s">
         <v>183</v>
@@ -32416,7 +32416,7 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D163" t="s">
         <v>183</v>
@@ -32455,13 +32455,13 @@
         <v>685</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32601,7 +32601,7 @@
         <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D164" t="s">
         <v>183</v>
@@ -33341,10 +33341,10 @@
         <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D168" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E168" t="s">
         <v>351</v>
@@ -33526,10 +33526,10 @@
         <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E169" t="s">
         <v>352</v>
@@ -33711,7 +33711,7 @@
         <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
         <v>183</v>
@@ -34081,10 +34081,10 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D172" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E172" t="s">
         <v>355</v>
@@ -34266,10 +34266,10 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D173" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E173" t="s">
         <v>356</v>
@@ -34305,13 +34305,13 @@
         <v>685</v>
       </c>
       <c r="P173">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34821,7 +34821,7 @@
         <v>95</v>
       </c>
       <c r="C176" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D176" t="s">
         <v>183</v>
@@ -35006,7 +35006,7 @@
         <v>95</v>
       </c>
       <c r="C177" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D177" t="s">
         <v>183</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35376,10 +35376,10 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="D179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E179" t="s">
         <v>362</v>
@@ -35561,7 +35561,7 @@
         <v>96</v>
       </c>
       <c r="C180" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D180" t="s">
         <v>182</v>
@@ -35746,10 +35746,10 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E181" t="s">
         <v>364</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,10 +35830,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="D182" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E182" t="s">
         <v>365</v>
@@ -35970,13 +35970,13 @@
         <v>685</v>
       </c>
       <c r="P182">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q182">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36015,10 +36015,10 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF182">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG182">
         <v>0</v>
@@ -36116,10 +36116,10 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D183" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E183" t="s">
         <v>366</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36856,7 +36856,7 @@
         <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D187" t="s">
         <v>183</v>
@@ -37044,7 +37044,7 @@
         <v>172</v>
       </c>
       <c r="D188" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E188" t="s">
         <v>371</v>
@@ -37411,10 +37411,10 @@
         <v>98</v>
       </c>
       <c r="C190" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D190" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E190" t="s">
         <v>373</v>
@@ -37450,13 +37450,13 @@
         <v>685</v>
       </c>
       <c r="P190">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37596,7 +37596,7 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D191" t="s">
         <v>183</v>
@@ -37781,7 +37781,7 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D192" t="s">
         <v>182</v>
@@ -37966,10 +37966,10 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D193" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38005,13 +38005,13 @@
         <v>685</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38151,10 +38151,10 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D194" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E194" t="s">
         <v>377</v>
@@ -38336,7 +38336,7 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D195" t="s">
         <v>183</v>
@@ -38930,13 +38930,13 @@
         <v>685</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S198">
         <v>0</v>
@@ -39076,7 +39076,7 @@
         <v>101</v>
       </c>
       <c r="C199" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D199" t="s">
         <v>182</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39485,13 +39485,13 @@
         <v>685</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39530,10 +39530,10 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39670,13 +39670,13 @@
         <v>685</v>
       </c>
       <c r="P202">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q202">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39715,10 +39715,10 @@
         <v>0</v>
       </c>
       <c r="AE202">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF202">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG202">
         <v>0</v>
@@ -39816,7 +39816,7 @@
         <v>102</v>
       </c>
       <c r="C203" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D203" t="s">
         <v>182</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -41335,13 +41335,13 @@
         <v>685</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41380,10 +41380,10 @@
         <v>0</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG211">
         <v>0</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42776,7 +42776,7 @@
         <v>108</v>
       </c>
       <c r="C219" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D219" t="s">
         <v>183</v>
@@ -42961,7 +42961,7 @@
         <v>108</v>
       </c>
       <c r="C220" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D220" t="s">
         <v>183</v>
@@ -43146,7 +43146,7 @@
         <v>108</v>
       </c>
       <c r="C221" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D221" t="s">
         <v>183</v>
@@ -43331,10 +43331,10 @@
         <v>108</v>
       </c>
       <c r="C222" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E222" t="s">
         <v>405</v>
@@ -43516,7 +43516,7 @@
         <v>108</v>
       </c>
       <c r="C223" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D223" t="s">
         <v>183</v>
@@ -43701,10 +43701,10 @@
         <v>108</v>
       </c>
       <c r="C224" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D224" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E224" t="s">
         <v>407</v>
@@ -43886,10 +43886,10 @@
         <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D225" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E225" t="s">
         <v>408</v>
@@ -44071,10 +44071,10 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E226" t="s">
         <v>409</v>
@@ -44110,13 +44110,13 @@
         <v>685</v>
       </c>
       <c r="P226">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q226">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R226">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44256,10 +44256,10 @@
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D227" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E227" t="s">
         <v>410</v>
@@ -44295,13 +44295,13 @@
         <v>685</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44626,7 +44626,7 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D229" t="s">
         <v>183</v>
@@ -44811,10 +44811,10 @@
         <v>108</v>
       </c>
       <c r="C230" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D230" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E230" t="s">
         <v>413</v>
@@ -44996,7 +44996,7 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D231" t="s">
         <v>183</v>
@@ -45181,7 +45181,7 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D232" t="s">
         <v>183</v>
@@ -45736,7 +45736,7 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D235" t="s">
         <v>183</v>
@@ -45921,10 +45921,10 @@
         <v>108</v>
       </c>
       <c r="C236" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D236" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E236" t="s">
         <v>419</v>
@@ -46106,7 +46106,7 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D237" t="s">
         <v>183</v>
@@ -46291,10 +46291,10 @@
         <v>108</v>
       </c>
       <c r="C238" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D238" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E238" t="s">
         <v>421</v>
@@ -46661,10 +46661,10 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D240" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E240" t="s">
         <v>423</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -364,15 +364,15 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
@@ -388,22 +388,28 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>England FA Women's Super League</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>England FA Women's Super League</t>
+    <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
-    <t>Lithuania A Lyga</t>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
   </si>
   <si>
     <t>England Premier League</t>
@@ -415,30 +421,24 @@
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -448,37 +448,40 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Italy Serie A</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
@@ -487,9 +490,6 @@
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -532,18 +532,18 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -571,15 +571,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
     <t>Hwaseong</t>
   </si>
   <si>
@@ -589,15 +589,15 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -607,15 +607,15 @@
     <t>St George City FA</t>
   </si>
   <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
@@ -625,40 +625,49 @@
     <t>Montana</t>
   </si>
   <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
     <t>Eintracht Braunschweig</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
+    <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Cibalia</t>
   </si>
   <si>
-    <t>Hegelmann Litauen</t>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Young Lions</t>
+  </si>
+  <si>
+    <t>Balestier Khalsa</t>
   </si>
   <si>
     <t>Liverpool</t>
@@ -670,66 +679,57 @@
     <t>Goa</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
     <t>Persis Solo</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
     <t>Osnabrück</t>
   </si>
   <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
     <t>1860 München</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
+    <t>Teplice</t>
   </si>
   <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
     <t>Elche CF</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -739,91 +739,103 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
     <t>Växjö</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
     <t>Orbit College</t>
   </si>
   <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
     <t>Panserraikos</t>
   </si>
   <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
     <t>Augsburg</t>
   </si>
   <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Hoffenheim</t>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
   </si>
   <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
-    <t>Fulham</t>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
   </si>
   <si>
     <t>Brighton &amp; Hove Albion</t>
   </si>
   <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
+    <t>Viktoria Plzeň</t>
   </si>
   <si>
     <t>Dinamo Zagreb</t>
@@ -832,40 +844,46 @@
     <t>Vaprus</t>
   </si>
   <si>
-    <t>Dundee</t>
-  </si>
-  <si>
     <t>Jamshedpur</t>
   </si>
   <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
+    <t>Burgos CF</t>
   </si>
   <si>
     <t>Albacete Balompié</t>
   </si>
   <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
     <t>Sevilla FC</t>
   </si>
   <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
     <t>Wattens</t>
   </si>
   <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Grazer AK</t>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Enosis</t>
   </si>
   <si>
     <t>Dubrava Zagreb</t>
@@ -874,28 +892,13 @@
     <t>Omonia Aradippou</t>
   </si>
   <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
+    <t>Tobol</t>
   </si>
   <si>
     <t>AEL</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>Jagiellonia Białystok</t>
@@ -904,46 +907,49 @@
     <t>Železničar Pančevo</t>
   </si>
   <si>
+    <t>Sumqayıt</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Zürich</t>
+    <t>Al Najma</t>
   </si>
   <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
-    <t>Al Najma</t>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
   </si>
   <si>
     <t>Atlético Madrid</t>
@@ -952,157 +958,160 @@
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Atromitos</t>
   </si>
   <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
     <t>Konyaspor</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
   </si>
   <si>
     <t>Kocaelispor</t>
   </si>
   <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
     <t>Bourg-en-Bresse</t>
   </si>
   <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Orléans</t>
   </si>
   <si>
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
-    <t>Orléans</t>
+    <t>Paris 13 Atletico</t>
   </si>
   <si>
     <t>Partizan</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Laval</t>
   </si>
   <si>
     <t>Grenoble Foot 38</t>
   </si>
   <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
+    <t>Saint-Étienne</t>
   </si>
   <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>Técnico Universitario</t>
+    <t>Luzern</t>
   </si>
   <si>
     <t>San Miguel</t>
@@ -1111,19 +1120,25 @@
     <t>Acassuso</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>Temperley</t>
+    <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>Lecce</t>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Málaga CF</t>
@@ -1132,27 +1147,12 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
+    <t>CD Mafra</t>
   </si>
   <si>
     <t>Motherwell</t>
   </si>
   <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
@@ -1162,18 +1162,18 @@
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1186,21 +1186,27 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
-    <t>Brooklyn FC</t>
-  </si>
-  <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
@@ -1210,84 +1216,78 @@
     <t>Real Tomayapo</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>CRB</t>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
   </si>
   <si>
     <t>Alverca</t>
   </si>
   <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
     <t>Sporting CP II</t>
   </si>
   <si>
-    <t>Lusitania Lourosa</t>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
   </si>
   <si>
     <t>FC Penafiel</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1297,12 +1297,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1321,15 +1321,15 @@
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>Suwon</t>
   </si>
   <si>
@@ -1339,15 +1339,15 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1357,15 +1357,15 @@
     <t>Sutherland Sharks</t>
   </si>
   <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Granada W</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
@@ -1375,40 +1375,49 @@
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
     <t>Ha Noi</t>
   </si>
   <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Sesvete</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Geylang International</t>
+  </si>
+  <si>
+    <t>Tanjong Pagar</t>
   </si>
   <si>
     <t>Chelsea</t>
@@ -1420,66 +1429,57 @@
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
     <t>Ulm</t>
   </si>
   <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
+    <t>Baník Ostrava</t>
   </si>
   <si>
     <t>Henan Jianye</t>
   </si>
   <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
     <t>Deportivo Alavés</t>
   </si>
   <si>
-    <t>Zlín</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1489,91 +1489,103 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
     <t>Chippa United</t>
   </si>
   <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
     <t>AIK Women</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
     <t>Kifisia</t>
   </si>
   <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
     <t>Bayer Leverkusen</t>
   </si>
   <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t>Werder Bremen</t>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
   </si>
   <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>AFC Bournemouth</t>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
   </si>
   <si>
     <t>Wolverhampton Wanderers</t>
   </si>
   <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
+    <t>Slovan Liberec</t>
   </si>
   <si>
     <t>Hajduk Split</t>
@@ -1582,40 +1594,46 @@
     <t>Trans</t>
   </si>
   <si>
-    <t>Livingston</t>
-  </si>
-  <si>
     <t>Bengaluru</t>
   </si>
   <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
+    <t>Almería</t>
   </si>
   <si>
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
     <t>Blau-Weiß Linz</t>
   </si>
   <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
-    <t>Rheindorf Altach</t>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
   </si>
   <si>
     <t>Orijent 1919</t>
@@ -1624,28 +1642,13 @@
     <t>Akritas</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
+    <t>Irtysh</t>
   </si>
   <si>
     <t>Olympiakos</t>
   </si>
   <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Pogoń Szczecin</t>
@@ -1654,46 +1657,49 @@
     <t>Radnik Surdulica</t>
   </si>
   <si>
+    <t>Araz</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
     <t>Aluminij</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
-    <t>Araz</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Deportivo de La Coruña W</t>
-  </si>
-  <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Grasshopper</t>
+    <t>Al Hazm</t>
   </si>
   <si>
     <t>Lommel United</t>
   </si>
   <si>
-    <t>Al Hazm</t>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Bayern München</t>
   </si>
   <si>
     <t>Celta de Vigo</t>
@@ -1702,157 +1708,160 @@
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
     <t>Brentford</t>
   </si>
   <si>
     <t>Panaitolikos</t>
   </si>
   <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
     <t>Fenerbahçe</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Trakai</t>
   </si>
   <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
     <t>Valenciennes</t>
   </si>
   <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
   </si>
   <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Fleury 91</t>
+    <t>Aubagne</t>
   </si>
   <si>
     <t>OFK Beograd</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
   </si>
   <si>
     <t>Troyes</t>
   </si>
   <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
+    <t>Amiens SC</t>
   </si>
   <si>
     <t>Midland</t>
   </si>
   <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Delfin SC</t>
+    <t>Servette</t>
   </si>
   <si>
     <t>Estudiantes Caseros</t>
@@ -1861,19 +1870,25 @@
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
+    <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
-    <t>Juventus</t>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
   </si>
   <si>
     <t>Sporting Gijón</t>
@@ -1882,27 +1897,12 @@
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
+    <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
     <t>Hearts</t>
   </si>
   <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
@@ -1912,18 +1912,18 @@
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1936,21 +1936,27 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Loudoun United</t>
-  </si>
-  <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
@@ -1960,84 +1966,78 @@
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Operário PR</t>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
   </si>
   <si>
     <t>GD Estoril Praia</t>
   </si>
   <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>Torreense</t>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
   </si>
   <si>
     <t>CS Marítimo</t>
   </si>
   <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
     <t>North Texas</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2047,10 +2047,10 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>DC United</t>
-  </si>
-  <si>
-    <t>Las Vegas Lights</t>
   </si>
   <si>
     <t>St. Louis City</t>
@@ -3186,7 +3186,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
@@ -3371,7 +3371,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
         <v>182</v>
@@ -3556,7 +3556,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -3741,7 +3741,7 @@
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
         <v>182</v>
@@ -3926,7 +3926,7 @@
         <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>182</v>
@@ -4111,7 +4111,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
         <v>182</v>
@@ -4481,7 +4481,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
         <v>182</v>
@@ -4666,7 +4666,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5036,7 +5036,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
         <v>182</v>
@@ -6146,10 +6146,10 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
         <v>204</v>
@@ -6331,10 +6331,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
         <v>205</v>
@@ -6370,13 +6370,13 @@
         <v>685</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>182</v>
@@ -6555,13 +6555,13 @@
         <v>685</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>182</v>
@@ -6740,13 +6740,13 @@
         <v>685</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -6886,7 +6886,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>183</v>
@@ -6925,13 +6925,13 @@
         <v>685</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="Q25">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R25">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6970,10 +6970,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -7071,7 +7071,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
         <v>183</v>
@@ -7110,13 +7110,13 @@
         <v>685</v>
       </c>
       <c r="P26">
-        <v>2.86</v>
+        <v>2.55</v>
       </c>
       <c r="Q26">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E27" t="s">
         <v>210</v>
@@ -7441,10 +7441,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
         <v>211</v>
@@ -7626,7 +7626,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
         <v>183</v>
@@ -7665,13 +7665,13 @@
         <v>685</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7710,10 +7710,10 @@
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29">
         <v>0</v>
@@ -7814,7 +7814,7 @@
         <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E30" t="s">
         <v>213</v>
@@ -7999,7 +7999,7 @@
         <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E31" t="s">
         <v>214</v>
@@ -8184,7 +8184,7 @@
         <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E32" t="s">
         <v>215</v>
@@ -8220,13 +8220,13 @@
         <v>685</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
         <v>216</v>
@@ -8551,10 +8551,10 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E34" t="s">
         <v>217</v>
@@ -8590,13 +8590,13 @@
         <v>685</v>
       </c>
       <c r="P34">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8635,10 +8635,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -8736,10 +8736,10 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
         <v>218</v>
@@ -8775,13 +8775,13 @@
         <v>685</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
         <v>219</v>
@@ -9109,7 +9109,7 @@
         <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E37" t="s">
         <v>220</v>
@@ -9145,13 +9145,13 @@
         <v>685</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9190,10 +9190,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -9291,7 +9291,7 @@
         <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
         <v>182</v>
@@ -9661,7 +9661,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
         <v>183</v>
@@ -9849,7 +9849,7 @@
         <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
         <v>224</v>
@@ -10031,7 +10031,7 @@
         <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -10216,10 +10216,10 @@
         <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E43" t="s">
         <v>226</v>
@@ -10255,13 +10255,13 @@
         <v>685</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10401,7 +10401,7 @@
         <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -10440,13 +10440,13 @@
         <v>685</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10586,7 +10586,7 @@
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
         <v>183</v>
@@ -10625,13 +10625,13 @@
         <v>685</v>
       </c>
       <c r="P45">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -10771,10 +10771,10 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
         <v>229</v>
@@ -10956,7 +10956,7 @@
         <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D47" t="s">
         <v>183</v>
@@ -11141,10 +11141,10 @@
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
         <v>231</v>
@@ -11326,10 +11326,10 @@
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
         <v>232</v>
@@ -11511,7 +11511,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
         <v>183</v>
@@ -11881,7 +11881,7 @@
         <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>183</v>
@@ -12066,10 +12066,10 @@
         <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E53" t="s">
         <v>236</v>
@@ -12251,7 +12251,7 @@
         <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D54" t="s">
         <v>183</v>
@@ -12991,10 +12991,10 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
         <v>241</v>
@@ -13179,7 +13179,7 @@
         <v>144</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E59" t="s">
         <v>242</v>
@@ -13361,10 +13361,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E60" t="s">
         <v>243</v>
@@ -13546,7 +13546,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
         <v>182</v>
@@ -13585,13 +13585,13 @@
         <v>685</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13731,10 +13731,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E62" t="s">
         <v>245</v>
@@ -13919,7 +13919,7 @@
         <v>144</v>
       </c>
       <c r="D63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E63" t="s">
         <v>246</v>
@@ -13955,13 +13955,13 @@
         <v>685</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14101,10 +14101,10 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
         <v>247</v>
@@ -14325,13 +14325,13 @@
         <v>685</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14510,13 +14510,13 @@
         <v>685</v>
       </c>
       <c r="P66">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14656,10 +14656,10 @@
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E67" t="s">
         <v>250</v>
@@ -14695,13 +14695,13 @@
         <v>685</v>
       </c>
       <c r="P67">
-        <v>2.54</v>
+        <v>3.26</v>
       </c>
       <c r="Q67">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R67">
-        <v>3.21</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14841,10 +14841,10 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
         <v>251</v>
@@ -15026,7 +15026,7 @@
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D69" t="s">
         <v>182</v>
@@ -15211,10 +15211,10 @@
         <v>77</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
         <v>253</v>
@@ -15396,10 +15396,10 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D71" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E71" t="s">
         <v>254</v>
@@ -15581,7 +15581,7 @@
         <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
         <v>183</v>
@@ -15620,13 +15620,13 @@
         <v>685</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15990,13 +15990,13 @@
         <v>685</v>
       </c>
       <c r="P74">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="Q74">
-        <v>4.16</v>
+        <v>5.18</v>
       </c>
       <c r="R74">
-        <v>3.23</v>
+        <v>7.21</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16041,10 +16041,10 @@
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH74">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI74">
         <v>0</v>
@@ -16175,13 +16175,13 @@
         <v>685</v>
       </c>
       <c r="P75">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="Q75">
-        <v>3.71</v>
+        <v>4.88</v>
       </c>
       <c r="R75">
-        <v>3.07</v>
+        <v>5.33</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -16220,16 +16220,16 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI75">
         <v>0</v>
@@ -16360,13 +16360,13 @@
         <v>685</v>
       </c>
       <c r="P76">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q76">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R76">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16411,10 +16411,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH76">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16545,61 +16545,61 @@
         <v>685</v>
       </c>
       <c r="P77">
+        <v>2.38</v>
+      </c>
+      <c r="Q77">
+        <v>3.71</v>
+      </c>
+      <c r="R77">
+        <v>3.07</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+      <c r="AE77">
         <v>1.61</v>
       </c>
-      <c r="Q77">
-        <v>4.88</v>
-      </c>
-      <c r="R77">
-        <v>5.33</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>0</v>
-      </c>
-      <c r="AB77">
-        <v>0</v>
-      </c>
-      <c r="AC77">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>0</v>
-      </c>
-      <c r="AE77">
-        <v>0</v>
-      </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH77">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16691,7 +16691,7 @@
         <v>80</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s">
         <v>183</v>
@@ -16730,13 +16730,13 @@
         <v>685</v>
       </c>
       <c r="P78">
-        <v>2.78</v>
+        <v>4.06</v>
       </c>
       <c r="Q78">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="R78">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16876,7 +16876,7 @@
         <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D79" t="s">
         <v>183</v>
@@ -17061,7 +17061,7 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D80" t="s">
         <v>183</v>
@@ -17100,13 +17100,13 @@
         <v>685</v>
       </c>
       <c r="P80">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17431,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="D82" t="s">
         <v>183</v>
@@ -17470,13 +17470,13 @@
         <v>685</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17616,7 +17616,7 @@
         <v>80</v>
       </c>
       <c r="C83" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D83" t="s">
         <v>183</v>
@@ -17655,13 +17655,13 @@
         <v>685</v>
       </c>
       <c r="P83">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q83">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="R83">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17700,10 +17700,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17801,7 +17801,7 @@
         <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="D84" t="s">
         <v>183</v>
@@ -17840,13 +17840,13 @@
         <v>685</v>
       </c>
       <c r="P84">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D85" t="s">
         <v>183</v>
@@ -18025,13 +18025,13 @@
         <v>685</v>
       </c>
       <c r="P85">
-        <v>4.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q85">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="R85">
-        <v>1.93</v>
+        <v>3.11</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18070,10 +18070,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18171,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D86" t="s">
         <v>183</v>
@@ -18210,13 +18210,13 @@
         <v>685</v>
       </c>
       <c r="P86">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="Q86">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="R86">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18255,10 +18255,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18356,7 +18356,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D87" t="s">
         <v>183</v>
@@ -18395,13 +18395,13 @@
         <v>685</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18440,10 +18440,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18541,10 +18541,10 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D88" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E88" t="s">
         <v>271</v>
@@ -18580,13 +18580,13 @@
         <v>685</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
         <v>183</v>
@@ -18765,13 +18765,13 @@
         <v>685</v>
       </c>
       <c r="P89">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="Q89">
-        <v>4.15</v>
+        <v>5.48</v>
       </c>
       <c r="R89">
-        <v>5.06</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18911,7 +18911,7 @@
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
         <v>183</v>
@@ -19281,10 +19281,10 @@
         <v>80</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D92" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E92" t="s">
         <v>275</v>
@@ -19320,13 +19320,13 @@
         <v>685</v>
       </c>
       <c r="P92">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19365,10 +19365,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>80</v>
       </c>
       <c r="C93" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
         <v>183</v>
@@ -19651,7 +19651,7 @@
         <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D94" t="s">
         <v>183</v>
@@ -19690,13 +19690,13 @@
         <v>685</v>
       </c>
       <c r="P94">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q94">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R94">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19735,10 +19735,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19836,7 +19836,7 @@
         <v>81</v>
       </c>
       <c r="C95" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D95" t="s">
         <v>183</v>
@@ -19875,13 +19875,13 @@
         <v>685</v>
       </c>
       <c r="P95">
-        <v>2.47</v>
+        <v>2.04</v>
       </c>
       <c r="Q95">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R95">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19920,10 +19920,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D97" t="s">
         <v>183</v>
@@ -20430,13 +20430,13 @@
         <v>685</v>
       </c>
       <c r="P98">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q98">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R98">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20475,10 +20475,10 @@
         <v>0</v>
       </c>
       <c r="AE98">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF98">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -20576,10 +20576,10 @@
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D99" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E99" t="s">
         <v>282</v>
@@ -20615,13 +20615,13 @@
         <v>685</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -20761,7 +20761,7 @@
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D100" t="s">
         <v>183</v>
@@ -20800,13 +20800,13 @@
         <v>685</v>
       </c>
       <c r="P100">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D101" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E101" t="s">
         <v>284</v>
@@ -20985,13 +20985,13 @@
         <v>685</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21170,13 +21170,13 @@
         <v>685</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21215,10 +21215,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21316,10 +21316,10 @@
         <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E103" t="s">
         <v>286</v>
@@ -21355,13 +21355,13 @@
         <v>685</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21501,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="C104" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D104" t="s">
         <v>183</v>
@@ -21686,7 +21686,7 @@
         <v>83</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D105" t="s">
         <v>183</v>
@@ -21871,7 +21871,7 @@
         <v>83</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="D106" t="s">
         <v>183</v>
@@ -21910,13 +21910,13 @@
         <v>685</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22056,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="C107" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D107" t="s">
         <v>183</v>
@@ -22241,10 +22241,10 @@
         <v>83</v>
       </c>
       <c r="C108" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="D108" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
         <v>291</v>
@@ -22280,13 +22280,13 @@
         <v>685</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22426,10 +22426,10 @@
         <v>83</v>
       </c>
       <c r="C109" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E109" t="s">
         <v>292</v>
@@ -22465,13 +22465,13 @@
         <v>685</v>
       </c>
       <c r="P109">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22611,10 +22611,10 @@
         <v>83</v>
       </c>
       <c r="C110" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D110" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
         <v>293</v>
@@ -22650,13 +22650,13 @@
         <v>685</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22695,10 +22695,10 @@
         <v>0</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG110">
         <v>0</v>
@@ -22796,7 +22796,7 @@
         <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
         <v>183</v>
@@ -22835,13 +22835,13 @@
         <v>685</v>
       </c>
       <c r="P111">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22981,7 +22981,7 @@
         <v>84</v>
       </c>
       <c r="C112" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D112" t="s">
         <v>183</v>
@@ -23020,13 +23020,13 @@
         <v>685</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23166,7 +23166,7 @@
         <v>84</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D113" t="s">
         <v>183</v>
@@ -23351,7 +23351,7 @@
         <v>84</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
         <v>183</v>
@@ -23536,7 +23536,7 @@
         <v>84</v>
       </c>
       <c r="C115" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D115" t="s">
         <v>183</v>
@@ -23721,7 +23721,7 @@
         <v>84</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D116" t="s">
         <v>183</v>
@@ -24276,7 +24276,7 @@
         <v>87</v>
       </c>
       <c r="C119" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D119" t="s">
         <v>183</v>
@@ -24315,13 +24315,13 @@
         <v>685</v>
       </c>
       <c r="P119">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R119">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S119">
         <v>0</v>
@@ -24461,7 +24461,7 @@
         <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D120" t="s">
         <v>183</v>
@@ -24646,7 +24646,7 @@
         <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D121" t="s">
         <v>183</v>
@@ -24685,13 +24685,13 @@
         <v>685</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24831,7 +24831,7 @@
         <v>87</v>
       </c>
       <c r="C122" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="D122" t="s">
         <v>183</v>
@@ -24870,13 +24870,13 @@
         <v>685</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25016,7 +25016,7 @@
         <v>87</v>
       </c>
       <c r="C123" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="D123" t="s">
         <v>183</v>
@@ -25055,13 +25055,13 @@
         <v>685</v>
       </c>
       <c r="P123">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25201,7 +25201,7 @@
         <v>87</v>
       </c>
       <c r="C124" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D124" t="s">
         <v>183</v>
@@ -25240,13 +25240,13 @@
         <v>685</v>
       </c>
       <c r="P124">
-        <v>2.24</v>
+        <v>4.55</v>
       </c>
       <c r="Q124">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="R124">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25386,7 +25386,7 @@
         <v>88</v>
       </c>
       <c r="C125" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D125" t="s">
         <v>183</v>
@@ -25571,7 +25571,7 @@
         <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D126" t="s">
         <v>183</v>
@@ -25756,7 +25756,7 @@
         <v>89</v>
       </c>
       <c r="C127" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D127" t="s">
         <v>183</v>
@@ -25941,10 +25941,10 @@
         <v>89</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D128" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E128" t="s">
         <v>311</v>
@@ -25980,13 +25980,13 @@
         <v>685</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S128">
         <v>0</v>
@@ -26126,7 +26126,7 @@
         <v>89</v>
       </c>
       <c r="C129" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D129" t="s">
         <v>183</v>
@@ -26165,13 +26165,13 @@
         <v>685</v>
       </c>
       <c r="P129">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26311,10 +26311,10 @@
         <v>89</v>
       </c>
       <c r="C130" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="D130" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E130" t="s">
         <v>313</v>
@@ -26350,13 +26350,13 @@
         <v>685</v>
       </c>
       <c r="P130">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26496,7 +26496,7 @@
         <v>89</v>
       </c>
       <c r="C131" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D131" t="s">
         <v>183</v>
@@ -26535,13 +26535,13 @@
         <v>685</v>
       </c>
       <c r="P131">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="Q131">
-        <v>3.33</v>
+        <v>6.19</v>
       </c>
       <c r="R131">
-        <v>3.96</v>
+        <v>8.6</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26681,7 +26681,7 @@
         <v>89</v>
       </c>
       <c r="C132" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D132" t="s">
         <v>183</v>
@@ -26720,13 +26720,13 @@
         <v>685</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26866,7 +26866,7 @@
         <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D133" t="s">
         <v>183</v>
@@ -27236,10 +27236,10 @@
         <v>91</v>
       </c>
       <c r="C135" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E135" t="s">
         <v>318</v>
@@ -27275,13 +27275,13 @@
         <v>685</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S135">
         <v>0</v>
@@ -27326,10 +27326,10 @@
         <v>0</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH135">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI135">
         <v>0</v>
@@ -27606,7 +27606,7 @@
         <v>91</v>
       </c>
       <c r="C137" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="D137" t="s">
         <v>183</v>
@@ -27791,10 +27791,10 @@
         <v>91</v>
       </c>
       <c r="C138" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E138" t="s">
         <v>321</v>
@@ -27976,10 +27976,10 @@
         <v>91</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E139" t="s">
         <v>322</v>
@@ -28015,13 +28015,13 @@
         <v>685</v>
       </c>
       <c r="P139">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28066,10 +28066,10 @@
         <v>0</v>
       </c>
       <c r="AG139">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH139">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI139">
         <v>0</v>
@@ -28901,10 +28901,10 @@
         <v>91</v>
       </c>
       <c r="C144" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="D144" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E144" t="s">
         <v>327</v>
@@ -29086,7 +29086,7 @@
         <v>91</v>
       </c>
       <c r="C145" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D145" t="s">
         <v>183</v>
@@ -29641,7 +29641,7 @@
         <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D148" t="s">
         <v>183</v>
@@ -29826,7 +29826,7 @@
         <v>93</v>
       </c>
       <c r="C149" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D149" t="s">
         <v>183</v>
@@ -30196,7 +30196,7 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D151" t="s">
         <v>183</v>
@@ -30381,7 +30381,7 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D152" t="s">
         <v>183</v>
@@ -30751,7 +30751,7 @@
         <v>93</v>
       </c>
       <c r="C154" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D154" t="s">
         <v>183</v>
@@ -30936,7 +30936,7 @@
         <v>93</v>
       </c>
       <c r="C155" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D155" t="s">
         <v>183</v>
@@ -31306,7 +31306,7 @@
         <v>93</v>
       </c>
       <c r="C157" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D157" t="s">
         <v>183</v>
@@ -31676,7 +31676,7 @@
         <v>93</v>
       </c>
       <c r="C159" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D159" t="s">
         <v>183</v>
@@ -32046,7 +32046,7 @@
         <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -32270,13 +32270,13 @@
         <v>685</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32416,7 +32416,7 @@
         <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D163" t="s">
         <v>183</v>
@@ -32455,13 +32455,13 @@
         <v>685</v>
       </c>
       <c r="P163">
-        <v>2.24</v>
+        <v>2.89</v>
       </c>
       <c r="Q163">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="R163">
-        <v>3.37</v>
+        <v>2.38</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32500,10 +32500,10 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG163">
         <v>0</v>
@@ -32601,10 +32601,10 @@
         <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D164" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E164" t="s">
         <v>347</v>
@@ -33010,13 +33010,13 @@
         <v>685</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33055,10 +33055,10 @@
         <v>0</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG166">
         <v>0</v>
@@ -33195,13 +33195,13 @@
         <v>685</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33341,7 +33341,7 @@
         <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D168" t="s">
         <v>183</v>
@@ -33565,13 +33565,13 @@
         <v>685</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33935,13 +33935,13 @@
         <v>685</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -33980,10 +33980,10 @@
         <v>0</v>
       </c>
       <c r="AE171">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF171">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG171">
         <v>0</v>
@@ -34081,10 +34081,10 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D172" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E172" t="s">
         <v>355</v>
@@ -34120,13 +34120,13 @@
         <v>685</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34266,10 +34266,10 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D173" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E173" t="s">
         <v>356</v>
@@ -34490,13 +34490,13 @@
         <v>685</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34541,10 +34541,10 @@
         <v>0</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH174">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI174">
         <v>0</v>
@@ -34636,10 +34636,10 @@
         <v>94</v>
       </c>
       <c r="C175" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E175" t="s">
         <v>358</v>
@@ -35006,7 +35006,7 @@
         <v>95</v>
       </c>
       <c r="C177" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D177" t="s">
         <v>183</v>
@@ -35191,7 +35191,7 @@
         <v>96</v>
       </c>
       <c r="C178" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D178" t="s">
         <v>182</v>
@@ -35376,10 +35376,10 @@
         <v>96</v>
       </c>
       <c r="C179" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="D179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E179" t="s">
         <v>362</v>
@@ -35415,13 +35415,13 @@
         <v>685</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35746,7 +35746,7 @@
         <v>96</v>
       </c>
       <c r="C181" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D181" t="s">
         <v>182</v>
@@ -35785,13 +35785,13 @@
         <v>685</v>
       </c>
       <c r="P181">
-        <v>2.82</v>
+        <v>1.65</v>
       </c>
       <c r="Q181">
-        <v>2.55</v>
+        <v>4.52</v>
       </c>
       <c r="R181">
-        <v>2.75</v>
+        <v>4.89</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35830,16 +35830,16 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF181">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH181">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI181">
         <v>0</v>
@@ -35931,7 +35931,7 @@
         <v>96</v>
       </c>
       <c r="C182" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="D182" t="s">
         <v>183</v>
@@ -36116,10 +36116,10 @@
         <v>96</v>
       </c>
       <c r="C183" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D183" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E183" t="s">
         <v>366</v>
@@ -36340,13 +36340,13 @@
         <v>685</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36385,10 +36385,10 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -36486,7 +36486,7 @@
         <v>97</v>
       </c>
       <c r="C185" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D185" t="s">
         <v>183</v>
@@ -36525,13 +36525,13 @@
         <v>685</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36671,7 +36671,7 @@
         <v>97</v>
       </c>
       <c r="C186" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D186" t="s">
         <v>183</v>
@@ -36710,13 +36710,13 @@
         <v>685</v>
       </c>
       <c r="P186">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q186">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="R186">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36856,10 +36856,10 @@
         <v>98</v>
       </c>
       <c r="C187" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D187" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E187" t="s">
         <v>370</v>
@@ -36895,13 +36895,13 @@
         <v>685</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37041,10 +37041,10 @@
         <v>98</v>
       </c>
       <c r="C188" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D188" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E188" t="s">
         <v>371</v>
@@ -37226,7 +37226,7 @@
         <v>98</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D189" t="s">
         <v>182</v>
@@ -37596,10 +37596,10 @@
         <v>98</v>
       </c>
       <c r="C191" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D191" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E191" t="s">
         <v>374</v>
@@ -37635,13 +37635,13 @@
         <v>685</v>
       </c>
       <c r="P191">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q191">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37680,10 +37680,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37781,10 +37781,10 @@
         <v>98</v>
       </c>
       <c r="C192" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D192" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E192" t="s">
         <v>375</v>
@@ -37966,10 +37966,10 @@
         <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D193" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E193" t="s">
         <v>376</v>
@@ -38005,13 +38005,13 @@
         <v>685</v>
       </c>
       <c r="P193">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q193">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38151,10 +38151,10 @@
         <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D194" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E194" t="s">
         <v>377</v>
@@ -38336,7 +38336,7 @@
         <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D195" t="s">
         <v>183</v>
@@ -38375,13 +38375,13 @@
         <v>685</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38420,10 +38420,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -39076,7 +39076,7 @@
         <v>101</v>
       </c>
       <c r="C199" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D199" t="s">
         <v>182</v>
@@ -39115,13 +39115,13 @@
         <v>685</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S199">
         <v>0</v>
@@ -39160,10 +39160,10 @@
         <v>0</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG199">
         <v>0</v>
@@ -39261,7 +39261,7 @@
         <v>101</v>
       </c>
       <c r="C200" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -39300,13 +39300,13 @@
         <v>685</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -39446,7 +39446,7 @@
         <v>101</v>
       </c>
       <c r="C201" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D201" t="s">
         <v>182</v>
@@ -39485,13 +39485,13 @@
         <v>685</v>
       </c>
       <c r="P201">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q201">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39530,10 +39530,10 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF201">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>101</v>
       </c>
       <c r="C202" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -39816,7 +39816,7 @@
         <v>102</v>
       </c>
       <c r="C203" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D203" t="s">
         <v>182</v>
@@ -40001,7 +40001,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D204" t="s">
         <v>182</v>
@@ -40186,7 +40186,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D205" t="s">
         <v>182</v>
@@ -40595,13 +40595,13 @@
         <v>685</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG207">
         <v>0</v>
@@ -40780,13 +40780,13 @@
         <v>685</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S208">
         <v>0</v>
@@ -40965,13 +40965,13 @@
         <v>685</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="S209">
         <v>0</v>
@@ -41150,13 +41150,13 @@
         <v>685</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41481,7 +41481,7 @@
         <v>107</v>
       </c>
       <c r="C212" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D212" t="s">
         <v>182</v>
@@ -41666,7 +41666,7 @@
         <v>107</v>
       </c>
       <c r="C213" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -41705,13 +41705,13 @@
         <v>685</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -41851,7 +41851,7 @@
         <v>107</v>
       </c>
       <c r="C214" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -41890,13 +41890,13 @@
         <v>685</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41935,10 +41935,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42036,7 +42036,7 @@
         <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -42075,13 +42075,13 @@
         <v>685</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42221,7 +42221,7 @@
         <v>107</v>
       </c>
       <c r="C216" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D216" t="s">
         <v>182</v>
@@ -42406,10 +42406,10 @@
         <v>108</v>
       </c>
       <c r="C217" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D217" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E217" t="s">
         <v>400</v>
@@ -42445,13 +42445,13 @@
         <v>685</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42591,7 +42591,7 @@
         <v>108</v>
       </c>
       <c r="C218" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D218" t="s">
         <v>183</v>
@@ -42776,7 +42776,7 @@
         <v>108</v>
       </c>
       <c r="C219" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D219" t="s">
         <v>183</v>
@@ -43331,7 +43331,7 @@
         <v>108</v>
       </c>
       <c r="C222" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D222" t="s">
         <v>183</v>
@@ -43516,10 +43516,10 @@
         <v>108</v>
       </c>
       <c r="C223" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D223" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E223" t="s">
         <v>406</v>
@@ -43555,13 +43555,13 @@
         <v>685</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S223">
         <v>0</v>
@@ -43600,10 +43600,10 @@
         <v>0</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG223">
         <v>0</v>
@@ -43701,7 +43701,7 @@
         <v>108</v>
       </c>
       <c r="C224" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D224" t="s">
         <v>183</v>
@@ -44071,7 +44071,7 @@
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D226" t="s">
         <v>183</v>
@@ -44256,10 +44256,10 @@
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D227" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E227" t="s">
         <v>410</v>
@@ -44295,13 +44295,13 @@
         <v>685</v>
       </c>
       <c r="P227">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q227">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R227">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44441,10 +44441,10 @@
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D228" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E228" t="s">
         <v>411</v>
@@ -44626,10 +44626,10 @@
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D229" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E229" t="s">
         <v>412</v>
@@ -44996,10 +44996,10 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D231" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E231" t="s">
         <v>414</v>
@@ -45181,7 +45181,7 @@
         <v>108</v>
       </c>
       <c r="C232" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D232" t="s">
         <v>183</v>
@@ -45366,7 +45366,7 @@
         <v>108</v>
       </c>
       <c r="C233" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D233" t="s">
         <v>183</v>
@@ -45736,7 +45736,7 @@
         <v>108</v>
       </c>
       <c r="C235" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D235" t="s">
         <v>183</v>
@@ -45921,10 +45921,10 @@
         <v>108</v>
       </c>
       <c r="C236" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D236" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E236" t="s">
         <v>419</v>
@@ -46106,7 +46106,7 @@
         <v>108</v>
       </c>
       <c r="C237" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D237" t="s">
         <v>183</v>
@@ -46291,10 +46291,10 @@
         <v>108</v>
       </c>
       <c r="C238" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D238" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E238" t="s">
         <v>421</v>
@@ -46661,7 +46661,7 @@
         <v>108</v>
       </c>
       <c r="C240" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D240" t="s">
         <v>182</v>
@@ -46846,7 +46846,7 @@
         <v>109</v>
       </c>
       <c r="C241" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D241" t="s">
         <v>182</v>
@@ -47070,13 +47070,13 @@
         <v>685</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47115,10 +47115,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47401,7 +47401,7 @@
         <v>112</v>
       </c>
       <c r="C244" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D244" t="s">
         <v>182</v>
@@ -47586,7 +47586,7 @@
         <v>112</v>
       </c>
       <c r="C245" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D245" t="s">
         <v>182</v>
@@ -48180,13 +48180,13 @@
         <v>685</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48365,13 +48365,13 @@
         <v>685</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -48410,10 +48410,10 @@
         <v>0</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG249">
         <v>0</v>
@@ -48550,13 +48550,13 @@
         <v>685</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -48601,10 +48601,10 @@
         <v>0</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH250">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI250">
         <v>0</v>
@@ -48735,13 +48735,13 @@
         <v>685</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -48786,10 +48786,10 @@
         <v>0</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH251">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI251">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,12 +370,12 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
@@ -388,66 +388,66 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
+    <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Croatia Druga HNL</t>
+    <t>Singapore S.League</t>
   </si>
   <si>
     <t>China China League One</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
@@ -460,45 +460,45 @@
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Portugal Liga 3</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -541,15 +541,15 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>Portugal Liga NOS</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -580,12 +580,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
     <t>Hwaseong</t>
   </si>
   <si>
@@ -598,18 +598,18 @@
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Cheongju</t>
   </si>
   <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -622,129 +622,129 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
     <t>Phu Dong</t>
   </si>
   <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
+    <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
-    <t>Cibalia</t>
+    <t>Young Lions</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Goa</t>
   </si>
   <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
     <t>Brommapojkarna W</t>
   </si>
   <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
     <t>Persis Solo</t>
   </si>
   <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
+    <t>Elche CF</t>
   </si>
   <si>
     <t>Rot-Weiss Essen</t>
   </si>
   <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -760,106 +760,109 @@
     <t>Västerås SK</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
     <t>Panserraikos</t>
   </si>
   <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
     <t>Augsburg</t>
   </si>
   <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
-    <t>CD Trofense</t>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Larissa</t>
   </si>
   <si>
     <t>Vaprus</t>
   </si>
   <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
     <t>Sunderland</t>
   </si>
   <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
     <t>Jamshedpur</t>
   </si>
   <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Dundee</t>
+    <t>Albacete Balompié</t>
   </si>
   <si>
     <t>Burgos CF</t>
@@ -868,66 +871,63 @@
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Albacete Balompié</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
     <t>Oţelul Galaţi</t>
   </si>
   <si>
-    <t>Dugopolje</t>
+    <t>Ried</t>
   </si>
   <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Ried</t>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
     <t>Sumqayıt</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
@@ -940,25 +940,28 @@
     <t>Prostějov</t>
   </si>
   <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Lazio</t>
-  </si>
-  <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
     <t>Winterthur</t>
   </si>
   <si>
+    <t>Beerschot-Wilrijk</t>
+  </si>
+  <si>
     <t>Al Najma</t>
   </si>
   <si>
-    <t>Beerschot-Wilrijk</t>
+    <t>Real Valladolid</t>
   </si>
   <si>
     <t>Manchester City</t>
@@ -976,219 +979,216 @@
     <t>Atlético Madrid</t>
   </si>
   <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
   </si>
   <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
     <t>Znicz Pruszków</t>
   </si>
   <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
+    <t>Stade Briochin</t>
   </si>
   <si>
     <t>Rouen</t>
   </si>
   <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Caen</t>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Annecy</t>
   </si>
   <si>
     <t>Laval</t>
   </si>
   <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
     <t>Clermont</t>
   </si>
   <si>
-    <t>Annecy</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
     <t>Luzern</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
     <t>Málaga CF</t>
   </si>
   <si>
-    <t>Motherwell</t>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>CD Mafra</t>
   </si>
   <si>
     <t>Real Oruro</t>
   </si>
   <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1204,108 +1204,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
     <t>Louisville City</t>
   </si>
   <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
     <t>Real Tomayapo</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
     <t>Gil Vicente</t>
   </si>
   <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
     <t>AVS</t>
   </si>
   <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1330,21 +1330,21 @@
     <t>Phoenix Rising</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
+    <t>FC Seoul</t>
   </si>
   <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Suwon</t>
   </si>
   <si>
@@ -1357,18 +1357,18 @@
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1381,129 +1381,129 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
     <t>Granada W</t>
   </si>
   <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
     <t>Hai Phong</t>
   </si>
   <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
     <t>Ha Noi</t>
   </si>
   <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
+    <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Sesvete</t>
+    <t>Geylang International</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
   </si>
   <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
     <t>Eskilstuna United</t>
   </si>
   <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
+    <t>Deportivo Alavés</t>
   </si>
   <si>
     <t>Verl</t>
   </si>
   <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1519,106 +1519,109 @@
     <t>GAIS</t>
   </si>
   <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
     <t>FC Caspiy</t>
   </si>
   <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
     <t>Kifisia</t>
   </si>
   <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
     <t>St. Pauli</t>
   </si>
   <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>Vitória Guimarães II</t>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
     <t>Manchester United</t>
   </si>
   <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
     <t>Bengaluru</t>
   </si>
   <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Livingston</t>
+    <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
     <t>Almería</t>
@@ -1627,66 +1630,63 @@
     <t>RCD Espanyol</t>
   </si>
   <si>
-    <t>Cultural y Deportiva Leonesa</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
     <t>SSC Farul</t>
   </si>
   <si>
-    <t>Bijelo Brdo</t>
+    <t>Wolfsberger AC</t>
   </si>
   <si>
     <t>Orijent 1919</t>
   </si>
   <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Siwelele</t>
   </si>
   <si>
+    <t>Aluminij</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Araz</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
@@ -1699,25 +1699,28 @@
     <t>České Budějovice</t>
   </si>
   <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
+    <t>Inter Milan</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>Inter Milan</t>
-  </si>
-  <si>
-    <t>Deportivo de La Coruña W</t>
-  </si>
-  <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
+    <t>Lommel United</t>
+  </si>
+  <si>
     <t>Al Hazm</t>
   </si>
   <si>
-    <t>Lommel United</t>
+    <t>Real Zaragoza</t>
   </si>
   <si>
     <t>Brentford</t>
@@ -1735,219 +1738,216 @@
     <t>Celta de Vigo</t>
   </si>
   <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Trakai</t>
   </si>
   <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
   </si>
   <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
+    <t>Quevilly Rouen</t>
   </si>
   <si>
     <t>Versailles</t>
   </si>
   <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Rodez</t>
   </si>
   <si>
     <t>Boulogne</t>
   </si>
   <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
     <t>Guingamp</t>
   </si>
   <si>
-    <t>Rodez</t>
-  </si>
-  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
     <t>Servette</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
     <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Real Betis</t>
   </si>
   <si>
     <t>Sporting Gijón</t>
   </si>
   <si>
-    <t>Hearts</t>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
+    <t>Unión Española</t>
   </si>
   <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Unión Española</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1963,108 +1963,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
     <t>Detroit City FC</t>
   </si>
   <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
     <t>FC Arouca</t>
   </si>
   <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
     <t>Porto</t>
   </si>
   <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2089,13 +2089,13 @@
     <t>San Antonio</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>San Diego</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -3028,7 +3028,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -5433,10 +5433,10 @@
         <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5618,7 +5618,7 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>186</v>
@@ -5806,7 +5806,7 @@
         <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5988,7 +5988,7 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
         <v>185</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6582,13 +6582,13 @@
         <v>694</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -6952,13 +6952,13 @@
         <v>694</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6997,10 +6997,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -7098,10 +7098,10 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7283,7 +7283,7 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -7322,13 +7322,13 @@
         <v>694</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R27">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7367,10 +7367,10 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>185</v>
@@ -7507,13 +7507,13 @@
         <v>694</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -7653,7 +7653,7 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
         <v>185</v>
@@ -7838,10 +7838,10 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
         <v>216</v>
@@ -8023,10 +8023,10 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8396,7 +8396,7 @@
         <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8581,7 +8581,7 @@
         <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8766,7 +8766,7 @@
         <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8802,13 +8802,13 @@
         <v>694</v>
       </c>
       <c r="P35">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -9318,10 +9318,10 @@
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9503,7 +9503,7 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
         <v>187</v>
@@ -9688,10 +9688,10 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -9727,13 +9727,13 @@
         <v>694</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -10061,7 +10061,7 @@
         <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
         <v>228</v>
@@ -10243,10 +10243,10 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10282,13 +10282,13 @@
         <v>694</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
         <v>186</v>
@@ -10467,13 +10467,13 @@
         <v>694</v>
       </c>
       <c r="P44">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
         <v>185</v>
@@ -10798,7 +10798,7 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
         <v>186</v>
@@ -10983,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
@@ -11168,7 +11168,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
@@ -11353,10 +11353,10 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11392,13 +11392,13 @@
         <v>694</v>
       </c>
       <c r="P49">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11538,10 +11538,10 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11723,7 +11723,7 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
         <v>186</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -11947,13 +11947,13 @@
         <v>694</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12093,7 +12093,7 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -13758,10 +13758,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
@@ -13982,13 +13982,13 @@
         <v>694</v>
       </c>
       <c r="P63">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14128,7 +14128,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -14313,7 +14313,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D65" t="s">
         <v>185</v>
@@ -14498,10 +14498,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14722,13 +14722,13 @@
         <v>694</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14868,7 +14868,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D68" t="s">
         <v>185</v>
@@ -14907,13 +14907,13 @@
         <v>694</v>
       </c>
       <c r="P68">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15053,10 +15053,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>3.26</v>
+        <v>2.54</v>
       </c>
       <c r="Q69">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R69">
-        <v>2.19</v>
+        <v>3.21</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15277,13 +15277,13 @@
         <v>694</v>
       </c>
       <c r="P70">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15608,7 +15608,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15793,10 +15793,10 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15832,13 +15832,13 @@
         <v>694</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15978,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
         <v>186</v>
@@ -16017,13 +16017,13 @@
         <v>694</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16387,13 +16387,13 @@
         <v>694</v>
       </c>
       <c r="P76">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q76">
-        <v>4.88</v>
+        <v>4.16</v>
       </c>
       <c r="R76">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16438,10 +16438,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH76">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16572,13 +16572,13 @@
         <v>694</v>
       </c>
       <c r="P77">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="Q77">
-        <v>3.71</v>
+        <v>4.88</v>
       </c>
       <c r="R77">
-        <v>3.07</v>
+        <v>5.33</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16617,16 +16617,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q78">
-        <v>4.16</v>
+        <v>3.71</v>
       </c>
       <c r="R78">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16802,16 +16802,16 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG78">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH78">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17458,10 +17458,10 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E82" t="s">
         <v>268</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>4.13</v>
+        <v>3.62</v>
       </c>
       <c r="R83">
-        <v>4.85</v>
+        <v>3.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q85">
-        <v>5.48</v>
+        <v>4.15</v>
       </c>
       <c r="R85">
-        <v>8.300000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18097,10 +18097,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18198,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18237,55 +18237,55 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>4.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q86">
-        <v>3.98</v>
+        <v>3.46</v>
       </c>
       <c r="R86">
+        <v>2.42</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86">
+        <v>0</v>
+      </c>
+      <c r="AD86">
+        <v>0</v>
+      </c>
+      <c r="AE86">
+        <v>1.77</v>
+      </c>
+      <c r="AF86">
         <v>1.93</v>
-      </c>
-      <c r="S86">
-        <v>0</v>
-      </c>
-      <c r="T86">
-        <v>0</v>
-      </c>
-      <c r="U86">
-        <v>0</v>
-      </c>
-      <c r="V86">
-        <v>0</v>
-      </c>
-      <c r="W86">
-        <v>0</v>
-      </c>
-      <c r="X86">
-        <v>0</v>
-      </c>
-      <c r="Y86">
-        <v>0</v>
-      </c>
-      <c r="Z86">
-        <v>0</v>
-      </c>
-      <c r="AA86">
-        <v>0</v>
-      </c>
-      <c r="AB86">
-        <v>0</v>
-      </c>
-      <c r="AC86">
-        <v>0</v>
-      </c>
-      <c r="AD86">
-        <v>0</v>
-      </c>
-      <c r="AE86">
-        <v>0</v>
-      </c>
-      <c r="AF86">
-        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="Q87">
-        <v>3.86</v>
+        <v>4.13</v>
       </c>
       <c r="R87">
-        <v>2.92</v>
+        <v>4.85</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="Q88">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="R88">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q91">
-        <v>3.01</v>
+        <v>5.48</v>
       </c>
       <c r="R91">
-        <v>3.11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19347,10 +19347,10 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="Q92">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="R92">
         <v>3.11</v>
@@ -19392,10 +19392,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19493,10 +19493,10 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E93" t="s">
         <v>279</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19577,10 +19577,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19717,13 +19717,13 @@
         <v>694</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19947,10 +19947,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>2.04</v>
       </c>
       <c r="Q96">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R96">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20502,10 +20502,10 @@
         <v>0</v>
       </c>
       <c r="AE98">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF98">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -20603,7 +20603,7 @@
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>2.4</v>
+        <v>3.87</v>
       </c>
       <c r="Q100">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R100">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20973,10 +20973,10 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21158,7 +21158,7 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21343,10 +21343,10 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q103">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R103">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21427,10 +21427,10 @@
         <v>0</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21612,10 +21612,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -21713,10 +21713,10 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E105" t="s">
         <v>291</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>8.01</v>
+        <v>2.7</v>
       </c>
       <c r="Q106">
-        <v>5.01</v>
+        <v>3.22</v>
       </c>
       <c r="R106">
-        <v>1.27</v>
+        <v>2.56</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -21982,10 +21982,10 @@
         <v>0</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG106">
         <v>0</v>
@@ -22083,10 +22083,10 @@
         <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22122,13 +22122,13 @@
         <v>694</v>
       </c>
       <c r="P107">
-        <v>3.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q107">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="R107">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22268,10 +22268,10 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="D108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E108" t="s">
         <v>294</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22352,10 +22352,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22453,7 +22453,7 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22492,13 +22492,13 @@
         <v>694</v>
       </c>
       <c r="P109">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="Q109">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="R109">
-        <v>2.56</v>
+        <v>3.27</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22537,10 +22537,10 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF109">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -22638,7 +22638,7 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22823,7 +22823,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q111">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23008,7 +23008,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -24858,7 +24858,7 @@
         <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="D122" t="s">
         <v>186</v>
@@ -24897,13 +24897,13 @@
         <v>694</v>
       </c>
       <c r="P122">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25267,13 +25267,13 @@
         <v>694</v>
       </c>
       <c r="P124">
-        <v>4.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q124">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R124">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25783,7 +25783,7 @@
         <v>90</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25968,7 +25968,7 @@
         <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26192,13 +26192,13 @@
         <v>694</v>
       </c>
       <c r="P129">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26338,10 +26338,10 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26377,13 +26377,13 @@
         <v>694</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26523,10 +26523,10 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26747,13 +26747,13 @@
         <v>694</v>
       </c>
       <c r="P132">
-        <v>5.74</v>
+        <v>1.93</v>
       </c>
       <c r="Q132">
-        <v>5.53</v>
+        <v>3.33</v>
       </c>
       <c r="R132">
-        <v>1.51</v>
+        <v>3.96</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26893,7 +26893,7 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -26932,13 +26932,13 @@
         <v>694</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27263,7 +27263,7 @@
         <v>92</v>
       </c>
       <c r="C135" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27448,10 +27448,10 @@
         <v>93</v>
       </c>
       <c r="C136" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D136" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E136" t="s">
         <v>322</v>
@@ -28003,10 +28003,10 @@
         <v>93</v>
       </c>
       <c r="C139" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E139" t="s">
         <v>325</v>
@@ -28042,13 +28042,13 @@
         <v>694</v>
       </c>
       <c r="P139">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S139">
         <v>0</v>
@@ -28093,10 +28093,10 @@
         <v>0</v>
       </c>
       <c r="AG139">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH139">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI139">
         <v>0</v>
@@ -28558,10 +28558,10 @@
         <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -29113,10 +29113,10 @@
         <v>93</v>
       </c>
       <c r="C145" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29152,13 +29152,13 @@
         <v>694</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29203,10 +29203,10 @@
         <v>0</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH145">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI145">
         <v>0</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29483,7 +29483,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="D147" t="s">
         <v>186</v>
@@ -29853,7 +29853,7 @@
         <v>95</v>
       </c>
       <c r="C149" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -30038,7 +30038,7 @@
         <v>95</v>
       </c>
       <c r="C150" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30077,13 +30077,13 @@
         <v>694</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30408,7 +30408,7 @@
         <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30447,13 +30447,13 @@
         <v>694</v>
       </c>
       <c r="P152">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q152">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R152">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S152">
         <v>0</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30778,7 +30778,7 @@
         <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30817,13 +30817,13 @@
         <v>694</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S154">
         <v>0</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31002,13 +31002,13 @@
         <v>694</v>
       </c>
       <c r="P155">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q155">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R155">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S155">
         <v>0</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31703,7 +31703,7 @@
         <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D159" t="s">
         <v>186</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -32073,7 +32073,7 @@
         <v>95</v>
       </c>
       <c r="C161" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32718,10 +32718,10 @@
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH164">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32813,10 +32813,10 @@
         <v>96</v>
       </c>
       <c r="C165" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D165" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E165" t="s">
         <v>351</v>
@@ -32998,10 +32998,10 @@
         <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D166" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E166" t="s">
         <v>352</v>
@@ -33037,13 +33037,13 @@
         <v>694</v>
       </c>
       <c r="P166">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q166">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R166">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33082,10 +33082,10 @@
         <v>0</v>
       </c>
       <c r="AE166">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF166">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG166">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q167">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R167">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33368,7 +33368,7 @@
         <v>96</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>3.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q168">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="R168">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33553,10 +33553,10 @@
         <v>96</v>
       </c>
       <c r="C169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D169" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E169" t="s">
         <v>355</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33777,13 +33777,13 @@
         <v>694</v>
       </c>
       <c r="P170">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q170">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R170">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33828,10 +33828,10 @@
         <v>0</v>
       </c>
       <c r="AG170">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH170">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI170">
         <v>0</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>3.79</v>
+        <v>1.45</v>
       </c>
       <c r="Q171">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="R171">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34007,10 +34007,10 @@
         <v>0</v>
       </c>
       <c r="AE171">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF171">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG171">
         <v>0</v>
@@ -34108,10 +34108,10 @@
         <v>96</v>
       </c>
       <c r="C172" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D172" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E172" t="s">
         <v>358</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34192,10 +34192,10 @@
         <v>0</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>2.24</v>
+        <v>3.79</v>
       </c>
       <c r="Q173">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R173">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34663,7 +34663,7 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q176">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R176">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -34932,10 +34932,10 @@
         <v>0</v>
       </c>
       <c r="AE176">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF176">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG176">
         <v>0</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>1.97</v>
+        <v>2.89</v>
       </c>
       <c r="Q177">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="R177">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35117,10 +35117,10 @@
         <v>0</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG177">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D180" t="s">
         <v>186</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35773,10 +35773,10 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="D181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q181">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R181">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35958,7 +35958,7 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D182" t="s">
         <v>185</v>
@@ -36143,7 +36143,7 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D183" t="s">
         <v>185</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36233,10 +36233,10 @@
         <v>0</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH183">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI183">
         <v>0</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q184">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36412,10 +36412,10 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF184">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG184">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D185" t="s">
         <v>185</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>1.65</v>
+        <v>2.82</v>
       </c>
       <c r="Q185">
-        <v>4.52</v>
+        <v>2.55</v>
       </c>
       <c r="R185">
-        <v>4.89</v>
+        <v>2.75</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36597,16 +36597,16 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG185">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH185">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI185">
         <v>0</v>
@@ -36698,10 +36698,10 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37253,7 +37253,7 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37292,13 +37292,13 @@
         <v>694</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37337,10 +37337,10 @@
         <v>0</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG189">
         <v>0</v>
@@ -37438,7 +37438,7 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37623,7 +37623,7 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37662,13 +37662,13 @@
         <v>694</v>
       </c>
       <c r="P191">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q191">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37707,10 +37707,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37808,10 +37808,10 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="D192" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -38178,7 +38178,7 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D194" t="s">
         <v>186</v>
@@ -38366,7 +38366,7 @@
         <v>177</v>
       </c>
       <c r="D195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38548,7 +38548,7 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D196" t="s">
         <v>185</v>
@@ -38733,7 +38733,7 @@
         <v>100</v>
       </c>
       <c r="C197" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D197" t="s">
         <v>185</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -39512,13 +39512,13 @@
         <v>694</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>103</v>
       </c>
       <c r="C202" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39697,13 +39697,13 @@
         <v>694</v>
       </c>
       <c r="P202">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q202">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39742,10 +39742,10 @@
         <v>0</v>
       </c>
       <c r="AE202">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF202">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG202">
         <v>0</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -39882,13 +39882,13 @@
         <v>694</v>
       </c>
       <c r="P203">
-        <v>2.32</v>
+        <v>1.56</v>
       </c>
       <c r="Q203">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R203">
-        <v>3.16</v>
+        <v>6.74</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG203">
         <v>0</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -41177,13 +41177,13 @@
         <v>694</v>
       </c>
       <c r="P210">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q210">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R210">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41222,10 +41222,10 @@
         <v>0</v>
       </c>
       <c r="AE210">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF210">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG210">
         <v>0</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q211">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R211">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41407,10 +41407,10 @@
         <v>0</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG211">
         <v>0</v>
@@ -41917,13 +41917,13 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q214">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="R214">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41962,10 +41962,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AF214">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42063,7 +42063,7 @@
         <v>109</v>
       </c>
       <c r="C215" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D215" t="s">
         <v>185</v>
@@ -42102,13 +42102,13 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q215">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R215">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42147,10 +42147,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="Q216">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R216">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AF216">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q217">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R217">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF217">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42657,13 +42657,13 @@
         <v>694</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -43173,7 +43173,7 @@
         <v>110</v>
       </c>
       <c r="C221" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D221" t="s">
         <v>186</v>
@@ -43358,10 +43358,10 @@
         <v>110</v>
       </c>
       <c r="C222" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D222" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43728,10 +43728,10 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D224" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43767,13 +43767,13 @@
         <v>694</v>
       </c>
       <c r="P224">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q224">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R224">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43913,7 +43913,7 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D225" t="s">
         <v>186</v>
@@ -44098,7 +44098,7 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44283,10 +44283,10 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D227" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44468,7 +44468,7 @@
         <v>110</v>
       </c>
       <c r="C228" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D228" t="s">
         <v>186</v>
@@ -44653,7 +44653,7 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44838,7 +44838,7 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D230" t="s">
         <v>186</v>
@@ -45208,10 +45208,10 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D232" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E232" t="s">
         <v>418</v>
@@ -45247,13 +45247,13 @@
         <v>694</v>
       </c>
       <c r="P232">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q232">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R232">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S232">
         <v>0</v>
@@ -45292,10 +45292,10 @@
         <v>0</v>
       </c>
       <c r="AE232">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF232">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG232">
         <v>0</v>
@@ -45578,7 +45578,7 @@
         <v>110</v>
       </c>
       <c r="C234" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D234" t="s">
         <v>186</v>
@@ -45763,7 +45763,7 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D235" t="s">
         <v>186</v>
@@ -45948,10 +45948,10 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D236" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E236" t="s">
         <v>422</v>
@@ -45987,13 +45987,13 @@
         <v>694</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R236">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S236">
         <v>0</v>
@@ -46133,7 +46133,7 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D237" t="s">
         <v>186</v>
@@ -46318,10 +46318,10 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D238" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E238" t="s">
         <v>424</v>
@@ -46503,10 +46503,10 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D239" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E239" t="s">
         <v>425</v>
@@ -46873,10 +46873,10 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D241" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E241" t="s">
         <v>427</v>
@@ -47058,7 +47058,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D242" t="s">
         <v>185</v>
@@ -47097,13 +47097,13 @@
         <v>694</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47142,10 +47142,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -48947,13 +48947,13 @@
         <v>694</v>
       </c>
       <c r="P252">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q252">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R252">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -48992,16 +48992,16 @@
         <v>0</v>
       </c>
       <c r="AE252">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF252">
+        <v>0</v>
+      </c>
+      <c r="AG252">
         <v>2.15</v>
       </c>
-      <c r="AG252">
-        <v>0</v>
-      </c>
       <c r="AH252">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>2.95</v>
+        <v>1.46</v>
       </c>
       <c r="Q253">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.2</v>
+        <v>5.15</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49183,10 +49183,10 @@
         <v>0</v>
       </c>
       <c r="AG253">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH253">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI253">
         <v>0</v>
@@ -49317,13 +49317,13 @@
         <v>694</v>
       </c>
       <c r="P254">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q254">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R254">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -49362,16 +49362,16 @@
         <v>0</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG254">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH254">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI254">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -373,12 +373,12 @@
     <t>South Korea K League 1</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>Australia A-League</t>
   </si>
   <si>
@@ -397,12 +397,12 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -418,78 +418,78 @@
     <t>Singapore S.League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
   </si>
   <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>France National</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>France National</t>
-  </si>
-  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
@@ -541,18 +541,18 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Portugal Liga NOS</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -583,15 +583,15 @@
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>Auckland</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
@@ -622,129 +622,129 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
     <t>Espanyol W</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Real Sociedad W</t>
+    <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
     <t>United Nordic</t>
   </si>
   <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
     <t>Young Lions</t>
   </si>
   <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
     <t>Nanjing City</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
     <t>Osnabrück</t>
   </si>
   <si>
-    <t>Sarpsborg 08</t>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
   </si>
   <si>
     <t>Dukla Praha</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
     <t>Brommapojkarna W</t>
   </si>
   <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,163 +754,166 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Norrby</t>
   </si>
   <si>
     <t>Qabala</t>
   </si>
   <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>Hoffenheim</t>
-  </si>
-  <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
   </si>
   <si>
     <t>CD Trofense</t>
   </si>
   <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion</t>
   </si>
   <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
     <t>Albacete Balompié</t>
   </si>
   <si>
+    <t>Sevilla FC</t>
+  </si>
+  <si>
     <t>Burgos CF</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
+    <t>Sumqayıt</t>
   </si>
   <si>
     <t>Golden Arrows</t>
@@ -922,273 +925,270 @@
     <t>Koper</t>
   </si>
   <si>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Zürich</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Zürich</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Winterthur</t>
   </si>
   <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
-    <t>Al Najma</t>
-  </si>
-  <si>
     <t>Real Valladolid</t>
   </si>
   <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
     <t>Manchester City</t>
   </si>
   <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
     <t>İstanbul Başakşehir</t>
   </si>
   <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
+    <t>Slavia Praha</t>
   </si>
   <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
     <t>Le Puy F.43 Auvergne</t>
   </si>
   <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
     <t>Rouen</t>
   </si>
   <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
     <t>Saint-Étienne</t>
   </si>
   <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
     <t>Nürnberg</t>
   </si>
   <si>
     <t>Técnico Universitario</t>
   </si>
   <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
     <t>Motherwell</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
     <t>Coritiba</t>
   </si>
   <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Goiás</t>
+    <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
     <t>Guayaquil City FC</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1204,108 +1204,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Real Tomayapo</t>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
   </si>
   <si>
     <t>Gil Vicente</t>
   </si>
   <si>
-    <t>Grafičar</t>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
   </si>
   <si>
     <t>Houston Dash</t>
   </si>
   <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>AVS</t>
   </si>
   <si>
     <t>Santa Clara</t>
   </si>
   <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
     <t>Farense</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
     <t>Alverca</t>
   </si>
   <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1324,33 +1324,33 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Phoenix Rising</t>
+  </si>
+  <si>
     <t>Oakland Roots</t>
   </si>
   <si>
-    <t>Phoenix Rising</t>
+    <t>Portland Timbers</t>
   </si>
   <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>Adelaide United</t>
   </si>
   <si>
@@ -1360,12 +1360,12 @@
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Daegu</t>
   </si>
   <si>
@@ -1381,129 +1381,129 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Granada W</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
     <t>Badalona W</t>
   </si>
   <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
-    <t>Granada W</t>
+    <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
     <t>Magdeburg</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
     <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
     <t>Geylang International</t>
   </si>
   <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>Ulm</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
   </si>
   <si>
     <t>Slovácko</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
     <t>Eskilstuna United</t>
   </si>
   <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,163 +1513,166 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Bayer Leverkusen</t>
   </si>
   <si>
-    <t>Werder Bremen</t>
-  </si>
-  <si>
-    <t>Borussia M'gladbach</t>
-  </si>
-  <si>
-    <t>St. Pauli</t>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
   </si>
   <si>
     <t>Vitória Guimarães II</t>
   </si>
   <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
     <t>Wolverhampton Wanderers</t>
   </si>
   <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
+    <t>RCD Espanyol</t>
+  </si>
+  <si>
     <t>Almería</t>
   </si>
   <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
     <t>Norrköping</t>
   </si>
   <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
+    <t>Araz</t>
   </si>
   <si>
     <t>Polokwane City</t>
@@ -1681,273 +1684,270 @@
     <t>Aluminij</t>
   </si>
   <si>
+    <t>Pogoń Szczecin</t>
+  </si>
+  <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Araz</t>
-  </si>
-  <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
+    <t>Al Hazm</t>
+  </si>
+  <si>
     <t>Lommel United</t>
   </si>
   <si>
-    <t>Al Hazm</t>
-  </si>
-  <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
     <t>Brentford</t>
   </si>
   <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
     <t>Samsunspor</t>
   </si>
   <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
+    <t>Sparta Praha</t>
   </si>
   <si>
     <t>Trakai</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
     <t>Dijon</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
     <t>Versailles</t>
   </si>
   <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
     <t>Amiens SC</t>
   </si>
   <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
     <t>Los Andes</t>
   </si>
   <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
     <t>Schalke 04</t>
   </si>
   <si>
     <t>Delfin SC</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
     <t>Hearts</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
+    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1963,108 +1963,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>Sporting JAX</t>
   </si>
   <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
     <t>Operário PR</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>San Antonio Bulo Bulo</t>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Porto II</t>
   </si>
   <si>
     <t>FC Arouca</t>
   </si>
   <si>
-    <t>Dubočica</t>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>North Texas</t>
   </si>
   <si>
     <t>Denver Summit W</t>
   </si>
   <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Porto</t>
   </si>
   <si>
     <t>CD Nacional</t>
   </si>
   <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
     <t>Paços de Ferreira</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
     <t>GD Estoril Praia</t>
   </si>
   <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2083,16 +2083,16 @@
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>El Paso Locomotive</t>
   </si>
   <si>
-    <t>San Antonio</t>
+    <t>Sporting KC</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
   </si>
   <si>
     <t>San Diego</t>
@@ -3028,7 +3028,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3953,7 +3953,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4138,7 +4138,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4323,7 +4323,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5803,10 +5803,10 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5988,10 +5988,10 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -6582,13 +6582,13 @@
         <v>694</v>
       </c>
       <c r="P23">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q23">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R23">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6627,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -6728,10 +6728,10 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -7098,10 +7098,10 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7322,13 +7322,13 @@
         <v>694</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7367,10 +7367,10 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG27">
         <v>0</v>
@@ -7507,13 +7507,13 @@
         <v>694</v>
       </c>
       <c r="P28">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="Q28">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R28">
-        <v>3.58</v>
+        <v>2.93</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
         <v>215</v>
@@ -7692,13 +7692,13 @@
         <v>694</v>
       </c>
       <c r="P29">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7838,7 +7838,7 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -8023,10 +8023,10 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8763,10 +8763,10 @@
         <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8948,10 +8948,10 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
         <v>222</v>
@@ -8987,13 +8987,13 @@
         <v>694</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9172,13 +9172,13 @@
         <v>694</v>
       </c>
       <c r="P37">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -9318,10 +9318,10 @@
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9357,13 +9357,13 @@
         <v>694</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9691,7 +9691,7 @@
         <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -9727,13 +9727,13 @@
         <v>694</v>
       </c>
       <c r="P40">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -10613,10 +10613,10 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E45" t="s">
         <v>231</v>
@@ -10798,7 +10798,7 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
         <v>186</v>
@@ -10983,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
@@ -11168,7 +11168,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11538,10 +11538,10 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
@@ -11723,7 +11723,7 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
         <v>186</v>
@@ -11908,10 +11908,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -11947,13 +11947,13 @@
         <v>694</v>
       </c>
       <c r="P52">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12093,7 +12093,7 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12132,13 +12132,13 @@
         <v>694</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,10 +12648,10 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -13391,7 +13391,7 @@
         <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E60" t="s">
         <v>246</v>
@@ -13576,7 +13576,7 @@
         <v>147</v>
       </c>
       <c r="D61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" t="s">
         <v>247</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13758,7 +13758,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D62" t="s">
         <v>186</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D63" t="s">
         <v>186</v>
@@ -14131,7 +14131,7 @@
         <v>148</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14167,13 +14167,13 @@
         <v>694</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14313,10 +14313,10 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,7 +14683,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
         <v>185</v>
@@ -14722,13 +14722,13 @@
         <v>694</v>
       </c>
       <c r="P67">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14868,7 +14868,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
         <v>185</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>2.54</v>
+        <v>3.13</v>
       </c>
       <c r="Q69">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>3.21</v>
+        <v>2.42</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="D70" t="s">
         <v>185</v>
@@ -15426,7 +15426,7 @@
         <v>148</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E71" t="s">
         <v>257</v>
@@ -15462,13 +15462,13 @@
         <v>694</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15608,10 +15608,10 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E72" t="s">
         <v>258</v>
@@ -16017,13 +16017,13 @@
         <v>694</v>
       </c>
       <c r="P74">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16387,13 +16387,13 @@
         <v>694</v>
       </c>
       <c r="P76">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q76">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R76">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16438,10 +16438,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH76">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16572,61 +16572,61 @@
         <v>694</v>
       </c>
       <c r="P77">
+        <v>2.38</v>
+      </c>
+      <c r="Q77">
+        <v>3.71</v>
+      </c>
+      <c r="R77">
+        <v>3.07</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+      <c r="AE77">
         <v>1.61</v>
       </c>
-      <c r="Q77">
-        <v>4.88</v>
-      </c>
-      <c r="R77">
-        <v>5.33</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>0</v>
-      </c>
-      <c r="AB77">
-        <v>0</v>
-      </c>
-      <c r="AC77">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>0</v>
-      </c>
-      <c r="AE77">
-        <v>0</v>
-      </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH77">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="Q78">
-        <v>3.71</v>
+        <v>5.18</v>
       </c>
       <c r="R78">
-        <v>3.07</v>
+        <v>7.21</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16802,16 +16802,16 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF78">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16942,13 +16942,13 @@
         <v>694</v>
       </c>
       <c r="P79">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q79">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R79">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16993,10 +16993,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH79">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="Q83">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R83">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF83">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="Q85">
-        <v>4.15</v>
+        <v>3.01</v>
       </c>
       <c r="R85">
-        <v>5.06</v>
+        <v>3.11</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18097,10 +18097,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.41</v>
+        <v>2.13</v>
       </c>
       <c r="Q88">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="R88">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18753,7 +18753,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18792,13 +18792,13 @@
         <v>694</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="D90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q91">
-        <v>5.48</v>
+        <v>4.15</v>
       </c>
       <c r="R91">
-        <v>8.300000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19207,10 +19207,10 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19347,13 +19347,13 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="Q92">
-        <v>3.01</v>
+        <v>3.86</v>
       </c>
       <c r="R92">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19493,10 +19493,10 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E93" t="s">
         <v>279</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19717,13 +19717,13 @@
         <v>694</v>
       </c>
       <c r="P94">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20603,7 +20603,7 @@
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20973,7 +20973,7 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
         <v>185</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21158,7 +21158,7 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21343,7 +21343,7 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="Q103">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R103">
-        <v>4.4</v>
+        <v>3.02</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21427,10 +21427,10 @@
         <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>8.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q105">
-        <v>5.01</v>
+        <v>3.33</v>
       </c>
       <c r="R105">
-        <v>1.27</v>
+        <v>3.27</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21797,10 +21797,10 @@
         <v>0</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG105">
         <v>0</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q106">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R106">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -21982,10 +21982,10 @@
         <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG106">
         <v>0</v>
@@ -22268,10 +22268,10 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E108" t="s">
         <v>294</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22352,10 +22352,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22453,10 +22453,10 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="D109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E109" t="s">
         <v>295</v>
@@ -22492,13 +22492,13 @@
         <v>694</v>
       </c>
       <c r="P109">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="Q109">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="R109">
-        <v>3.27</v>
+        <v>2.88</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22537,10 +22537,10 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -22638,7 +22638,7 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22823,7 +22823,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23008,10 +23008,10 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D112" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E112" t="s">
         <v>298</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -23972,13 +23972,13 @@
         <v>694</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24157,13 +24157,13 @@
         <v>694</v>
       </c>
       <c r="P118">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24712,13 +24712,13 @@
         <v>694</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24858,7 +24858,7 @@
         <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D122" t="s">
         <v>186</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25267,13 +25267,13 @@
         <v>694</v>
       </c>
       <c r="P124">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q124">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25452,13 +25452,13 @@
         <v>694</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25783,7 +25783,7 @@
         <v>90</v>
       </c>
       <c r="C127" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25968,7 +25968,7 @@
         <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26338,7 +26338,7 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26377,13 +26377,13 @@
         <v>694</v>
       </c>
       <c r="P130">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="Q130">
-        <v>6.19</v>
+        <v>3.33</v>
       </c>
       <c r="R130">
-        <v>8.6</v>
+        <v>3.96</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26523,10 +26523,10 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D131" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
         <v>317</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26747,13 +26747,13 @@
         <v>694</v>
       </c>
       <c r="P132">
-        <v>1.93</v>
+        <v>5.74</v>
       </c>
       <c r="Q132">
-        <v>3.33</v>
+        <v>5.53</v>
       </c>
       <c r="R132">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26893,7 +26893,7 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -26932,13 +26932,13 @@
         <v>694</v>
       </c>
       <c r="P133">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q133">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27078,10 +27078,10 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="D134" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E134" t="s">
         <v>320</v>
@@ -27633,10 +27633,10 @@
         <v>93</v>
       </c>
       <c r="C137" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27672,13 +27672,13 @@
         <v>694</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27723,10 +27723,10 @@
         <v>0</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH137">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI137">
         <v>0</v>
@@ -28558,10 +28558,10 @@
         <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -29113,10 +29113,10 @@
         <v>93</v>
       </c>
       <c r="C145" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29152,13 +29152,13 @@
         <v>694</v>
       </c>
       <c r="P145">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R145">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29203,10 +29203,10 @@
         <v>0</v>
       </c>
       <c r="AG145">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH145">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI145">
         <v>0</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29483,10 +29483,10 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D147" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E147" t="s">
         <v>333</v>
@@ -30077,13 +30077,13 @@
         <v>694</v>
       </c>
       <c r="P150">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q150">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30408,7 +30408,7 @@
         <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30817,13 +30817,13 @@
         <v>694</v>
       </c>
       <c r="P154">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q154">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R154">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S154">
         <v>0</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31333,7 +31333,7 @@
         <v>95</v>
       </c>
       <c r="C157" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D157" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31703,7 +31703,7 @@
         <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D159" t="s">
         <v>186</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -31927,13 +31927,13 @@
         <v>694</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S160">
         <v>0</v>
@@ -32073,7 +32073,7 @@
         <v>95</v>
       </c>
       <c r="C161" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32112,13 +32112,13 @@
         <v>694</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32443,7 +32443,7 @@
         <v>95</v>
       </c>
       <c r="C163" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>1.3</v>
+        <v>2.89</v>
       </c>
       <c r="Q164">
-        <v>5.65</v>
+        <v>3.32</v>
       </c>
       <c r="R164">
-        <v>8.4</v>
+        <v>2.38</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,16 +32712,16 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG164">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH164">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI164">
         <v>0</v>
@@ -32813,10 +32813,10 @@
         <v>96</v>
       </c>
       <c r="C165" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D165" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E165" t="s">
         <v>351</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32998,10 +32998,10 @@
         <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D166" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E166" t="s">
         <v>352</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33267,10 +33267,10 @@
         <v>0</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG167">
         <v>0</v>
@@ -33368,7 +33368,7 @@
         <v>96</v>
       </c>
       <c r="C168" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q168">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33777,13 +33777,13 @@
         <v>694</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33923,7 +33923,7 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q171">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R171">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>2.61</v>
+        <v>3.79</v>
       </c>
       <c r="Q172">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R172">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34192,10 +34192,10 @@
         <v>0</v>
       </c>
       <c r="AE172">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AF172">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>3.79</v>
+        <v>1.3</v>
       </c>
       <c r="Q173">
-        <v>3.6</v>
+        <v>5.65</v>
       </c>
       <c r="R173">
-        <v>1.9</v>
+        <v>8.4</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34377,16 +34377,16 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF173">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG173">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH173">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI173">
         <v>0</v>
@@ -34478,10 +34478,10 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D174" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E174" t="s">
         <v>360</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34663,7 +34663,7 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q175">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R175">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34848,10 +34848,10 @@
         <v>96</v>
       </c>
       <c r="C176" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D176" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -35033,7 +35033,7 @@
         <v>96</v>
       </c>
       <c r="C177" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D177" t="s">
         <v>186</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>2.89</v>
+        <v>2.24</v>
       </c>
       <c r="Q177">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="R177">
-        <v>2.38</v>
+        <v>3.37</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35117,10 +35117,10 @@
         <v>0</v>
       </c>
       <c r="AE177">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF177">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG177">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35588,10 +35588,10 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D180" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E180" t="s">
         <v>366</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>2.87</v>
+        <v>1.65</v>
       </c>
       <c r="Q180">
-        <v>3.45</v>
+        <v>4.52</v>
       </c>
       <c r="R180">
-        <v>2.3</v>
+        <v>4.89</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35678,10 +35678,10 @@
         <v>0</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH180">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI180">
         <v>0</v>
@@ -35773,7 +35773,7 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35958,10 +35958,10 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E182" t="s">
         <v>368</v>
@@ -36143,7 +36143,7 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D183" t="s">
         <v>185</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>1.65</v>
+        <v>2.82</v>
       </c>
       <c r="Q183">
-        <v>4.52</v>
+        <v>2.55</v>
       </c>
       <c r="R183">
-        <v>4.89</v>
+        <v>2.75</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36227,16 +36227,16 @@
         <v>0</v>
       </c>
       <c r="AE183">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG183">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH183">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI183">
         <v>0</v>
@@ -36513,10 +36513,10 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="D185" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E185" t="s">
         <v>371</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="Q185">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="R185">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36597,10 +36597,10 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF185">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG185">
         <v>0</v>
@@ -36698,10 +36698,10 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D186" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37253,7 +37253,7 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37292,13 +37292,13 @@
         <v>694</v>
       </c>
       <c r="P189">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q189">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R189">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37337,10 +37337,10 @@
         <v>0</v>
       </c>
       <c r="AE189">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF189">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG189">
         <v>0</v>
@@ -37438,7 +37438,7 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37477,13 +37477,13 @@
         <v>694</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37522,10 +37522,10 @@
         <v>0</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG190">
         <v>0</v>
@@ -37623,10 +37623,10 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="D191" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37993,10 +37993,10 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38032,13 +38032,13 @@
         <v>694</v>
       </c>
       <c r="P193">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q193">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38178,10 +38178,10 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D194" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38363,7 +38363,7 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D195" t="s">
         <v>185</v>
@@ -38548,10 +38548,10 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D196" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38772,13 +38772,13 @@
         <v>694</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -39512,13 +39512,13 @@
         <v>694</v>
       </c>
       <c r="P201">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q201">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>103</v>
       </c>
       <c r="C202" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -39882,13 +39882,13 @@
         <v>694</v>
       </c>
       <c r="P203">
-        <v>1.56</v>
+        <v>2.32</v>
       </c>
       <c r="Q203">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R203">
-        <v>6.74</v>
+        <v>3.16</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF203">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG203">
         <v>0</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40067,13 +40067,13 @@
         <v>694</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40112,10 +40112,10 @@
         <v>0</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG204">
         <v>0</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -40398,7 +40398,7 @@
         <v>105</v>
       </c>
       <c r="C206" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D206" t="s">
         <v>185</v>
@@ -40768,7 +40768,7 @@
         <v>106</v>
       </c>
       <c r="C208" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D208" t="s">
         <v>185</v>
@@ -41180,10 +41180,10 @@
         <v>1.57</v>
       </c>
       <c r="Q210">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R210">
-        <v>4.75</v>
+        <v>5.53</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q211">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R211">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41407,10 +41407,10 @@
         <v>0</v>
       </c>
       <c r="AE211">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF211">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG211">
         <v>0</v>
@@ -41547,13 +41547,13 @@
         <v>694</v>
       </c>
       <c r="P212">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q212">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R212">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41592,10 +41592,10 @@
         <v>0</v>
       </c>
       <c r="AE212">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF212">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG212">
         <v>0</v>
@@ -41878,7 +41878,7 @@
         <v>109</v>
       </c>
       <c r="C214" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D214" t="s">
         <v>185</v>
@@ -41917,13 +41917,13 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q214">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R214">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41962,10 +41962,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF214">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42102,55 +42102,55 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q215">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R215">
+        <v>3.5</v>
+      </c>
+      <c r="S215">
+        <v>0</v>
+      </c>
+      <c r="T215">
+        <v>0</v>
+      </c>
+      <c r="U215">
+        <v>0</v>
+      </c>
+      <c r="V215">
+        <v>0</v>
+      </c>
+      <c r="W215">
+        <v>0</v>
+      </c>
+      <c r="X215">
+        <v>0</v>
+      </c>
+      <c r="Y215">
+        <v>0</v>
+      </c>
+      <c r="Z215">
+        <v>0</v>
+      </c>
+      <c r="AA215">
+        <v>0</v>
+      </c>
+      <c r="AB215">
+        <v>0</v>
+      </c>
+      <c r="AC215">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>0</v>
+      </c>
+      <c r="AE215">
+        <v>1.55</v>
+      </c>
+      <c r="AF215">
         <v>2.25</v>
-      </c>
-      <c r="S215">
-        <v>0</v>
-      </c>
-      <c r="T215">
-        <v>0</v>
-      </c>
-      <c r="U215">
-        <v>0</v>
-      </c>
-      <c r="V215">
-        <v>0</v>
-      </c>
-      <c r="W215">
-        <v>0</v>
-      </c>
-      <c r="X215">
-        <v>0</v>
-      </c>
-      <c r="Y215">
-        <v>0</v>
-      </c>
-      <c r="Z215">
-        <v>0</v>
-      </c>
-      <c r="AA215">
-        <v>0</v>
-      </c>
-      <c r="AB215">
-        <v>0</v>
-      </c>
-      <c r="AC215">
-        <v>0</v>
-      </c>
-      <c r="AD215">
-        <v>0</v>
-      </c>
-      <c r="AE215">
-        <v>1.98</v>
-      </c>
-      <c r="AF215">
-        <v>1.75</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q216">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R216">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AF216">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42657,13 +42657,13 @@
         <v>694</v>
       </c>
       <c r="P218">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q218">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R218">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42702,10 +42702,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -43173,7 +43173,7 @@
         <v>110</v>
       </c>
       <c r="C221" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D221" t="s">
         <v>186</v>
@@ -43358,10 +43358,10 @@
         <v>110</v>
       </c>
       <c r="C222" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D222" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E222" t="s">
         <v>408</v>
@@ -43543,7 +43543,7 @@
         <v>110</v>
       </c>
       <c r="C223" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D223" t="s">
         <v>186</v>
@@ -43728,7 +43728,7 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43913,10 +43913,10 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="D225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -44098,10 +44098,10 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D226" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44137,13 +44137,13 @@
         <v>694</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44653,7 +44653,7 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44838,7 +44838,7 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D230" t="s">
         <v>186</v>
@@ -45393,7 +45393,7 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D233" t="s">
         <v>186</v>
@@ -45763,7 +45763,7 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D235" t="s">
         <v>186</v>
@@ -45948,7 +45948,7 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -45987,13 +45987,13 @@
         <v>694</v>
       </c>
       <c r="P236">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q236">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R236">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S236">
         <v>0</v>
@@ -46133,10 +46133,10 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D237" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -46318,7 +46318,7 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D238" t="s">
         <v>185</v>
@@ -46357,13 +46357,13 @@
         <v>694</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46402,10 +46402,10 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG238">
         <v>0</v>
@@ -46503,7 +46503,7 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D239" t="s">
         <v>186</v>
@@ -46688,7 +46688,7 @@
         <v>110</v>
       </c>
       <c r="C240" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D240" t="s">
         <v>186</v>
@@ -46873,10 +46873,10 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D241" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E241" t="s">
         <v>427</v>
@@ -47058,10 +47058,10 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D242" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E242" t="s">
         <v>428</v>
@@ -47097,13 +47097,13 @@
         <v>694</v>
       </c>
       <c r="P242">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q242">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R242">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S242">
         <v>0</v>
@@ -47142,10 +47142,10 @@
         <v>0</v>
       </c>
       <c r="AE242">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF242">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG242">
         <v>0</v>
@@ -47243,7 +47243,7 @@
         <v>110</v>
       </c>
       <c r="C243" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D243" t="s">
         <v>186</v>
@@ -47428,7 +47428,7 @@
         <v>111</v>
       </c>
       <c r="C244" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -48577,13 +48577,13 @@
         <v>694</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -48762,13 +48762,13 @@
         <v>694</v>
       </c>
       <c r="P251">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q251">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R251">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -48947,13 +48947,13 @@
         <v>694</v>
       </c>
       <c r="P252">
-        <v>2.95</v>
+        <v>1.46</v>
       </c>
       <c r="Q252">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R252">
-        <v>2.2</v>
+        <v>5.15</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -48998,10 +48998,10 @@
         <v>0</v>
       </c>
       <c r="AG252">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH252">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>1.46</v>
+        <v>2.95</v>
       </c>
       <c r="Q253">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R253">
-        <v>5.15</v>
+        <v>2.2</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49183,10 +49183,10 @@
         <v>0</v>
       </c>
       <c r="AG253">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH253">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI253">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,15 +370,15 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>Australia A-League</t>
   </si>
   <si>
@@ -388,114 +388,114 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
+    <t>Lithuania A Lyga</t>
+  </si>
+  <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
-    <t>Lithuania A Lyga</t>
-  </si>
-  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
     <t>India Indian Super League</t>
   </si>
   <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
+    <t>Austria Bundesliga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -532,24 +532,24 @@
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>Portugal LigaPro</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -580,18 +580,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>Auckland</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
@@ -622,60 +622,60 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
     <t>Phu Dong</t>
   </si>
   <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
     <t>Zhetysu</t>
   </si>
   <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
     <t>Oddevold</t>
   </si>
   <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
+    <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Cibalia</t>
   </si>
   <si>
-    <t>Hegelmann Litauen</t>
-  </si>
-  <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
@@ -685,66 +685,66 @@
     <t>Goa</t>
   </si>
   <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
   </si>
   <si>
     <t>Adama Kenema</t>
   </si>
   <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,16 +754,40 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Norrby</t>
   </si>
   <si>
     <t>Västerås SK</t>
@@ -772,177 +796,156 @@
     <t>Bravo</t>
   </si>
   <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
     <t>Växjö</t>
   </si>
   <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
   </si>
   <si>
     <t>Zulte-Waregem</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
     <t>Albacete Balompié</t>
   </si>
   <si>
+    <t>Burgos CF</t>
+  </si>
+  <si>
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
-    <t>Tobol</t>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Omonia Aradippou</t>
   </si>
   <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
     <t>Sandviken</t>
   </si>
   <si>
     <t>Dugopolje</t>
   </si>
   <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Sumqayıt</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
+    <t>Železničar Pančevo</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
@@ -952,193 +955,193 @@
     <t>Lazio</t>
   </si>
   <si>
-    <t>Winterthur</t>
+    <t>Beerschot-Wilrijk</t>
   </si>
   <si>
     <t>Al Najma</t>
   </si>
   <si>
-    <t>Beerschot-Wilrijk</t>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
   </si>
   <si>
     <t>Real Valladolid</t>
   </si>
   <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
     <t>Atromitos</t>
   </si>
   <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
     <t>Göztepe</t>
   </si>
   <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
-    <t>Orléans</t>
+    <t>Le Puy F.43 Auvergne</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
     <t>Caen</t>
   </si>
   <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Rouen</t>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Annecy</t>
   </si>
   <si>
     <t>Clermont</t>
   </si>
   <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Red Star</t>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
   </si>
   <si>
     <t>Nancy</t>
   </si>
   <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Acassuso</t>
   </si>
   <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
     <t>Nürnberg</t>
   </si>
   <si>
-    <t>Técnico Universitario</t>
+    <t>Club Brugge</t>
   </si>
   <si>
     <t>Lecce</t>
   </si>
   <si>
-    <t>Club Brugge</t>
+    <t>CD Mafra</t>
   </si>
   <si>
     <t>Real Sociedad</t>
@@ -1147,33 +1150,30 @@
     <t>Motherwell</t>
   </si>
   <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
     <t>Coritiba</t>
   </si>
   <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
@@ -1207,13 +1207,25 @@
     <t>Louisville City</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
   </si>
   <si>
     <t>Real Tomayapo</t>
@@ -1222,90 +1234,78 @@
     <t>Charlotte</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>CRB</t>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
   </si>
   <si>
     <t>CD Feirense</t>
   </si>
   <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Bahia</t>
   </si>
   <si>
     <t>Lusitania Lourosa</t>
   </si>
   <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Bahia</t>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
   </si>
   <si>
     <t>Sporting CP II</t>
   </si>
   <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1330,27 +1330,27 @@
     <t>Oakland Roots</t>
   </si>
   <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Seattle Sounders</t>
+    <t>Seoul E-Land</t>
   </si>
   <si>
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>Adelaide United</t>
   </si>
   <si>
@@ -1360,12 +1360,12 @@
     <t>Gangwon</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Daegu</t>
   </si>
   <si>
@@ -1381,60 +1381,60 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
     <t>Granada W</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Hai Phong</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
     <t>Ha Noi</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Öster</t>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Sesvete</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
-  </si>
-  <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
@@ -1444,66 +1444,66 @@
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
     <t>Zlín</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Ulm</t>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
   </si>
   <si>
     <t>Shire Endaselassie</t>
   </si>
   <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,16 +1513,40 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
   </si>
   <si>
     <t>GAIS</t>
@@ -1531,177 +1555,156 @@
     <t>Radomlje</t>
   </si>
   <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
     <t>AIK Women</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
-    <t>Borussia M'gladbach</t>
-  </si>
-  <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t>Bayer Leverkusen</t>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
   </si>
   <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
+    <t>Almería</t>
+  </si>
+  <si>
     <t>RCD Espanyol</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
     <t>Orijent 1919</t>
   </si>
   <si>
-    <t>Irtysh</t>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
   </si>
   <si>
     <t>Akritas</t>
   </si>
   <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
     <t>Ljungskile</t>
   </si>
   <si>
     <t>Bijelo Brdo</t>
   </si>
   <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
     <t>Norrköping</t>
   </si>
   <si>
+    <t>Pogoń Szczecin</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
     <t>Araz</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
+    <t>Radnik Surdulica</t>
   </si>
   <si>
     <t>Aluminij</t>
   </si>
   <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
@@ -1711,193 +1714,193 @@
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
+    <t>Lommel United</t>
   </si>
   <si>
     <t>Al Hazm</t>
   </si>
   <si>
-    <t>Lommel United</t>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
+    <t>Brentford</t>
   </si>
   <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
     <t>Panaitolikos</t>
   </si>
   <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
     <t>Gaziantep FK</t>
   </si>
   <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Trakai</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
-    <t>Fleury 91</t>
+    <t>Dijon</t>
   </si>
   <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
     <t>Concarneau</t>
   </si>
   <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Versailles</t>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Rodez</t>
   </si>
   <si>
     <t>Guingamp</t>
   </si>
   <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Troyes</t>
   </si>
   <si>
     <t>Dunkerque</t>
   </si>
   <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
     <t>New York RB</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
     <t>Schalke 04</t>
   </si>
   <si>
-    <t>Delfin SC</t>
+    <t>Sint-Truiden</t>
   </si>
   <si>
     <t>Juventus</t>
   </si>
   <si>
-    <t>Sint-Truiden</t>
+    <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
     <t>Real Betis</t>
@@ -1906,33 +1909,30 @@
     <t>Hearts</t>
   </si>
   <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Internacional</t>
   </si>
   <si>
+    <t>Crown Legacy</t>
+  </si>
+  <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
@@ -1966,13 +1966,25 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Sporting JAX</t>
   </si>
   <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
   </si>
   <si>
     <t>San Antonio Bulo Bulo</t>
@@ -1981,90 +1993,78 @@
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>Operário PR</t>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Leixões</t>
   </si>
   <si>
     <t>UD Oliveirense</t>
   </si>
   <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
   </si>
   <si>
     <t>Torreense</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>North Texas</t>
   </si>
   <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2074,12 +2074,12 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>Las Vegas Lights</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
@@ -2089,13 +2089,13 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Sporting KC</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>San Diego</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2697,13 +2697,13 @@
         <v>694</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3067,13 +3067,13 @@
         <v>694</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3437,13 +3437,13 @@
         <v>694</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3768,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
         <v>185</v>
@@ -3953,7 +3953,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4323,7 +4323,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4362,13 +4362,13 @@
         <v>694</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5102,13 +5102,13 @@
         <v>694</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -5153,10 +5153,10 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI15">
         <v>0</v>
@@ -5436,7 +5436,7 @@
         <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5803,7 +5803,7 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
         <v>185</v>
@@ -5991,7 +5991,7 @@
         <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>186</v>
@@ -6728,10 +6728,10 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -7098,7 +7098,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7322,13 +7322,13 @@
         <v>694</v>
       </c>
       <c r="P27">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8396,7 +8396,7 @@
         <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -9503,7 +9503,7 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
         <v>185</v>
@@ -10097,13 +10097,13 @@
         <v>694</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10243,10 +10243,10 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10282,13 +10282,13 @@
         <v>694</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10428,10 +10428,10 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10467,13 +10467,13 @@
         <v>694</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -11171,7 +11171,7 @@
         <v>142</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11538,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11908,10 +11908,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E52" t="s">
         <v>238</v>
@@ -12093,7 +12093,7 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12132,13 +12132,13 @@
         <v>694</v>
       </c>
       <c r="P53">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -12278,10 +12278,10 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,10 +12648,10 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
         <v>242</v>
@@ -13391,7 +13391,7 @@
         <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E60" t="s">
         <v>246</v>
@@ -13427,13 +13427,13 @@
         <v>694</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13573,7 +13573,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D61" t="s">
         <v>186</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13758,7 +13758,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D62" t="s">
         <v>186</v>
@@ -13946,7 +13946,7 @@
         <v>147</v>
       </c>
       <c r="D63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E63" t="s">
         <v>249</v>
@@ -13982,13 +13982,13 @@
         <v>694</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14128,7 +14128,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
         <v>185</v>
@@ -14167,13 +14167,13 @@
         <v>694</v>
       </c>
       <c r="P64">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14313,10 +14313,10 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14498,7 +14498,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14868,10 +14868,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -15053,7 +15053,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15277,13 +15277,13 @@
         <v>694</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D71" t="s">
         <v>185</v>
@@ -15462,13 +15462,13 @@
         <v>694</v>
       </c>
       <c r="P71">
-        <v>3.26</v>
+        <v>2.65</v>
       </c>
       <c r="Q71">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R71">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15608,7 +15608,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D72" t="s">
         <v>185</v>
@@ -15647,13 +15647,13 @@
         <v>694</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15793,10 +15793,10 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15832,13 +15832,13 @@
         <v>694</v>
       </c>
       <c r="P73">
-        <v>2.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q73">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="R73">
-        <v>2.46</v>
+        <v>5.16</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15978,10 +15978,10 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16387,13 +16387,13 @@
         <v>694</v>
       </c>
       <c r="P76">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q76">
-        <v>4.88</v>
+        <v>4.16</v>
       </c>
       <c r="R76">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16438,10 +16438,10 @@
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH76">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16942,13 +16942,13 @@
         <v>694</v>
       </c>
       <c r="P79">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q79">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R79">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16993,10 +16993,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH79">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -17088,7 +17088,7 @@
         <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D80" t="s">
         <v>186</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="Q80">
-        <v>4.13</v>
+        <v>3.86</v>
       </c>
       <c r="R80">
-        <v>4.85</v>
+        <v>2.92</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17273,10 +17273,10 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E81" t="s">
         <v>267</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17497,13 +17497,13 @@
         <v>694</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17542,10 +17542,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -18198,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q86">
-        <v>3.46</v>
+        <v>4.15</v>
       </c>
       <c r="R86">
-        <v>2.42</v>
+        <v>5.06</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18282,10 +18282,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AF86">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18792,13 +18792,13 @@
         <v>694</v>
       </c>
       <c r="P89">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="Q89">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="R89">
-        <v>2.43</v>
+        <v>3.32</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18837,10 +18837,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="D90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19022,10 +19022,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19207,10 +19207,10 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF91">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -19347,13 +19347,13 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>2.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q92">
-        <v>3.86</v>
+        <v>5.48</v>
       </c>
       <c r="R92">
-        <v>2.92</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19493,7 +19493,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>4.06</v>
+        <v>2.78</v>
       </c>
       <c r="Q93">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="R93">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Q95">
-        <v>5.48</v>
+        <v>4.13</v>
       </c>
       <c r="R95">
-        <v>8.300000000000001</v>
+        <v>4.85</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20973,10 +20973,10 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="D101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21158,7 +21158,7 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21343,7 +21343,7 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q103">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R103">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>8.01</v>
+        <v>2.7</v>
       </c>
       <c r="Q104">
-        <v>5.01</v>
+        <v>3.22</v>
       </c>
       <c r="R104">
-        <v>1.27</v>
+        <v>2.56</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21612,10 +21612,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>2.4</v>
+        <v>8.01</v>
       </c>
       <c r="Q106">
-        <v>3.25</v>
+        <v>5.01</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22083,7 +22083,7 @@
         <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D107" t="s">
         <v>186</v>
@@ -22122,13 +22122,13 @@
         <v>694</v>
       </c>
       <c r="P107">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q107">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R107">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22268,7 +22268,7 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22352,10 +22352,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22453,10 +22453,10 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E109" t="s">
         <v>295</v>
@@ -22492,13 +22492,13 @@
         <v>694</v>
       </c>
       <c r="P109">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q109">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R109">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22537,10 +22537,10 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E110" t="s">
         <v>296</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22823,7 +22823,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23232,13 +23232,13 @@
         <v>694</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -23972,13 +23972,13 @@
         <v>694</v>
       </c>
       <c r="P117">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R117">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24157,13 +24157,13 @@
         <v>694</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24712,13 +24712,13 @@
         <v>694</v>
       </c>
       <c r="P121">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24897,13 +24897,13 @@
         <v>694</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25413,7 +25413,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25452,13 +25452,13 @@
         <v>694</v>
       </c>
       <c r="P125">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25637,13 +25637,13 @@
         <v>694</v>
       </c>
       <c r="P126">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="Q126">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="R126">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25783,7 +25783,7 @@
         <v>90</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25968,7 +25968,7 @@
         <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26338,7 +26338,7 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26377,13 +26377,13 @@
         <v>694</v>
       </c>
       <c r="P130">
-        <v>1.93</v>
+        <v>5.74</v>
       </c>
       <c r="Q130">
-        <v>3.33</v>
+        <v>5.53</v>
       </c>
       <c r="R130">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26708,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26747,13 +26747,13 @@
         <v>694</v>
       </c>
       <c r="P132">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26893,10 +26893,10 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D133" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E133" t="s">
         <v>319</v>
@@ -27078,10 +27078,10 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E134" t="s">
         <v>320</v>
@@ -27117,13 +27117,13 @@
         <v>694</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27263,7 +27263,7 @@
         <v>92</v>
       </c>
       <c r="C135" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27633,10 +27633,10 @@
         <v>93</v>
       </c>
       <c r="C137" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27672,13 +27672,13 @@
         <v>694</v>
       </c>
       <c r="P137">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q137">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R137">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27723,10 +27723,10 @@
         <v>0</v>
       </c>
       <c r="AG137">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH137">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI137">
         <v>0</v>
@@ -28743,10 +28743,10 @@
         <v>93</v>
       </c>
       <c r="C143" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D143" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E143" t="s">
         <v>329</v>
@@ -28928,7 +28928,7 @@
         <v>93</v>
       </c>
       <c r="C144" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29483,7 +29483,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="D147" t="s">
         <v>185</v>
@@ -29522,13 +29522,13 @@
         <v>694</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29573,10 +29573,10 @@
         <v>0</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH147">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI147">
         <v>0</v>
@@ -29853,7 +29853,7 @@
         <v>95</v>
       </c>
       <c r="C149" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30408,7 +30408,7 @@
         <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31557,13 +31557,13 @@
         <v>694</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S158">
         <v>0</v>
@@ -31703,7 +31703,7 @@
         <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D159" t="s">
         <v>186</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -31927,13 +31927,13 @@
         <v>694</v>
       </c>
       <c r="P160">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q160">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R160">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S160">
         <v>0</v>
@@ -32112,13 +32112,13 @@
         <v>694</v>
       </c>
       <c r="P161">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q161">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R161">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32297,13 +32297,13 @@
         <v>694</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32631,7 +32631,7 @@
         <v>172</v>
       </c>
       <c r="D164" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E164" t="s">
         <v>350</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF164">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32813,7 +32813,7 @@
         <v>96</v>
       </c>
       <c r="C165" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q165">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R165">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32998,7 +32998,7 @@
         <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33037,13 +33037,13 @@
         <v>694</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33088,10 +33088,10 @@
         <v>0</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH166">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI166">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>2.61</v>
+        <v>1.45</v>
       </c>
       <c r="Q167">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="R167">
-        <v>2.56</v>
+        <v>6</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33267,10 +33267,10 @@
         <v>0</v>
       </c>
       <c r="AE167">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF167">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG167">
         <v>0</v>
@@ -33371,7 +33371,7 @@
         <v>172</v>
       </c>
       <c r="D168" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E168" t="s">
         <v>354</v>
@@ -33553,7 +33553,7 @@
         <v>96</v>
       </c>
       <c r="C169" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q169">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R169">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33777,13 +33777,13 @@
         <v>694</v>
       </c>
       <c r="P170">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q170">
-        <v>4.7</v>
+        <v>3.68</v>
       </c>
       <c r="R170">
-        <v>6</v>
+        <v>4.61</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33923,7 +33923,7 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34108,7 +34108,7 @@
         <v>96</v>
       </c>
       <c r="C172" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>3.79</v>
+        <v>1.97</v>
       </c>
       <c r="Q172">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="R172">
-        <v>1.9</v>
+        <v>3.48</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34192,10 +34192,10 @@
         <v>0</v>
       </c>
       <c r="AE172">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF172">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>1.3</v>
+        <v>2.89</v>
       </c>
       <c r="Q173">
-        <v>5.65</v>
+        <v>3.32</v>
       </c>
       <c r="R173">
-        <v>8.4</v>
+        <v>2.38</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34377,16 +34377,16 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG173">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH173">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI173">
         <v>0</v>
@@ -34481,7 +34481,7 @@
         <v>173</v>
       </c>
       <c r="D174" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E174" t="s">
         <v>360</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34663,7 +34663,7 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34851,7 +34851,7 @@
         <v>173</v>
       </c>
       <c r="D176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -34932,10 +34932,10 @@
         <v>0</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG176">
         <v>0</v>
@@ -35033,7 +35033,7 @@
         <v>96</v>
       </c>
       <c r="C177" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D177" t="s">
         <v>186</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>2.24</v>
+        <v>2.61</v>
       </c>
       <c r="Q177">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R177">
-        <v>3.37</v>
+        <v>2.56</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35117,10 +35117,10 @@
         <v>0</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG177">
         <v>0</v>
@@ -35257,13 +35257,13 @@
         <v>694</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35302,10 +35302,10 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG178">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35442,13 +35442,13 @@
         <v>694</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q180">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R180">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35678,10 +35678,10 @@
         <v>0</v>
       </c>
       <c r="AG180">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH180">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI180">
         <v>0</v>
@@ -35773,10 +35773,10 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35958,10 +35958,10 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E182" t="s">
         <v>368</v>
@@ -36143,7 +36143,7 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D183" t="s">
         <v>185</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q183">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R183">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36227,10 +36227,10 @@
         <v>0</v>
       </c>
       <c r="AE183">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF183">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG183">
         <v>0</v>
@@ -36328,7 +36328,7 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D184" t="s">
         <v>185</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36418,10 +36418,10 @@
         <v>0</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH184">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI184">
         <v>0</v>
@@ -36513,10 +36513,10 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="D185" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E185" t="s">
         <v>371</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="Q185">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="R185">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36597,10 +36597,10 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG185">
         <v>0</v>
@@ -36698,10 +36698,10 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="D186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -36922,13 +36922,13 @@
         <v>694</v>
       </c>
       <c r="P187">
-        <v>5.93</v>
+        <v>1.48</v>
       </c>
       <c r="Q187">
-        <v>4.81</v>
+        <v>4.95</v>
       </c>
       <c r="R187">
-        <v>1.57</v>
+        <v>5.98</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37107,13 +37107,13 @@
         <v>694</v>
       </c>
       <c r="P188">
-        <v>1.48</v>
+        <v>5.93</v>
       </c>
       <c r="Q188">
-        <v>4.95</v>
+        <v>4.81</v>
       </c>
       <c r="R188">
-        <v>5.98</v>
+        <v>1.57</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37253,7 +37253,7 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37438,7 +37438,7 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37477,13 +37477,13 @@
         <v>694</v>
       </c>
       <c r="P190">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37522,10 +37522,10 @@
         <v>0</v>
       </c>
       <c r="AE190">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF190">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG190">
         <v>0</v>
@@ -37623,10 +37623,10 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D191" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37662,13 +37662,13 @@
         <v>694</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37707,10 +37707,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37808,10 +37808,10 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="D192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -37993,7 +37993,7 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38178,10 +38178,10 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38217,13 +38217,13 @@
         <v>694</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38363,7 +38363,7 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D195" t="s">
         <v>185</v>
@@ -38551,7 +38551,7 @@
         <v>177</v>
       </c>
       <c r="D196" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -40398,7 +40398,7 @@
         <v>105</v>
       </c>
       <c r="C206" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D206" t="s">
         <v>185</v>
@@ -40768,7 +40768,7 @@
         <v>106</v>
       </c>
       <c r="C208" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D208" t="s">
         <v>185</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="Q211">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R211">
-        <v>4.75</v>
+        <v>2.65</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41547,13 +41547,13 @@
         <v>694</v>
       </c>
       <c r="P212">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q212">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R212">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41592,10 +41592,10 @@
         <v>0</v>
       </c>
       <c r="AE212">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF212">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG212">
         <v>0</v>
@@ -41732,13 +41732,13 @@
         <v>694</v>
       </c>
       <c r="P213">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q213">
         <v>3.4</v>
       </c>
       <c r="R213">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -41777,10 +41777,10 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -41878,7 +41878,7 @@
         <v>109</v>
       </c>
       <c r="C214" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D214" t="s">
         <v>185</v>
@@ -41917,13 +41917,13 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41962,10 +41962,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42063,7 +42063,7 @@
         <v>109</v>
       </c>
       <c r="C215" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D215" t="s">
         <v>185</v>
@@ -42102,13 +42102,13 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q215">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="R215">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42147,10 +42147,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF215">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42248,7 +42248,7 @@
         <v>109</v>
       </c>
       <c r="C216" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q216">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R216">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF216">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q217">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R217">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42657,13 +42657,13 @@
         <v>694</v>
       </c>
       <c r="P218">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q218">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R218">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42702,10 +42702,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF218">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -42842,13 +42842,13 @@
         <v>694</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42887,10 +42887,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -43358,7 +43358,7 @@
         <v>110</v>
       </c>
       <c r="C222" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D222" t="s">
         <v>186</v>
@@ -43728,7 +43728,7 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43913,10 +43913,10 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -44098,10 +44098,10 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44137,13 +44137,13 @@
         <v>694</v>
       </c>
       <c r="P226">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q226">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R226">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S226">
         <v>0</v>
@@ -44283,10 +44283,10 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D227" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44322,13 +44322,13 @@
         <v>694</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44367,10 +44367,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44653,7 +44653,7 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44838,7 +44838,7 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D230" t="s">
         <v>186</v>
@@ -45023,7 +45023,7 @@
         <v>110</v>
       </c>
       <c r="C231" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D231" t="s">
         <v>186</v>
@@ -45208,10 +45208,10 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D232" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E232" t="s">
         <v>418</v>
@@ -45393,7 +45393,7 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D233" t="s">
         <v>186</v>
@@ -45578,7 +45578,7 @@
         <v>110</v>
       </c>
       <c r="C234" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D234" t="s">
         <v>186</v>
@@ -45948,7 +45948,7 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D236" t="s">
         <v>185</v>
@@ -46133,10 +46133,10 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D237" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -46318,7 +46318,7 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D238" t="s">
         <v>185</v>
@@ -46357,13 +46357,13 @@
         <v>694</v>
       </c>
       <c r="P238">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="Q238">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="R238">
-        <v>5.5</v>
+        <v>3.31</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46402,10 +46402,10 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF238">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG238">
         <v>0</v>
@@ -46688,7 +46688,7 @@
         <v>110</v>
       </c>
       <c r="C240" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D240" t="s">
         <v>186</v>
@@ -46873,7 +46873,7 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
         <v>186</v>
@@ -47058,10 +47058,10 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D242" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E242" t="s">
         <v>428</v>
@@ -47243,7 +47243,7 @@
         <v>110</v>
       </c>
       <c r="C243" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D243" t="s">
         <v>186</v>
@@ -47428,7 +47428,7 @@
         <v>111</v>
       </c>
       <c r="C244" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47983,7 +47983,7 @@
         <v>114</v>
       </c>
       <c r="C247" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48168,7 +48168,7 @@
         <v>114</v>
       </c>
       <c r="C248" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48947,13 +48947,13 @@
         <v>694</v>
       </c>
       <c r="P252">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q252">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R252">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -48992,16 +48992,16 @@
         <v>0</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG252">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH252">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>2.95</v>
+        <v>1.46</v>
       </c>
       <c r="Q253">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.2</v>
+        <v>5.15</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49183,10 +49183,10 @@
         <v>0</v>
       </c>
       <c r="AG253">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH253">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI253">
         <v>0</v>
@@ -49317,13 +49317,13 @@
         <v>694</v>
       </c>
       <c r="P254">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q254">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R254">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -49362,16 +49362,16 @@
         <v>0</v>
       </c>
       <c r="AE254">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF254">
+        <v>0</v>
+      </c>
+      <c r="AG254">
         <v>2.15</v>
       </c>
-      <c r="AG254">
-        <v>0</v>
-      </c>
       <c r="AH254">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI254">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,12 +370,12 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
@@ -385,108 +385,108 @@
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
+    <t>Croatia Druga HNL</t>
+  </si>
+  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Croatia Druga HNL</t>
-  </si>
-  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -532,27 +532,27 @@
     <t>Poland 1. Liga</t>
   </si>
   <si>
+    <t>France Ligue 2</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>France Ligue 2</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
     <t>Portugal Liga NOS</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -580,36 +580,36 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>Auckland</t>
   </si>
   <si>
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -622,129 +622,129 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
     <t>Espanyol W</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
     <t>Eintracht Braunschweig</t>
   </si>
   <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
     <t>Zhetysu</t>
   </si>
   <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
+    <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
-    <t>Cibalia</t>
+    <t>Young Lions</t>
   </si>
   <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
-    <t>Young Lions</t>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
   </si>
   <si>
     <t>Goa</t>
   </si>
   <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
     <t>Ceuta</t>
   </si>
   <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
     <t>Persis Solo</t>
   </si>
   <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,211 +754,223 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>Cagliari</t>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
   </si>
   <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
     <t>Norrby</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
     <t>Hoffenheim</t>
   </si>
   <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
     <t>Fulham</t>
   </si>
   <si>
-    <t>Vaprus</t>
+    <t>CD Trofense</t>
   </si>
   <si>
     <t>Aberdeen</t>
   </si>
   <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Larissa</t>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
   </si>
   <si>
     <t>Dundee</t>
   </si>
   <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion</t>
   </si>
   <si>
-    <t>RAAL La Louvière</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
+    <t>Burgos CF</t>
+  </si>
+  <si>
+    <t>Sevilla FC</t>
   </si>
   <si>
     <t>Albacete Balompié</t>
   </si>
   <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
     <t>Enosis</t>
   </si>
   <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
+    <t>Sumqayıt</t>
+  </si>
+  <si>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Koper</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
     <t>Lazio</t>
   </si>
   <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
-    <t>Al Najma</t>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Real Valladolid</t>
   </si>
   <si>
     <t>Atlético Madrid</t>
@@ -967,345 +979,333 @@
     <t>Wolfsburg</t>
   </si>
   <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
     <t>Kocaelispor</t>
   </si>
   <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
     <t>Beşiktaş</t>
   </si>
   <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
     <t>Orléans</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
     <t>Bourg-en-Bresse</t>
   </si>
   <si>
     <t>Châteauroux</t>
   </si>
   <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Znicz Pruszków</t>
   </si>
   <si>
+    <t>Caen</t>
+  </si>
+  <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
-    <t>Caen</t>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Reims</t>
   </si>
   <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
-    <t>Red Star</t>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Annecy</t>
   </si>
   <si>
     <t>Saint-Étienne</t>
   </si>
   <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
     <t>Magesi</t>
   </si>
   <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
     <t>Temperley</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>Luzern</t>
   </si>
   <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
     <t>Club Brugge</t>
   </si>
   <si>
     <t>Lecce</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>CD Mafra</t>
   </si>
   <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
     <t>Málaga CF</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
+    <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
+    <t>SD Aucas</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>SD Aucas</t>
-  </si>
-  <si>
     <t>Ceará</t>
   </si>
   <si>
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Louisville City</t>
   </si>
   <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
   </si>
   <si>
     <t>FC Penafiel</t>
   </si>
   <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
     <t>Farense</t>
   </si>
   <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
     <t>CD Tondela</t>
   </si>
   <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1330,45 +1330,45 @@
     <t>Oakland Roots</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>Adelaide United</t>
   </si>
   <si>
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1381,129 +1381,129 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
     <t>Badalona W</t>
   </si>
   <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
     <t>Granada W</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
     <t>Magdeburg</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
+    <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Sesvete</t>
+    <t>Geylang International</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
-    <t>Geylang International</t>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
   </si>
   <si>
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
     <t>CD Castellón</t>
   </si>
   <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,211 +1513,223 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Udinese</t>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
   </si>
   <si>
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
     <t>Bayer Leverkusen</t>
   </si>
   <si>
-    <t>Borussia M'gladbach</t>
-  </si>
-  <si>
     <t>St. Pauli</t>
   </si>
   <si>
     <t>Werder Bremen</t>
   </si>
   <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
     <t>AFC Bournemouth</t>
   </si>
   <si>
-    <t>Trans</t>
+    <t>Vitória Guimarães II</t>
   </si>
   <si>
     <t>Dundee United</t>
   </si>
   <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
   </si>
   <si>
     <t>Livingston</t>
   </si>
   <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
     <t>Wolverhampton Wanderers</t>
   </si>
   <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
+    <t>Almería</t>
+  </si>
+  <si>
+    <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
     <t>Irtysh</t>
   </si>
   <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
     <t>Ethnikos Achna</t>
   </si>
   <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
+    <t>Araz</t>
+  </si>
+  <si>
+    <t>Aluminij</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Pogoń Szczecin</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
     <t>Siwelele</t>
   </si>
   <si>
-    <t>Araz</t>
-  </si>
-  <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>Deportivo de La Coruña W</t>
-  </si>
-  <si>
     <t>Inter Milan</t>
   </si>
   <si>
+    <t>Al Hazm</t>
+  </si>
+  <si>
     <t>Lommel United</t>
   </si>
   <si>
-    <t>Al Hazm</t>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Real Zaragoza</t>
   </si>
   <si>
     <t>Celta de Vigo</t>
@@ -1726,345 +1738,333 @@
     <t>Bayern München</t>
   </si>
   <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
     <t>Trabzonspor</t>
   </si>
   <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
     <t>Trakai</t>
   </si>
   <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
     <t>Fleury 91</t>
   </si>
   <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
     <t>Valenciennes</t>
   </si>
   <si>
     <t>Sochaux</t>
   </si>
   <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Concarneau</t>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Pau</t>
   </si>
   <si>
     <t>Los Andes</t>
   </si>
   <si>
-    <t>Montpellier</t>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Rodez</t>
   </si>
   <si>
     <t>Amiens SC</t>
   </si>
   <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
+    <t>New York RB</t>
+  </si>
+  <si>
     <t>Servette</t>
   </si>
   <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
     <t>Juventus</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Real Betis</t>
   </si>
   <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Sporting Gijón</t>
   </si>
   <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Internacional</t>
+    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
+    <t>CD Universidad Católica</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>CD Universidad Católica</t>
-  </si>
-  <si>
     <t>Atlético GO</t>
   </si>
   <si>
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
   </si>
   <si>
     <t>CS Marítimo</t>
   </si>
   <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
     <t>Paços de Ferreira</t>
   </si>
   <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
     <t>Moreirense FC</t>
   </si>
   <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2089,10 +2089,10 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>San Diego</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
@@ -2697,13 +2697,13 @@
         <v>694</v>
       </c>
       <c r="P2">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         <v>694</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -2927,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3067,13 +3067,13 @@
         <v>694</v>
       </c>
       <c r="P4">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
         <v>185</v>
@@ -3252,13 +3252,13 @@
         <v>694</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -3297,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -3768,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>185</v>
@@ -3992,13 +3992,13 @@
         <v>694</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4362,13 +4362,13 @@
         <v>694</v>
       </c>
       <c r="P11">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -5433,10 +5433,10 @@
         <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5618,10 +5618,10 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E18" t="s">
         <v>204</v>
@@ -5803,10 +5803,10 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5991,7 +5991,7 @@
         <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6361,7 +6361,7 @@
         <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E22" t="s">
         <v>208</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q22">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="R22">
-        <v>2.38</v>
+        <v>3.58</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6582,13 +6582,13 @@
         <v>694</v>
       </c>
       <c r="P23">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6627,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG23">
         <v>0</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -6952,13 +6952,13 @@
         <v>694</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -7101,7 +7101,7 @@
         <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.86</v>
+        <v>2.27</v>
       </c>
       <c r="Q26">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R26">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7468,10 +7468,10 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -7507,13 +7507,13 @@
         <v>694</v>
       </c>
       <c r="P28">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -7653,7 +7653,7 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
         <v>186</v>
@@ -7692,13 +7692,13 @@
         <v>694</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7838,7 +7838,7 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
         <v>186</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7922,10 +7922,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -8023,7 +8023,7 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
         <v>185</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8396,7 +8396,7 @@
         <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8987,13 +8987,13 @@
         <v>694</v>
       </c>
       <c r="P36">
-        <v>3.59</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>3.25</v>
+        <v>4.17</v>
       </c>
       <c r="R36">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -9357,14 +9357,14 @@
         <v>694</v>
       </c>
       <c r="P38">
+        <v>3.59</v>
+      </c>
+      <c r="Q38">
+        <v>3.25</v>
+      </c>
+      <c r="R38">
         <v>1.95</v>
       </c>
-      <c r="Q38">
-        <v>4.17</v>
-      </c>
-      <c r="R38">
-        <v>3.8</v>
-      </c>
       <c r="S38">
         <v>0</v>
       </c>
@@ -9402,10 +9402,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -9503,7 +9503,7 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
         <v>185</v>
@@ -9688,7 +9688,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
         <v>185</v>
@@ -10061,7 +10061,7 @@
         <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E42" t="s">
         <v>228</v>
@@ -10097,13 +10097,13 @@
         <v>694</v>
       </c>
       <c r="P42">
-        <v>3.79</v>
+        <v>1.96</v>
       </c>
       <c r="Q42">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="R42">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10243,7 +10243,7 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10428,10 +10428,10 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10467,13 +10467,13 @@
         <v>694</v>
       </c>
       <c r="P44">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10798,7 +10798,7 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
         <v>186</v>
@@ -10983,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
@@ -11168,10 +11168,10 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11207,13 +11207,13 @@
         <v>694</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11538,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11723,10 +11723,10 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -12093,10 +12093,10 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12278,10 +12278,10 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -13391,7 +13391,7 @@
         <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E60" t="s">
         <v>246</v>
@@ -13427,13 +13427,13 @@
         <v>694</v>
       </c>
       <c r="P60">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="Q60">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="R60">
-        <v>1.85</v>
+        <v>3.21</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13758,10 +13758,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13797,13 +13797,13 @@
         <v>694</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
         <v>185</v>
@@ -14128,10 +14128,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14313,10 +14313,10 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14498,7 +14498,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14868,10 +14868,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -15053,7 +15053,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15277,13 +15277,13 @@
         <v>694</v>
       </c>
       <c r="P70">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="Q70">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R70">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
         <v>185</v>
@@ -15462,13 +15462,13 @@
         <v>694</v>
       </c>
       <c r="P71">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15608,10 +15608,10 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D72" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E72" t="s">
         <v>258</v>
@@ -15647,13 +15647,13 @@
         <v>694</v>
       </c>
       <c r="P72">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15793,7 +15793,7 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
@@ -15832,13 +15832,13 @@
         <v>694</v>
       </c>
       <c r="P73">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15978,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>185</v>
@@ -16017,13 +16017,13 @@
         <v>694</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16387,13 +16387,13 @@
         <v>694</v>
       </c>
       <c r="P76">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q76">
-        <v>4.16</v>
+        <v>3.71</v>
       </c>
       <c r="R76">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16432,16 +16432,16 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG76">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH76">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16572,13 +16572,13 @@
         <v>694</v>
       </c>
       <c r="P77">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q77">
-        <v>3.71</v>
+        <v>4.16</v>
       </c>
       <c r="R77">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16617,16 +16617,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -17088,7 +17088,7 @@
         <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D80" t="s">
         <v>186</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17273,10 +17273,10 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D81" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E81" t="s">
         <v>267</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17497,10 +17497,10 @@
         <v>694</v>
       </c>
       <c r="P82">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="Q82">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="R82">
         <v>3.11</v>
@@ -17542,10 +17542,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,10 +18013,10 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18198,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q86">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="R86">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18282,10 +18282,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>4.06</v>
+        <v>2.41</v>
       </c>
       <c r="Q87">
-        <v>3.98</v>
+        <v>3.86</v>
       </c>
       <c r="R87">
-        <v>1.93</v>
+        <v>2.92</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18792,13 +18792,13 @@
         <v>694</v>
       </c>
       <c r="P89">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="Q89">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R89">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18837,10 +18837,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AF89">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19022,10 +19022,10 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19347,13 +19347,13 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>1.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q92">
-        <v>5.48</v>
+        <v>3.61</v>
       </c>
       <c r="R92">
-        <v>8.300000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19493,7 +19493,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>2.78</v>
+        <v>4.06</v>
       </c>
       <c r="Q93">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="R93">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19717,13 +19717,13 @@
         <v>694</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19762,10 +19762,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="Q95">
-        <v>4.13</v>
+        <v>5.48</v>
       </c>
       <c r="R95">
-        <v>4.85</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q96">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R96">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20502,10 +20502,10 @@
         <v>0</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -20603,7 +20603,7 @@
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20973,10 +20973,10 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>2.24</v>
+        <v>3.87</v>
       </c>
       <c r="Q101">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R101">
-        <v>3.02</v>
+        <v>1.81</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21158,7 +21158,7 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21343,10 +21343,10 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R103">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q104">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="R104">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21612,10 +21612,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AF104">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21797,10 +21797,10 @@
         <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG105">
         <v>0</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>8.01</v>
+        <v>2.4</v>
       </c>
       <c r="Q106">
-        <v>5.01</v>
+        <v>3.25</v>
       </c>
       <c r="R106">
-        <v>1.27</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22083,7 +22083,7 @@
         <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="D107" t="s">
         <v>186</v>
@@ -22122,13 +22122,13 @@
         <v>694</v>
       </c>
       <c r="P107">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22268,7 +22268,7 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22492,13 +22492,13 @@
         <v>694</v>
       </c>
       <c r="P109">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="Q109">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="R109">
-        <v>4.4</v>
+        <v>3.27</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22537,10 +22537,10 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AF109">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E110" t="s">
         <v>296</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22823,10 +22823,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -23008,10 +23008,10 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E112" t="s">
         <v>298</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>3.87</v>
+        <v>8.01</v>
       </c>
       <c r="Q112">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="R112">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23232,13 +23232,13 @@
         <v>694</v>
       </c>
       <c r="P113">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R113">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23417,13 +23417,13 @@
         <v>694</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23787,13 +23787,13 @@
         <v>694</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24157,13 +24157,13 @@
         <v>694</v>
       </c>
       <c r="P118">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24673,7 +24673,7 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="D121" t="s">
         <v>186</v>
@@ -24858,7 +24858,7 @@
         <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D122" t="s">
         <v>186</v>
@@ -24897,13 +24897,13 @@
         <v>694</v>
       </c>
       <c r="P122">
-        <v>3.78</v>
+        <v>2.24</v>
       </c>
       <c r="Q122">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R122">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>2.24</v>
+        <v>3.78</v>
       </c>
       <c r="Q123">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R123">
-        <v>2.86</v>
+        <v>1.8</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25413,7 +25413,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25783,7 +25783,7 @@
         <v>90</v>
       </c>
       <c r="C127" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25968,7 +25968,7 @@
         <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26192,13 +26192,13 @@
         <v>694</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26338,10 +26338,10 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D130" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26377,13 +26377,13 @@
         <v>694</v>
       </c>
       <c r="P130">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26523,7 +26523,7 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26708,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26893,10 +26893,10 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E133" t="s">
         <v>319</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27117,13 +27117,13 @@
         <v>694</v>
       </c>
       <c r="P134">
-        <v>1.93</v>
+        <v>5.74</v>
       </c>
       <c r="Q134">
-        <v>3.33</v>
+        <v>5.53</v>
       </c>
       <c r="R134">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -28743,7 +28743,7 @@
         <v>93</v>
       </c>
       <c r="C143" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="D143" t="s">
         <v>185</v>
@@ -28782,13 +28782,13 @@
         <v>694</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S143">
         <v>0</v>
@@ -28833,10 +28833,10 @@
         <v>0</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH143">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI143">
         <v>0</v>
@@ -28928,7 +28928,7 @@
         <v>93</v>
       </c>
       <c r="C144" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29483,7 +29483,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="D147" t="s">
         <v>185</v>
@@ -29522,13 +29522,13 @@
         <v>694</v>
       </c>
       <c r="P147">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q147">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R147">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S147">
         <v>0</v>
@@ -29573,10 +29573,10 @@
         <v>0</v>
       </c>
       <c r="AG147">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH147">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI147">
         <v>0</v>
@@ -29853,7 +29853,7 @@
         <v>95</v>
       </c>
       <c r="C149" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -30038,7 +30038,7 @@
         <v>95</v>
       </c>
       <c r="C150" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30778,7 +30778,7 @@
         <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30817,13 +30817,13 @@
         <v>694</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S154">
         <v>0</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31557,13 +31557,13 @@
         <v>694</v>
       </c>
       <c r="P158">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q158">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R158">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S158">
         <v>0</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32297,13 +32297,13 @@
         <v>694</v>
       </c>
       <c r="P162">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q162">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R162">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>95</v>
       </c>
       <c r="C163" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32482,13 +32482,13 @@
         <v>694</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32631,7 +32631,7 @@
         <v>172</v>
       </c>
       <c r="D164" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E164" t="s">
         <v>350</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32816,7 +32816,7 @@
         <v>173</v>
       </c>
       <c r="D165" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E165" t="s">
         <v>351</v>
@@ -32998,7 +32998,7 @@
         <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33037,13 +33037,13 @@
         <v>694</v>
       </c>
       <c r="P166">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q166">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R166">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33088,10 +33088,10 @@
         <v>0</v>
       </c>
       <c r="AG166">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH166">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI166">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q167">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R167">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33371,7 +33371,7 @@
         <v>172</v>
       </c>
       <c r="D168" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E168" t="s">
         <v>354</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33452,10 +33452,10 @@
         <v>0</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG168">
         <v>0</v>
@@ -33553,7 +33553,7 @@
         <v>96</v>
       </c>
       <c r="C169" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33637,10 +33637,10 @@
         <v>0</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33923,7 +33923,7 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q171">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="R171">
-        <v>3.37</v>
+        <v>6</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34111,7 +34111,7 @@
         <v>173</v>
       </c>
       <c r="D172" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E172" t="s">
         <v>358</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q172">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R172">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>2.89</v>
+        <v>3.03</v>
       </c>
       <c r="Q173">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="R173">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF173">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>3.03</v>
+        <v>1.97</v>
       </c>
       <c r="Q174">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="R174">
-        <v>2.31</v>
+        <v>3.48</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34663,7 +34663,7 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34753,10 +34753,10 @@
         <v>0</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH175">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI175">
         <v>0</v>
@@ -34848,7 +34848,7 @@
         <v>96</v>
       </c>
       <c r="C176" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>3.79</v>
+        <v>2.24</v>
       </c>
       <c r="Q176">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R176">
-        <v>1.9</v>
+        <v>3.37</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -34932,10 +34932,10 @@
         <v>0</v>
       </c>
       <c r="AE176">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF176">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG176">
         <v>0</v>
@@ -35033,7 +35033,7 @@
         <v>96</v>
       </c>
       <c r="C177" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D177" t="s">
         <v>186</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q177">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R177">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35117,10 +35117,10 @@
         <v>0</v>
       </c>
       <c r="AE177">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF177">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG177">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35672,10 +35672,10 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -35773,10 +35773,10 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q181">
-        <v>3.76</v>
+        <v>3.02</v>
       </c>
       <c r="R181">
-        <v>2.92</v>
+        <v>3.53</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35958,7 +35958,7 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D182" t="s">
         <v>185</v>
@@ -36143,10 +36143,10 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="D183" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E183" t="s">
         <v>369</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36328,7 +36328,7 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D184" t="s">
         <v>185</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q184">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36418,10 +36418,10 @@
         <v>0</v>
       </c>
       <c r="AG184">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH184">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI184">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D185" t="s">
         <v>185</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>2.82</v>
+        <v>1.65</v>
       </c>
       <c r="Q185">
-        <v>2.55</v>
+        <v>4.52</v>
       </c>
       <c r="R185">
-        <v>2.75</v>
+        <v>4.89</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36597,16 +36597,16 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF185">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH185">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI185">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="D186" t="s">
         <v>186</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="Q186">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="R186">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37253,10 +37253,10 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="D189" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -37438,10 +37438,10 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="D190" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E190" t="s">
         <v>376</v>
@@ -37623,7 +37623,7 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37662,13 +37662,13 @@
         <v>694</v>
       </c>
       <c r="P191">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q191">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37707,10 +37707,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37808,7 +37808,7 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D192" t="s">
         <v>185</v>
@@ -37847,13 +37847,13 @@
         <v>694</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -37993,10 +37993,10 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D193" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38178,7 +38178,7 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D194" t="s">
         <v>186</v>
@@ -38217,13 +38217,13 @@
         <v>694</v>
       </c>
       <c r="P194">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="Q194">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="R194">
-        <v>3.71</v>
+        <v>2.6</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38262,10 +38262,10 @@
         <v>0</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG194">
         <v>0</v>
@@ -38363,10 +38363,10 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D195" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38548,10 +38548,10 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="D196" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38733,10 +38733,10 @@
         <v>100</v>
       </c>
       <c r="C197" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="D197" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38772,13 +38772,13 @@
         <v>694</v>
       </c>
       <c r="P197">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="Q197">
-        <v>3.17</v>
+        <v>3.73</v>
       </c>
       <c r="R197">
-        <v>3.15</v>
+        <v>3.71</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -39512,13 +39512,13 @@
         <v>694</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39557,10 +39557,10 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>103</v>
       </c>
       <c r="C202" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40067,13 +40067,13 @@
         <v>694</v>
       </c>
       <c r="P204">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q204">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40112,10 +40112,10 @@
         <v>0</v>
       </c>
       <c r="AE204">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF204">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG204">
         <v>0</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -40398,7 +40398,7 @@
         <v>105</v>
       </c>
       <c r="C206" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D206" t="s">
         <v>185</v>
@@ -40583,7 +40583,7 @@
         <v>105</v>
       </c>
       <c r="C207" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D207" t="s">
         <v>185</v>
@@ -40768,7 +40768,7 @@
         <v>106</v>
       </c>
       <c r="C208" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D208" t="s">
         <v>185</v>
@@ -41180,10 +41180,10 @@
         <v>1.57</v>
       </c>
       <c r="Q210">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R210">
-        <v>5.53</v>
+        <v>4.75</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q211">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R211">
-        <v>2.65</v>
+        <v>5.53</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41547,13 +41547,13 @@
         <v>694</v>
       </c>
       <c r="P212">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="Q212">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R212">
-        <v>4.75</v>
+        <v>2.65</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41917,13 +41917,13 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q214">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="R214">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41962,10 +41962,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AF214">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42063,7 +42063,7 @@
         <v>109</v>
       </c>
       <c r="C215" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D215" t="s">
         <v>185</v>
@@ -42102,13 +42102,13 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q215">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R215">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42147,10 +42147,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42248,7 +42248,7 @@
         <v>109</v>
       </c>
       <c r="C216" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q217">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R217">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF217">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42842,13 +42842,13 @@
         <v>694</v>
       </c>
       <c r="P219">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q219">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="R219">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42887,10 +42887,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AF219">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -42988,10 +42988,10 @@
         <v>110</v>
       </c>
       <c r="C220" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D220" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43027,13 +43027,13 @@
         <v>694</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43072,10 +43072,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43173,10 +43173,10 @@
         <v>110</v>
       </c>
       <c r="C221" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D221" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43358,7 +43358,7 @@
         <v>110</v>
       </c>
       <c r="C222" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D222" t="s">
         <v>186</v>
@@ -43728,7 +43728,7 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43913,10 +43913,10 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -43952,13 +43952,13 @@
         <v>694</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44098,7 +44098,7 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44283,7 +44283,7 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D227" t="s">
         <v>185</v>
@@ -44322,13 +44322,13 @@
         <v>694</v>
       </c>
       <c r="P227">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q227">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R227">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44367,10 +44367,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF227">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44838,10 +44838,10 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D230" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E230" t="s">
         <v>416</v>
@@ -45208,10 +45208,10 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D232" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E232" t="s">
         <v>418</v>
@@ -45393,7 +45393,7 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D233" t="s">
         <v>186</v>
@@ -45578,7 +45578,7 @@
         <v>110</v>
       </c>
       <c r="C234" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D234" t="s">
         <v>186</v>
@@ -45763,7 +45763,7 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D235" t="s">
         <v>186</v>
@@ -45948,10 +45948,10 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D236" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E236" t="s">
         <v>422</v>
@@ -46133,7 +46133,7 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D237" t="s">
         <v>186</v>
@@ -46318,10 +46318,10 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D238" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E238" t="s">
         <v>424</v>
@@ -46357,13 +46357,13 @@
         <v>694</v>
       </c>
       <c r="P238">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q238">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R238">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S238">
         <v>0</v>
@@ -46503,7 +46503,7 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D239" t="s">
         <v>186</v>
@@ -46873,7 +46873,7 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D241" t="s">
         <v>186</v>
@@ -47058,10 +47058,10 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D242" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E242" t="s">
         <v>428</v>
@@ -47243,7 +47243,7 @@
         <v>110</v>
       </c>
       <c r="C243" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D243" t="s">
         <v>186</v>
@@ -47428,7 +47428,7 @@
         <v>111</v>
       </c>
       <c r="C244" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -48947,61 +48947,61 @@
         <v>694</v>
       </c>
       <c r="P252">
+        <v>1.46</v>
+      </c>
+      <c r="Q252">
+        <v>4.6</v>
+      </c>
+      <c r="R252">
+        <v>5.15</v>
+      </c>
+      <c r="S252">
+        <v>0</v>
+      </c>
+      <c r="T252">
+        <v>0</v>
+      </c>
+      <c r="U252">
+        <v>0</v>
+      </c>
+      <c r="V252">
+        <v>0</v>
+      </c>
+      <c r="W252">
+        <v>0</v>
+      </c>
+      <c r="X252">
+        <v>0</v>
+      </c>
+      <c r="Y252">
+        <v>0</v>
+      </c>
+      <c r="Z252">
+        <v>0</v>
+      </c>
+      <c r="AA252">
+        <v>0</v>
+      </c>
+      <c r="AB252">
+        <v>0</v>
+      </c>
+      <c r="AC252">
+        <v>0</v>
+      </c>
+      <c r="AD252">
+        <v>0</v>
+      </c>
+      <c r="AE252">
+        <v>0</v>
+      </c>
+      <c r="AF252">
+        <v>0</v>
+      </c>
+      <c r="AG252">
+        <v>1.95</v>
+      </c>
+      <c r="AH252">
         <v>1.75</v>
-      </c>
-      <c r="Q252">
-        <v>3.9</v>
-      </c>
-      <c r="R252">
-        <v>4.2</v>
-      </c>
-      <c r="S252">
-        <v>0</v>
-      </c>
-      <c r="T252">
-        <v>0</v>
-      </c>
-      <c r="U252">
-        <v>0</v>
-      </c>
-      <c r="V252">
-        <v>0</v>
-      </c>
-      <c r="W252">
-        <v>0</v>
-      </c>
-      <c r="X252">
-        <v>0</v>
-      </c>
-      <c r="Y252">
-        <v>0</v>
-      </c>
-      <c r="Z252">
-        <v>0</v>
-      </c>
-      <c r="AA252">
-        <v>0</v>
-      </c>
-      <c r="AB252">
-        <v>0</v>
-      </c>
-      <c r="AC252">
-        <v>0</v>
-      </c>
-      <c r="AD252">
-        <v>0</v>
-      </c>
-      <c r="AE252">
-        <v>1.61</v>
-      </c>
-      <c r="AF252">
-        <v>2.15</v>
-      </c>
-      <c r="AG252">
-        <v>0</v>
-      </c>
-      <c r="AH252">
-        <v>0</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q253">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R253">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49177,16 +49177,16 @@
         <v>0</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG253">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH253">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI253">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,15 +370,15 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>Australia A-League</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
@@ -403,24 +403,24 @@
     <t>Vietnam V.League 1</t>
   </si>
   <si>
+    <t>England FA Women's Super League</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>England FA Women's Super League</t>
+    <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
-    <t>Lithuania A Lyga</t>
+    <t>England Premier League</t>
   </si>
   <si>
     <t>Singapore S.League</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
+    <t>Spain Segunda División</t>
   </si>
   <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -457,39 +457,39 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -526,33 +526,33 @@
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>France National</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
+    <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>France Ligue 2</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -580,18 +580,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
     <t>Hwaseong</t>
   </si>
   <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
     <t>Auckland</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Cheongju</t>
   </si>
   <si>
@@ -625,126 +625,126 @@
     <t>Kedus Giorgis</t>
   </si>
   <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
     <t>Oddevold</t>
   </si>
   <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>United Nordic</t>
   </si>
   <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
+    <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Cibalia</t>
   </si>
   <si>
-    <t>Hegelmann Litauen</t>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Young Lions</t>
   </si>
   <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
     <t>Elche CF</t>
   </si>
   <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
   </si>
   <si>
     <t>Adama Kenema</t>
   </si>
   <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,183 +754,183 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
     <t>Cagliari</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
     <t>Augsburg</t>
   </si>
   <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
     <t>Viktoria Plzeň</t>
   </si>
   <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
   </si>
   <si>
     <t>Falkirk</t>
   </si>
   <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
     <t>Jamshedpur</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
+    <t>Albacete Balompié</t>
+  </si>
+  <si>
+    <t>Sevilla FC</t>
   </si>
   <si>
     <t>Burgos CF</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
-    <t>Albacete Balompié</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
     <t>Grazer AK</t>
   </si>
   <si>
-    <t>GIF Sundsvall</t>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Tobol</t>
   </si>
   <si>
     <t>Wattens</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>AEL</t>
+    <t>Enosis</t>
   </si>
   <si>
     <t>Dugopolje</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Enosis</t>
+    <t>Koper</t>
   </si>
   <si>
     <t>Sumqayıt</t>
   </si>
   <si>
-    <t>Koper</t>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
@@ -940,201 +940,201 @@
     <t>Athletic Club W</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Lazio</t>
+    <t>Beerschot-Wilrijk</t>
   </si>
   <si>
     <t>Al Najma</t>
   </si>
   <si>
-    <t>Beerschot-Wilrijk</t>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
   </si>
   <si>
     <t>Atromitos</t>
   </si>
   <si>
-    <t>Recoleta</t>
+    <t>Real Valladolid</t>
   </si>
   <si>
     <t>Manchester City</t>
   </si>
   <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
     <t>Galatasaray</t>
   </si>
   <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
     <t>İstanbul Başakşehir</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
     <t>Partizan</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
     <t>Le Puy F.43 Auvergne</t>
   </si>
   <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
     <t>Orléans</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
     <t>Caen</t>
   </si>
   <si>
-    <t>Wieczysta Kraków</t>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Nancy</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
     <t>Red Star</t>
   </si>
   <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
     <t>Deportivo Morón</t>
   </si>
   <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Magesi</t>
+    <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
-    <t>Maribor</t>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Luzern</t>
   </si>
   <si>
     <t>Acassuso</t>
   </si>
   <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Club Brugge</t>
   </si>
   <si>
@@ -1144,51 +1144,51 @@
     <t>Goiás</t>
   </si>
   <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>CD Mafra</t>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
   </si>
   <si>
     <t>Coritiba</t>
   </si>
   <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1204,15 +1204,15 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
@@ -1222,90 +1222,90 @@
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>Real Tomayapo</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
   </si>
   <si>
     <t>CSD Independiente del Valle</t>
   </si>
   <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Benfica</t>
   </si>
   <si>
     <t>AVS</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
   </si>
   <si>
     <t>Felgueiras 1932</t>
   </si>
   <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1324,33 +1324,33 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Oakland Roots</t>
+  </si>
+  <si>
     <t>Phoenix Rising</t>
   </si>
   <si>
-    <t>Oakland Roots</t>
+    <t>Seattle Sounders</t>
   </si>
   <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>Adelaide United</t>
   </si>
   <si>
@@ -1360,12 +1360,12 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
@@ -1384,126 +1384,126 @@
     <t>Mekelle Kenema</t>
   </si>
   <si>
+    <t>Granada W</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
-    <t>Granada W</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Sesvete</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Geylang International</t>
   </si>
   <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
     <t>Zlín</t>
   </si>
   <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
     <t>Deportivo Alavés</t>
   </si>
   <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
   </si>
   <si>
     <t>Shire Endaselassie</t>
   </si>
   <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,183 +1513,183 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
     <t>Udinese</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Bayer Leverkusen</t>
   </si>
   <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
     <t>Slovan Liberec</t>
   </si>
   <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
   </si>
   <si>
     <t>Hibernian</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
     <t>Bengaluru</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
+    <t>Cultural y Deportiva Leonesa</t>
+  </si>
+  <si>
+    <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Almería</t>
   </si>
   <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
-    <t>Cultural y Deportiva Leonesa</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
-    <t>Norrköping</t>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
   </si>
   <si>
     <t>Blau-Weiß Linz</t>
   </si>
   <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
+    <t>Ethnikos Achna</t>
   </si>
   <si>
     <t>Bijelo Brdo</t>
   </si>
   <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
+    <t>Aluminij</t>
   </si>
   <si>
     <t>Araz</t>
   </si>
   <si>
-    <t>Aluminij</t>
+    <t>Pogoń Szczecin</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
   </si>
   <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
@@ -1699,201 +1699,201 @@
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Inter Milan</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Inter Milan</t>
+    <t>Lommel United</t>
   </si>
   <si>
     <t>Al Hazm</t>
   </si>
   <si>
-    <t>Lommel United</t>
+    <t>Bayern München</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Celta de Vigo</t>
   </si>
   <si>
     <t>Panaitolikos</t>
   </si>
   <si>
-    <t>Deportes Santa Cruz</t>
+    <t>Real Zaragoza</t>
   </si>
   <si>
     <t>Brentford</t>
   </si>
   <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
     <t>Antalyaspor</t>
   </si>
   <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
     <t>Samsunspor</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
     <t>Trakai</t>
   </si>
   <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
     <t>OFK Beograd</t>
   </si>
   <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
     <t>Dijon</t>
   </si>
   <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
     <t>Fleury 91</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
     <t>Concarneau</t>
   </si>
   <si>
-    <t>Miedź Legnica</t>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Dunkerque</t>
   </si>
   <si>
-    <t>Midland</t>
-  </si>
-  <si>
     <t>Montpellier</t>
   </si>
   <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
     <t>Los Andes</t>
   </si>
   <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
+    <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Olimpija</t>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Servette</t>
   </si>
   <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
@@ -1903,51 +1903,51 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
     <t>Unión Española</t>
   </si>
   <si>
-    <t>Associação Académica de Coimbra OAF</t>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1963,15 +1963,15 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>Sporting JAX</t>
   </si>
   <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
     <t>Loudoun United</t>
   </si>
   <si>
@@ -1981,90 +1981,90 @@
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Operário PR</t>
   </si>
   <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
   </si>
   <si>
     <t>Barcelona</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
   </si>
   <si>
     <t>Porto</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
   </si>
   <si>
     <t>Portimonense</t>
   </si>
   <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2083,16 +2083,16 @@
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>San Antonio</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
+    <t>San Diego</t>
   </si>
   <si>
     <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>San Diego</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
@@ -2882,13 +2882,13 @@
         <v>694</v>
       </c>
       <c r="P3">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -2927,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -3067,13 +3067,13 @@
         <v>694</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
         <v>185</v>
@@ -3252,13 +3252,13 @@
         <v>694</v>
       </c>
       <c r="P5">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="Q5">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="R5">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -3297,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3768,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
         <v>185</v>
@@ -3992,13 +3992,13 @@
         <v>694</v>
       </c>
       <c r="P9">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4177,13 +4177,13 @@
         <v>694</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5433,10 +5433,10 @@
         <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5618,7 +5618,7 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
         <v>185</v>
@@ -5803,7 +5803,7 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>186</v>
@@ -5991,7 +5991,7 @@
         <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6543,10 +6543,10 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6728,7 +6728,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>186</v>
@@ -6913,7 +6913,7 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>186</v>
@@ -6952,13 +6952,13 @@
         <v>694</v>
       </c>
       <c r="P25">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6997,10 +6997,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -7098,10 +7098,10 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q26">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7283,7 +7283,7 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
         <v>186</v>
@@ -7468,10 +7468,10 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -7653,10 +7653,10 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E29" t="s">
         <v>215</v>
@@ -7692,13 +7692,13 @@
         <v>694</v>
       </c>
       <c r="P29">
-        <v>2.86</v>
+        <v>2.27</v>
       </c>
       <c r="Q29">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7838,10 +7838,10 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E30" t="s">
         <v>216</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -7922,10 +7922,10 @@
         <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG30">
         <v>0</v>
@@ -8023,10 +8023,10 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8396,7 +8396,7 @@
         <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8581,7 +8581,7 @@
         <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8617,13 +8617,13 @@
         <v>694</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8763,7 +8763,7 @@
         <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
         <v>187</v>
@@ -8948,10 +8948,10 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" t="s">
         <v>222</v>
@@ -8987,13 +8987,13 @@
         <v>694</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9172,13 +9172,13 @@
         <v>694</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -9318,10 +9318,10 @@
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9357,13 +9357,13 @@
         <v>694</v>
       </c>
       <c r="P38">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9402,10 +9402,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9688,7 +9688,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
         <v>185</v>
@@ -10061,7 +10061,7 @@
         <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
         <v>228</v>
@@ -10097,13 +10097,13 @@
         <v>694</v>
       </c>
       <c r="P42">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10243,7 +10243,7 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
         <v>186</v>
@@ -10428,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
         <v>186</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10798,10 +10798,10 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -10837,13 +10837,13 @@
         <v>694</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -11168,10 +11168,10 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11207,13 +11207,13 @@
         <v>694</v>
       </c>
       <c r="P48">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11392,13 +11392,13 @@
         <v>694</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11723,10 +11723,10 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -12093,10 +12093,10 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E53" t="s">
         <v>239</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12463,10 +12463,10 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -13388,10 +13388,10 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="D60" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E60" t="s">
         <v>246</v>
@@ -13427,13 +13427,13 @@
         <v>694</v>
       </c>
       <c r="P60">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="Q60">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="R60">
-        <v>3.21</v>
+        <v>2.46</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13573,10 +13573,10 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D61" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E61" t="s">
         <v>247</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13758,7 +13758,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D62" t="s">
         <v>185</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D63" t="s">
         <v>185</v>
@@ -13982,13 +13982,13 @@
         <v>694</v>
       </c>
       <c r="P63">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14128,10 +14128,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14313,7 +14313,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -14352,13 +14352,13 @@
         <v>694</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14498,7 +14498,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
         <v>186</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14868,10 +14868,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -15053,10 +15053,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15277,13 +15277,13 @@
         <v>694</v>
       </c>
       <c r="P70">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
         <v>185</v>
@@ -15462,13 +15462,13 @@
         <v>694</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15608,7 +15608,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15647,13 +15647,13 @@
         <v>694</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15793,7 +15793,7 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D73" t="s">
         <v>186</v>
@@ -15978,10 +15978,10 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16017,13 +16017,13 @@
         <v>694</v>
       </c>
       <c r="P74">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="Q74">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="R74">
-        <v>2.46</v>
+        <v>3.21</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16572,13 +16572,13 @@
         <v>694</v>
       </c>
       <c r="P77">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="Q77">
-        <v>4.16</v>
+        <v>5.18</v>
       </c>
       <c r="R77">
-        <v>3.23</v>
+        <v>7.21</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16623,10 +16623,10 @@
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH77">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q78">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R78">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH78">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -17088,7 +17088,7 @@
         <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="D80" t="s">
         <v>186</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17172,10 +17172,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17497,13 +17497,13 @@
         <v>694</v>
       </c>
       <c r="P82">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q84">
-        <v>3.46</v>
+        <v>5.48</v>
       </c>
       <c r="R84">
-        <v>2.42</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,10 +18013,10 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E85" t="s">
         <v>271</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18198,10 +18198,10 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E86" t="s">
         <v>272</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="Q87">
-        <v>3.86</v>
+        <v>3.01</v>
       </c>
       <c r="R87">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18753,7 +18753,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18792,13 +18792,13 @@
         <v>694</v>
       </c>
       <c r="P89">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18837,10 +18837,10 @@
         <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG89">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19347,13 +19347,13 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19493,7 +19493,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19532,55 +19532,55 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>4.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q93">
-        <v>3.98</v>
+        <v>3.46</v>
       </c>
       <c r="R93">
+        <v>2.42</v>
+      </c>
+      <c r="S93">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>0</v>
+      </c>
+      <c r="U93">
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+      <c r="AA93">
+        <v>0</v>
+      </c>
+      <c r="AB93">
+        <v>0</v>
+      </c>
+      <c r="AC93">
+        <v>0</v>
+      </c>
+      <c r="AD93">
+        <v>0</v>
+      </c>
+      <c r="AE93">
+        <v>1.77</v>
+      </c>
+      <c r="AF93">
         <v>1.93</v>
-      </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-      <c r="T93">
-        <v>0</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <v>0</v>
-      </c>
-      <c r="W93">
-        <v>0</v>
-      </c>
-      <c r="X93">
-        <v>0</v>
-      </c>
-      <c r="Y93">
-        <v>0</v>
-      </c>
-      <c r="Z93">
-        <v>0</v>
-      </c>
-      <c r="AA93">
-        <v>0</v>
-      </c>
-      <c r="AB93">
-        <v>0</v>
-      </c>
-      <c r="AC93">
-        <v>0</v>
-      </c>
-      <c r="AD93">
-        <v>0</v>
-      </c>
-      <c r="AE93">
-        <v>0</v>
-      </c>
-      <c r="AF93">
-        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19717,13 +19717,13 @@
         <v>694</v>
       </c>
       <c r="P94">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19762,10 +19762,10 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG94">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>1.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q95">
-        <v>5.48</v>
+        <v>3.61</v>
       </c>
       <c r="R95">
-        <v>8.300000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>2.04</v>
       </c>
       <c r="Q96">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R96">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q98">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R98">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20502,10 +20502,10 @@
         <v>0</v>
       </c>
       <c r="AE98">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF98">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -20603,7 +20603,7 @@
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q100">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R100">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20973,10 +20973,10 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>3.87</v>
+        <v>2.03</v>
       </c>
       <c r="Q101">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="R101">
-        <v>1.81</v>
+        <v>3.27</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21057,10 +21057,10 @@
         <v>0</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG101">
         <v>0</v>
@@ -21158,10 +21158,10 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="Q102">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R102">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>2.27</v>
+        <v>3.87</v>
       </c>
       <c r="Q103">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R103">
-        <v>2.88</v>
+        <v>1.81</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q104">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21612,10 +21612,10 @@
         <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG104">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22083,7 +22083,7 @@
         <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="D107" t="s">
         <v>186</v>
@@ -22122,13 +22122,13 @@
         <v>694</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22268,7 +22268,7 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q108">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R108">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22352,10 +22352,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22453,10 +22453,10 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="D109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E109" t="s">
         <v>295</v>
@@ -22492,13 +22492,13 @@
         <v>694</v>
       </c>
       <c r="P109">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22537,10 +22537,10 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -22638,7 +22638,7 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22722,10 +22722,10 @@
         <v>0</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG110">
         <v>0</v>
@@ -22823,10 +22823,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23008,7 +23008,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23232,13 +23232,13 @@
         <v>694</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23417,13 +23417,13 @@
         <v>694</v>
       </c>
       <c r="P114">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23602,13 +23602,13 @@
         <v>694</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23787,13 +23787,13 @@
         <v>694</v>
       </c>
       <c r="P116">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24673,7 +24673,7 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D121" t="s">
         <v>186</v>
@@ -24897,13 +24897,13 @@
         <v>694</v>
       </c>
       <c r="P122">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25267,13 +25267,13 @@
         <v>694</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25637,13 +25637,13 @@
         <v>694</v>
       </c>
       <c r="P126">
-        <v>4.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q126">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R126">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -25783,7 +25783,7 @@
         <v>90</v>
       </c>
       <c r="C127" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D127" t="s">
         <v>186</v>
@@ -25968,7 +25968,7 @@
         <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D128" t="s">
         <v>186</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26192,13 +26192,13 @@
         <v>694</v>
       </c>
       <c r="P129">
-        <v>1.93</v>
+        <v>5.74</v>
       </c>
       <c r="Q129">
-        <v>3.33</v>
+        <v>5.53</v>
       </c>
       <c r="R129">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26523,7 +26523,7 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26747,13 +26747,13 @@
         <v>694</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26893,7 +26893,7 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27117,13 +27117,13 @@
         <v>694</v>
       </c>
       <c r="P134">
-        <v>5.74</v>
+        <v>1.36</v>
       </c>
       <c r="Q134">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="R134">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27263,7 +27263,7 @@
         <v>92</v>
       </c>
       <c r="C135" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -28558,10 +28558,10 @@
         <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -28597,13 +28597,13 @@
         <v>694</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28648,10 +28648,10 @@
         <v>0</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH142">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI142">
         <v>0</v>
@@ -28743,10 +28743,10 @@
         <v>93</v>
       </c>
       <c r="C143" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D143" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E143" t="s">
         <v>329</v>
@@ -28782,13 +28782,13 @@
         <v>694</v>
       </c>
       <c r="P143">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R143">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S143">
         <v>0</v>
@@ -28833,10 +28833,10 @@
         <v>0</v>
       </c>
       <c r="AG143">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH143">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI143">
         <v>0</v>
@@ -28928,7 +28928,7 @@
         <v>93</v>
       </c>
       <c r="C144" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D144" t="s">
         <v>186</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29483,7 +29483,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D147" t="s">
         <v>185</v>
@@ -29853,7 +29853,7 @@
         <v>95</v>
       </c>
       <c r="C149" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -29892,13 +29892,13 @@
         <v>694</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30262,13 +30262,13 @@
         <v>694</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30778,7 +30778,7 @@
         <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30817,13 +30817,13 @@
         <v>694</v>
       </c>
       <c r="P154">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q154">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R154">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S154">
         <v>0</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31333,7 +31333,7 @@
         <v>95</v>
       </c>
       <c r="C157" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D157" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31703,7 +31703,7 @@
         <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D159" t="s">
         <v>186</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32482,13 +32482,13 @@
         <v>694</v>
       </c>
       <c r="P163">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q163">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R163">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S163">
         <v>0</v>
@@ -32631,7 +32631,7 @@
         <v>172</v>
       </c>
       <c r="D164" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E164" t="s">
         <v>350</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF164">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32816,7 +32816,7 @@
         <v>173</v>
       </c>
       <c r="D165" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E165" t="s">
         <v>351</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32897,10 +32897,10 @@
         <v>0</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG165">
         <v>0</v>
@@ -32998,7 +32998,7 @@
         <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33037,13 +33037,13 @@
         <v>694</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33273,10 +33273,10 @@
         <v>0</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH167">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI167">
         <v>0</v>
@@ -33368,7 +33368,7 @@
         <v>96</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q168">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33452,10 +33452,10 @@
         <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF168">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG168">
         <v>0</v>
@@ -33553,7 +33553,7 @@
         <v>96</v>
       </c>
       <c r="C169" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>2.89</v>
+        <v>3.79</v>
       </c>
       <c r="Q169">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="R169">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33637,10 +33637,10 @@
         <v>0</v>
       </c>
       <c r="AE169">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AF169">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33923,7 +33923,7 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="Q171">
-        <v>4.7</v>
+        <v>3.68</v>
       </c>
       <c r="R171">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34111,7 +34111,7 @@
         <v>173</v>
       </c>
       <c r="D172" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E172" t="s">
         <v>358</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>3.03</v>
+        <v>1.45</v>
       </c>
       <c r="Q173">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="R173">
-        <v>2.31</v>
+        <v>6</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q174">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34663,7 +34663,7 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>1.3</v>
+        <v>2.61</v>
       </c>
       <c r="Q175">
-        <v>5.65</v>
+        <v>3.35</v>
       </c>
       <c r="R175">
-        <v>8.4</v>
+        <v>2.56</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34747,16 +34747,16 @@
         <v>0</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG175">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH175">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI175">
         <v>0</v>
@@ -34848,7 +34848,7 @@
         <v>96</v>
       </c>
       <c r="C176" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q176">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R176">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -35033,10 +35033,10 @@
         <v>96</v>
       </c>
       <c r="C177" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D177" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E177" t="s">
         <v>363</v>
@@ -35218,7 +35218,7 @@
         <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35257,13 +35257,13 @@
         <v>694</v>
       </c>
       <c r="P178">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="Q178">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="R178">
-        <v>4.81</v>
+        <v>3.57</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35302,10 +35302,10 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF178">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG178">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35442,13 +35442,13 @@
         <v>694</v>
       </c>
       <c r="P179">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q179">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="R179">
-        <v>3.57</v>
+        <v>4.81</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35487,10 +35487,10 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q180">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R180">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35672,10 +35672,10 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF180">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -35773,10 +35773,10 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="D181" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q181">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="R181">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35958,7 +35958,7 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D182" t="s">
         <v>185</v>
@@ -35997,13 +35997,13 @@
         <v>694</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36143,10 +36143,10 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="D183" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E183" t="s">
         <v>369</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>2.87</v>
+        <v>1.65</v>
       </c>
       <c r="Q183">
-        <v>3.45</v>
+        <v>4.52</v>
       </c>
       <c r="R183">
-        <v>2.3</v>
+        <v>4.89</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36233,10 +36233,10 @@
         <v>0</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH183">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI183">
         <v>0</v>
@@ -36328,7 +36328,7 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D184" t="s">
         <v>185</v>
@@ -36513,10 +36513,10 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D185" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E185" t="s">
         <v>371</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q185">
-        <v>4.52</v>
+        <v>3.76</v>
       </c>
       <c r="R185">
-        <v>4.89</v>
+        <v>2.92</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36603,10 +36603,10 @@
         <v>0</v>
       </c>
       <c r="AG185">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH185">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI185">
         <v>0</v>
@@ -36698,10 +36698,10 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="D186" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>2.18</v>
+        <v>2.82</v>
       </c>
       <c r="Q186">
-        <v>3.76</v>
+        <v>2.55</v>
       </c>
       <c r="R186">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36782,10 +36782,10 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37438,10 +37438,10 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D190" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E190" t="s">
         <v>376</v>
@@ -37623,10 +37623,10 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D191" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37808,10 +37808,10 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D192" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -37847,13 +37847,13 @@
         <v>694</v>
       </c>
       <c r="P192">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q192">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R192">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -37993,10 +37993,10 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38178,10 +38178,10 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D194" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38217,13 +38217,13 @@
         <v>694</v>
       </c>
       <c r="P194">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q194">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S194">
         <v>0</v>
@@ -38262,10 +38262,10 @@
         <v>0</v>
       </c>
       <c r="AE194">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF194">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG194">
         <v>0</v>
@@ -38363,7 +38363,7 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38402,13 +38402,13 @@
         <v>694</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38447,10 +38447,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -38548,7 +38548,7 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38587,13 +38587,13 @@
         <v>694</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38733,10 +38733,10 @@
         <v>100</v>
       </c>
       <c r="C197" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="D197" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38772,13 +38772,13 @@
         <v>694</v>
       </c>
       <c r="P197">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="Q197">
-        <v>3.73</v>
+        <v>3.17</v>
       </c>
       <c r="R197">
-        <v>3.71</v>
+        <v>3.15</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -39512,13 +39512,13 @@
         <v>694</v>
       </c>
       <c r="P201">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q201">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39557,10 +39557,10 @@
         <v>0</v>
       </c>
       <c r="AE201">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF201">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG201">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>103</v>
       </c>
       <c r="C202" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39697,13 +39697,13 @@
         <v>694</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -39882,13 +39882,13 @@
         <v>694</v>
       </c>
       <c r="P203">
-        <v>2.32</v>
+        <v>1.56</v>
       </c>
       <c r="Q203">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R203">
-        <v>3.16</v>
+        <v>6.74</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG203">
         <v>0</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -40992,13 +40992,13 @@
         <v>694</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="S209">
         <v>0</v>
@@ -41037,10 +41037,10 @@
         <v>0</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG209">
         <v>0</v>
@@ -41177,13 +41177,13 @@
         <v>694</v>
       </c>
       <c r="P210">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="Q210">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R210">
-        <v>4.75</v>
+        <v>2.65</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41547,13 +41547,13 @@
         <v>694</v>
       </c>
       <c r="P212">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q212">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R212">
-        <v>2.65</v>
+        <v>4.75</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -42248,7 +42248,7 @@
         <v>109</v>
       </c>
       <c r="C216" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q217">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R217">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -42842,13 +42842,13 @@
         <v>694</v>
       </c>
       <c r="P219">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q219">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R219">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -42887,10 +42887,10 @@
         <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF219">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG219">
         <v>0</v>
@@ -42988,10 +42988,10 @@
         <v>110</v>
       </c>
       <c r="C220" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D220" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E220" t="s">
         <v>406</v>
@@ -43027,13 +43027,13 @@
         <v>694</v>
       </c>
       <c r="P220">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q220">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R220">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S220">
         <v>0</v>
@@ -43072,10 +43072,10 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF220">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG220">
         <v>0</v>
@@ -43358,7 +43358,7 @@
         <v>110</v>
       </c>
       <c r="C222" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D222" t="s">
         <v>186</v>
@@ -43543,10 +43543,10 @@
         <v>110</v>
       </c>
       <c r="C223" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D223" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43728,10 +43728,10 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D224" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43767,13 +43767,13 @@
         <v>694</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43913,7 +43913,7 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D225" t="s">
         <v>185</v>
@@ -43952,13 +43952,13 @@
         <v>694</v>
       </c>
       <c r="P225">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q225">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R225">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S225">
         <v>0</v>
@@ -44098,7 +44098,7 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D226" t="s">
         <v>186</v>
@@ -44283,10 +44283,10 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D227" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44838,10 +44838,10 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D230" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E230" t="s">
         <v>416</v>
@@ -45023,7 +45023,7 @@
         <v>110</v>
       </c>
       <c r="C231" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D231" t="s">
         <v>186</v>
@@ -45208,7 +45208,7 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D232" t="s">
         <v>186</v>
@@ -45393,10 +45393,10 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D233" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45432,13 +45432,13 @@
         <v>694</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S233">
         <v>0</v>
@@ -45477,10 +45477,10 @@
         <v>0</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG233">
         <v>0</v>
@@ -45578,7 +45578,7 @@
         <v>110</v>
       </c>
       <c r="C234" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D234" t="s">
         <v>186</v>
@@ -45948,7 +45948,7 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D236" t="s">
         <v>186</v>
@@ -46318,7 +46318,7 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D238" t="s">
         <v>186</v>
@@ -46503,7 +46503,7 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D239" t="s">
         <v>186</v>
@@ -46688,7 +46688,7 @@
         <v>110</v>
       </c>
       <c r="C240" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D240" t="s">
         <v>186</v>
@@ -47243,7 +47243,7 @@
         <v>110</v>
       </c>
       <c r="C243" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D243" t="s">
         <v>186</v>
@@ -48577,13 +48577,13 @@
         <v>694</v>
       </c>
       <c r="P250">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q250">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R250">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="S250">
         <v>0</v>
@@ -48762,13 +48762,13 @@
         <v>694</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="S251">
         <v>0</v>
@@ -48947,13 +48947,13 @@
         <v>694</v>
       </c>
       <c r="P252">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q252">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R252">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -48992,16 +48992,16 @@
         <v>0</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG252">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH252">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,61 +49132,61 @@
         <v>694</v>
       </c>
       <c r="P253">
+        <v>1.46</v>
+      </c>
+      <c r="Q253">
+        <v>4.6</v>
+      </c>
+      <c r="R253">
+        <v>5.15</v>
+      </c>
+      <c r="S253">
+        <v>0</v>
+      </c>
+      <c r="T253">
+        <v>0</v>
+      </c>
+      <c r="U253">
+        <v>0</v>
+      </c>
+      <c r="V253">
+        <v>0</v>
+      </c>
+      <c r="W253">
+        <v>0</v>
+      </c>
+      <c r="X253">
+        <v>0</v>
+      </c>
+      <c r="Y253">
+        <v>0</v>
+      </c>
+      <c r="Z253">
+        <v>0</v>
+      </c>
+      <c r="AA253">
+        <v>0</v>
+      </c>
+      <c r="AB253">
+        <v>0</v>
+      </c>
+      <c r="AC253">
+        <v>0</v>
+      </c>
+      <c r="AD253">
+        <v>0</v>
+      </c>
+      <c r="AE253">
+        <v>0</v>
+      </c>
+      <c r="AF253">
+        <v>0</v>
+      </c>
+      <c r="AG253">
+        <v>1.95</v>
+      </c>
+      <c r="AH253">
         <v>1.75</v>
-      </c>
-      <c r="Q253">
-        <v>3.9</v>
-      </c>
-      <c r="R253">
-        <v>4.2</v>
-      </c>
-      <c r="S253">
-        <v>0</v>
-      </c>
-      <c r="T253">
-        <v>0</v>
-      </c>
-      <c r="U253">
-        <v>0</v>
-      </c>
-      <c r="V253">
-        <v>0</v>
-      </c>
-      <c r="W253">
-        <v>0</v>
-      </c>
-      <c r="X253">
-        <v>0</v>
-      </c>
-      <c r="Y253">
-        <v>0</v>
-      </c>
-      <c r="Z253">
-        <v>0</v>
-      </c>
-      <c r="AA253">
-        <v>0</v>
-      </c>
-      <c r="AB253">
-        <v>0</v>
-      </c>
-      <c r="AC253">
-        <v>0</v>
-      </c>
-      <c r="AD253">
-        <v>0</v>
-      </c>
-      <c r="AE253">
-        <v>1.61</v>
-      </c>
-      <c r="AF253">
-        <v>2.15</v>
-      </c>
-      <c r="AG253">
-        <v>0</v>
-      </c>
-      <c r="AH253">
-        <v>0</v>
       </c>
       <c r="AI253">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,111 +370,111 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>Australia A-League</t>
   </si>
   <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>England FA Women's Super League</t>
+  </si>
+  <si>
     <t>Vietnam V.League 1</t>
   </si>
   <si>
-    <t>England FA Women's Super League</t>
-  </si>
-  <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
+    <t>Sweden Damallsvenskan</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Greece Super League</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -532,12 +532,12 @@
     <t>France National</t>
   </si>
   <si>
+    <t>France Ligue 2</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>France Ligue 2</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -580,18 +580,18 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Jeju United</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>Auckland</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
     <t>Cheongju</t>
   </si>
   <si>
@@ -622,51 +622,51 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
     <t>Real Sociedad W</t>
   </si>
   <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
     <t>Oddevold</t>
   </si>
   <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
     <t>Phu Dong</t>
   </si>
   <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Holstein Kiel</t>
-  </si>
-  <si>
     <t>FLC Thanh Hoa</t>
   </si>
   <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
     <t>Bochum</t>
   </si>
   <si>
@@ -676,75 +676,75 @@
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
-    <t>Goa</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
+    <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Young Lions</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Teplice</t>
+  </si>
+  <si>
     <t>1860 München</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
+    <t>Brommapojkarna W</t>
   </si>
   <si>
     <t>Dukla Praha</t>
   </si>
   <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
     <t>Ceuta</t>
   </si>
   <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,54 +754,57 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
     <t>Norrby</t>
   </si>
   <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
     <t>Augsburg</t>
   </si>
   <si>
@@ -811,7 +814,16 @@
     <t>Stuttgart</t>
   </si>
   <si>
-    <t>Hoffenheim</t>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Larissa</t>
   </si>
   <si>
     <t>Dundee</t>
@@ -820,46 +832,37 @@
     <t>Eibar W</t>
   </si>
   <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
     <t>Dinamo Zagreb</t>
   </si>
   <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
     <t>St. Mirren</t>
   </si>
   <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
+    <t>Burgos CF</t>
   </si>
   <si>
     <t>Albacete Balompié</t>
@@ -868,49 +871,55 @@
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
     <t>Ried</t>
   </si>
   <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
     <t>AEL</t>
   </si>
   <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>Koper</t>
@@ -922,39 +931,30 @@
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
@@ -967,213 +967,213 @@
     <t>Recoleta</t>
   </si>
   <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
     <t>Atlético Madrid</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
     <t>Alanyaspor</t>
   </si>
   <si>
-    <t>Gençlerbirliği</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
+    <t>Toronto</t>
   </si>
   <si>
     <t>Kocaelispor</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Toronto</t>
+    <t>Beşiktaş</t>
   </si>
   <si>
     <t>Göztepe</t>
   </si>
   <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
     <t>Stal Mielec</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
     <t>Partizan</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Caen</t>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
   </si>
   <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
     <t>Red Star</t>
   </si>
   <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
     <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Nürnberg</t>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
   </si>
   <si>
     <t>Técnico Universitario</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
+    <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
-    <t>Lecce</t>
-  </si>
-  <si>
     <t>Goiás</t>
   </si>
   <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
     <t>CD Mafra</t>
   </si>
   <si>
     <t>Real Oruro</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
     <t>Coritiba</t>
   </si>
   <si>
+    <t>San Jose Earthquakes II</t>
+  </si>
+  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
@@ -1183,27 +1183,30 @@
     <t>Guayaquil City FC</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
     <t>SD Aucas</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
     <t>Ceará</t>
   </si>
   <si>
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
@@ -1213,13 +1216,13 @@
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Brooklyn FC</t>
+    <t>New England Revolution</t>
   </si>
   <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>New England Revolution</t>
+    <t>Rhode Island</t>
   </si>
   <si>
     <t>Atlanta United FC</t>
@@ -1231,81 +1234,78 @@
     <t>Real Tomayapo</t>
   </si>
   <si>
-    <t>Rhode Island</t>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Benfica</t>
   </si>
   <si>
     <t>Grafičar</t>
   </si>
   <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
     <t>Santiago Wanderers</t>
   </si>
   <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
+    <t>FC Vizela</t>
   </si>
   <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
     <t>AVS</t>
   </si>
   <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>New Mexico United</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1339,18 +1339,18 @@
     <t>SJ Earthquakes</t>
   </si>
   <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>Adelaide United</t>
   </si>
   <si>
@@ -1360,12 +1360,12 @@
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
@@ -1381,51 +1381,51 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
     <t>Granada W</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
     <t>Hai Phong</t>
   </si>
   <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
     <t>Ha Noi</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Hannover 96</t>
   </si>
   <si>
@@ -1435,75 +1435,75 @@
     <t>Sesvete</t>
   </si>
   <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
-    <t>ATK Mohun Bagan</t>
-  </si>
-  <si>
-    <t>Changchun Yatai</t>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Geylang International</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>Verl</t>
+    <t>Eskilstuna United</t>
   </si>
   <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
     <t>CD Castellón</t>
   </si>
   <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,54 +1513,57 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
@@ -1570,7 +1573,16 @@
     <t>Bayer Leverkusen</t>
   </si>
   <si>
-    <t>Werder Bremen</t>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
   </si>
   <si>
     <t>Livingston</t>
@@ -1579,46 +1591,37 @@
     <t>Alhama</t>
   </si>
   <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
     <t>Hajduk Split</t>
   </si>
   <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
     <t>Kilmarnock</t>
   </si>
   <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
+    <t>Almería</t>
   </si>
   <si>
     <t>Cultural y Deportiva Leonesa</t>
@@ -1627,49 +1630,55 @@
     <t>RCD Espanyol</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
     <t>Olympiakos</t>
   </si>
   <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
+    <t>Siwelele</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Aluminij</t>
@@ -1681,39 +1690,30 @@
     <t>Pogoń Szczecin</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
     <t>Inter Milan</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
     <t>Lommel United</t>
   </si>
   <si>
@@ -1726,213 +1726,213 @@
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
     <t>Celta de Vigo</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
-    <t>Brentford</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
     <t>Kayserispor</t>
   </si>
   <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
+    <t>Inter Miami</t>
   </si>
   <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Inter Miami</t>
+    <t>Trabzonspor</t>
   </si>
   <si>
     <t>Gaziantep FK</t>
   </si>
   <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Trakai</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
     <t>OFK Beograd</t>
   </si>
   <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
   </si>
   <si>
     <t>Midland</t>
   </si>
   <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
     <t>Montpellier</t>
   </si>
   <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
-    <t>Schalke 04</t>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Estudiantes Caseros</t>
   </si>
   <si>
     <t>Delfin SC</t>
   </si>
   <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
+    <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
-    <t>Juventus</t>
-  </si>
-  <si>
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
     <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
     <t>Internacional</t>
   </si>
   <si>
+    <t>Whitecaps II</t>
+  </si>
+  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Whitecaps II</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
@@ -1942,27 +1942,30 @@
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
     <t>CD Universidad Católica</t>
   </si>
   <si>
-    <t>Sport Recife</t>
-  </si>
-  <si>
     <t>Atlético GO</t>
   </si>
   <si>
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
@@ -1972,13 +1975,13 @@
     <t>Sporting JAX</t>
   </si>
   <si>
-    <t>Loudoun United</t>
+    <t>Philadelphia Union</t>
   </si>
   <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
+    <t>Tampa Bay Rowdies</t>
   </si>
   <si>
     <t>LA Galaxy</t>
@@ -1990,81 +1993,78 @@
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
   </si>
   <si>
     <t>Dubočica</t>
   </si>
   <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
     <t>Cobreloa</t>
   </si>
   <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
+    <t>União de Leiria</t>
   </si>
   <si>
     <t>Casa Pia</t>
   </si>
   <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
     <t>Porto</t>
   </si>
   <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2074,10 +2074,10 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
-  </si>
-  <si>
-    <t>DC United</t>
   </si>
   <si>
     <t>St. Louis City</t>
@@ -2697,13 +2697,13 @@
         <v>694</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3067,13 +3067,13 @@
         <v>694</v>
       </c>
       <c r="P4">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="Q4">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3252,13 +3252,13 @@
         <v>694</v>
       </c>
       <c r="P5">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -3297,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3953,7 +3953,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -3992,13 +3992,13 @@
         <v>694</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4177,13 +4177,13 @@
         <v>694</v>
       </c>
       <c r="P10">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5436,7 +5436,7 @@
         <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5803,7 +5803,7 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>186</v>
@@ -5988,10 +5988,10 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6361,7 +6361,7 @@
         <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
         <v>208</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="R22">
-        <v>3.58</v>
+        <v>2.38</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6582,13 +6582,13 @@
         <v>694</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6728,10 +6728,10 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -6952,13 +6952,13 @@
         <v>694</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6997,10 +6997,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -7098,7 +7098,7 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>186</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7182,10 +7182,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -7286,7 +7286,7 @@
         <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7322,13 +7322,13 @@
         <v>694</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7468,10 +7468,10 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
         <v>214</v>
@@ -7653,10 +7653,10 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
         <v>215</v>
@@ -7692,13 +7692,13 @@
         <v>694</v>
       </c>
       <c r="P29">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7838,10 +7838,10 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
         <v>216</v>
@@ -8023,7 +8023,7 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
         <v>186</v>
@@ -8617,14 +8617,14 @@
         <v>694</v>
       </c>
       <c r="P34">
+        <v>3.59</v>
+      </c>
+      <c r="Q34">
+        <v>3.25</v>
+      </c>
+      <c r="R34">
         <v>1.95</v>
       </c>
-      <c r="Q34">
-        <v>4.17</v>
-      </c>
-      <c r="R34">
-        <v>3.8</v>
-      </c>
       <c r="S34">
         <v>0</v>
       </c>
@@ -8662,10 +8662,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8948,7 +8948,7 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
         <v>185</v>
@@ -9133,10 +9133,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9172,13 +9172,13 @@
         <v>694</v>
       </c>
       <c r="P37">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -9318,10 +9318,10 @@
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9357,13 +9357,13 @@
         <v>694</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9688,10 +9688,10 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -10058,7 +10058,7 @@
         <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10246,7 +10246,7 @@
         <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10282,13 +10282,13 @@
         <v>694</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
         <v>186</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10801,7 +10801,7 @@
         <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -10837,13 +10837,13 @@
         <v>694</v>
       </c>
       <c r="P46">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -11168,10 +11168,10 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11392,13 +11392,13 @@
         <v>694</v>
       </c>
       <c r="P49">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11723,10 +11723,10 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -12093,7 +12093,7 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12278,10 +12278,10 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12463,10 +12463,10 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
         <v>241</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -12687,13 +12687,13 @@
         <v>694</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E60" t="s">
         <v>246</v>
@@ -13427,13 +13427,13 @@
         <v>694</v>
       </c>
       <c r="P60">
-        <v>2.65</v>
+        <v>3.13</v>
       </c>
       <c r="Q60">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R60">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13573,7 +13573,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D61" t="s">
         <v>185</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R61">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13758,7 +13758,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D62" t="s">
         <v>185</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
         <v>185</v>
@@ -14128,10 +14128,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14313,7 +14313,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -14352,13 +14352,13 @@
         <v>694</v>
       </c>
       <c r="P65">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -14498,10 +14498,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14722,13 +14722,13 @@
         <v>694</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14868,10 +14868,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -15053,10 +15053,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D70" t="s">
         <v>186</v>
@@ -15277,13 +15277,13 @@
         <v>694</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15423,10 +15423,10 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D71" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E71" t="s">
         <v>257</v>
@@ -15462,13 +15462,13 @@
         <v>694</v>
       </c>
       <c r="P71">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15608,7 +15608,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15647,13 +15647,13 @@
         <v>694</v>
       </c>
       <c r="P72">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15793,10 +15793,10 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15832,13 +15832,13 @@
         <v>694</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15978,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s">
         <v>186</v>
@@ -16017,13 +16017,13 @@
         <v>694</v>
       </c>
       <c r="P74">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16387,13 +16387,13 @@
         <v>694</v>
       </c>
       <c r="P76">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="Q76">
-        <v>3.71</v>
+        <v>4.88</v>
       </c>
       <c r="R76">
-        <v>3.07</v>
+        <v>5.33</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16432,16 +16432,16 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH76">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16572,13 +16572,13 @@
         <v>694</v>
       </c>
       <c r="P77">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q77">
-        <v>5.18</v>
+        <v>3.71</v>
       </c>
       <c r="R77">
-        <v>7.21</v>
+        <v>3.07</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16617,16 +16617,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH77">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="Q78">
-        <v>4.16</v>
+        <v>5.18</v>
       </c>
       <c r="R78">
-        <v>3.23</v>
+        <v>7.21</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH78">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16942,13 +16942,13 @@
         <v>694</v>
       </c>
       <c r="P79">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q79">
-        <v>4.88</v>
+        <v>4.16</v>
       </c>
       <c r="R79">
-        <v>5.33</v>
+        <v>3.23</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16993,10 +16993,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH79">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>1.59</v>
+        <v>2.13</v>
       </c>
       <c r="Q80">
-        <v>4.15</v>
+        <v>3.62</v>
       </c>
       <c r="R80">
-        <v>5.06</v>
+        <v>3.11</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17172,10 +17172,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AF80">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17312,13 +17312,13 @@
         <v>694</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17497,13 +17497,13 @@
         <v>694</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q83">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="R83">
-        <v>3.32</v>
+        <v>3.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q84">
-        <v>5.48</v>
+        <v>4.15</v>
       </c>
       <c r="R84">
-        <v>8.300000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18198,10 +18198,10 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E86" t="s">
         <v>272</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="Q88">
-        <v>3.62</v>
+        <v>3.46</v>
       </c>
       <c r="R88">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AF88">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18753,7 +18753,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18938,10 +18938,10 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>1.67</v>
+        <v>2.78</v>
       </c>
       <c r="Q91">
-        <v>4.13</v>
+        <v>3.61</v>
       </c>
       <c r="R91">
-        <v>4.85</v>
+        <v>2.43</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19493,7 +19493,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q93">
-        <v>3.46</v>
+        <v>4.13</v>
       </c>
       <c r="R93">
-        <v>2.42</v>
+        <v>4.85</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19577,10 +19577,10 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG93">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="Q95">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="R95">
-        <v>2.43</v>
+        <v>3.32</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19947,10 +19947,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q96">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R96">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20317,10 +20317,10 @@
         <v>0</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20603,7 +20603,7 @@
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="Q100">
         <v>3.4</v>
       </c>
       <c r="R100">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20973,7 +20973,7 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D101" t="s">
         <v>186</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q101">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="R101">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21057,10 +21057,10 @@
         <v>0</v>
       </c>
       <c r="AE101">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF101">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG101">
         <v>0</v>
@@ -21158,10 +21158,10 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
         <v>288</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q102">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R102">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21343,10 +21343,10 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E103" t="s">
         <v>289</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>3.87</v>
+        <v>8.01</v>
       </c>
       <c r="Q103">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="R103">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -22083,10 +22083,10 @@
         <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="D107" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22122,13 +22122,13 @@
         <v>694</v>
       </c>
       <c r="P107">
-        <v>2.5</v>
+        <v>3.87</v>
       </c>
       <c r="Q107">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="R107">
-        <v>2.75</v>
+        <v>1.81</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22268,7 +22268,7 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q108">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R108">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22352,10 +22352,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AF108">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22453,7 +22453,7 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D109" t="s">
         <v>185</v>
@@ -22638,7 +22638,7 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22722,10 +22722,10 @@
         <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG110">
         <v>0</v>
@@ -22823,7 +22823,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>8.01</v>
+        <v>2.5</v>
       </c>
       <c r="Q111">
-        <v>5.01</v>
+        <v>3.1</v>
       </c>
       <c r="R111">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -23008,7 +23008,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23092,10 +23092,10 @@
         <v>0</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23232,13 +23232,13 @@
         <v>694</v>
       </c>
       <c r="P113">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R113">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23602,13 +23602,13 @@
         <v>694</v>
       </c>
       <c r="P115">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q115">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R115">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S115">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23787,13 +23787,13 @@
         <v>694</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24157,13 +24157,13 @@
         <v>694</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24673,7 +24673,7 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="D121" t="s">
         <v>186</v>
@@ -24712,13 +24712,13 @@
         <v>694</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24897,13 +24897,13 @@
         <v>694</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25267,13 +25267,13 @@
         <v>694</v>
       </c>
       <c r="P124">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q124">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25637,13 +25637,13 @@
         <v>694</v>
       </c>
       <c r="P126">
-        <v>2.24</v>
+        <v>4.55</v>
       </c>
       <c r="Q126">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="R126">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -26523,7 +26523,7 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,7 +26708,7 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D132" t="s">
         <v>186</v>
@@ -26747,13 +26747,13 @@
         <v>694</v>
       </c>
       <c r="P132">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -26893,7 +26893,7 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -26932,13 +26932,13 @@
         <v>694</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27117,13 +27117,13 @@
         <v>694</v>
       </c>
       <c r="P134">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q134">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R134">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27633,10 +27633,10 @@
         <v>93</v>
       </c>
       <c r="C137" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27818,7 +27818,7 @@
         <v>93</v>
       </c>
       <c r="C138" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D138" t="s">
         <v>186</v>
@@ -28558,10 +28558,10 @@
         <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D142" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -28597,13 +28597,13 @@
         <v>694</v>
       </c>
       <c r="P142">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q142">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R142">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -28648,10 +28648,10 @@
         <v>0</v>
       </c>
       <c r="AG142">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH142">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI142">
         <v>0</v>
@@ -28928,10 +28928,10 @@
         <v>93</v>
       </c>
       <c r="C144" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="D144" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
@@ -28967,13 +28967,13 @@
         <v>694</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S144">
         <v>0</v>
@@ -29018,10 +29018,10 @@
         <v>0</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH144">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI144">
         <v>0</v>
@@ -29483,10 +29483,10 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" t="s">
         <v>333</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30262,13 +30262,13 @@
         <v>694</v>
       </c>
       <c r="P151">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R151">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30408,7 +30408,7 @@
         <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -30778,7 +30778,7 @@
         <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32297,13 +32297,13 @@
         <v>694</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>95</v>
       </c>
       <c r="C163" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32631,7 +32631,7 @@
         <v>172</v>
       </c>
       <c r="D164" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E164" t="s">
         <v>350</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32813,7 +32813,7 @@
         <v>96</v>
       </c>
       <c r="C165" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="Q165">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="R165">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32897,10 +32897,10 @@
         <v>0</v>
       </c>
       <c r="AE165">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AF165">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG165">
         <v>0</v>
@@ -32998,7 +32998,7 @@
         <v>96</v>
       </c>
       <c r="C166" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D166" t="s">
         <v>186</v>
@@ -33037,13 +33037,13 @@
         <v>694</v>
       </c>
       <c r="P166">
-        <v>2.24</v>
+        <v>3.79</v>
       </c>
       <c r="Q166">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R166">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33082,10 +33082,10 @@
         <v>0</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG166">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q167">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R167">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33273,10 +33273,10 @@
         <v>0</v>
       </c>
       <c r="AG167">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH167">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI167">
         <v>0</v>
@@ -33368,7 +33368,7 @@
         <v>96</v>
       </c>
       <c r="C168" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D168" t="s">
         <v>186</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33458,10 +33458,10 @@
         <v>0</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH168">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI168">
         <v>0</v>
@@ -33553,7 +33553,7 @@
         <v>96</v>
       </c>
       <c r="C169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D169" t="s">
         <v>186</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>3.79</v>
+        <v>3.03</v>
       </c>
       <c r="Q169">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="R169">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33637,10 +33637,10 @@
         <v>0</v>
       </c>
       <c r="AE169">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF169">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33777,13 +33777,13 @@
         <v>694</v>
       </c>
       <c r="P170">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="Q170">
         <v>3.68</v>
       </c>
       <c r="R170">
-        <v>4.61</v>
+        <v>3.48</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33923,7 +33923,7 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="Q171">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="R171">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34108,7 +34108,7 @@
         <v>96</v>
       </c>
       <c r="C172" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>3.03</v>
+        <v>1.73</v>
       </c>
       <c r="Q172">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="R172">
-        <v>2.31</v>
+        <v>4.61</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34666,7 +34666,7 @@
         <v>173</v>
       </c>
       <c r="D175" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E175" t="s">
         <v>361</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q175">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R175">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34747,10 +34747,10 @@
         <v>0</v>
       </c>
       <c r="AE175">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF175">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG175">
         <v>0</v>
@@ -34851,7 +34851,7 @@
         <v>173</v>
       </c>
       <c r="D176" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -35036,7 +35036,7 @@
         <v>172</v>
       </c>
       <c r="D177" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E177" t="s">
         <v>363</v>
@@ -35218,7 +35218,7 @@
         <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35672,10 +35672,10 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -35773,10 +35773,10 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E181" t="s">
         <v>367</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>2.87</v>
+        <v>1.65</v>
       </c>
       <c r="Q181">
-        <v>3.45</v>
+        <v>4.52</v>
       </c>
       <c r="R181">
-        <v>2.3</v>
+        <v>4.89</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35863,10 +35863,10 @@
         <v>0</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH181">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI181">
         <v>0</v>
@@ -35958,10 +35958,10 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="D182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E182" t="s">
         <v>368</v>
@@ -35997,13 +35997,13 @@
         <v>694</v>
       </c>
       <c r="P182">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q182">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="R182">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36143,7 +36143,7 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D183" t="s">
         <v>185</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q183">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R183">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36233,10 +36233,10 @@
         <v>0</v>
       </c>
       <c r="AG183">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH183">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI183">
         <v>0</v>
@@ -36328,10 +36328,10 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36513,10 +36513,10 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D185" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E185" t="s">
         <v>371</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D186" t="s">
         <v>185</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q186">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="R186">
-        <v>2.75</v>
+        <v>3.53</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36782,10 +36782,10 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF186">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -36922,13 +36922,13 @@
         <v>694</v>
       </c>
       <c r="P187">
-        <v>1.48</v>
+        <v>5.93</v>
       </c>
       <c r="Q187">
-        <v>4.95</v>
+        <v>4.81</v>
       </c>
       <c r="R187">
-        <v>5.98</v>
+        <v>1.57</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37107,13 +37107,13 @@
         <v>694</v>
       </c>
       <c r="P188">
-        <v>5.93</v>
+        <v>1.48</v>
       </c>
       <c r="Q188">
-        <v>4.81</v>
+        <v>4.95</v>
       </c>
       <c r="R188">
-        <v>1.57</v>
+        <v>5.98</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37438,7 +37438,7 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D190" t="s">
         <v>186</v>
@@ -37477,13 +37477,13 @@
         <v>694</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37623,10 +37623,10 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D191" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37808,7 +37808,7 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -37847,13 +37847,13 @@
         <v>694</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -37892,10 +37892,10 @@
         <v>0</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG192">
         <v>0</v>
@@ -37993,7 +37993,7 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38178,7 +38178,7 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D194" t="s">
         <v>185</v>
@@ -38363,10 +38363,10 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38402,13 +38402,13 @@
         <v>694</v>
       </c>
       <c r="P195">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q195">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38447,10 +38447,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF195">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -38548,7 +38548,7 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38587,13 +38587,13 @@
         <v>694</v>
       </c>
       <c r="P196">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -39882,13 +39882,13 @@
         <v>694</v>
       </c>
       <c r="P203">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q203">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R203">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF203">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG203">
         <v>0</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40067,13 +40067,13 @@
         <v>694</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40112,10 +40112,10 @@
         <v>0</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG204">
         <v>0</v>
@@ -40398,7 +40398,7 @@
         <v>105</v>
       </c>
       <c r="C206" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D206" t="s">
         <v>185</v>
@@ -40583,7 +40583,7 @@
         <v>105</v>
       </c>
       <c r="C207" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D207" t="s">
         <v>185</v>
@@ -41177,13 +41177,13 @@
         <v>694</v>
       </c>
       <c r="P210">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q210">
         <v>3.4</v>
       </c>
       <c r="R210">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41222,10 +41222,10 @@
         <v>0</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG210">
         <v>0</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="Q211">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R211">
-        <v>5.53</v>
+        <v>2.65</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41550,10 +41550,10 @@
         <v>1.57</v>
       </c>
       <c r="Q212">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R212">
-        <v>4.75</v>
+        <v>5.53</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41732,13 +41732,13 @@
         <v>694</v>
       </c>
       <c r="P213">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q213">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R213">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -41777,10 +41777,10 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF213">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -41917,13 +41917,13 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q214">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="R214">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41962,10 +41962,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AF214">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42102,55 +42102,55 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q215">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R215">
+        <v>3.5</v>
+      </c>
+      <c r="S215">
+        <v>0</v>
+      </c>
+      <c r="T215">
+        <v>0</v>
+      </c>
+      <c r="U215">
+        <v>0</v>
+      </c>
+      <c r="V215">
+        <v>0</v>
+      </c>
+      <c r="W215">
+        <v>0</v>
+      </c>
+      <c r="X215">
+        <v>0</v>
+      </c>
+      <c r="Y215">
+        <v>0</v>
+      </c>
+      <c r="Z215">
+        <v>0</v>
+      </c>
+      <c r="AA215">
+        <v>0</v>
+      </c>
+      <c r="AB215">
+        <v>0</v>
+      </c>
+      <c r="AC215">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>0</v>
+      </c>
+      <c r="AE215">
+        <v>1.55</v>
+      </c>
+      <c r="AF215">
         <v>2.25</v>
-      </c>
-      <c r="S215">
-        <v>0</v>
-      </c>
-      <c r="T215">
-        <v>0</v>
-      </c>
-      <c r="U215">
-        <v>0</v>
-      </c>
-      <c r="V215">
-        <v>0</v>
-      </c>
-      <c r="W215">
-        <v>0</v>
-      </c>
-      <c r="X215">
-        <v>0</v>
-      </c>
-      <c r="Y215">
-        <v>0</v>
-      </c>
-      <c r="Z215">
-        <v>0</v>
-      </c>
-      <c r="AA215">
-        <v>0</v>
-      </c>
-      <c r="AB215">
-        <v>0</v>
-      </c>
-      <c r="AC215">
-        <v>0</v>
-      </c>
-      <c r="AD215">
-        <v>0</v>
-      </c>
-      <c r="AE215">
-        <v>1.98</v>
-      </c>
-      <c r="AF215">
-        <v>1.75</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42248,7 +42248,7 @@
         <v>109</v>
       </c>
       <c r="C216" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q216">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R216">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF216">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -42842,13 +42842,13 @@
         <v>694</v>
       </c>
       <c r="P219">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q219">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R219">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -43173,10 +43173,10 @@
         <v>110</v>
       </c>
       <c r="C221" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D221" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E221" t="s">
         <v>407</v>
@@ -43543,10 +43543,10 @@
         <v>110</v>
       </c>
       <c r="C223" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D223" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43728,10 +43728,10 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D224" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E224" t="s">
         <v>410</v>
@@ -43767,13 +43767,13 @@
         <v>694</v>
       </c>
       <c r="P224">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q224">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R224">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S224">
         <v>0</v>
@@ -43913,10 +43913,10 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -44098,10 +44098,10 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44283,10 +44283,10 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D227" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44322,13 +44322,13 @@
         <v>694</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44367,10 +44367,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44653,7 +44653,7 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44838,10 +44838,10 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D230" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E230" t="s">
         <v>416</v>
@@ -44877,13 +44877,13 @@
         <v>694</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S230">
         <v>0</v>
@@ -45208,7 +45208,7 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D232" t="s">
         <v>186</v>
@@ -45393,10 +45393,10 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D233" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E233" t="s">
         <v>419</v>
@@ -45432,13 +45432,13 @@
         <v>694</v>
       </c>
       <c r="P233">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q233">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R233">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S233">
         <v>0</v>
@@ -45477,10 +45477,10 @@
         <v>0</v>
       </c>
       <c r="AE233">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF233">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG233">
         <v>0</v>
@@ -45578,7 +45578,7 @@
         <v>110</v>
       </c>
       <c r="C234" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D234" t="s">
         <v>186</v>
@@ -45763,10 +45763,10 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D235" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E235" t="s">
         <v>421</v>
@@ -45948,7 +45948,7 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D236" t="s">
         <v>186</v>
@@ -46133,7 +46133,7 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D237" t="s">
         <v>186</v>
@@ -46318,7 +46318,7 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D238" t="s">
         <v>186</v>
@@ -46503,7 +46503,7 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D239" t="s">
         <v>186</v>
@@ -46688,10 +46688,10 @@
         <v>110</v>
       </c>
       <c r="C240" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="D240" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E240" t="s">
         <v>426</v>
@@ -46873,7 +46873,7 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D241" t="s">
         <v>186</v>
@@ -47058,7 +47058,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D242" t="s">
         <v>186</v>
@@ -47243,7 +47243,7 @@
         <v>110</v>
       </c>
       <c r="C243" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D243" t="s">
         <v>186</v>
@@ -47983,7 +47983,7 @@
         <v>114</v>
       </c>
       <c r="C247" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48022,13 +48022,13 @@
         <v>694</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48067,10 +48067,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48168,7 +48168,7 @@
         <v>114</v>
       </c>
       <c r="C248" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48392,13 +48392,13 @@
         <v>694</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S249">
         <v>0</v>
@@ -48443,10 +48443,10 @@
         <v>0</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH249">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI249">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -373,12 +373,12 @@
     <t>South Korea K League 2</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>Australia A-League</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
@@ -415,90 +415,90 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
     <t>China China League One</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Singapore S.League</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Greece Super League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>South Africa Premier Soccer League</t>
-  </si>
-  <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Portugal Liga 3</t>
+  </si>
+  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
-    <t>Portugal Liga 3</t>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -541,18 +541,18 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>Portugal Liga NOS</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -583,33 +583,33 @@
     <t>Asan Mugunghwa</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
     <t>Jeju United</t>
   </si>
   <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
     <t>Auckland</t>
   </si>
   <si>
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -625,126 +625,126 @@
     <t>Espanyol W</t>
   </si>
   <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
     <t>Oddevold</t>
   </si>
   <si>
     <t>Zhetysu</t>
   </si>
   <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
-  </si>
-  <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
     <t>Goa</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Nanjing City</t>
+    <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Balestier Khalsa</t>
   </si>
   <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
     <t>Young Lions</t>
   </si>
   <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
     <t>Persis Solo</t>
   </si>
   <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
     <t>Teplice</t>
   </si>
   <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
     <t>Rot-Weiss Essen</t>
   </si>
   <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,201 +754,201 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Växjö</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Kristianstad</t>
+  </si>
+  <si>
+    <t>Norrby</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
     <t>Panserraikos</t>
   </si>
   <si>
-    <t>Kristianstad</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
     <t>Yelimay Semey</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Växjö</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
-    <t>Norrby</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
     <t>RB Leipzig</t>
   </si>
   <si>
-    <t>Stuttgart</t>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
   </si>
   <si>
     <t>Aberdeen</t>
   </si>
   <si>
-    <t>Fulham</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion</t>
   </si>
   <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
     <t>Vaprus</t>
   </si>
   <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
+    <t>Albacete Balompié</t>
+  </si>
+  <si>
+    <t>Sevilla FC</t>
   </si>
   <si>
     <t>Burgos CF</t>
   </si>
   <si>
-    <t>Albacete Balompié</t>
-  </si>
-  <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
     <t>Sandviken</t>
   </si>
   <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
     <t>Wattens</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
     <t>Grazer AK</t>
   </si>
   <si>
-    <t>AEL</t>
+    <t>Koper</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Sumqayıt</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Athletic Club W</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
     <t>Winterthur</t>
   </si>
   <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Athletic Club W</t>
-  </si>
-  <si>
     <t>Prostějov</t>
   </si>
   <si>
@@ -961,121 +961,145 @@
     <t>Al Najma</t>
   </si>
   <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
     <t>Wolfsburg</t>
   </si>
   <si>
     <t>Recoleta</t>
   </si>
   <si>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
     <t>Atromitos</t>
   </si>
   <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Kocaelispor</t>
+  </si>
+  <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
-    <t>Džiugas Telšiai</t>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
   </si>
   <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>İstanbul Başakşehir</t>
-  </si>
-  <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
     <t>Galatasaray</t>
   </si>
   <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Alanyaspor</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Kocaelispor</t>
-  </si>
-  <si>
     <t>Beşiktaş</t>
   </si>
   <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
     <t>Stal Mielec</t>
   </si>
   <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Rouen</t>
   </si>
   <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
     <t>Paris 13 Atletico</t>
   </si>
   <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Orléans</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
-    <t>Partizan</t>
+    <t>Reims</t>
+  </si>
+  <si>
+    <t>Laval</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Magesi</t>
   </si>
   <si>
     <t>Clermont</t>
   </si>
   <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
     <t>Nancy</t>
   </si>
   <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
   </si>
   <si>
     <t>Saint-Étienne</t>
@@ -1084,90 +1108,66 @@
     <t>Bastia</t>
   </si>
   <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Red Star</t>
+    <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Górnik Zabrze</t>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
   </si>
   <si>
     <t>Acassuso</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>CD Mafra</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
     <t>Goiás</t>
   </si>
   <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>CD Mafra</t>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
   </si>
   <si>
     <t>Real Oruro</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
@@ -1177,135 +1177,135 @@
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>Guayaquil City FC</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>St. Louis City II</t>
   </si>
   <si>
-    <t>Guayaquil City FC</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Guabirá</t>
   </si>
   <si>
+    <t>SD Aucas</t>
+  </si>
+  <si>
     <t>Ponte Preta</t>
   </si>
   <si>
-    <t>SD Aucas</t>
-  </si>
-  <si>
     <t>Ceará</t>
   </si>
   <si>
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
-    <t>Louisville City</t>
-  </si>
-  <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
     <t>CRB</t>
   </si>
   <si>
     <t>Real Tomayapo</t>
   </si>
   <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
     <t>Rio Ave FC</t>
   </si>
   <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
     <t>Benfica</t>
   </si>
   <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
     <t>Grafičar</t>
   </si>
   <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
     <t>Santa Clara</t>
   </si>
   <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
     <t>GD Chaves</t>
   </si>
   <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1330,45 +1330,45 @@
     <t>Phoenix Rising</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>Adelaide United</t>
   </si>
   <si>
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1384,126 +1384,126 @@
     <t>Badalona W</t>
   </si>
   <si>
+    <t>Granada W</t>
+  </si>
+  <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
     <t>Atyrau</t>
   </si>
   <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
-    <t>Granada W</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Magdeburg</t>
   </si>
   <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
     <t>Zhenys</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Sesvete</t>
   </si>
   <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Tanjong Pagar</t>
   </si>
   <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Geylang International</t>
   </si>
   <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
     <t>Baník Ostrava</t>
   </si>
   <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
     <t>Zlín</t>
   </si>
   <si>
     <t>Verl</t>
   </si>
   <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,201 +1513,201 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>AIK Women</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Norrköping W</t>
+  </si>
+  <si>
+    <t>Helsingborg</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
     <t>Kifisia</t>
   </si>
   <si>
-    <t>Norrköping W</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
     <t>FC Caspiy</t>
   </si>
   <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>AIK Women</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
-    <t>Helsingborg</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>Borussia M'gladbach</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
-    <t>Borussia M'gladbach</t>
-  </si>
-  <si>
     <t>St. Pauli</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Alhama</t>
+  </si>
+  <si>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
   </si>
   <si>
     <t>Dundee United</t>
   </si>
   <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
     <t>Wolverhampton Wanderers</t>
   </si>
   <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
     <t>Trans</t>
   </si>
   <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
+    <t>Cultural y Deportiva Leonesa</t>
+  </si>
+  <si>
+    <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Almería</t>
   </si>
   <si>
-    <t>Cultural y Deportiva Leonesa</t>
-  </si>
-  <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Ljungskile</t>
   </si>
   <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Akritas</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
     <t>Orijent 1919</t>
   </si>
   <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
     <t>Blau-Weiß Linz</t>
   </si>
   <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
-    <t>Olympiakos</t>
+    <t>Aluminij</t>
   </si>
   <si>
     <t>Siwelele</t>
   </si>
   <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Araz</t>
+  </si>
+  <si>
+    <t>Pogoń Szczecin</t>
+  </si>
+  <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Aluminij</t>
-  </si>
-  <si>
-    <t>Araz</t>
-  </si>
-  <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Deportivo de La Coruña W</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
-    <t>Deportivo de La Coruña W</t>
-  </si>
-  <si>
     <t>České Budějovice</t>
   </si>
   <si>
@@ -1720,121 +1720,145 @@
     <t>Al Hazm</t>
   </si>
   <si>
+    <t>Brentford</t>
+  </si>
+  <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
     <t>Bayern München</t>
   </si>
   <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
     <t>Panaitolikos</t>
   </si>
   <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Fatih Karagümrük</t>
+  </si>
+  <si>
+    <t>Samsunspor</t>
+  </si>
+  <si>
+    <t>Trakai</t>
+  </si>
+  <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
-    <t>Trakai</t>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
   </si>
   <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Samsunspor</t>
-  </si>
-  <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
     <t>Antalyaspor</t>
   </si>
   <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Kayserispor</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Fatih Karagümrük</t>
-  </si>
-  <si>
     <t>Trabzonspor</t>
   </si>
   <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
     <t>Versailles</t>
   </si>
   <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
     <t>Aubagne</t>
   </si>
   <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
-    <t>OFK Beograd</t>
+    <t>Pau</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
   </si>
   <si>
     <t>Guingamp</t>
   </si>
   <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
     <t>Dunkerque</t>
   </si>
   <si>
-    <t>Troyes</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
   </si>
   <si>
     <t>Amiens SC</t>
@@ -1843,90 +1867,66 @@
     <t>Le Mans</t>
   </si>
   <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
+    <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
+    <t>Estudiantes Caseros</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
+    <t>New York RB</t>
   </si>
   <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
-    <t>Estudiantes Caseros</t>
-  </si>
-  <si>
-    <t>Delfin SC</t>
-  </si>
-  <si>
     <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Associação Académica de Coimbra OAF</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Associação Académica de Coimbra OAF</t>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Whitecaps II</t>
   </si>
   <si>
@@ -1936,135 +1936,135 @@
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
+    <t>CD Universidad Católica</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>CD Universidad Católica</t>
-  </si>
-  <si>
     <t>Atlético GO</t>
   </si>
   <si>
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>Tampa Bay Rowdies</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Tampa Bay Rowdies</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
     <t>Sporting CP</t>
   </si>
   <si>
+    <t>Torreense</t>
+  </si>
+  <si>
     <t>Sporting Braga</t>
   </si>
   <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
     <t>Dubočica</t>
   </si>
   <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
     <t>CD Nacional</t>
   </si>
   <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
     <t>Leixões</t>
   </si>
   <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2089,10 +2089,10 @@
     <t>San Antonio</t>
   </si>
   <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>San Diego</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3768,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>185</v>
@@ -3807,13 +3807,13 @@
         <v>694</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -3992,13 +3992,13 @@
         <v>694</v>
       </c>
       <c r="P9">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4323,7 +4323,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
         <v>185</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5433,10 +5433,10 @@
         <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5618,10 +5618,10 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
         <v>204</v>
@@ -5806,7 +5806,7 @@
         <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5988,10 +5988,10 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6442,10 +6442,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -6543,10 +6543,10 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6582,13 +6582,13 @@
         <v>694</v>
       </c>
       <c r="P23">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q23">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="R23">
-        <v>3.58</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6728,7 +6728,7 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
         <v>185</v>
@@ -6767,13 +6767,13 @@
         <v>694</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R26">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7182,10 +7182,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7322,13 +7322,13 @@
         <v>694</v>
       </c>
       <c r="P27">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -7653,10 +7653,10 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E29" t="s">
         <v>215</v>
@@ -7838,10 +7838,10 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E30" t="s">
         <v>216</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -8023,10 +8023,10 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8617,13 +8617,13 @@
         <v>694</v>
       </c>
       <c r="P34">
-        <v>3.59</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>4.17</v>
       </c>
       <c r="R34">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8662,10 +8662,10 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8802,13 +8802,13 @@
         <v>694</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8847,10 +8847,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8948,7 +8948,7 @@
         <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
         <v>185</v>
@@ -9136,7 +9136,7 @@
         <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9321,7 +9321,7 @@
         <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9357,13 +9357,13 @@
         <v>694</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="Q38">
-        <v>4.17</v>
+        <v>5.4</v>
       </c>
       <c r="R38">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9506,7 +9506,7 @@
         <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9688,7 +9688,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
         <v>187</v>
@@ -10058,7 +10058,7 @@
         <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
         <v>186</v>
@@ -10243,10 +10243,10 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10282,13 +10282,13 @@
         <v>694</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -10431,7 +10431,7 @@
         <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10798,10 +10798,10 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -10983,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
@@ -11168,7 +11168,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
@@ -11207,13 +11207,13 @@
         <v>694</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D49" t="s">
         <v>186</v>
@@ -11723,7 +11723,7 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D51" t="s">
         <v>185</v>
@@ -11762,13 +11762,13 @@
         <v>694</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -12278,10 +12278,10 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
         <v>240</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -12687,13 +12687,13 @@
         <v>694</v>
       </c>
       <c r="P56">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -13388,7 +13388,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
         <v>186</v>
@@ -13427,13 +13427,13 @@
         <v>694</v>
       </c>
       <c r="P60">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13573,7 +13573,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D61" t="s">
         <v>185</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13758,7 +13758,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D62" t="s">
         <v>185</v>
@@ -13797,13 +13797,13 @@
         <v>694</v>
       </c>
       <c r="P62">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D63" t="s">
         <v>185</v>
@@ -13982,13 +13982,13 @@
         <v>694</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14128,7 +14128,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -14313,10 +14313,10 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14498,7 +14498,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D66" t="s">
         <v>185</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>3.26</v>
+        <v>2.65</v>
       </c>
       <c r="Q66">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14722,13 +14722,13 @@
         <v>694</v>
       </c>
       <c r="P67">
-        <v>3.12</v>
+        <v>1.49</v>
       </c>
       <c r="Q67">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="R67">
-        <v>2.27</v>
+        <v>5.16</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14868,10 +14868,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -15053,10 +15053,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>2.54</v>
+        <v>3.26</v>
       </c>
       <c r="Q69">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R69">
-        <v>3.21</v>
+        <v>2.19</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
         <v>186</v>
@@ -15277,13 +15277,13 @@
         <v>694</v>
       </c>
       <c r="P70">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15608,7 +15608,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="D72" t="s">
         <v>186</v>
@@ -15647,13 +15647,13 @@
         <v>694</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15793,10 +15793,10 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15832,13 +15832,13 @@
         <v>694</v>
       </c>
       <c r="P73">
-        <v>2.65</v>
+        <v>3.13</v>
       </c>
       <c r="Q73">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R73">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -15978,10 +15978,10 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="D74" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E74" t="s">
         <v>260</v>
@@ -16387,61 +16387,61 @@
         <v>694</v>
       </c>
       <c r="P76">
+        <v>2.38</v>
+      </c>
+      <c r="Q76">
+        <v>3.71</v>
+      </c>
+      <c r="R76">
+        <v>3.07</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
+      <c r="AE76">
         <v>1.61</v>
       </c>
-      <c r="Q76">
-        <v>4.88</v>
-      </c>
-      <c r="R76">
-        <v>5.33</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>0</v>
-      </c>
-      <c r="Z76">
-        <v>0</v>
-      </c>
-      <c r="AA76">
-        <v>0</v>
-      </c>
-      <c r="AB76">
-        <v>0</v>
-      </c>
-      <c r="AC76">
-        <v>0</v>
-      </c>
-      <c r="AD76">
-        <v>0</v>
-      </c>
-      <c r="AE76">
-        <v>0</v>
-      </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG76">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH76">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16572,13 +16572,13 @@
         <v>694</v>
       </c>
       <c r="P77">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q77">
-        <v>3.71</v>
+        <v>4.16</v>
       </c>
       <c r="R77">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16617,16 +16617,16 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Q78">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="R78">
-        <v>7.21</v>
+        <v>5.33</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AH78">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16942,13 +16942,13 @@
         <v>694</v>
       </c>
       <c r="P79">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="Q79">
-        <v>4.16</v>
+        <v>5.18</v>
       </c>
       <c r="R79">
-        <v>3.23</v>
+        <v>7.21</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16993,10 +16993,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH79">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q80">
-        <v>3.62</v>
+        <v>4.13</v>
       </c>
       <c r="R80">
-        <v>3.11</v>
+        <v>4.85</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17172,10 +17172,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17312,13 +17312,13 @@
         <v>694</v>
       </c>
       <c r="P81">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="Q81">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="R81">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17357,10 +17357,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17497,13 +17497,13 @@
         <v>694</v>
       </c>
       <c r="P82">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>2.32</v>
+        <v>4.06</v>
       </c>
       <c r="Q83">
-        <v>3.01</v>
+        <v>3.98</v>
       </c>
       <c r="R83">
-        <v>3.11</v>
+        <v>1.93</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18097,10 +18097,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18198,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18383,7 +18383,7 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
         <v>186</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18467,10 +18467,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="Q88">
-        <v>3.46</v>
+        <v>3.01</v>
       </c>
       <c r="R88">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG88">
         <v>0</v>
@@ -18753,7 +18753,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18792,13 +18792,13 @@
         <v>694</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E90" t="s">
         <v>276</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19347,13 +19347,13 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19392,10 +19392,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19493,7 +19493,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="Q93">
-        <v>4.13</v>
+        <v>5.48</v>
       </c>
       <c r="R93">
-        <v>4.85</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19678,10 +19678,10 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D94" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E94" t="s">
         <v>280</v>
@@ -19717,13 +19717,13 @@
         <v>694</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="Q95">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="R95">
-        <v>3.32</v>
+        <v>2.43</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -19947,10 +19947,10 @@
         <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>2.04</v>
       </c>
       <c r="Q96">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R96">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20317,10 +20317,10 @@
         <v>0</v>
       </c>
       <c r="AE97">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="D100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q100">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R100">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20872,10 +20872,10 @@
         <v>0</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG100">
         <v>0</v>
@@ -20973,10 +20973,10 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="D101" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21158,7 +21158,7 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="Q102">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="R102">
-        <v>4.4</v>
+        <v>3.27</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AF102">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21343,7 +21343,7 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21713,7 +21713,7 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22268,10 +22268,10 @@
         <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="D108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E108" t="s">
         <v>294</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="Q108">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R108">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22352,10 +22352,10 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG108">
         <v>0</v>
@@ -22456,7 +22456,7 @@
         <v>124</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E109" t="s">
         <v>295</v>
@@ -22823,7 +22823,7 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D111" t="s">
         <v>186</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q111">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R111">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22907,10 +22907,10 @@
         <v>0</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
         <v>0</v>
@@ -23008,7 +23008,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q112">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="R112">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23092,10 +23092,10 @@
         <v>0</v>
       </c>
       <c r="AE112">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF112">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG112">
         <v>0</v>
@@ -23232,13 +23232,13 @@
         <v>694</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23787,13 +23787,13 @@
         <v>694</v>
       </c>
       <c r="P116">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -23972,13 +23972,13 @@
         <v>694</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24157,13 +24157,13 @@
         <v>694</v>
       </c>
       <c r="P118">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q118">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24673,7 +24673,7 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="D121" t="s">
         <v>186</v>
@@ -24712,13 +24712,13 @@
         <v>694</v>
       </c>
       <c r="P121">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26192,13 +26192,13 @@
         <v>694</v>
       </c>
       <c r="P129">
-        <v>5.74</v>
+        <v>1.36</v>
       </c>
       <c r="Q129">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="R129">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26338,10 +26338,10 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130" t="s">
         <v>316</v>
@@ -26523,7 +26523,7 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>1.93</v>
+        <v>5.74</v>
       </c>
       <c r="Q131">
-        <v>3.33</v>
+        <v>5.53</v>
       </c>
       <c r="R131">
-        <v>3.96</v>
+        <v>1.51</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,10 +26708,10 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="D132" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E132" t="s">
         <v>318</v>
@@ -26893,7 +26893,7 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
         <v>186</v>
@@ -26932,13 +26932,13 @@
         <v>694</v>
       </c>
       <c r="P133">
-        <v>1.36</v>
+        <v>2.19</v>
       </c>
       <c r="Q133">
-        <v>6.19</v>
+        <v>3.37</v>
       </c>
       <c r="R133">
-        <v>8.6</v>
+        <v>3.47</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -26977,10 +26977,10 @@
         <v>0</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG133">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27117,13 +27117,13 @@
         <v>694</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27263,7 +27263,7 @@
         <v>92</v>
       </c>
       <c r="C135" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27633,10 +27633,10 @@
         <v>93</v>
       </c>
       <c r="C137" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D137" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27818,10 +27818,10 @@
         <v>93</v>
       </c>
       <c r="C138" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D138" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
@@ -28373,10 +28373,10 @@
         <v>93</v>
       </c>
       <c r="C141" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D141" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E141" t="s">
         <v>327</v>
@@ -28412,13 +28412,13 @@
         <v>694</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28463,10 +28463,10 @@
         <v>0</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH141">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI141">
         <v>0</v>
@@ -28743,7 +28743,7 @@
         <v>93</v>
       </c>
       <c r="C143" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -28928,10 +28928,10 @@
         <v>93</v>
       </c>
       <c r="C144" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E144" t="s">
         <v>330</v>
@@ -28967,13 +28967,13 @@
         <v>694</v>
       </c>
       <c r="P144">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q144">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R144">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S144">
         <v>0</v>
@@ -29018,10 +29018,10 @@
         <v>0</v>
       </c>
       <c r="AG144">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH144">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI144">
         <v>0</v>
@@ -30038,7 +30038,7 @@
         <v>95</v>
       </c>
       <c r="C150" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30262,13 +30262,13 @@
         <v>694</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30408,7 +30408,7 @@
         <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31888,7 +31888,7 @@
         <v>95</v>
       </c>
       <c r="C160" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D160" t="s">
         <v>186</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32297,13 +32297,13 @@
         <v>694</v>
       </c>
       <c r="P162">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q162">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R162">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S162">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>95</v>
       </c>
       <c r="C163" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D163" t="s">
         <v>186</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>2.89</v>
+        <v>1.45</v>
       </c>
       <c r="Q164">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="R164">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF164">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>2.61</v>
+        <v>1.73</v>
       </c>
       <c r="Q165">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="R165">
-        <v>2.56</v>
+        <v>4.61</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32897,10 +32897,10 @@
         <v>0</v>
       </c>
       <c r="AE165">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF165">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG165">
         <v>0</v>
@@ -33037,13 +33037,13 @@
         <v>694</v>
       </c>
       <c r="P166">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q166">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R166">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S166">
         <v>0</v>
@@ -33082,10 +33082,10 @@
         <v>0</v>
       </c>
       <c r="AE166">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF166">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG166">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>1.3</v>
+        <v>2.89</v>
       </c>
       <c r="Q168">
-        <v>5.65</v>
+        <v>3.32</v>
       </c>
       <c r="R168">
-        <v>8.4</v>
+        <v>2.38</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33452,16 +33452,16 @@
         <v>0</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG168">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH168">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI168">
         <v>0</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>3.03</v>
+        <v>3.79</v>
       </c>
       <c r="Q169">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="R169">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33637,10 +33637,10 @@
         <v>0</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33777,13 +33777,13 @@
         <v>694</v>
       </c>
       <c r="P170">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q170">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R170">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33923,10 +33923,10 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D171" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E171" t="s">
         <v>357</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q171">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R171">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="Q172">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="R172">
-        <v>4.61</v>
+        <v>2.56</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34192,10 +34192,10 @@
         <v>0</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R173">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="Q174">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="R174">
-        <v>6</v>
+        <v>3.37</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34848,10 +34848,10 @@
         <v>96</v>
       </c>
       <c r="C176" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E176" t="s">
         <v>362</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -34938,10 +34938,10 @@
         <v>0</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH176">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI176">
         <v>0</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35218,7 +35218,7 @@
         <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35257,13 +35257,13 @@
         <v>694</v>
       </c>
       <c r="P178">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q178">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="R178">
-        <v>3.57</v>
+        <v>4.81</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35302,10 +35302,10 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG178">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35442,13 +35442,13 @@
         <v>694</v>
       </c>
       <c r="P179">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="Q179">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="R179">
-        <v>4.81</v>
+        <v>3.57</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35487,10 +35487,10 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF179">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q180">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R180">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35672,10 +35672,10 @@
         <v>0</v>
       </c>
       <c r="AE180">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF180">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG180">
         <v>0</v>
@@ -35773,7 +35773,7 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q181">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R181">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35863,10 +35863,10 @@
         <v>0</v>
       </c>
       <c r="AG181">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH181">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI181">
         <v>0</v>
@@ -36143,10 +36143,10 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D183" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E183" t="s">
         <v>369</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36328,10 +36328,10 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D184" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q184">
-        <v>3.76</v>
+        <v>3.02</v>
       </c>
       <c r="R184">
-        <v>2.92</v>
+        <v>3.53</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D185" t="s">
         <v>185</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36603,10 +36603,10 @@
         <v>0</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH185">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI185">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D186" t="s">
         <v>185</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="Q186">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="R186">
-        <v>3.53</v>
+        <v>2.75</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36782,10 +36782,10 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37253,10 +37253,10 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -37438,10 +37438,10 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="D190" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E190" t="s">
         <v>376</v>
@@ -37477,13 +37477,13 @@
         <v>694</v>
       </c>
       <c r="P190">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="Q190">
-        <v>3.73</v>
+        <v>3.17</v>
       </c>
       <c r="R190">
-        <v>3.71</v>
+        <v>3.15</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37623,7 +37623,7 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37662,13 +37662,13 @@
         <v>694</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37707,10 +37707,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37808,7 +37808,7 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -37847,13 +37847,13 @@
         <v>694</v>
       </c>
       <c r="P192">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="Q192">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="R192">
-        <v>2.6</v>
+        <v>3.71</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -37892,10 +37892,10 @@
         <v>0</v>
       </c>
       <c r="AE192">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF192">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG192">
         <v>0</v>
@@ -37993,7 +37993,7 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D193" t="s">
         <v>186</v>
@@ -38772,13 +38772,13 @@
         <v>694</v>
       </c>
       <c r="P197">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q197">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R197">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -39512,13 +39512,13 @@
         <v>694</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>103</v>
       </c>
       <c r="C202" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39697,13 +39697,13 @@
         <v>694</v>
       </c>
       <c r="P202">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q202">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -40398,7 +40398,7 @@
         <v>105</v>
       </c>
       <c r="C206" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D206" t="s">
         <v>185</v>
@@ -40583,7 +40583,7 @@
         <v>105</v>
       </c>
       <c r="C207" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D207" t="s">
         <v>185</v>
@@ -40622,13 +40622,13 @@
         <v>694</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S207">
         <v>0</v>
@@ -40667,10 +40667,10 @@
         <v>0</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG207">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>106</v>
       </c>
       <c r="C208" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D208" t="s">
         <v>185</v>
@@ -40807,13 +40807,13 @@
         <v>694</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="S208">
         <v>0</v>
@@ -41177,13 +41177,13 @@
         <v>694</v>
       </c>
       <c r="P210">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q210">
         <v>3.4</v>
       </c>
       <c r="R210">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41222,10 +41222,10 @@
         <v>0</v>
       </c>
       <c r="AE210">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF210">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG210">
         <v>0</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q211">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R211">
-        <v>2.65</v>
+        <v>5.53</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41550,10 +41550,10 @@
         <v>1.57</v>
       </c>
       <c r="Q212">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R212">
-        <v>5.53</v>
+        <v>4.75</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41732,13 +41732,13 @@
         <v>694</v>
       </c>
       <c r="P213">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q213">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R213">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -41777,10 +41777,10 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -42063,7 +42063,7 @@
         <v>109</v>
       </c>
       <c r="C215" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D215" t="s">
         <v>185</v>
@@ -42102,13 +42102,13 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q215">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="R215">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42147,10 +42147,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF215">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42248,7 +42248,7 @@
         <v>109</v>
       </c>
       <c r="C216" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q216">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R216">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q217">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="R217">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AF217">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42657,13 +42657,13 @@
         <v>694</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -43173,7 +43173,7 @@
         <v>110</v>
       </c>
       <c r="C221" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D221" t="s">
         <v>186</v>
@@ -43543,7 +43543,7 @@
         <v>110</v>
       </c>
       <c r="C223" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D223" t="s">
         <v>186</v>
@@ -43728,7 +43728,7 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43913,10 +43913,10 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="D225" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -44098,10 +44098,10 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44283,7 +44283,7 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D227" t="s">
         <v>185</v>
@@ -44322,13 +44322,13 @@
         <v>694</v>
       </c>
       <c r="P227">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q227">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R227">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S227">
         <v>0</v>
@@ -44367,10 +44367,10 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF227">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG227">
         <v>0</v>
@@ -44468,10 +44468,10 @@
         <v>110</v>
       </c>
       <c r="C228" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44507,13 +44507,13 @@
         <v>694</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44552,10 +44552,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44653,7 +44653,7 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D229" t="s">
         <v>186</v>
@@ -44838,10 +44838,10 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D230" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E230" t="s">
         <v>416</v>
@@ -44877,13 +44877,13 @@
         <v>694</v>
       </c>
       <c r="P230">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q230">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R230">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S230">
         <v>0</v>
@@ -45023,10 +45023,10 @@
         <v>110</v>
       </c>
       <c r="C231" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D231" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E231" t="s">
         <v>417</v>
@@ -45208,7 +45208,7 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D232" t="s">
         <v>186</v>
@@ -45393,7 +45393,7 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D233" t="s">
         <v>186</v>
@@ -45763,10 +45763,10 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D235" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E235" t="s">
         <v>421</v>
@@ -46133,7 +46133,7 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D237" t="s">
         <v>186</v>
@@ -46688,7 +46688,7 @@
         <v>110</v>
       </c>
       <c r="C240" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D240" t="s">
         <v>185</v>
@@ -46727,13 +46727,13 @@
         <v>694</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S240">
         <v>0</v>
@@ -46873,7 +46873,7 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
         <v>186</v>
@@ -47243,7 +47243,7 @@
         <v>110</v>
       </c>
       <c r="C243" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D243" t="s">
         <v>186</v>
@@ -47428,7 +47428,7 @@
         <v>111</v>
       </c>
       <c r="C244" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D244" t="s">
         <v>185</v>
@@ -47467,13 +47467,13 @@
         <v>694</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S244">
         <v>0</v>
@@ -47837,13 +47837,13 @@
         <v>694</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S246">
         <v>0</v>
@@ -47882,10 +47882,10 @@
         <v>0</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG246">
         <v>0</v>
@@ -48947,61 +48947,61 @@
         <v>694</v>
       </c>
       <c r="P252">
+        <v>1.46</v>
+      </c>
+      <c r="Q252">
+        <v>4.6</v>
+      </c>
+      <c r="R252">
+        <v>5.15</v>
+      </c>
+      <c r="S252">
+        <v>0</v>
+      </c>
+      <c r="T252">
+        <v>0</v>
+      </c>
+      <c r="U252">
+        <v>0</v>
+      </c>
+      <c r="V252">
+        <v>0</v>
+      </c>
+      <c r="W252">
+        <v>0</v>
+      </c>
+      <c r="X252">
+        <v>0</v>
+      </c>
+      <c r="Y252">
+        <v>0</v>
+      </c>
+      <c r="Z252">
+        <v>0</v>
+      </c>
+      <c r="AA252">
+        <v>0</v>
+      </c>
+      <c r="AB252">
+        <v>0</v>
+      </c>
+      <c r="AC252">
+        <v>0</v>
+      </c>
+      <c r="AD252">
+        <v>0</v>
+      </c>
+      <c r="AE252">
+        <v>0</v>
+      </c>
+      <c r="AF252">
+        <v>0</v>
+      </c>
+      <c r="AG252">
+        <v>1.95</v>
+      </c>
+      <c r="AH252">
         <v>1.75</v>
-      </c>
-      <c r="Q252">
-        <v>3.9</v>
-      </c>
-      <c r="R252">
-        <v>4.2</v>
-      </c>
-      <c r="S252">
-        <v>0</v>
-      </c>
-      <c r="T252">
-        <v>0</v>
-      </c>
-      <c r="U252">
-        <v>0</v>
-      </c>
-      <c r="V252">
-        <v>0</v>
-      </c>
-      <c r="W252">
-        <v>0</v>
-      </c>
-      <c r="X252">
-        <v>0</v>
-      </c>
-      <c r="Y252">
-        <v>0</v>
-      </c>
-      <c r="Z252">
-        <v>0</v>
-      </c>
-      <c r="AA252">
-        <v>0</v>
-      </c>
-      <c r="AB252">
-        <v>0</v>
-      </c>
-      <c r="AC252">
-        <v>0</v>
-      </c>
-      <c r="AD252">
-        <v>0</v>
-      </c>
-      <c r="AE252">
-        <v>1.61</v>
-      </c>
-      <c r="AF252">
-        <v>2.15</v>
-      </c>
-      <c r="AG252">
-        <v>0</v>
-      </c>
-      <c r="AH252">
-        <v>0</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q253">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R253">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49177,16 +49177,16 @@
         <v>0</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG253">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH253">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI253">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,12 +370,12 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>Australia New South Wales NPL</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>Australia New South Wales NPL</t>
-  </si>
-  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
@@ -385,15 +385,15 @@
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
@@ -415,102 +415,102 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Singapore S.League</t>
+  </si>
+  <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
-    <t>Singapore S.League</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Malaysia Super League</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>South Africa Premier Soccer League</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>South Africa Premier Soccer League</t>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Azerbaijan Premyer Liqası</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Greece Super League</t>
   </si>
   <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
@@ -541,18 +541,18 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Portugal Liga NOS</t>
   </si>
   <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -580,15 +580,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Western Sydney W. II</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
-    <t>Western Sydney W. II</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
     <t>Jeju United</t>
   </si>
   <si>
@@ -598,18 +598,18 @@
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Suwon Bluewings</t>
   </si>
   <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -622,129 +622,129 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Kedus Giorgis</t>
+  </si>
+  <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
     <t>Espanyol W</t>
   </si>
   <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
-    <t>Kedus Giorgis</t>
-  </si>
-  <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>Bochum</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Eintracht Braunschweig</t>
   </si>
   <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
     <t>Östersunds FK</t>
   </si>
   <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
-    <t>Bochum</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
-  </si>
-  <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Tallinna FC Levadia</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Balestier Khalsa</t>
+  </si>
+  <si>
     <t>Liverpool</t>
   </si>
   <si>
-    <t>Goa</t>
+    <t>Young Lions</t>
   </si>
   <si>
     <t>Nanjing City</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Balestier Khalsa</t>
-  </si>
-  <si>
-    <t>Young Lions</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
     <t>Elche CF</t>
   </si>
   <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
     <t>Persis Solo</t>
   </si>
   <si>
-    <t>Brommapojkarna W</t>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
   </si>
   <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Ceuta</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>1860 München</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
     <t>Teplice</t>
   </si>
   <si>
     <t>Mladá Boleslav</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,51 +754,51 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Degerfors</t>
+  </si>
+  <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
+    <t>Qabala</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
     <t>Växjö</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
     <t>Kristianstad</t>
   </si>
   <si>
+    <t>Panserraikos</t>
+  </si>
+  <si>
     <t>Norrby</t>
   </si>
   <si>
-    <t>Bravo</t>
-  </si>
-  <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Degerfors</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Qabala</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
-  </si>
-  <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
     <t>Cherno More</t>
   </si>
   <si>
@@ -808,58 +808,61 @@
     <t>Stuttgart</t>
   </si>
   <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
     <t>Hoffenheim</t>
   </si>
   <si>
-    <t>RB Leipzig</t>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>RAAL La Louvière</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Fulham</t>
+  </si>
+  <si>
+    <t>Dinamo Zagreb</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
   </si>
   <si>
     <t>Zulte-Waregem</t>
   </si>
   <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
+    <t>Eibar W</t>
   </si>
   <si>
     <t>CD Trofense</t>
   </si>
   <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Larissa</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
-    <t>RAAL La Louvière</t>
+    <t>Burgos CF</t>
   </si>
   <si>
     <t>Albacete Balompié</t>
@@ -868,49 +871,55 @@
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Burgos CF</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Wattens</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
     <t>Omonia Aradippou</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Wattens</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
+  </si>
+  <si>
+    <t>Sumqayıt</t>
   </si>
   <si>
     <t>Koper</t>
@@ -922,36 +931,27 @@
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
     <t>Winterthur</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Lazio</t>
   </si>
   <si>
@@ -961,213 +961,213 @@
     <t>Al Najma</t>
   </si>
   <si>
+    <t>Atromitos</t>
+  </si>
+  <si>
+    <t>Wolfsburg</t>
+  </si>
+  <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Atlético Madrid</t>
   </si>
   <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
     <t>Recoleta</t>
   </si>
   <si>
     <t>Real Valladolid</t>
   </si>
   <si>
-    <t>Atromitos</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Džiugas Telšiai</t>
+  </si>
+  <si>
+    <t>Gençlerbirliği</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
     <t>Kocaelispor</t>
   </si>
   <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>İstanbul Başakşehir</t>
   </si>
   <si>
-    <t>Džiugas Telšiai</t>
-  </si>
-  <si>
-    <t>Gençlerbirliği</t>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
   </si>
   <si>
     <t>Eyüpspor</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Wieczysta Kraków</t>
+  </si>
+  <si>
+    <t>Stade Briochin</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
     <t>Stal Mielec</t>
   </si>
   <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Wieczysta Kraków</t>
-  </si>
-  <si>
     <t>Znicz Pruszków</t>
   </si>
   <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Stade Briochin</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Rouen</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
     <t>Orléans</t>
   </si>
   <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Paris 13 Atletico</t>
+    <t>Nancy</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
+  </si>
+  <si>
+    <t>Red Star</t>
+  </si>
+  <si>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Annecy</t>
+  </si>
+  <si>
+    <t>Clermont</t>
+  </si>
+  <si>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Laval</t>
   </si>
   <si>
     <t>Reims</t>
   </si>
   <si>
-    <t>Laval</t>
-  </si>
-  <si>
-    <t>Red Star</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Nancy</t>
-  </si>
-  <si>
-    <t>Annecy</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Saint-Étienne</t>
-  </si>
-  <si>
-    <t>Bastia</t>
+    <t>Maribor</t>
   </si>
   <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
-    <t>Maribor</t>
+    <t>Chicago Fire</t>
   </si>
   <si>
     <t>San Miguel</t>
   </si>
   <si>
+    <t>Acassuso</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
     <t>Temperley</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Técnico Universitario</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Club Brugge</t>
   </si>
   <si>
+    <t>Málaga CF</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Raja Casablanca</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
     <t>CD Mafra</t>
   </si>
   <si>
     <t>Coritiba</t>
   </si>
   <si>
-    <t>Motherwell</t>
-  </si>
-  <si>
-    <t>Málaga CF</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
-    <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
@@ -1177,18 +1177,18 @@
     <t>Montreal Impact</t>
   </si>
   <si>
+    <t>St. Louis City II</t>
+  </si>
+  <si>
     <t>Guayaquil City FC</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>St. Louis City II</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1204,108 +1204,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Indy Eleven</t>
+  </si>
+  <si>
     <t>Hartford Athletic</t>
   </si>
   <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
     <t>Louisville City</t>
   </si>
   <si>
-    <t>Indy Eleven</t>
-  </si>
-  <si>
-    <t>Brooklyn FC</t>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>CRB</t>
   </si>
   <si>
     <t>New England Revolution</t>
   </si>
   <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
     <t>Real Tomayapo</t>
   </si>
   <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
     <t>AVS</t>
   </si>
   <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
     <t>Benfica II</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
     <t>Estrela Amadora</t>
   </si>
   <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>New Mexico United</t>
+  </si>
+  <si>
     <t>Nashville SC</t>
   </si>
   <si>
-    <t>New Mexico United</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1333,21 +1333,21 @@
     <t>Portland Timbers</t>
   </si>
   <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>SJ Earthquakes</t>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
+    <t>Suwon</t>
   </si>
   <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>FC Seoul</t>
   </si>
   <si>
@@ -1357,18 +1357,18 @@
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Gangwon</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1381,129 +1381,129 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Mekelle Kenema</t>
+  </si>
+  <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Granada W</t>
+  </si>
+  <si>
     <t>Badalona W</t>
   </si>
   <si>
-    <t>Granada W</t>
-  </si>
-  <si>
-    <t>Mekelle Kenema</t>
-  </si>
-  <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Arsenal Women</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
     <t>Magdeburg</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
     <t>Falkenberg</t>
   </si>
   <si>
-    <t>Arsenal Women</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Sesvete</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
+    <t>ATK Mohun Bagan</t>
+  </si>
+  <si>
+    <t>Tanjong Pagar</t>
+  </si>
+  <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>ATK Mohun Bagan</t>
+    <t>Geylang International</t>
   </si>
   <si>
     <t>Meizhou Hakka</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>Geylang International</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
     <t>Deportivo Alavés</t>
   </si>
   <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
     <t>Persebaya Surabaya</t>
   </si>
   <si>
-    <t>Eskilstuna United</t>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>CD Castellón</t>
+  </si>
+  <si>
+    <t>Ulm</t>
   </si>
   <si>
     <t>Stuttgart II</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>CD Castellón</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
     <t>Baník Ostrava</t>
   </si>
   <si>
     <t>Zlín</t>
   </si>
   <si>
-    <t>Verl</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,51 +1513,51 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Chippa United</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
+    <t>FC Caspiy</t>
+  </si>
+  <si>
+    <t>Qarabağ</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>AIK Women</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
     <t>Norrköping W</t>
   </si>
   <si>
+    <t>Kifisia</t>
+  </si>
+  <si>
     <t>Helsingborg</t>
   </si>
   <si>
-    <t>Radomlje</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
-    <t>Chippa United</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Udinese</t>
-  </si>
-  <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
-    <t>FC Caspiy</t>
-  </si>
-  <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
@@ -1567,58 +1567,61 @@
     <t>Bayer Leverkusen</t>
   </si>
   <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
     <t>Werder Bremen</t>
   </si>
   <si>
-    <t>St. Pauli</t>
+    <t>Kilmarnock</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Trans</t>
+  </si>
+  <si>
+    <t>AFC Bournemouth</t>
+  </si>
+  <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
   </si>
   <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Slovan Liberec</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
+    <t>Alhama</t>
   </si>
   <si>
     <t>Vitória Guimarães II</t>
   </si>
   <si>
-    <t>Livingston</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Kilmarnock</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
-    <t>AFC Bournemouth</t>
-  </si>
-  <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Trans</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
+    <t>Almería</t>
   </si>
   <si>
     <t>Cultural y Deportiva Leonesa</t>
@@ -1627,49 +1630,55 @@
     <t>RCD Espanyol</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Irtysh</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
     <t>Akritas</t>
   </si>
   <si>
-    <t>Irtysh</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Pogoń Szczecin</t>
+  </si>
+  <si>
+    <t>Araz</t>
   </si>
   <si>
     <t>Aluminij</t>
@@ -1681,36 +1690,27 @@
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Araz</t>
-  </si>
-  <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Grasshopper</t>
   </si>
   <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Inter Milan</t>
   </si>
   <si>
@@ -1720,213 +1720,213 @@
     <t>Al Hazm</t>
   </si>
   <si>
+    <t>Panaitolikos</t>
+  </si>
+  <si>
+    <t>Bayern München</t>
+  </si>
+  <si>
     <t>Brentford</t>
   </si>
   <si>
     <t>Celta de Vigo</t>
   </si>
   <si>
-    <t>Bayern München</t>
-  </si>
-  <si>
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
-    <t>Panaitolikos</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Trakai</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
+    <t>Kayserispor</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Samsunspor</t>
   </si>
   <si>
-    <t>Trakai</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Sparta Praha</t>
   </si>
   <si>
     <t>Rizespor</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Miedź Legnica</t>
+  </si>
+  <si>
+    <t>Quevilly Rouen</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Versailles</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Miedź Legnica</t>
-  </si>
-  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Quevilly Rouen</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Versailles</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
     <t>Fleury 91</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Aubagne</t>
+    <t>Dunkerque</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
+  </si>
+  <si>
+    <t>Montpellier</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Rodez</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
+  </si>
+  <si>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Boulogne</t>
   </si>
   <si>
     <t>Pau</t>
   </si>
   <si>
-    <t>Boulogne</t>
-  </si>
-  <si>
-    <t>Montpellier</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
     <t>Al Quadisiya</t>
   </si>
   <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
-    <t>Rodez</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Amiens SC</t>
-  </si>
-  <si>
-    <t>Le Mans</t>
+    <t>Olimpija</t>
   </si>
   <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Olimpija</t>
+    <t>New York RB</t>
   </si>
   <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Servette</t>
-  </si>
-  <si>
     <t>Delfin SC</t>
   </si>
   <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
     <t>Juventus</t>
   </si>
   <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Sporting Gijón</t>
+  </si>
+  <si>
+    <t>Unión Española</t>
+  </si>
+  <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
     <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Sporting Gijón</t>
-  </si>
-  <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Unión Española</t>
-  </si>
-  <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
     <t>Whitecaps II</t>
   </si>
   <si>
@@ -1936,18 +1936,18 @@
     <t>Orlando City</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1963,108 +1963,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Sporting JAX</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
+    <t>Loudoun United</t>
+  </si>
+  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
-    <t>Sporting JAX</t>
-  </si>
-  <si>
-    <t>Loudoun United</t>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
   </si>
   <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
-    <t>FC Cincinnati</t>
-  </si>
-  <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
     <t>San Antonio Bulo Bulo</t>
   </si>
   <si>
+    <t>CS Marítimo</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Portimonense</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
     <t>Porto</t>
   </si>
   <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
     <t>Academico Viseu</t>
   </si>
   <si>
-    <t>Portimonense</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>CS Marítimo</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
     <t>Famalicão</t>
   </si>
   <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2074,12 +2074,12 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>DC United</t>
   </si>
   <si>
-    <t>Las Vegas Lights</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
@@ -2092,10 +2092,10 @@
     <t>Sporting KC</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>San Diego</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2697,13 +2697,13 @@
         <v>694</v>
       </c>
       <c r="P2">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         <v>694</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -2927,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
         <v>185</v>
@@ -3067,13 +3067,13 @@
         <v>694</v>
       </c>
       <c r="P4">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="Q4">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3768,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
         <v>185</v>
@@ -3807,13 +3807,13 @@
         <v>694</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4138,7 +4138,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4177,13 +4177,13 @@
         <v>694</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5433,10 +5433,10 @@
         <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5618,7 +5618,7 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
         <v>186</v>
@@ -5806,7 +5806,7 @@
         <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R22">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6442,10 +6442,10 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG22">
         <v>0</v>
@@ -6543,10 +6543,10 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6582,13 +6582,13 @@
         <v>694</v>
       </c>
       <c r="P23">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6728,10 +6728,10 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6767,13 +6767,13 @@
         <v>694</v>
       </c>
       <c r="P24">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7182,10 +7182,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -7507,13 +7507,13 @@
         <v>694</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -7692,13 +7692,13 @@
         <v>694</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7838,10 +7838,10 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
         <v>216</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -8023,7 +8023,7 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
         <v>185</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8581,7 +8581,7 @@
         <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" t="s">
         <v>220</v>
@@ -8617,13 +8617,13 @@
         <v>694</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="Q34">
-        <v>4.17</v>
+        <v>5.4</v>
       </c>
       <c r="R34">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8766,7 +8766,7 @@
         <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -8802,13 +8802,13 @@
         <v>694</v>
       </c>
       <c r="P35">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -8847,10 +8847,10 @@
         <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -8951,7 +8951,7 @@
         <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
         <v>222</v>
@@ -8987,13 +8987,13 @@
         <v>694</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -9133,10 +9133,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E37" t="s">
         <v>223</v>
@@ -9318,10 +9318,10 @@
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
         <v>224</v>
@@ -9357,13 +9357,13 @@
         <v>694</v>
       </c>
       <c r="P38">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>5.4</v>
+        <v>4.17</v>
       </c>
       <c r="R38">
-        <v>9.699999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -9503,7 +9503,7 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D39" t="s">
         <v>187</v>
@@ -9688,10 +9688,10 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -10243,10 +10243,10 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10431,7 +10431,7 @@
         <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
         <v>230</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10798,7 +10798,7 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D46" t="s">
         <v>185</v>
@@ -10837,13 +10837,13 @@
         <v>694</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -11168,7 +11168,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D48" t="s">
         <v>186</v>
@@ -11207,13 +11207,13 @@
         <v>694</v>
       </c>
       <c r="P48">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -11353,10 +11353,10 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
         <v>235</v>
@@ -11538,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11723,10 +11723,10 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
         <v>237</v>
@@ -11762,13 +11762,13 @@
         <v>694</v>
       </c>
       <c r="P51">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -11947,13 +11947,13 @@
         <v>694</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12093,7 +12093,7 @@
         <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" t="s">
         <v>186</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -13388,7 +13388,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D60" t="s">
         <v>186</v>
@@ -13573,7 +13573,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D61" t="s">
         <v>185</v>
@@ -13758,10 +13758,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" t="s">
         <v>248</v>
@@ -13797,13 +13797,13 @@
         <v>694</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13943,7 +13943,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D63" t="s">
         <v>185</v>
@@ -13982,13 +13982,13 @@
         <v>694</v>
       </c>
       <c r="P63">
-        <v>3.95</v>
+        <v>3.26</v>
       </c>
       <c r="Q63">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R63">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14128,10 +14128,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
         <v>250</v>
@@ -14313,10 +14313,10 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
         <v>251</v>
@@ -14498,7 +14498,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
         <v>185</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="Q66">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R66">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,7 +14683,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D67" t="s">
         <v>186</v>
@@ -14868,7 +14868,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
         <v>186</v>
@@ -15053,10 +15053,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
         <v>255</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15608,10 +15608,10 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E72" t="s">
         <v>258</v>
@@ -15647,13 +15647,13 @@
         <v>694</v>
       </c>
       <c r="P72">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -15978,7 +15978,7 @@
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D74" t="s">
         <v>185</v>
@@ -16017,13 +16017,13 @@
         <v>694</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="Q78">
-        <v>4.88</v>
+        <v>5.18</v>
       </c>
       <c r="R78">
-        <v>5.33</v>
+        <v>7.21</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH78">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16942,13 +16942,13 @@
         <v>694</v>
       </c>
       <c r="P79">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Q79">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="R79">
-        <v>7.21</v>
+        <v>5.33</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -16993,10 +16993,10 @@
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AH79">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="Q80">
-        <v>4.13</v>
+        <v>3.5</v>
       </c>
       <c r="R80">
-        <v>4.85</v>
+        <v>3.32</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17172,10 +17172,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17312,13 +17312,13 @@
         <v>694</v>
       </c>
       <c r="P81">
-        <v>2.7</v>
+        <v>4.06</v>
       </c>
       <c r="Q81">
-        <v>3.46</v>
+        <v>3.98</v>
       </c>
       <c r="R81">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -17357,10 +17357,10 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>4.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="R83">
-        <v>1.93</v>
+        <v>3.11</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>1.59</v>
+        <v>2.78</v>
       </c>
       <c r="Q85">
-        <v>4.15</v>
+        <v>3.61</v>
       </c>
       <c r="R85">
-        <v>5.06</v>
+        <v>2.43</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18097,10 +18097,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18198,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18282,10 +18282,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18383,10 +18383,10 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E87" t="s">
         <v>273</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q87">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R87">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18467,10 +18467,10 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="Q88">
-        <v>3.01</v>
+        <v>3.86</v>
       </c>
       <c r="R88">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18753,7 +18753,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18792,13 +18792,13 @@
         <v>694</v>
       </c>
       <c r="P89">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S89">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19207,10 +19207,10 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19347,13 +19347,13 @@
         <v>694</v>
       </c>
       <c r="P92">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -19392,10 +19392,10 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG92">
         <v>0</v>
@@ -19493,7 +19493,7 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="D93" t="s">
         <v>186</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Q93">
-        <v>5.48</v>
+        <v>4.13</v>
       </c>
       <c r="R93">
-        <v>8.300000000000001</v>
+        <v>4.85</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19678,10 +19678,10 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D94" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E94" t="s">
         <v>280</v>
@@ -19717,13 +19717,13 @@
         <v>694</v>
       </c>
       <c r="P94">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q96">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R96">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20132,10 +20132,10 @@
         <v>0</v>
       </c>
       <c r="AE96">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG96">
         <v>0</v>
@@ -20233,7 +20233,7 @@
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D97" t="s">
         <v>186</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20317,10 +20317,10 @@
         <v>0</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20603,7 +20603,7 @@
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D99" t="s">
         <v>186</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20872,10 +20872,10 @@
         <v>0</v>
       </c>
       <c r="AE100">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF100">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG100">
         <v>0</v>
@@ -20973,10 +20973,10 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E101" t="s">
         <v>287</v>
@@ -21197,13 +21197,13 @@
         <v>694</v>
       </c>
       <c r="P102">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Q102">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="R102">
-        <v>3.27</v>
+        <v>2.8</v>
       </c>
       <c r="S102">
         <v>0</v>
@@ -21242,10 +21242,10 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG102">
         <v>0</v>
@@ -21343,7 +21343,7 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>8.01</v>
+        <v>2.7</v>
       </c>
       <c r="Q103">
-        <v>5.01</v>
+        <v>3.22</v>
       </c>
       <c r="R103">
-        <v>1.27</v>
+        <v>2.56</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21427,10 +21427,10 @@
         <v>0</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21567,13 +21567,13 @@
         <v>694</v>
       </c>
       <c r="P104">
-        <v>2.4</v>
+        <v>8.01</v>
       </c>
       <c r="Q104">
-        <v>3.25</v>
+        <v>5.01</v>
       </c>
       <c r="R104">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D105" t="s">
         <v>186</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22453,7 +22453,7 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22638,7 +22638,7 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="Q111">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="R111">
-        <v>2.56</v>
+        <v>3.27</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22907,10 +22907,10 @@
         <v>0</v>
       </c>
       <c r="AE111">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF111">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG111">
         <v>0</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="Q112">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="R112">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23092,10 +23092,10 @@
         <v>0</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23232,13 +23232,13 @@
         <v>694</v>
       </c>
       <c r="P113">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R113">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S113">
         <v>0</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23417,13 +23417,13 @@
         <v>694</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23787,13 +23787,13 @@
         <v>694</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -23972,13 +23972,13 @@
         <v>694</v>
       </c>
       <c r="P117">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R117">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S117">
         <v>0</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24673,7 +24673,7 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="D121" t="s">
         <v>186</v>
@@ -24858,7 +24858,7 @@
         <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="D122" t="s">
         <v>186</v>
@@ -24897,13 +24897,13 @@
         <v>694</v>
       </c>
       <c r="P122">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S122">
         <v>0</v>
@@ -25082,13 +25082,13 @@
         <v>694</v>
       </c>
       <c r="P123">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -25228,7 +25228,7 @@
         <v>89</v>
       </c>
       <c r="C124" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D124" t="s">
         <v>186</v>
@@ -25267,13 +25267,13 @@
         <v>694</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25452,13 +25452,13 @@
         <v>694</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26192,13 +26192,13 @@
         <v>694</v>
       </c>
       <c r="P129">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="Q129">
-        <v>6.19</v>
+        <v>3.33</v>
       </c>
       <c r="R129">
-        <v>8.6</v>
+        <v>3.96</v>
       </c>
       <c r="S129">
         <v>0</v>
@@ -26338,7 +26338,7 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26377,13 +26377,13 @@
         <v>694</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26523,7 +26523,7 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>5.74</v>
+        <v>1.36</v>
       </c>
       <c r="Q131">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="R131">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,10 +26708,10 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="D132" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E132" t="s">
         <v>318</v>
@@ -26893,10 +26893,10 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D133" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E133" t="s">
         <v>319</v>
@@ -26932,13 +26932,13 @@
         <v>694</v>
       </c>
       <c r="P133">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q133">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -26977,10 +26977,10 @@
         <v>0</v>
       </c>
       <c r="AE133">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF133">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG133">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27117,55 +27117,55 @@
         <v>694</v>
       </c>
       <c r="P134">
+        <v>2.19</v>
+      </c>
+      <c r="Q134">
+        <v>3.37</v>
+      </c>
+      <c r="R134">
+        <v>3.47</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>0</v>
+      </c>
+      <c r="U134">
+        <v>0</v>
+      </c>
+      <c r="V134">
+        <v>0</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
+      </c>
+      <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134">
+        <v>0</v>
+      </c>
+      <c r="Z134">
+        <v>0</v>
+      </c>
+      <c r="AA134">
+        <v>0</v>
+      </c>
+      <c r="AB134">
+        <v>0</v>
+      </c>
+      <c r="AC134">
+        <v>0</v>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134">
         <v>1.93</v>
       </c>
-      <c r="Q134">
-        <v>3.33</v>
-      </c>
-      <c r="R134">
-        <v>3.96</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG134">
         <v>0</v>
@@ -27263,7 +27263,7 @@
         <v>92</v>
       </c>
       <c r="C135" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27448,10 +27448,10 @@
         <v>93</v>
       </c>
       <c r="C136" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D136" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E136" t="s">
         <v>322</v>
@@ -27818,10 +27818,10 @@
         <v>93</v>
       </c>
       <c r="C138" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E138" t="s">
         <v>324</v>
@@ -28373,10 +28373,10 @@
         <v>93</v>
       </c>
       <c r="C141" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D141" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E141" t="s">
         <v>327</v>
@@ -28412,13 +28412,13 @@
         <v>694</v>
       </c>
       <c r="P141">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q141">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R141">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S141">
         <v>0</v>
@@ -28463,10 +28463,10 @@
         <v>0</v>
       </c>
       <c r="AG141">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH141">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI141">
         <v>0</v>
@@ -28743,7 +28743,7 @@
         <v>93</v>
       </c>
       <c r="C143" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="D143" t="s">
         <v>186</v>
@@ -29113,10 +29113,10 @@
         <v>93</v>
       </c>
       <c r="C145" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29152,13 +29152,13 @@
         <v>694</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29203,10 +29203,10 @@
         <v>0</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH145">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI145">
         <v>0</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29853,7 +29853,7 @@
         <v>95</v>
       </c>
       <c r="C149" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -29892,13 +29892,13 @@
         <v>694</v>
       </c>
       <c r="P149">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q149">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R149">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -30038,7 +30038,7 @@
         <v>95</v>
       </c>
       <c r="C150" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30077,13 +30077,13 @@
         <v>694</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30262,13 +30262,13 @@
         <v>694</v>
       </c>
       <c r="P151">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R151">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30408,7 +30408,7 @@
         <v>95</v>
       </c>
       <c r="C152" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D152" t="s">
         <v>186</v>
@@ -30778,7 +30778,7 @@
         <v>95</v>
       </c>
       <c r="C154" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D154" t="s">
         <v>186</v>
@@ -30963,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C155" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D155" t="s">
         <v>186</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31333,7 +31333,7 @@
         <v>95</v>
       </c>
       <c r="C157" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D157" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31703,7 +31703,7 @@
         <v>95</v>
       </c>
       <c r="C159" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D159" t="s">
         <v>186</v>
@@ -32073,7 +32073,7 @@
         <v>95</v>
       </c>
       <c r="C161" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32112,13 +32112,13 @@
         <v>694</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>1.45</v>
+        <v>2.61</v>
       </c>
       <c r="Q164">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="R164">
-        <v>6</v>
+        <v>2.56</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="Q165">
-        <v>3.68</v>
+        <v>5.65</v>
       </c>
       <c r="R165">
-        <v>4.61</v>
+        <v>8.4</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32903,10 +32903,10 @@
         <v>0</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH165">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI165">
         <v>0</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33368,10 +33368,10 @@
         <v>96</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D168" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E168" t="s">
         <v>354</v>
@@ -33407,13 +33407,13 @@
         <v>694</v>
       </c>
       <c r="P168">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q168">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R168">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S168">
         <v>0</v>
@@ -33452,10 +33452,10 @@
         <v>0</v>
       </c>
       <c r="AE168">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF168">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG168">
         <v>0</v>
@@ -33553,10 +33553,10 @@
         <v>96</v>
       </c>
       <c r="C169" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D169" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E169" t="s">
         <v>355</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q169">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R169">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33637,10 +33637,10 @@
         <v>0</v>
       </c>
       <c r="AE169">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF169">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33923,10 +33923,10 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D171" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E171" t="s">
         <v>357</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>2.61</v>
+        <v>1.97</v>
       </c>
       <c r="Q172">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="R172">
-        <v>2.56</v>
+        <v>3.48</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34192,10 +34192,10 @@
         <v>0</v>
       </c>
       <c r="AE172">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF172">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>1.97</v>
+        <v>2.89</v>
       </c>
       <c r="Q173">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="R173">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF173">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34517,13 +34517,13 @@
         <v>694</v>
       </c>
       <c r="P174">
-        <v>2.24</v>
+        <v>3.79</v>
       </c>
       <c r="Q174">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R174">
-        <v>3.37</v>
+        <v>1.9</v>
       </c>
       <c r="S174">
         <v>0</v>
@@ -34562,10 +34562,10 @@
         <v>0</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG174">
         <v>0</v>
@@ -34663,10 +34663,10 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D175" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E175" t="s">
         <v>361</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="Q176">
-        <v>5.65</v>
+        <v>4.7</v>
       </c>
       <c r="R176">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -34938,10 +34938,10 @@
         <v>0</v>
       </c>
       <c r="AG176">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH176">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI176">
         <v>0</v>
@@ -35033,7 +35033,7 @@
         <v>96</v>
       </c>
       <c r="C177" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D177" t="s">
         <v>186</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q177">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R177">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35218,7 +35218,7 @@
         <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35257,13 +35257,13 @@
         <v>694</v>
       </c>
       <c r="P178">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="Q178">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="R178">
-        <v>4.81</v>
+        <v>3.57</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35302,10 +35302,10 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF178">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG178">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35442,13 +35442,13 @@
         <v>694</v>
       </c>
       <c r="P179">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q179">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="R179">
-        <v>3.57</v>
+        <v>4.81</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35487,10 +35487,10 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35678,10 +35678,10 @@
         <v>0</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH180">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI180">
         <v>0</v>
@@ -35958,10 +35958,10 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="D182" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E182" t="s">
         <v>368</v>
@@ -35997,13 +35997,13 @@
         <v>694</v>
       </c>
       <c r="P182">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="Q182">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="R182">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36042,10 +36042,10 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG182">
         <v>0</v>
@@ -36143,7 +36143,7 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D183" t="s">
         <v>186</v>
@@ -36328,10 +36328,10 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="D184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q184">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="R184">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D185" t="s">
         <v>185</v>
@@ -36552,13 +36552,13 @@
         <v>694</v>
       </c>
       <c r="P185">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q185">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="S185">
         <v>0</v>
@@ -36603,10 +36603,10 @@
         <v>0</v>
       </c>
       <c r="AG185">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH185">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI185">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D186" t="s">
         <v>185</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q186">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="R186">
-        <v>2.75</v>
+        <v>3.53</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36782,10 +36782,10 @@
         <v>0</v>
       </c>
       <c r="AE186">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF186">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG186">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37253,7 +37253,7 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D189" t="s">
         <v>186</v>
@@ -37292,13 +37292,13 @@
         <v>694</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37438,7 +37438,7 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D190" t="s">
         <v>185</v>
@@ -37477,13 +37477,13 @@
         <v>694</v>
       </c>
       <c r="P190">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37623,7 +37623,7 @@
         <v>100</v>
       </c>
       <c r="C191" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="D191" t="s">
         <v>186</v>
@@ -37662,13 +37662,13 @@
         <v>694</v>
       </c>
       <c r="P191">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q191">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>0</v>
@@ -37707,10 +37707,10 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF191">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG191">
         <v>0</v>
@@ -37808,7 +37808,7 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D192" t="s">
         <v>186</v>
@@ -37847,13 +37847,13 @@
         <v>694</v>
       </c>
       <c r="P192">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q192">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R192">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="S192">
         <v>0</v>
@@ -37993,10 +37993,10 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="D193" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38178,7 +38178,7 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D194" t="s">
         <v>185</v>
@@ -38363,10 +38363,10 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D195" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E195" t="s">
         <v>381</v>
@@ -38402,13 +38402,13 @@
         <v>694</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38447,10 +38447,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -38548,7 +38548,7 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="D196" t="s">
         <v>186</v>
@@ -38772,13 +38772,13 @@
         <v>694</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -39473,7 +39473,7 @@
         <v>103</v>
       </c>
       <c r="C201" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D201" t="s">
         <v>185</v>
@@ -39512,13 +39512,13 @@
         <v>694</v>
       </c>
       <c r="P201">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q201">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>103</v>
       </c>
       <c r="C202" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D202" t="s">
         <v>185</v>
@@ -39697,13 +39697,13 @@
         <v>694</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S202">
         <v>0</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -39882,13 +39882,13 @@
         <v>694</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG203">
         <v>0</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40067,13 +40067,13 @@
         <v>694</v>
       </c>
       <c r="P204">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q204">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40112,10 +40112,10 @@
         <v>0</v>
       </c>
       <c r="AE204">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF204">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG204">
         <v>0</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -41177,13 +41177,13 @@
         <v>694</v>
       </c>
       <c r="P210">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q210">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R210">
-        <v>2.65</v>
+        <v>4.75</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41362,13 +41362,13 @@
         <v>694</v>
       </c>
       <c r="P211">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="Q211">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R211">
-        <v>5.53</v>
+        <v>2.65</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -41547,13 +41547,13 @@
         <v>694</v>
       </c>
       <c r="P212">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q212">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R212">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41592,10 +41592,10 @@
         <v>0</v>
       </c>
       <c r="AE212">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF212">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG212">
         <v>0</v>
@@ -41732,13 +41732,13 @@
         <v>694</v>
       </c>
       <c r="P213">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q213">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R213">
-        <v>2.88</v>
+        <v>5.53</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -41777,10 +41777,10 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF213">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -41917,55 +41917,55 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q214">
-        <v>3.2</v>
+        <v>3.89</v>
       </c>
       <c r="R214">
+        <v>3.5</v>
+      </c>
+      <c r="S214">
+        <v>0</v>
+      </c>
+      <c r="T214">
+        <v>0</v>
+      </c>
+      <c r="U214">
+        <v>0</v>
+      </c>
+      <c r="V214">
+        <v>0</v>
+      </c>
+      <c r="W214">
+        <v>0</v>
+      </c>
+      <c r="X214">
+        <v>0</v>
+      </c>
+      <c r="Y214">
+        <v>0</v>
+      </c>
+      <c r="Z214">
+        <v>0</v>
+      </c>
+      <c r="AA214">
+        <v>0</v>
+      </c>
+      <c r="AB214">
+        <v>0</v>
+      </c>
+      <c r="AC214">
+        <v>0</v>
+      </c>
+      <c r="AD214">
+        <v>0</v>
+      </c>
+      <c r="AE214">
+        <v>1.55</v>
+      </c>
+      <c r="AF214">
         <v>2.25</v>
-      </c>
-      <c r="S214">
-        <v>0</v>
-      </c>
-      <c r="T214">
-        <v>0</v>
-      </c>
-      <c r="U214">
-        <v>0</v>
-      </c>
-      <c r="V214">
-        <v>0</v>
-      </c>
-      <c r="W214">
-        <v>0</v>
-      </c>
-      <c r="X214">
-        <v>0</v>
-      </c>
-      <c r="Y214">
-        <v>0</v>
-      </c>
-      <c r="Z214">
-        <v>0</v>
-      </c>
-      <c r="AA214">
-        <v>0</v>
-      </c>
-      <c r="AB214">
-        <v>0</v>
-      </c>
-      <c r="AC214">
-        <v>0</v>
-      </c>
-      <c r="AD214">
-        <v>0</v>
-      </c>
-      <c r="AE214">
-        <v>1.98</v>
-      </c>
-      <c r="AF214">
-        <v>1.75</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42063,7 +42063,7 @@
         <v>109</v>
       </c>
       <c r="C215" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D215" t="s">
         <v>185</v>
@@ -42102,13 +42102,13 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="Q215">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="R215">
-        <v>2.35</v>
+        <v>3.39</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q216">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R216">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AF216">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q217">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="R217">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AF217">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42657,13 +42657,13 @@
         <v>694</v>
       </c>
       <c r="P218">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="Q218">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="R218">
-        <v>3.39</v>
+        <v>2.35</v>
       </c>
       <c r="S218">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -43543,10 +43543,10 @@
         <v>110</v>
       </c>
       <c r="C223" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="D223" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43728,7 +43728,7 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43913,10 +43913,10 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D225" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E225" t="s">
         <v>411</v>
@@ -44098,10 +44098,10 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D226" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44283,10 +44283,10 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D227" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E227" t="s">
         <v>413</v>
@@ -44468,10 +44468,10 @@
         <v>110</v>
       </c>
       <c r="C228" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D228" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44507,13 +44507,13 @@
         <v>694</v>
       </c>
       <c r="P228">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S228">
         <v>0</v>
@@ -44552,10 +44552,10 @@
         <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG228">
         <v>0</v>
@@ -44838,7 +44838,7 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D230" t="s">
         <v>186</v>
@@ -45023,7 +45023,7 @@
         <v>110</v>
       </c>
       <c r="C231" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D231" t="s">
         <v>185</v>
@@ -45062,13 +45062,13 @@
         <v>694</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S231">
         <v>0</v>
@@ -45208,10 +45208,10 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D232" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E232" t="s">
         <v>418</v>
@@ -45247,13 +45247,13 @@
         <v>694</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S232">
         <v>0</v>
@@ -45292,10 +45292,10 @@
         <v>0</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG232">
         <v>0</v>
@@ -45763,7 +45763,7 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D235" t="s">
         <v>186</v>
@@ -45948,10 +45948,10 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D236" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E236" t="s">
         <v>422</v>
@@ -46503,7 +46503,7 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D239" t="s">
         <v>186</v>
@@ -46688,10 +46688,10 @@
         <v>110</v>
       </c>
       <c r="C240" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D240" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E240" t="s">
         <v>426</v>
@@ -46727,13 +46727,13 @@
         <v>694</v>
       </c>
       <c r="P240">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q240">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R240">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S240">
         <v>0</v>
@@ -46873,7 +46873,7 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D241" t="s">
         <v>186</v>
@@ -47983,7 +47983,7 @@
         <v>114</v>
       </c>
       <c r="C247" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48022,13 +48022,13 @@
         <v>694</v>
       </c>
       <c r="P247">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q247">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R247">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48067,10 +48067,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF247">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48168,7 +48168,7 @@
         <v>114</v>
       </c>
       <c r="C248" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48207,13 +48207,13 @@
         <v>694</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48252,10 +48252,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q253">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R253">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49177,16 +49177,16 @@
         <v>0</v>
       </c>
       <c r="AE253">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF253">
+        <v>0</v>
+      </c>
+      <c r="AG253">
         <v>2.15</v>
       </c>
-      <c r="AG253">
-        <v>0</v>
-      </c>
       <c r="AH253">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI253">
         <v>0</v>
@@ -49317,13 +49317,13 @@
         <v>694</v>
       </c>
       <c r="P254">
-        <v>2.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q254">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R254">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -49362,16 +49362,16 @@
         <v>0</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG254">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH254">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI254">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -370,12 +370,12 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
@@ -385,42 +385,42 @@
     <t>Indonesia Liga 1</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Vietnam V.League 1</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>England FA Women's Super League</t>
   </si>
   <si>
-    <t>Vietnam V.League 1</t>
+    <t>Croatia Druga HNL</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
-    <t>Croatia Druga HNL</t>
+    <t>China China League One</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
@@ -433,21 +433,21 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
@@ -457,13 +457,16 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>South Africa Premier Soccer League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Italy Serie A</t>
+    <t>Greece Super League</t>
   </si>
   <si>
     <t>Azerbaijan Premyer Liqası</t>
@@ -472,33 +475,30 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Greece Super League</t>
-  </si>
-  <si>
     <t>Germany Bundesliga</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Portugal Liga 3</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -532,24 +532,24 @@
     <t>France National</t>
   </si>
   <si>
+    <t>Argentina Prim B Nacional</t>
+  </si>
+  <si>
     <t>France Ligue 2</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
-    <t>Bolivia LFPB</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Portugal Liga NOS</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Portugal Liga NOS</t>
-  </si>
-  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
@@ -580,15 +580,15 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
     <t>Jeju United</t>
   </si>
   <si>
@@ -598,18 +598,18 @@
     <t>SD Raiders</t>
   </si>
   <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Suwon Bluewings</t>
-  </si>
-  <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Arema</t>
   </si>
   <si>
@@ -622,66 +622,66 @@
     <t>Sydney FC</t>
   </si>
   <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Real Sociedad W</t>
+  </si>
+  <si>
+    <t>Espanyol W</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Kedus Giorgis</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
-  </si>
-  <si>
-    <t>Real Sociedad W</t>
-  </si>
-  <si>
-    <t>Espanyol W</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
-  </si>
-  <si>
     <t>Montana</t>
   </si>
   <si>
+    <t>FLC Thanh Hoa</t>
+  </si>
+  <si>
+    <t>Phu Dong</t>
+  </si>
+  <si>
+    <t>United Nordic</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Östersunds FK</t>
+  </si>
+  <si>
     <t>Bochum</t>
   </si>
   <si>
-    <t>United Nordic</t>
-  </si>
-  <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>FLC Thanh Hoa</t>
+    <t>Oddevold</t>
   </si>
   <si>
     <t>Holstein Kiel</t>
   </si>
   <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Phu Dong</t>
-  </si>
-  <si>
-    <t>Östersunds FK</t>
+    <t>Cibalia</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
-    <t>Cibalia</t>
+    <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Tallinna FC Levadia</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Goa</t>
   </si>
   <si>
@@ -691,60 +691,60 @@
     <t>Liverpool</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Young Lions</t>
   </si>
   <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
+    <t>Osnabrück</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>1860 München</t>
+  </si>
+  <si>
+    <t>Brommapojkarna W</t>
+  </si>
+  <si>
+    <t>Chengdu Better City FC</t>
+  </si>
+  <si>
+    <t>Mladá Boleslav</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
+    <t>Persis Solo</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
     <t>Dukla Praha</t>
   </si>
   <si>
-    <t>Chengdu Better City FC</t>
-  </si>
-  <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Brommapojkarna W</t>
-  </si>
-  <si>
-    <t>Persis Solo</t>
-  </si>
-  <si>
-    <t>1860 München</t>
+    <t>Teplice</t>
   </si>
   <si>
     <t>Ceuta</t>
   </si>
   <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Teplice</t>
-  </si>
-  <si>
-    <t>Mladá Boleslav</t>
-  </si>
-  <si>
     <t>DPMM FC</t>
   </si>
   <si>
@@ -754,112 +754,115 @@
     <t>Widzew Łódź</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>Orbit College</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Hadiya Hosaena</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Cagliari</t>
+    <t>Yelimay Semey</t>
   </si>
   <si>
     <t>Degerfors</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
+    <t>Panserraikos</t>
   </si>
   <si>
     <t>Qabala</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
     <t>Bravo</t>
   </si>
   <si>
-    <t>Orbit College</t>
-  </si>
-  <si>
-    <t>Hadiya Hosaena</t>
-  </si>
-  <si>
     <t>Växjö</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Kristianstad</t>
   </si>
   <si>
-    <t>Panserraikos</t>
-  </si>
-  <si>
     <t>Norrby</t>
   </si>
   <si>
     <t>Cherno More</t>
   </si>
   <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Hoffenheim</t>
+  </si>
+  <si>
+    <t>Stuttgart</t>
+  </si>
+  <si>
     <t>Augsburg</t>
   </si>
   <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>RB Leipzig</t>
-  </si>
-  <si>
-    <t>Hoffenheim</t>
+    <t>Sunderland</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Brighton &amp; Hove Albion</t>
   </si>
   <si>
     <t>St. Mirren</t>
   </si>
   <si>
-    <t>Sunderland</t>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Eibar W</t>
   </si>
   <si>
     <t>Viktoria Plzeň</t>
   </si>
   <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Larissa</t>
+    <t>Dinamo Zagreb</t>
   </si>
   <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
-    <t>Dundee</t>
+    <t>Zulte-Waregem</t>
+  </si>
+  <si>
+    <t>CD Trofense</t>
   </si>
   <si>
     <t>Vaprus</t>
   </si>
   <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
     <t>Fulham</t>
   </si>
   <si>
-    <t>Dinamo Zagreb</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
-    <t>Zulte-Waregem</t>
-  </si>
-  <si>
-    <t>Eibar W</t>
-  </si>
-  <si>
-    <t>CD Trofense</t>
+    <t>Sevilla FC</t>
   </si>
   <si>
     <t>Burgos CF</t>
@@ -868,93 +871,90 @@
     <t>Albacete Balompié</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Waldhof Mannheim</t>
   </si>
   <si>
+    <t>Omonia Aradippou</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Oţelul Galaţi</t>
+  </si>
+  <si>
+    <t>Dubrava Zagreb</t>
+  </si>
+  <si>
+    <t>Enosis</t>
+  </si>
+  <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Ried</t>
+  </si>
+  <si>
+    <t>Ethiopia Bunna</t>
+  </si>
+  <si>
+    <t>GIF Sundsvall</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>Dugopolje</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Dubrava Zagreb</t>
-  </si>
-  <si>
-    <t>Oţelul Galaţi</t>
-  </si>
-  <si>
     <t>Wattens</t>
   </si>
   <si>
-    <t>Enosis</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Dugopolje</t>
-  </si>
-  <si>
-    <t>GIF Sundsvall</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Ethiopia Bunna</t>
-  </si>
-  <si>
-    <t>Ried</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>Omonia Aradippou</t>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Sumqayıt</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
   </si>
   <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Sumqayıt</t>
-  </si>
-  <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>Levski Sofia</t>
   </si>
   <si>
     <t>Al Khaleej</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>Athletic Club W</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Winterthur</t>
-  </si>
-  <si>
-    <t>Lazio</t>
-  </si>
-  <si>
     <t>Beerschot-Wilrijk</t>
   </si>
   <si>
@@ -964,210 +964,210 @@
     <t>Atromitos</t>
   </si>
   <si>
+    <t>Real Valladolid</t>
+  </si>
+  <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
     <t>Wolfsburg</t>
   </si>
   <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Atlético Madrid</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Real Valladolid</t>
-  </si>
-  <si>
     <t>Varaždin</t>
   </si>
   <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Konyaspor</t>
+  </si>
+  <si>
+    <t>Eyüpspor</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Džiugas Telšiai</t>
   </si>
   <si>
     <t>Gençlerbirliği</t>
   </si>
   <si>
-    <t>Beşiktaş</t>
+    <t>Alanyaspor</t>
   </si>
   <si>
     <t>Kocaelispor</t>
   </si>
   <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>Konyaspor</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
     <t>İstanbul Başakşehir</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>Eyüpspor</t>
-  </si>
-  <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Znicz Pruszków</t>
+  </si>
+  <si>
     <t>Partizan</t>
   </si>
   <si>
     <t>Wieczysta Kraków</t>
   </si>
   <si>
+    <t>Orléans</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Caen</t>
+  </si>
+  <si>
+    <t>Bourg-en-Bresse</t>
+  </si>
+  <si>
+    <t>Paris 13 Atletico</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Le Puy F.43 Auvergne</t>
+  </si>
+  <si>
+    <t>Châteauroux</t>
+  </si>
+  <si>
     <t>Stade Briochin</t>
   </si>
   <si>
-    <t>Paris 13 Atletico</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>Châteauroux</t>
-  </si>
-  <si>
-    <t>Bourg-en-Bresse</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Le Puy F.43 Auvergne</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Rouen</t>
   </si>
   <si>
-    <t>Stal Mielec</t>
-  </si>
-  <si>
-    <t>Znicz Pruszków</t>
-  </si>
-  <si>
-    <t>Orléans</t>
+    <t>Al Feiha</t>
+  </si>
+  <si>
+    <t>Magesi</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Tristán Suárez</t>
+  </si>
+  <si>
+    <t>Saint-Étienne</t>
   </si>
   <si>
     <t>Nancy</t>
   </si>
   <si>
-    <t>Saint-Étienne</t>
+    <t>Bastia</t>
+  </si>
+  <si>
+    <t>Clermont</t>
   </si>
   <si>
     <t>Red Star</t>
   </si>
   <si>
-    <t>Bastia</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
-  </si>
-  <si>
-    <t>Tristán Suárez</t>
-  </si>
-  <si>
-    <t>Magesi</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
+    <t>Grenoble Foot 38</t>
+  </si>
+  <si>
+    <t>Reims</t>
   </si>
   <si>
     <t>Annecy</t>
   </si>
   <si>
-    <t>Clermont</t>
-  </si>
-  <si>
-    <t>Grenoble Foot 38</t>
-  </si>
-  <si>
     <t>Laval</t>
   </si>
   <si>
-    <t>Reims</t>
-  </si>
-  <si>
-    <t>Al Feiha</t>
+    <t>Górnik Zabrze</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Górnik Zabrze</t>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Acassuso</t>
   </si>
   <si>
     <t>Chicago Fire</t>
   </si>
   <si>
+    <t>Nürnberg</t>
+  </si>
+  <si>
+    <t>Técnico Universitario</t>
+  </si>
+  <si>
     <t>San Miguel</t>
   </si>
   <si>
-    <t>Acassuso</t>
-  </si>
-  <si>
     <t>Luzern</t>
   </si>
   <si>
-    <t>Nürnberg</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Técnico Universitario</t>
+    <t>Club Brugge</t>
   </si>
   <si>
     <t>Lecce</t>
   </si>
   <si>
-    <t>Club Brugge</t>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>Málaga CF</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
+    <t>Real Oruro</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Motherwell</t>
+  </si>
+  <si>
+    <t>Real Sociedad</t>
   </si>
   <si>
     <t>Raja Casablanca</t>
   </si>
   <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Real Oruro</t>
-  </si>
-  <si>
-    <t>Motherwell</t>
+    <t>Coritiba</t>
   </si>
   <si>
     <t>CD Mafra</t>
   </si>
   <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
@@ -1183,12 +1183,12 @@
     <t>Guayaquil City FC</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Guabirá</t>
   </si>
   <si>
@@ -1204,108 +1204,108 @@
     <t>Gotham FC</t>
   </si>
   <si>
+    <t>Louisville City</t>
+  </si>
+  <si>
+    <t>Hartford Athletic</t>
+  </si>
+  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
-    <t>Hartford Athletic</t>
-  </si>
-  <si>
     <t>Brooklyn FC</t>
   </si>
   <si>
-    <t>Louisville City</t>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>Real Tomayapo</t>
+  </si>
+  <si>
+    <t>CRB</t>
   </si>
   <si>
     <t>Charlotte</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Atlanta United FC</t>
-  </si>
-  <si>
     <t>Rhode Island</t>
   </si>
   <si>
-    <t>Real Tomayapo</t>
+    <t>Rio Ave FC</t>
+  </si>
+  <si>
+    <t>Alverca</t>
+  </si>
+  <si>
+    <t>FC Vizela</t>
+  </si>
+  <si>
+    <t>Benfica II</t>
+  </si>
+  <si>
+    <t>GD Chaves</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>Santa Clara</t>
+  </si>
+  <si>
+    <t>Estrela Amadora</t>
+  </si>
+  <si>
+    <t>Minnesota United II</t>
+  </si>
+  <si>
+    <t>CSD Independiente del Valle</t>
+  </si>
+  <si>
+    <t>Lusitania Lourosa</t>
+  </si>
+  <si>
+    <t>CD Feirense</t>
+  </si>
+  <si>
+    <t>Gil Vicente</t>
+  </si>
+  <si>
+    <t>Grafičar</t>
+  </si>
+  <si>
+    <t>Sporting CP II</t>
+  </si>
+  <si>
+    <t>CD Tondela</t>
+  </si>
+  <si>
+    <t>Farense</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Houston Dash</t>
+  </si>
+  <si>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães</t>
+  </si>
+  <si>
+    <t>Benfica</t>
   </si>
   <si>
     <t>FC Penafiel</t>
   </si>
   <si>
-    <t>Rio Ave FC</t>
-  </si>
-  <si>
-    <t>Gil Vicente</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>FC Vizela</t>
-  </si>
-  <si>
-    <t>Grafičar</t>
-  </si>
-  <si>
-    <t>Minnesota United II</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Sporting CP II</t>
-  </si>
-  <si>
-    <t>Santa Clara</t>
-  </si>
-  <si>
     <t>Felgueiras 1932</t>
   </si>
   <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>CSD Independiente del Valle</t>
-  </si>
-  <si>
-    <t>CD Tondela</t>
-  </si>
-  <si>
-    <t>CD Feirense</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães</t>
-  </si>
-  <si>
-    <t>Houston Dash</t>
-  </si>
-  <si>
-    <t>Lusitania Lourosa</t>
-  </si>
-  <si>
-    <t>Farense</t>
-  </si>
-  <si>
-    <t>Alverca</t>
-  </si>
-  <si>
-    <t>GD Chaves</t>
-  </si>
-  <si>
-    <t>AVS</t>
-  </si>
-  <si>
-    <t>Benfica II</t>
-  </si>
-  <si>
-    <t>Estrela Amadora</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Angel City</t>
   </si>
   <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
     <t>New Mexico United</t>
   </si>
   <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -1330,24 +1330,24 @@
     <t>Phoenix Rising</t>
   </si>
   <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
     <t>SJ Earthquakes</t>
   </si>
   <si>
-    <t>Seattle Sounders</t>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Suwon</t>
   </si>
   <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
     <t>FC Seoul</t>
   </si>
   <si>
@@ -1357,18 +1357,18 @@
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
-    <t>Daegu</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>PSM</t>
   </si>
   <si>
@@ -1381,66 +1381,66 @@
     <t>Newcastle Jets FC</t>
   </si>
   <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
+    <t>Granada W</t>
+  </si>
+  <si>
+    <t>Badalona W</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Mekelle Kenema</t>
   </si>
   <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
-    <t>Granada W</t>
-  </si>
-  <si>
-    <t>Badalona W</t>
-  </si>
-  <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Lokomotiv Sofia 1929</t>
   </si>
   <si>
+    <t>Ha Noi</t>
+  </si>
+  <si>
+    <t>Hai Phong</t>
+  </si>
+  <si>
+    <t>Öster</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Ha Noi</t>
+    <t>Landskrona</t>
   </si>
   <si>
     <t>Magdeburg</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Hai Phong</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
+    <t>Sesvete</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Sesvete</t>
+    <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
     <t>ATK Mohun Bagan</t>
   </si>
   <si>
@@ -1450,60 +1450,60 @@
     <t>Chelsea</t>
   </si>
   <si>
+    <t>Meizhou Hakka</t>
+  </si>
+  <si>
     <t>Geylang International</t>
   </si>
   <si>
-    <t>Meizhou Hakka</t>
-  </si>
-  <si>
     <t>Chongqing Tongliang Long</t>
   </si>
   <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Verl</t>
+  </si>
+  <si>
+    <t>Shire Endaselassie</t>
+  </si>
+  <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Stuttgart II</t>
+  </si>
+  <si>
+    <t>Ingolstadt</t>
+  </si>
+  <si>
+    <t>Eskilstuna United</t>
+  </si>
+  <si>
+    <t>Henan Jianye</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés</t>
+  </si>
+  <si>
+    <t>Persebaya Surabaya</t>
+  </si>
+  <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>Henan Jianye</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
-    <t>Shire Endaselassie</t>
-  </si>
-  <si>
-    <t>Fredrikstad</t>
-  </si>
-  <si>
-    <t>Deportivo Alavés</t>
-  </si>
-  <si>
-    <t>Verl</t>
-  </si>
-  <si>
-    <t>Eskilstuna United</t>
-  </si>
-  <si>
-    <t>Persebaya Surabaya</t>
-  </si>
-  <si>
-    <t>Ingolstadt</t>
+    <t>Baník Ostrava</t>
   </si>
   <si>
     <t>CD Castellón</t>
   </si>
   <si>
-    <t>Ulm</t>
-  </si>
-  <si>
-    <t>Stuttgart II</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
     <t>Sabah</t>
   </si>
   <si>
@@ -1513,112 +1513,115 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Udinese</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
     <t>Chippa United</t>
   </si>
   <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Udinese</t>
+    <t>FC Caspiy</t>
   </si>
   <si>
     <t>Mjällby</t>
   </si>
   <si>
-    <t>FC Caspiy</t>
+    <t>Kifisia</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
     <t>Radomlje</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
     <t>AIK Women</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
     <t>Norrköping W</t>
   </si>
   <si>
-    <t>Kifisia</t>
-  </si>
-  <si>
     <t>Helsingborg</t>
   </si>
   <si>
     <t>Botev Plovdiv</t>
   </si>
   <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
     <t>Borussia M'gladbach</t>
   </si>
   <si>
-    <t>Bayer Leverkusen</t>
-  </si>
-  <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t>Werder Bremen</t>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Wolverhampton Wanderers</t>
   </si>
   <si>
     <t>Kilmarnock</t>
   </si>
   <si>
-    <t>Manchester United</t>
+    <t>Livingston</t>
+  </si>
+  <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
+    <t>Alhama</t>
   </si>
   <si>
     <t>Slovan Liberec</t>
   </si>
   <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
+    <t>Hajduk Split</t>
   </si>
   <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>Livingston</t>
+    <t>FCV Dender EH</t>
+  </si>
+  <si>
+    <t>Vitória Guimarães II</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
     <t>AFC Bournemouth</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>FCV Dender EH</t>
-  </si>
-  <si>
-    <t>Alhama</t>
-  </si>
-  <si>
-    <t>Vitória Guimarães II</t>
+    <t>RCD Espanyol</t>
   </si>
   <si>
     <t>Almería</t>
@@ -1627,93 +1630,90 @@
     <t>Cultural y Deportiva Leonesa</t>
   </si>
   <si>
-    <t>RCD Espanyol</t>
-  </si>
-  <si>
     <t>Jahn Regensburg</t>
   </si>
   <si>
+    <t>Akritas</t>
+  </si>
+  <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Orijent 1919</t>
+  </si>
+  <si>
+    <t>Ethnikos Achna</t>
+  </si>
+  <si>
+    <t>Ljungskile</t>
+  </si>
+  <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
+    <t>Olympiakos</t>
+  </si>
+  <si>
+    <t>Bijelo Brdo</t>
+  </si>
+  <si>
     <t>Irtysh</t>
   </si>
   <si>
-    <t>Orijent 1919</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
     <t>Blau-Weiß Linz</t>
   </si>
   <si>
-    <t>Ethnikos Achna</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
-    <t>Bijelo Brdo</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Ljungskile</t>
-  </si>
-  <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
-    <t>Olympiakos</t>
-  </si>
-  <si>
-    <t>Akritas</t>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Siwelele</t>
+  </si>
+  <si>
+    <t>Araz</t>
+  </si>
+  <si>
+    <t>Pogoń Szczecin</t>
   </si>
   <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Pogoń Szczecin</t>
-  </si>
-  <si>
-    <t>Araz</t>
-  </si>
-  <si>
     <t>Aluminij</t>
   </si>
   <si>
-    <t>Siwelele</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
     <t>Ludogorets</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
+    <t>Inter Milan</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Novi Pazar</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>Deportivo de La Coruña W</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Grasshopper</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Inter Milan</t>
-  </si>
-  <si>
     <t>Lommel United</t>
   </si>
   <si>
@@ -1723,210 +1723,210 @@
     <t>Panaitolikos</t>
   </si>
   <si>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Deportes Santa Cruz</t>
+  </si>
+  <si>
+    <t>Brentford</t>
+  </si>
+  <si>
     <t>Bayern München</t>
   </si>
   <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Celta de Vigo</t>
-  </si>
-  <si>
-    <t>Deportes Santa Cruz</t>
-  </si>
-  <si>
-    <t>Real Zaragoza</t>
-  </si>
-  <si>
     <t>Lokomotiva Zagreb</t>
   </si>
   <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Fenerbahçe</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
+    <t>Gaziantep FK</t>
+  </si>
+  <si>
     <t>Trakai</t>
   </si>
   <si>
     <t>Kasımpaşa</t>
   </si>
   <si>
-    <t>Trabzonspor</t>
+    <t>Kayserispor</t>
   </si>
   <si>
     <t>Fatih Karagümrük</t>
   </si>
   <si>
-    <t>Kayserispor</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
-    <t>Fenerbahçe</t>
-  </si>
-  <si>
-    <t>Gaziantep FK</t>
-  </si>
-  <si>
     <t>Samsunspor</t>
   </si>
   <si>
-    <t>Inter Miami</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
     <t>Ironi Kiryat Shmona</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>OFK Beograd</t>
   </si>
   <si>
     <t>Miedź Legnica</t>
   </si>
   <si>
+    <t>Fleury 91</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Concarneau</t>
+  </si>
+  <si>
+    <t>Valenciennes</t>
+  </si>
+  <si>
+    <t>Aubagne</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Dijon</t>
+  </si>
+  <si>
+    <t>Sochaux</t>
+  </si>
+  <si>
     <t>Quevilly Rouen</t>
   </si>
   <si>
-    <t>Aubagne</t>
-  </si>
-  <si>
-    <t>Concarneau</t>
-  </si>
-  <si>
-    <t>Sochaux</t>
-  </si>
-  <si>
-    <t>Valenciennes</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
     <t>Versailles</t>
   </si>
   <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Fleury 91</t>
+    <t>Al Quadisiya</t>
+  </si>
+  <si>
+    <t>Orlando Pirates</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
+    <t>Midland</t>
+  </si>
+  <si>
+    <t>Amiens SC</t>
   </si>
   <si>
     <t>Dunkerque</t>
   </si>
   <si>
-    <t>Amiens SC</t>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Guingamp</t>
   </si>
   <si>
     <t>Montpellier</t>
   </si>
   <si>
-    <t>Le Mans</t>
-  </si>
-  <si>
-    <t>Los Andes</t>
-  </si>
-  <si>
-    <t>Midland</t>
-  </si>
-  <si>
-    <t>Orlando Pirates</t>
-  </si>
-  <si>
-    <t>Rapid Bucureşti</t>
+    <t>Troyes</t>
+  </si>
+  <si>
+    <t>Pau</t>
   </si>
   <si>
     <t>Rodez</t>
   </si>
   <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
-    <t>Troyes</t>
-  </si>
-  <si>
     <t>Boulogne</t>
   </si>
   <si>
-    <t>Pau</t>
-  </si>
-  <si>
-    <t>Al Quadisiya</t>
+    <t>Zagłębie Lubin</t>
   </si>
   <si>
     <t>Olimpija</t>
   </si>
   <si>
-    <t>Zagłębie Lubin</t>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
   </si>
   <si>
     <t>New York RB</t>
   </si>
   <si>
+    <t>Schalke 04</t>
+  </si>
+  <si>
+    <t>Delfin SC</t>
+  </si>
+  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
     <t>Servette</t>
   </si>
   <si>
-    <t>Schalke 04</t>
-  </si>
-  <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Delfin SC</t>
+    <t>Sint-Truiden</t>
   </si>
   <si>
     <t>Juventus</t>
   </si>
   <si>
-    <t>Sint-Truiden</t>
+    <t>Unión Española</t>
   </si>
   <si>
     <t>Sporting Gijón</t>
   </si>
   <si>
-    <t>Unión Española</t>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Real Betis</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
-    <t>Hearts</t>
+    <t>Internacional</t>
   </si>
   <si>
     <t>Associação Académica de Coimbra OAF</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Whitecaps II</t>
   </si>
   <si>
@@ -1942,12 +1942,12 @@
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Gualberto Villarroel SJ</t>
   </si>
   <si>
@@ -1963,108 +1963,108 @@
     <t>Boston Legacy W</t>
   </si>
   <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Sporting JAX</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
     <t>Loudoun United</t>
   </si>
   <si>
-    <t>Pittsburgh Riverhounds</t>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>San Antonio Bulo Bulo</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
   </si>
   <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>Operário PR</t>
-  </si>
-  <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Tampa Bay Rowdies</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>GD Estoril Praia</t>
+  </si>
+  <si>
+    <t>União de Leiria</t>
+  </si>
+  <si>
+    <t>Academico Viseu</t>
+  </si>
+  <si>
+    <t>Leixões</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>CD Nacional</t>
+  </si>
+  <si>
+    <t>Famalicão</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>UD Oliveirense</t>
+  </si>
+  <si>
+    <t>FC Arouca</t>
+  </si>
+  <si>
+    <t>Dubočica</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Moreirense FC</t>
+  </si>
+  <si>
+    <t>Paços de Ferreira</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Denver Summit W</t>
+  </si>
+  <si>
+    <t>Cobreloa</t>
+  </si>
+  <si>
+    <t>Casa Pia</t>
+  </si>
+  <si>
+    <t>Sporting Braga</t>
   </si>
   <si>
     <t>CS Marítimo</t>
   </si>
   <si>
-    <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>FC Arouca</t>
-  </si>
-  <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
-    <t>União de Leiria</t>
-  </si>
-  <si>
-    <t>Dubočica</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting Braga</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>CD Nacional</t>
-  </si>
-  <si>
     <t>Portimonense</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Moreirense FC</t>
-  </si>
-  <si>
-    <t>UD Oliveirense</t>
-  </si>
-  <si>
-    <t>Casa Pia</t>
-  </si>
-  <si>
-    <t>Denver Summit W</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Paços de Ferreira</t>
-  </si>
-  <si>
-    <t>GD Estoril Praia</t>
-  </si>
-  <si>
-    <t>Leixões</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>Academico Viseu</t>
-  </si>
-  <si>
-    <t>Famalicão</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -2074,12 +2074,12 @@
     <t>San Diego Wave</t>
   </si>
   <si>
+    <t>DC United</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>DC United</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
@@ -2089,13 +2089,13 @@
     <t>San Antonio</t>
   </si>
   <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>Sporting KC</t>
   </si>
   <si>
     <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
-    <t>San Diego</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -2697,13 +2697,13 @@
         <v>694</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
         <v>185</v>
@@ -3067,13 +3067,13 @@
         <v>694</v>
       </c>
       <c r="P4">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>185</v>
@@ -3768,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
         <v>185</v>
@@ -3807,13 +3807,13 @@
         <v>694</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>185</v>
@@ -4138,7 +4138,7 @@
         <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
@@ -4177,13 +4177,13 @@
         <v>694</v>
       </c>
       <c r="P10">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -4693,7 +4693,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>185</v>
@@ -4878,7 +4878,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
         <v>185</v>
@@ -5251,7 +5251,7 @@
         <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
         <v>202</v>
@@ -5436,7 +5436,7 @@
         <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
         <v>203</v>
@@ -5618,7 +5618,7 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
         <v>186</v>
@@ -5803,10 +5803,10 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E19" t="s">
         <v>205</v>
@@ -5988,10 +5988,10 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
         <v>206</v>
@@ -6397,13 +6397,13 @@
         <v>694</v>
       </c>
       <c r="P22">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -6543,10 +6543,10 @@
         <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>209</v>
@@ -6728,10 +6728,10 @@
         <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
         <v>210</v>
@@ -6913,10 +6913,10 @@
         <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
         <v>211</v>
@@ -6952,13 +6952,13 @@
         <v>694</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -6997,10 +6997,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -7098,10 +7098,10 @@
         <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" t="s">
         <v>212</v>
@@ -7137,13 +7137,13 @@
         <v>694</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -7182,10 +7182,10 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" t="s">
         <v>213</v>
@@ -7322,13 +7322,13 @@
         <v>694</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
         <v>186</v>
@@ -7507,13 +7507,13 @@
         <v>694</v>
       </c>
       <c r="P28">
-        <v>2.55</v>
+        <v>2.86</v>
       </c>
       <c r="Q28">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
         <v>215</v>
@@ -7692,13 +7692,13 @@
         <v>694</v>
       </c>
       <c r="P29">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -7838,10 +7838,10 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E30" t="s">
         <v>216</v>
@@ -7877,13 +7877,13 @@
         <v>694</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -8023,10 +8023,10 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
         <v>217</v>
@@ -8062,13 +8062,13 @@
         <v>694</v>
       </c>
       <c r="P31">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q31">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="R31">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
         <v>218</v>
@@ -8396,7 +8396,7 @@
         <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" t="s">
         <v>219</v>
@@ -8617,13 +8617,13 @@
         <v>694</v>
       </c>
       <c r="P34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -8802,13 +8802,13 @@
         <v>694</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E39" t="s">
         <v>225</v>
@@ -9688,10 +9688,10 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
         <v>226</v>
@@ -10061,7 +10061,7 @@
         <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E42" t="s">
         <v>228</v>
@@ -10097,13 +10097,13 @@
         <v>694</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -10243,10 +10243,10 @@
         <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
         <v>229</v>
@@ -10428,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
         <v>186</v>
@@ -10613,7 +10613,7 @@
         <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -10798,10 +10798,10 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
         <v>232</v>
@@ -10837,13 +10837,13 @@
         <v>694</v>
       </c>
       <c r="P46">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D47" t="s">
         <v>186</v>
@@ -11168,10 +11168,10 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E48" t="s">
         <v>234</v>
@@ -11353,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
         <v>185</v>
@@ -11538,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="D50" t="s">
         <v>186</v>
@@ -11723,7 +11723,7 @@
         <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D51" t="s">
         <v>186</v>
@@ -11908,7 +11908,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="D52" t="s">
         <v>186</v>
@@ -11947,13 +11947,13 @@
         <v>694</v>
       </c>
       <c r="P52">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
         <v>186</v>
@@ -12463,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D55" t="s">
         <v>186</v>
@@ -12648,7 +12648,7 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
         <v>186</v>
@@ -12687,13 +12687,13 @@
         <v>694</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -13391,7 +13391,7 @@
         <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E60" t="s">
         <v>246</v>
@@ -13427,13 +13427,13 @@
         <v>694</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>148</v>
       </c>
       <c r="D61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E61" t="s">
         <v>247</v>
@@ -13612,13 +13612,13 @@
         <v>694</v>
       </c>
       <c r="P61">
-        <v>3.12</v>
+        <v>2.54</v>
       </c>
       <c r="Q61">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R61">
-        <v>2.27</v>
+        <v>3.21</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -13797,13 +13797,13 @@
         <v>694</v>
       </c>
       <c r="P62">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -13943,10 +13943,10 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E63" t="s">
         <v>249</v>
@@ -13982,13 +13982,13 @@
         <v>694</v>
       </c>
       <c r="P63">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -14128,7 +14128,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
         <v>185</v>
@@ -14167,13 +14167,13 @@
         <v>694</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -14313,7 +14313,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
         <v>186</v>
@@ -14498,10 +14498,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E66" t="s">
         <v>252</v>
@@ -14537,13 +14537,13 @@
         <v>694</v>
       </c>
       <c r="P66">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -14683,10 +14683,10 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="D67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" t="s">
         <v>253</v>
@@ -14722,13 +14722,13 @@
         <v>694</v>
       </c>
       <c r="P67">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -14871,7 +14871,7 @@
         <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E68" t="s">
         <v>254</v>
@@ -14907,13 +14907,13 @@
         <v>694</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -15053,7 +15053,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="D69" t="s">
         <v>186</v>
@@ -15092,13 +15092,13 @@
         <v>694</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
         <v>256</v>
@@ -15423,7 +15423,7 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D71" t="s">
         <v>186</v>
@@ -15462,13 +15462,13 @@
         <v>694</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -15608,7 +15608,7 @@
         <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D72" t="s">
         <v>185</v>
@@ -15793,10 +15793,10 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
@@ -15832,13 +15832,13 @@
         <v>694</v>
       </c>
       <c r="P73">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -16387,13 +16387,13 @@
         <v>694</v>
       </c>
       <c r="P76">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="Q76">
-        <v>3.71</v>
+        <v>5.18</v>
       </c>
       <c r="R76">
-        <v>3.07</v>
+        <v>7.21</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -16432,16 +16432,16 @@
         <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI76">
         <v>0</v>
@@ -16572,13 +16572,13 @@
         <v>694</v>
       </c>
       <c r="P77">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="Q77">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="R77">
-        <v>3.23</v>
+        <v>5.33</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -16623,10 +16623,10 @@
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH77">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AI77">
         <v>0</v>
@@ -16757,13 +16757,13 @@
         <v>694</v>
       </c>
       <c r="P78">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="Q78">
-        <v>5.18</v>
+        <v>4.16</v>
       </c>
       <c r="R78">
-        <v>7.21</v>
+        <v>3.23</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH78">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI78">
         <v>0</v>
@@ -16942,61 +16942,61 @@
         <v>694</v>
       </c>
       <c r="P79">
+        <v>2.38</v>
+      </c>
+      <c r="Q79">
+        <v>3.71</v>
+      </c>
+      <c r="R79">
+        <v>3.07</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0</v>
+      </c>
+      <c r="AB79">
+        <v>0</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
+      <c r="AE79">
         <v>1.61</v>
       </c>
-      <c r="Q79">
-        <v>4.88</v>
-      </c>
-      <c r="R79">
-        <v>5.33</v>
-      </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>0</v>
-      </c>
-      <c r="V79">
-        <v>0</v>
-      </c>
-      <c r="W79">
-        <v>0</v>
-      </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>0</v>
-      </c>
-      <c r="Z79">
-        <v>0</v>
-      </c>
-      <c r="AA79">
-        <v>0</v>
-      </c>
-      <c r="AB79">
-        <v>0</v>
-      </c>
-      <c r="AC79">
-        <v>0</v>
-      </c>
-      <c r="AD79">
-        <v>0</v>
-      </c>
-      <c r="AE79">
-        <v>0</v>
-      </c>
       <c r="AF79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG79">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH79">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI79">
         <v>0</v>
@@ -17088,7 +17088,7 @@
         <v>82</v>
       </c>
       <c r="C80" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D80" t="s">
         <v>186</v>
@@ -17127,13 +17127,13 @@
         <v>694</v>
       </c>
       <c r="P80">
-        <v>2.08</v>
+        <v>4.06</v>
       </c>
       <c r="Q80">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="R80">
-        <v>3.32</v>
+        <v>1.93</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17172,10 +17172,10 @@
         <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG80">
         <v>0</v>
@@ -17273,7 +17273,7 @@
         <v>82</v>
       </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D81" t="s">
         <v>186</v>
@@ -17312,55 +17312,55 @@
         <v>694</v>
       </c>
       <c r="P81">
-        <v>4.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q81">
-        <v>3.98</v>
+        <v>3.46</v>
       </c>
       <c r="R81">
+        <v>2.42</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>0</v>
+      </c>
+      <c r="AD81">
+        <v>0</v>
+      </c>
+      <c r="AE81">
+        <v>1.77</v>
+      </c>
+      <c r="AF81">
         <v>1.93</v>
-      </c>
-      <c r="S81">
-        <v>0</v>
-      </c>
-      <c r="T81">
-        <v>0</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>0</v>
-      </c>
-      <c r="W81">
-        <v>0</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
-      </c>
-      <c r="Z81">
-        <v>0</v>
-      </c>
-      <c r="AA81">
-        <v>0</v>
-      </c>
-      <c r="AB81">
-        <v>0</v>
-      </c>
-      <c r="AC81">
-        <v>0</v>
-      </c>
-      <c r="AD81">
-        <v>0</v>
-      </c>
-      <c r="AE81">
-        <v>0</v>
-      </c>
-      <c r="AF81">
-        <v>0</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D82" t="s">
         <v>186</v>
@@ -17497,13 +17497,13 @@
         <v>694</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -17542,10 +17542,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -17643,7 +17643,7 @@
         <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D83" t="s">
         <v>186</v>
@@ -17682,13 +17682,13 @@
         <v>694</v>
       </c>
       <c r="P83">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="Q83">
-        <v>3.62</v>
+        <v>5.48</v>
       </c>
       <c r="R83">
-        <v>3.11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -17727,10 +17727,10 @@
         <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -17828,7 +17828,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D84" t="s">
         <v>186</v>
@@ -17867,13 +17867,13 @@
         <v>694</v>
       </c>
       <c r="P84">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q84">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="R84">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -17912,10 +17912,10 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84">
         <v>0</v>
@@ -18013,7 +18013,7 @@
         <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D85" t="s">
         <v>186</v>
@@ -18052,13 +18052,13 @@
         <v>694</v>
       </c>
       <c r="P85">
-        <v>2.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q85">
-        <v>3.61</v>
+        <v>4.15</v>
       </c>
       <c r="R85">
-        <v>2.43</v>
+        <v>5.06</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -18097,10 +18097,10 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG85">
         <v>0</v>
@@ -18198,7 +18198,7 @@
         <v>82</v>
       </c>
       <c r="C86" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D86" t="s">
         <v>186</v>
@@ -18237,13 +18237,13 @@
         <v>694</v>
       </c>
       <c r="P86">
-        <v>1.59</v>
+        <v>2.32</v>
       </c>
       <c r="Q86">
-        <v>4.15</v>
+        <v>3.01</v>
       </c>
       <c r="R86">
-        <v>5.06</v>
+        <v>3.11</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -18282,10 +18282,10 @@
         <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG86">
         <v>0</v>
@@ -18383,10 +18383,10 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E87" t="s">
         <v>273</v>
@@ -18422,13 +18422,13 @@
         <v>694</v>
       </c>
       <c r="P87">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S87">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
         <v>186</v>
@@ -18607,13 +18607,13 @@
         <v>694</v>
       </c>
       <c r="P88">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S88">
         <v>0</v>
@@ -18753,7 +18753,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D89" t="s">
         <v>186</v>
@@ -18938,7 +18938,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D90" t="s">
         <v>186</v>
@@ -18977,13 +18977,13 @@
         <v>694</v>
       </c>
       <c r="P90">
-        <v>1.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q90">
-        <v>5.48</v>
+        <v>3.61</v>
       </c>
       <c r="R90">
-        <v>8.300000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -19123,7 +19123,7 @@
         <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D91" t="s">
         <v>186</v>
@@ -19162,13 +19162,13 @@
         <v>694</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q91">
-        <v>3.46</v>
+        <v>4.13</v>
       </c>
       <c r="R91">
-        <v>2.42</v>
+        <v>4.85</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -19207,10 +19207,10 @@
         <v>0</v>
       </c>
       <c r="AE91">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF91">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG91">
         <v>0</v>
@@ -19308,7 +19308,7 @@
         <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="D92" t="s">
         <v>186</v>
@@ -19493,10 +19493,10 @@
         <v>82</v>
       </c>
       <c r="C93" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E93" t="s">
         <v>279</v>
@@ -19532,13 +19532,13 @@
         <v>694</v>
       </c>
       <c r="P93">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="Q93">
-        <v>4.13</v>
+        <v>3.55</v>
       </c>
       <c r="R93">
-        <v>4.85</v>
+        <v>2.84</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -19678,7 +19678,7 @@
         <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D94" t="s">
         <v>186</v>
@@ -19863,7 +19863,7 @@
         <v>82</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D95" t="s">
         <v>186</v>
@@ -19902,13 +19902,13 @@
         <v>694</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -20048,7 +20048,7 @@
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
         <v>186</v>
@@ -20087,13 +20087,13 @@
         <v>694</v>
       </c>
       <c r="P96">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R96">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S96">
         <v>0</v>
@@ -20272,13 +20272,13 @@
         <v>694</v>
       </c>
       <c r="P97">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="Q97">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="R97">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -20317,10 +20317,10 @@
         <v>0</v>
       </c>
       <c r="AE97">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG97">
         <v>0</v>
@@ -20418,7 +20418,7 @@
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
         <v>186</v>
@@ -20457,13 +20457,13 @@
         <v>694</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -20502,10 +20502,10 @@
         <v>0</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG98">
         <v>0</v>
@@ -20788,10 +20788,10 @@
         <v>85</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="D100" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E100" t="s">
         <v>286</v>
@@ -20827,13 +20827,13 @@
         <v>694</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -20872,10 +20872,10 @@
         <v>0</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG100">
         <v>0</v>
@@ -20973,7 +20973,7 @@
         <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D101" t="s">
         <v>186</v>
@@ -21012,13 +21012,13 @@
         <v>694</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -21158,7 +21158,7 @@
         <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D102" t="s">
         <v>186</v>
@@ -21343,7 +21343,7 @@
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="D103" t="s">
         <v>186</v>
@@ -21382,13 +21382,13 @@
         <v>694</v>
       </c>
       <c r="P103">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S103">
         <v>0</v>
@@ -21427,10 +21427,10 @@
         <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG103">
         <v>0</v>
@@ -21528,7 +21528,7 @@
         <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D104" t="s">
         <v>186</v>
@@ -21713,10 +21713,10 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="D105" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E105" t="s">
         <v>291</v>
@@ -21752,13 +21752,13 @@
         <v>694</v>
       </c>
       <c r="P105">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q105">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R105">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S105">
         <v>0</v>
@@ -21898,7 +21898,7 @@
         <v>85</v>
       </c>
       <c r="C106" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D106" t="s">
         <v>186</v>
@@ -21937,13 +21937,13 @@
         <v>694</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -22083,10 +22083,10 @@
         <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -22122,13 +22122,13 @@
         <v>694</v>
       </c>
       <c r="P107">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q107">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S107">
         <v>0</v>
@@ -22307,13 +22307,13 @@
         <v>694</v>
       </c>
       <c r="P108">
-        <v>2.27</v>
+        <v>3.87</v>
       </c>
       <c r="Q108">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R108">
-        <v>2.88</v>
+        <v>1.81</v>
       </c>
       <c r="S108">
         <v>0</v>
@@ -22453,7 +22453,7 @@
         <v>85</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="D109" t="s">
         <v>186</v>
@@ -22492,13 +22492,13 @@
         <v>694</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S109">
         <v>0</v>
@@ -22537,10 +22537,10 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG109">
         <v>0</v>
@@ -22638,7 +22638,7 @@
         <v>85</v>
       </c>
       <c r="C110" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="D110" t="s">
         <v>186</v>
@@ -22677,13 +22677,13 @@
         <v>694</v>
       </c>
       <c r="P110">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>0</v>
@@ -22823,10 +22823,10 @@
         <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="D111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E111" t="s">
         <v>297</v>
@@ -22862,13 +22862,13 @@
         <v>694</v>
       </c>
       <c r="P111">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q111">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S111">
         <v>0</v>
@@ -22907,10 +22907,10 @@
         <v>0</v>
       </c>
       <c r="AE111">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF111">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG111">
         <v>0</v>
@@ -23008,7 +23008,7 @@
         <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
@@ -23047,13 +23047,13 @@
         <v>694</v>
       </c>
       <c r="P112">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q112">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R112">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="S112">
         <v>0</v>
@@ -23092,10 +23092,10 @@
         <v>0</v>
       </c>
       <c r="AE112">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AF112">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG112">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D113" t="s">
         <v>186</v>
@@ -23378,7 +23378,7 @@
         <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D114" t="s">
         <v>186</v>
@@ -23417,13 +23417,13 @@
         <v>694</v>
       </c>
       <c r="P114">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q114">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S114">
         <v>0</v>
@@ -23563,7 +23563,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D115" t="s">
         <v>186</v>
@@ -23748,7 +23748,7 @@
         <v>86</v>
       </c>
       <c r="C116" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D116" t="s">
         <v>186</v>
@@ -23787,13 +23787,13 @@
         <v>694</v>
       </c>
       <c r="P116">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="Q116">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="R116">
-        <v>7.15</v>
+        <v>4.04</v>
       </c>
       <c r="S116">
         <v>0</v>
@@ -23933,7 +23933,7 @@
         <v>86</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D117" t="s">
         <v>186</v>
@@ -24118,7 +24118,7 @@
         <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D118" t="s">
         <v>186</v>
@@ -24157,13 +24157,13 @@
         <v>694</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="S118">
         <v>0</v>
@@ -24673,7 +24673,7 @@
         <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D121" t="s">
         <v>186</v>
@@ -24712,13 +24712,13 @@
         <v>694</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S121">
         <v>0</v>
@@ -24858,7 +24858,7 @@
         <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="D122" t="s">
         <v>186</v>
@@ -25043,7 +25043,7 @@
         <v>89</v>
       </c>
       <c r="C123" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D123" t="s">
         <v>186</v>
@@ -25267,13 +25267,13 @@
         <v>694</v>
       </c>
       <c r="P124">
-        <v>2.24</v>
+        <v>3.78</v>
       </c>
       <c r="Q124">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="R124">
-        <v>2.86</v>
+        <v>1.8</v>
       </c>
       <c r="S124">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>89</v>
       </c>
       <c r="C125" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="D125" t="s">
         <v>186</v>
@@ -25452,13 +25452,13 @@
         <v>694</v>
       </c>
       <c r="P125">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S125">
         <v>0</v>
@@ -25598,7 +25598,7 @@
         <v>89</v>
       </c>
       <c r="C126" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="D126" t="s">
         <v>186</v>
@@ -25637,13 +25637,13 @@
         <v>694</v>
       </c>
       <c r="P126">
-        <v>4.55</v>
+        <v>2.24</v>
       </c>
       <c r="Q126">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R126">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="S126">
         <v>0</v>
@@ -26153,7 +26153,7 @@
         <v>91</v>
       </c>
       <c r="C129" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D129" t="s">
         <v>186</v>
@@ -26338,7 +26338,7 @@
         <v>91</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D130" t="s">
         <v>186</v>
@@ -26377,13 +26377,13 @@
         <v>694</v>
       </c>
       <c r="P130">
-        <v>5.74</v>
+        <v>2.19</v>
       </c>
       <c r="Q130">
-        <v>5.53</v>
+        <v>3.37</v>
       </c>
       <c r="R130">
-        <v>1.51</v>
+        <v>3.47</v>
       </c>
       <c r="S130">
         <v>0</v>
@@ -26422,10 +26422,10 @@
         <v>0</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG130">
         <v>0</v>
@@ -26523,7 +26523,7 @@
         <v>91</v>
       </c>
       <c r="C131" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
         <v>186</v>
@@ -26562,13 +26562,13 @@
         <v>694</v>
       </c>
       <c r="P131">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -26708,10 +26708,10 @@
         <v>91</v>
       </c>
       <c r="C132" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D132" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E132" t="s">
         <v>318</v>
@@ -26893,10 +26893,10 @@
         <v>91</v>
       </c>
       <c r="C133" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D133" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E133" t="s">
         <v>319</v>
@@ -26932,13 +26932,13 @@
         <v>694</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S133">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>91</v>
       </c>
       <c r="C134" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D134" t="s">
         <v>186</v>
@@ -27117,13 +27117,13 @@
         <v>694</v>
       </c>
       <c r="P134">
-        <v>2.19</v>
+        <v>5.74</v>
       </c>
       <c r="Q134">
-        <v>3.37</v>
+        <v>5.53</v>
       </c>
       <c r="R134">
-        <v>3.47</v>
+        <v>1.51</v>
       </c>
       <c r="S134">
         <v>0</v>
@@ -27162,10 +27162,10 @@
         <v>0</v>
       </c>
       <c r="AE134">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF134">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG134">
         <v>0</v>
@@ -27263,7 +27263,7 @@
         <v>92</v>
       </c>
       <c r="C135" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D135" t="s">
         <v>186</v>
@@ -27448,10 +27448,10 @@
         <v>93</v>
       </c>
       <c r="C136" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="D136" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E136" t="s">
         <v>322</v>
@@ -27633,10 +27633,10 @@
         <v>93</v>
       </c>
       <c r="C137" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" t="s">
         <v>323</v>
@@ -27672,13 +27672,13 @@
         <v>694</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S137">
         <v>0</v>
@@ -27723,10 +27723,10 @@
         <v>0</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH137">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI137">
         <v>0</v>
@@ -28558,10 +28558,10 @@
         <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="D142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E142" t="s">
         <v>328</v>
@@ -29113,10 +29113,10 @@
         <v>93</v>
       </c>
       <c r="C145" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E145" t="s">
         <v>331</v>
@@ -29152,13 +29152,13 @@
         <v>694</v>
       </c>
       <c r="P145">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R145">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -29203,10 +29203,10 @@
         <v>0</v>
       </c>
       <c r="AG145">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH145">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI145">
         <v>0</v>
@@ -29298,7 +29298,7 @@
         <v>93</v>
       </c>
       <c r="C146" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="D146" t="s">
         <v>186</v>
@@ -29483,7 +29483,7 @@
         <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="D147" t="s">
         <v>186</v>
@@ -29853,7 +29853,7 @@
         <v>95</v>
       </c>
       <c r="C149" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D149" t="s">
         <v>186</v>
@@ -30038,7 +30038,7 @@
         <v>95</v>
       </c>
       <c r="C150" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D150" t="s">
         <v>186</v>
@@ -30077,13 +30077,13 @@
         <v>694</v>
       </c>
       <c r="P150">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q150">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -30223,7 +30223,7 @@
         <v>95</v>
       </c>
       <c r="C151" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D151" t="s">
         <v>186</v>
@@ -30262,13 +30262,13 @@
         <v>694</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -30593,7 +30593,7 @@
         <v>95</v>
       </c>
       <c r="C153" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D153" t="s">
         <v>186</v>
@@ -31148,7 +31148,7 @@
         <v>95</v>
       </c>
       <c r="C156" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D156" t="s">
         <v>186</v>
@@ -31518,7 +31518,7 @@
         <v>95</v>
       </c>
       <c r="C158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D158" t="s">
         <v>186</v>
@@ -31557,13 +31557,13 @@
         <v>694</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S158">
         <v>0</v>
@@ -32073,7 +32073,7 @@
         <v>95</v>
       </c>
       <c r="C161" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D161" t="s">
         <v>186</v>
@@ -32112,13 +32112,13 @@
         <v>694</v>
       </c>
       <c r="P161">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q161">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R161">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S161">
         <v>0</v>
@@ -32258,7 +32258,7 @@
         <v>95</v>
       </c>
       <c r="C162" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D162" t="s">
         <v>186</v>
@@ -32628,7 +32628,7 @@
         <v>96</v>
       </c>
       <c r="C164" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D164" t="s">
         <v>186</v>
@@ -32667,13 +32667,13 @@
         <v>694</v>
       </c>
       <c r="P164">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S164">
         <v>0</v>
@@ -32712,10 +32712,10 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF164">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG164">
         <v>0</v>
@@ -32813,7 +32813,7 @@
         <v>96</v>
       </c>
       <c r="C165" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D165" t="s">
         <v>186</v>
@@ -32852,13 +32852,13 @@
         <v>694</v>
       </c>
       <c r="P165">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q165">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R165">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S165">
         <v>0</v>
@@ -32903,10 +32903,10 @@
         <v>0</v>
       </c>
       <c r="AG165">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH165">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI165">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>172</v>
       </c>
       <c r="D166" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E166" t="s">
         <v>352</v>
@@ -33183,7 +33183,7 @@
         <v>96</v>
       </c>
       <c r="C167" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D167" t="s">
         <v>186</v>
@@ -33222,13 +33222,13 @@
         <v>694</v>
       </c>
       <c r="P167">
-        <v>3.03</v>
+        <v>2.24</v>
       </c>
       <c r="Q167">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="R167">
-        <v>2.31</v>
+        <v>3.37</v>
       </c>
       <c r="S167">
         <v>0</v>
@@ -33368,7 +33368,7 @@
         <v>96</v>
       </c>
       <c r="C168" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D168" t="s">
         <v>185</v>
@@ -33556,7 +33556,7 @@
         <v>173</v>
       </c>
       <c r="D169" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E169" t="s">
         <v>355</v>
@@ -33592,13 +33592,13 @@
         <v>694</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S169">
         <v>0</v>
@@ -33643,10 +33643,10 @@
         <v>0</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH169">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI169">
         <v>0</v>
@@ -33738,7 +33738,7 @@
         <v>96</v>
       </c>
       <c r="C170" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D170" t="s">
         <v>186</v>
@@ -33777,13 +33777,13 @@
         <v>694</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S170">
         <v>0</v>
@@ -33822,10 +33822,10 @@
         <v>0</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG170">
         <v>0</v>
@@ -33923,7 +33923,7 @@
         <v>96</v>
       </c>
       <c r="C171" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="D171" t="s">
         <v>186</v>
@@ -33962,13 +33962,13 @@
         <v>694</v>
       </c>
       <c r="P171">
-        <v>2.24</v>
+        <v>3.03</v>
       </c>
       <c r="Q171">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="R171">
-        <v>3.37</v>
+        <v>2.31</v>
       </c>
       <c r="S171">
         <v>0</v>
@@ -34108,7 +34108,7 @@
         <v>96</v>
       </c>
       <c r="C172" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D172" t="s">
         <v>186</v>
@@ -34147,13 +34147,13 @@
         <v>694</v>
       </c>
       <c r="P172">
-        <v>1.97</v>
+        <v>2.89</v>
       </c>
       <c r="Q172">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="R172">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="S172">
         <v>0</v>
@@ -34192,10 +34192,10 @@
         <v>0</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG172">
         <v>0</v>
@@ -34293,7 +34293,7 @@
         <v>96</v>
       </c>
       <c r="C173" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D173" t="s">
         <v>186</v>
@@ -34332,13 +34332,13 @@
         <v>694</v>
       </c>
       <c r="P173">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R173">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF173">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG173">
         <v>0</v>
@@ -34478,7 +34478,7 @@
         <v>96</v>
       </c>
       <c r="C174" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D174" t="s">
         <v>186</v>
@@ -34663,7 +34663,7 @@
         <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D175" t="s">
         <v>186</v>
@@ -34702,13 +34702,13 @@
         <v>694</v>
       </c>
       <c r="P175">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="Q175">
-        <v>3.68</v>
+        <v>4.7</v>
       </c>
       <c r="R175">
-        <v>4.61</v>
+        <v>6</v>
       </c>
       <c r="S175">
         <v>0</v>
@@ -34848,7 +34848,7 @@
         <v>96</v>
       </c>
       <c r="C176" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D176" t="s">
         <v>186</v>
@@ -34887,13 +34887,13 @@
         <v>694</v>
       </c>
       <c r="P176">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="Q176">
-        <v>4.7</v>
+        <v>3.68</v>
       </c>
       <c r="R176">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -35033,7 +35033,7 @@
         <v>96</v>
       </c>
       <c r="C177" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D177" t="s">
         <v>186</v>
@@ -35072,13 +35072,13 @@
         <v>694</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="S177">
         <v>0</v>
@@ -35218,7 +35218,7 @@
         <v>97</v>
       </c>
       <c r="C178" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D178" t="s">
         <v>186</v>
@@ -35257,13 +35257,13 @@
         <v>694</v>
       </c>
       <c r="P178">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="Q178">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="R178">
-        <v>3.57</v>
+        <v>4.81</v>
       </c>
       <c r="S178">
         <v>0</v>
@@ -35302,10 +35302,10 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG178">
         <v>0</v>
@@ -35403,7 +35403,7 @@
         <v>97</v>
       </c>
       <c r="C179" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D179" t="s">
         <v>186</v>
@@ -35442,13 +35442,13 @@
         <v>694</v>
       </c>
       <c r="P179">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="Q179">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="R179">
-        <v>4.81</v>
+        <v>3.57</v>
       </c>
       <c r="S179">
         <v>0</v>
@@ -35487,10 +35487,10 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF179">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG179">
         <v>0</v>
@@ -35588,7 +35588,7 @@
         <v>98</v>
       </c>
       <c r="C180" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D180" t="s">
         <v>185</v>
@@ -35627,13 +35627,13 @@
         <v>694</v>
       </c>
       <c r="P180">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q180">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R180">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="S180">
         <v>0</v>
@@ -35678,10 +35678,10 @@
         <v>0</v>
       </c>
       <c r="AG180">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH180">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI180">
         <v>0</v>
@@ -35773,7 +35773,7 @@
         <v>98</v>
       </c>
       <c r="C181" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D181" t="s">
         <v>185</v>
@@ -35812,13 +35812,13 @@
         <v>694</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S181">
         <v>0</v>
@@ -35857,10 +35857,10 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG181">
         <v>0</v>
@@ -35958,7 +35958,7 @@
         <v>98</v>
       </c>
       <c r="C182" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D182" t="s">
         <v>185</v>
@@ -35997,13 +35997,13 @@
         <v>694</v>
       </c>
       <c r="P182">
-        <v>2.82</v>
+        <v>1.65</v>
       </c>
       <c r="Q182">
-        <v>2.55</v>
+        <v>4.52</v>
       </c>
       <c r="R182">
-        <v>2.75</v>
+        <v>4.89</v>
       </c>
       <c r="S182">
         <v>0</v>
@@ -36042,16 +36042,16 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF182">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH182">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI182">
         <v>0</v>
@@ -36143,7 +36143,7 @@
         <v>98</v>
       </c>
       <c r="C183" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="D183" t="s">
         <v>186</v>
@@ -36182,13 +36182,13 @@
         <v>694</v>
       </c>
       <c r="P183">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="Q183">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="R183">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="S183">
         <v>0</v>
@@ -36328,10 +36328,10 @@
         <v>98</v>
       </c>
       <c r="C184" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="D184" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E184" t="s">
         <v>370</v>
@@ -36367,13 +36367,13 @@
         <v>694</v>
       </c>
       <c r="P184">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q184">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="R184">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="S184">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>98</v>
       </c>
       <c r="C185" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D185" t="s">
         <v>185</v>
@@ -36698,10 +36698,10 @@
         <v>98</v>
       </c>
       <c r="C186" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D186" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E186" t="s">
         <v>372</v>
@@ -36737,13 +36737,13 @@
         <v>694</v>
       </c>
       <c r="P186">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q186">
-        <v>3.02</v>
+        <v>3.76</v>
       </c>
       <c r="R186">
-        <v>3.53</v>
+        <v>2.92</v>
       </c>
       <c r="S186">
         <v>0</v>
@@ -36883,7 +36883,7 @@
         <v>99</v>
       </c>
       <c r="C187" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D187" t="s">
         <v>186</v>
@@ -36922,13 +36922,13 @@
         <v>694</v>
       </c>
       <c r="P187">
-        <v>5.93</v>
+        <v>1.48</v>
       </c>
       <c r="Q187">
-        <v>4.81</v>
+        <v>4.95</v>
       </c>
       <c r="R187">
-        <v>1.57</v>
+        <v>5.98</v>
       </c>
       <c r="S187">
         <v>0</v>
@@ -37068,7 +37068,7 @@
         <v>99</v>
       </c>
       <c r="C188" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D188" t="s">
         <v>186</v>
@@ -37107,13 +37107,13 @@
         <v>694</v>
       </c>
       <c r="P188">
-        <v>1.48</v>
+        <v>5.93</v>
       </c>
       <c r="Q188">
-        <v>4.95</v>
+        <v>4.81</v>
       </c>
       <c r="R188">
-        <v>5.98</v>
+        <v>1.57</v>
       </c>
       <c r="S188">
         <v>0</v>
@@ -37253,10 +37253,10 @@
         <v>100</v>
       </c>
       <c r="C189" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="D189" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E189" t="s">
         <v>375</v>
@@ -37292,13 +37292,13 @@
         <v>694</v>
       </c>
       <c r="P189">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q189">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R189">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="S189">
         <v>0</v>
@@ -37438,10 +37438,10 @@
         <v>100</v>
       </c>
       <c r="C190" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="D190" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E190" t="s">
         <v>376</v>
@@ -37477,13 +37477,13 @@
         <v>694</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S190">
         <v>0</v>
@@ -37626,7 +37626,7 @@
         <v>175</v>
       </c>
       <c r="D191" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E191" t="s">
         <v>377</v>
@@ -37808,10 +37808,10 @@
         <v>100</v>
       </c>
       <c r="C192" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="D192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E192" t="s">
         <v>378</v>
@@ -37993,10 +37993,10 @@
         <v>100</v>
       </c>
       <c r="C193" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D193" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E193" t="s">
         <v>379</v>
@@ -38032,13 +38032,13 @@
         <v>694</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S193">
         <v>0</v>
@@ -38077,10 +38077,10 @@
         <v>0</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG193">
         <v>0</v>
@@ -38178,10 +38178,10 @@
         <v>100</v>
       </c>
       <c r="C194" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="D194" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
         <v>380</v>
@@ -38363,7 +38363,7 @@
         <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="D195" t="s">
         <v>186</v>
@@ -38402,13 +38402,13 @@
         <v>694</v>
       </c>
       <c r="P195">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q195">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -38447,10 +38447,10 @@
         <v>0</v>
       </c>
       <c r="AE195">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF195">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG195">
         <v>0</v>
@@ -38548,10 +38548,10 @@
         <v>100</v>
       </c>
       <c r="C196" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D196" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E196" t="s">
         <v>382</v>
@@ -38587,13 +38587,13 @@
         <v>694</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S196">
         <v>0</v>
@@ -38733,10 +38733,10 @@
         <v>100</v>
       </c>
       <c r="C197" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D197" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E197" t="s">
         <v>383</v>
@@ -38772,13 +38772,13 @@
         <v>694</v>
       </c>
       <c r="P197">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q197">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R197">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S197">
         <v>0</v>
@@ -39843,7 +39843,7 @@
         <v>103</v>
       </c>
       <c r="C203" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D203" t="s">
         <v>185</v>
@@ -39882,13 +39882,13 @@
         <v>694</v>
       </c>
       <c r="P203">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q203">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R203">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="S203">
         <v>0</v>
@@ -39927,10 +39927,10 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF203">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG203">
         <v>0</v>
@@ -40028,7 +40028,7 @@
         <v>103</v>
       </c>
       <c r="C204" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D204" t="s">
         <v>185</v>
@@ -40067,13 +40067,13 @@
         <v>694</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -40112,10 +40112,10 @@
         <v>0</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG204">
         <v>0</v>
@@ -40213,7 +40213,7 @@
         <v>104</v>
       </c>
       <c r="C205" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D205" t="s">
         <v>185</v>
@@ -41180,10 +41180,10 @@
         <v>1.57</v>
       </c>
       <c r="Q210">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R210">
-        <v>4.75</v>
+        <v>5.53</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -41547,13 +41547,13 @@
         <v>694</v>
       </c>
       <c r="P212">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Q212">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R212">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -41592,10 +41592,10 @@
         <v>0</v>
       </c>
       <c r="AE212">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF212">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG212">
         <v>0</v>
@@ -41732,13 +41732,13 @@
         <v>694</v>
       </c>
       <c r="P213">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Q213">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R213">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -41777,10 +41777,10 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG213">
         <v>0</v>
@@ -41917,13 +41917,13 @@
         <v>694</v>
       </c>
       <c r="P214">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Q214">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="R214">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="S214">
         <v>0</v>
@@ -41962,10 +41962,10 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AF214">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AG214">
         <v>0</v>
@@ -42063,7 +42063,7 @@
         <v>109</v>
       </c>
       <c r="C215" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D215" t="s">
         <v>185</v>
@@ -42102,13 +42102,13 @@
         <v>694</v>
       </c>
       <c r="P215">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="Q215">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="R215">
-        <v>3.39</v>
+        <v>2.6</v>
       </c>
       <c r="S215">
         <v>0</v>
@@ -42147,10 +42147,10 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG215">
         <v>0</v>
@@ -42248,7 +42248,7 @@
         <v>109</v>
       </c>
       <c r="C216" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D216" t="s">
         <v>185</v>
@@ -42287,13 +42287,13 @@
         <v>694</v>
       </c>
       <c r="P216">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q216">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R216">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -42332,10 +42332,10 @@
         <v>0</v>
       </c>
       <c r="AE216">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF216">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG216">
         <v>0</v>
@@ -42433,7 +42433,7 @@
         <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D217" t="s">
         <v>185</v>
@@ -42472,13 +42472,13 @@
         <v>694</v>
       </c>
       <c r="P217">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="Q217">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R217">
-        <v>2.6</v>
+        <v>3.39</v>
       </c>
       <c r="S217">
         <v>0</v>
@@ -42517,10 +42517,10 @@
         <v>0</v>
       </c>
       <c r="AE217">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF217">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG217">
         <v>0</v>
@@ -42618,7 +42618,7 @@
         <v>109</v>
       </c>
       <c r="C218" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D218" t="s">
         <v>185</v>
@@ -42657,14 +42657,14 @@
         <v>694</v>
       </c>
       <c r="P218">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q218">
+        <v>3.89</v>
+      </c>
+      <c r="R218">
         <v>3.5</v>
       </c>
-      <c r="R218">
-        <v>2.35</v>
-      </c>
       <c r="S218">
         <v>0</v>
       </c>
@@ -42702,10 +42702,10 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG218">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>109</v>
       </c>
       <c r="C219" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D219" t="s">
         <v>185</v>
@@ -42842,13 +42842,13 @@
         <v>694</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S219">
         <v>0</v>
@@ -43173,7 +43173,7 @@
         <v>110</v>
       </c>
       <c r="C221" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D221" t="s">
         <v>186</v>
@@ -43543,10 +43543,10 @@
         <v>110</v>
       </c>
       <c r="C223" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="D223" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E223" t="s">
         <v>409</v>
@@ -43728,7 +43728,7 @@
         <v>110</v>
       </c>
       <c r="C224" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D224" t="s">
         <v>186</v>
@@ -43913,7 +43913,7 @@
         <v>110</v>
       </c>
       <c r="C225" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D225" t="s">
         <v>186</v>
@@ -44098,10 +44098,10 @@
         <v>110</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E226" t="s">
         <v>412</v>
@@ -44283,7 +44283,7 @@
         <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D227" t="s">
         <v>186</v>
@@ -44468,10 +44468,10 @@
         <v>110</v>
       </c>
       <c r="C228" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D228" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E228" t="s">
         <v>414</v>
@@ -44653,10 +44653,10 @@
         <v>110</v>
       </c>
       <c r="C229" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E229" t="s">
         <v>415</v>
@@ -44692,13 +44692,13 @@
         <v>694</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S229">
         <v>0</v>
@@ -44737,10 +44737,10 @@
         <v>0</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG229">
         <v>0</v>
@@ -44838,7 +44838,7 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D230" t="s">
         <v>186</v>
@@ -45023,10 +45023,10 @@
         <v>110</v>
       </c>
       <c r="C231" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D231" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E231" t="s">
         <v>417</v>
@@ -45062,13 +45062,13 @@
         <v>694</v>
       </c>
       <c r="P231">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q231">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R231">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S231">
         <v>0</v>
@@ -45208,10 +45208,10 @@
         <v>110</v>
       </c>
       <c r="C232" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D232" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E232" t="s">
         <v>418</v>
@@ -45247,13 +45247,13 @@
         <v>694</v>
       </c>
       <c r="P232">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q232">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R232">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S232">
         <v>0</v>
@@ -45292,10 +45292,10 @@
         <v>0</v>
       </c>
       <c r="AE232">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF232">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG232">
         <v>0</v>
@@ -45393,7 +45393,7 @@
         <v>110</v>
       </c>
       <c r="C233" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D233" t="s">
         <v>186</v>
@@ -45578,7 +45578,7 @@
         <v>110</v>
       </c>
       <c r="C234" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D234" t="s">
         <v>186</v>
@@ -45763,7 +45763,7 @@
         <v>110</v>
       </c>
       <c r="C235" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D235" t="s">
         <v>186</v>
@@ -45948,10 +45948,10 @@
         <v>110</v>
       </c>
       <c r="C236" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D236" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E236" t="s">
         <v>422</v>
@@ -46133,10 +46133,10 @@
         <v>110</v>
       </c>
       <c r="C237" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D237" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E237" t="s">
         <v>423</v>
@@ -46172,13 +46172,13 @@
         <v>694</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S237">
         <v>0</v>
@@ -46318,10 +46318,10 @@
         <v>110</v>
       </c>
       <c r="C238" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D238" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E238" t="s">
         <v>424</v>
@@ -46503,10 +46503,10 @@
         <v>110</v>
       </c>
       <c r="C239" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="D239" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E239" t="s">
         <v>425</v>
@@ -46873,7 +46873,7 @@
         <v>110</v>
       </c>
       <c r="C241" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
         <v>186</v>
@@ -47058,7 +47058,7 @@
         <v>110</v>
       </c>
       <c r="C242" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D242" t="s">
         <v>186</v>
@@ -47983,7 +47983,7 @@
         <v>114</v>
       </c>
       <c r="C247" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D247" t="s">
         <v>185</v>
@@ -48022,13 +48022,13 @@
         <v>694</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="S247">
         <v>0</v>
@@ -48067,10 +48067,10 @@
         <v>0</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG247">
         <v>0</v>
@@ -48168,7 +48168,7 @@
         <v>114</v>
       </c>
       <c r="C248" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D248" t="s">
         <v>185</v>
@@ -48207,13 +48207,13 @@
         <v>694</v>
       </c>
       <c r="P248">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R248">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="S248">
         <v>0</v>
@@ -48252,10 +48252,10 @@
         <v>0</v>
       </c>
       <c r="AE248">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF248">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG248">
         <v>0</v>
@@ -48947,13 +48947,13 @@
         <v>694</v>
       </c>
       <c r="P252">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q252">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="R252">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="S252">
         <v>0</v>
@@ -48992,16 +48992,16 @@
         <v>0</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG252">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH252">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI252">
         <v>0</v>
@@ -49132,13 +49132,13 @@
         <v>694</v>
       </c>
       <c r="P253">
-        <v>2.95</v>
+        <v>1.46</v>
       </c>
       <c r="Q253">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.2</v>
+        <v>5.15</v>
       </c>
       <c r="S253">
         <v>0</v>
@@ -49183,10 +49183,10 @@
         <v>0</v>
       </c>
       <c r="AG253">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH253">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI253">
         <v>0</v>
@@ -49317,13 +49317,13 @@
         <v>694</v>
       </c>
       <c r="P254">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q254">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R254">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="S254">
         <v>0</v>
@@ -49362,16 +49362,16 @@
         <v>0</v>
       </c>
       <c r="AE254">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF254">
+        <v>0</v>
+      </c>
+      <c r="AG254">
         <v>2.15</v>
       </c>
-      <c r="AG254">
-        <v>0</v>
-      </c>
       <c r="AH254">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI254">
         <v>0</v>

--- a/jogos_2026-05-09.xlsx
+++ b/jogos_2026-05-09.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.86</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.03</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>2.86</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>3.58</v>
+        <v>2.23</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>3.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>9.699999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.95</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.12</v>
+        <v>1.49</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="R62" t="n">
-        <v>2.27</v>
+        <v>5.16</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R63" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.74</v>
+        <v>3.13</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.94</v>
+        <v>2.88</v>
       </c>
       <c r="R64" t="n">
-        <v>4.27</v>
+        <v>2.42</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.49</v>
+        <v>2.54</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.25</v>
+        <v>3.22</v>
       </c>
       <c r="R66" t="n">
-        <v>5.16</v>
+        <v>3.21</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.54</v>
+        <v>3.12</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="R71" t="n">
-        <v>3.21</v>
+        <v>2.27</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.18</v>
+        <v>3.71</v>
       </c>
       <c r="R77" t="n">
-        <v>7.21</v>
+        <v>3.07</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.71</v>
+        <v>5.18</v>
       </c>
       <c r="R79" t="n">
-        <v>3.07</v>
+        <v>7.21</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.67</v>
+        <v>2.53</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.13</v>
+        <v>3.08</v>
       </c>
       <c r="R83" t="n">
-        <v>4.85</v>
+        <v>2.84</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.55</v>
+        <v>5.48</v>
       </c>
       <c r="R86" t="n">
-        <v>2.84</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.59</v>
+        <v>2.41</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="R87" t="n">
-        <v>5.06</v>
+        <v>2.92</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4.06</v>
+        <v>1.59</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="R88" t="n">
-        <v>1.93</v>
+        <v>5.06</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R89" t="n">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="R91" t="n">
-        <v>2.43</v>
+        <v>3.32</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.01</v>
+        <v>4.13</v>
       </c>
       <c r="R95" t="n">
-        <v>3.11</v>
+        <v>4.85</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.48</v>
+        <v>3.61</v>
       </c>
       <c r="R96" t="n">
-        <v>8.300000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.47</v>
+        <v>2.04</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R98" t="n">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="R103" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R104" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="R105" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="R106" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="R107" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.27</v>
+        <v>8.01</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.4</v>
+        <v>5.01</v>
       </c>
       <c r="R109" t="n">
-        <v>2.88</v>
+        <v>1.27</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>8.01</v>
+        <v>2.4</v>
       </c>
       <c r="Q111" t="n">
-        <v>5.01</v>
+        <v>3.25</v>
       </c>
       <c r="R111" t="n">
-        <v>1.27</v>
+        <v>2.8</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R112" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.5</v>
+        <v>3.87</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="R113" t="n">
-        <v>2.75</v>
+        <v>1.81</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="R118" t="n">
-        <v>4.04</v>
+        <v>7.15</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.24</v>
+        <v>1.06</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="R124" t="n">
-        <v>2.86</v>
+        <v>24</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.06</v>
+        <v>4.55</v>
       </c>
       <c r="Q127" t="n">
-        <v>10.5</v>
+        <v>3.87</v>
       </c>
       <c r="R127" t="n">
-        <v>24</v>
+        <v>1.86</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>5.74</v>
+        <v>1.36</v>
       </c>
       <c r="Q132" t="n">
-        <v>5.53</v>
+        <v>6.19</v>
       </c>
       <c r="R132" t="n">
-        <v>1.51</v>
+        <v>8.6</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,55 +26608,55 @@
         </is>
       </c>
       <c r="P133" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R133" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q133" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R133" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0</v>
-      </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.19</v>
+        <v>5.74</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.37</v>
+        <v>5.53</v>
       </c>
       <c r="R135" t="n">
-        <v>3.47</v>
+        <v>1.51</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
         <v>0</v>
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29811,10 +29811,10 @@
         <v>0</v>
       </c>
       <c r="AG149" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH149" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI149" t="n">
         <v>0</v>
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.89</v>
+        <v>1.3</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.32</v>
+        <v>5.65</v>
       </c>
       <c r="R167" t="n">
-        <v>2.38</v>
+        <v>8.4</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,16 +33351,16 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH167" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF168" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>3.03</v>
+        <v>1.45</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="R169" t="n">
-        <v>2.31</v>
+        <v>6</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.31</v>
+        <v>3.79</v>
       </c>
       <c r="Q170" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="R170" t="n">
-        <v>3.12</v>
+        <v>1.9</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -33936,16 +33936,16 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD170" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE170" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF170" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q172" t="n">
-        <v>5.65</v>
+        <v>2.89</v>
       </c>
       <c r="R172" t="n">
-        <v>8.4</v>
+        <v>3.12</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34330,10 +34330,10 @@
         <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD172" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE172" t="n">
         <v>0</v>
@@ -34342,10 +34342,10 @@
         <v>0</v>
       </c>
       <c r="AG172" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH172" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI172" t="n">
         <v>0</v>
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="Q176" t="n">
-        <v>4.7</v>
+        <v>3.68</v>
       </c>
       <c r="R176" t="n">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@